--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26024"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11100" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE05D358-F1CD-447F-A84E-5D6F69FAF4DF}"/>
+  <xr:revisionPtr revIDLastSave="11101" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C59231-C952-4EF4-A3B7-FF26B688B366}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="24" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="22" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -25,21 +25,20 @@
     <sheet name="GVREIT" sheetId="195" r:id="rId10"/>
     <sheet name="IVL" sheetId="196" r:id="rId11"/>
     <sheet name="JASIF" sheetId="46" r:id="rId12"/>
-    <sheet name="GFPT" sheetId="201" r:id="rId13"/>
-    <sheet name="JMART" sheetId="200" r:id="rId14"/>
-    <sheet name="MAKRO" sheetId="179" r:id="rId15"/>
-    <sheet name="MCS" sheetId="20" r:id="rId16"/>
-    <sheet name="NER" sheetId="117" r:id="rId17"/>
-    <sheet name="ORI" sheetId="184" r:id="rId18"/>
-    <sheet name="RCL" sheetId="161" r:id="rId19"/>
-    <sheet name="SCC" sheetId="152" r:id="rId20"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId21"/>
-    <sheet name="SENA" sheetId="183" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
-    <sheet name="TMT" sheetId="145" r:id="rId25"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
-    <sheet name="WHART" sheetId="171" r:id="rId27"/>
+    <sheet name="JMART" sheetId="200" r:id="rId13"/>
+    <sheet name="MAKRO" sheetId="179" r:id="rId14"/>
+    <sheet name="MCS" sheetId="20" r:id="rId15"/>
+    <sheet name="NER" sheetId="117" r:id="rId16"/>
+    <sheet name="ORI" sheetId="184" r:id="rId17"/>
+    <sheet name="RCL" sheetId="161" r:id="rId18"/>
+    <sheet name="SCC" sheetId="152" r:id="rId19"/>
+    <sheet name="SCCC" sheetId="177" r:id="rId20"/>
+    <sheet name="SENA" sheetId="183" r:id="rId21"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
+    <sheet name="TMT" sheetId="145" r:id="rId24"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
+    <sheet name="WHART" sheetId="171" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -119,9 +118,6 @@
   </si>
   <si>
     <t>JASIF</t>
-  </si>
-  <si>
-    <t>GFPT</t>
   </si>
   <si>
     <t>JMART</t>
@@ -4803,7 +4799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24633546-7D6B-4E6E-A7CC-AA819F3057BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C56F41-4A4D-49E3-9DEE-4D1E17C59DB3}">
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
@@ -4836,34 +4832,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="16">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="D2" s="40">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="E2" s="18">
         <f>C2*D2</f>
-        <v>93750</v>
+        <v>120000</v>
       </c>
       <c r="F2" s="18">
         <f>E2*0.002</f>
-        <v>187.5</v>
+        <v>240</v>
       </c>
       <c r="G2" s="18">
         <f>E2*0.00006</f>
-        <v>5.625</v>
+        <v>7.2</v>
       </c>
       <c r="H2" s="18">
         <f>E2*0.00001</f>
-        <v>0.93750000000000011</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="I2" s="18">
         <f>(F2+G2+H2)*0.07</f>
-        <v>13.584375000000001</v>
+        <v>17.388000000000002</v>
       </c>
       <c r="J2" s="18">
         <f>E2+F2+I2+G2+H2</f>
-        <v>93957.646875000006</v>
+        <v>120265.788</v>
       </c>
       <c r="K2" s="29"/>
       <c r="L2" s="17"/>
@@ -4877,34 +4873,34 @@
         <v>1</v>
       </c>
       <c r="C3" s="10">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="D3" s="64">
-        <v>11.5</v>
+        <v>36.5</v>
       </c>
       <c r="E3" s="20">
         <f>C3*D3</f>
-        <v>28750</v>
+        <v>43800</v>
       </c>
       <c r="F3" s="20">
         <f>E3*0.002</f>
-        <v>57.5</v>
+        <v>87.600000000000009</v>
       </c>
       <c r="G3" s="20">
         <f>E3*0.00006</f>
-        <v>1.7250000000000001</v>
+        <v>2.6280000000000001</v>
       </c>
       <c r="H3" s="20">
         <f>E3*0.00001</f>
-        <v>0.28750000000000003</v>
+        <v>0.43800000000000006</v>
       </c>
       <c r="I3" s="20">
         <f>(F3+G3+H3)*0.07</f>
-        <v>4.1658750000000007</v>
+        <v>6.3466200000000015</v>
       </c>
       <c r="J3" s="20">
         <f>E3+F3+I3+G3+H3</f>
-        <v>28813.678374999996</v>
+        <v>43897.012619999994</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="11"/>
@@ -4913,39 +4909,39 @@
     <row r="4" spans="1:13">
       <c r="B4" s="25">
         <f>(D3-D2)/D2</f>
-        <v>-0.08</v>
+        <v>-8.7499999999999994E-2</v>
       </c>
       <c r="C4" s="22">
         <f>SUM(C2:C3)</f>
-        <v>10000</v>
+        <v>4200</v>
       </c>
       <c r="D4" s="65">
         <f>E4/C4</f>
-        <v>12.25</v>
+        <v>39</v>
       </c>
       <c r="E4" s="22">
         <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>122500</v>
+        <v>163800</v>
       </c>
       <c r="F4" s="22">
         <f t="shared" si="0"/>
-        <v>245</v>
+        <v>327.60000000000002</v>
       </c>
       <c r="G4" s="22">
         <f t="shared" si="0"/>
-        <v>7.35</v>
+        <v>9.8279999999999994</v>
       </c>
       <c r="H4" s="22">
         <f t="shared" si="0"/>
-        <v>1.2250000000000001</v>
+        <v>1.6380000000000003</v>
       </c>
       <c r="I4" s="22">
         <f t="shared" si="0"/>
-        <v>17.750250000000001</v>
+        <v>23.734620000000003</v>
       </c>
       <c r="J4" s="22">
         <f t="shared" si="0"/>
-        <v>122771.32524999999</v>
+        <v>164162.80061999999</v>
       </c>
       <c r="L4" s="25"/>
       <c r="M4" s="21"/>
@@ -4959,162 +4955,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C56F41-4A4D-49E3-9DEE-4D1E17C59DB3}">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="65" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44915</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>3000</v>
-      </c>
-      <c r="D2" s="40">
-        <v>40</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>120000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="67">
-        <v>44656</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="64">
-        <v>36.5</v>
-      </c>
-      <c r="E3" s="20">
-        <f>C3*D3</f>
-        <v>43800</v>
-      </c>
-      <c r="F3" s="20">
-        <f>E3*0.002</f>
-        <v>87.600000000000009</v>
-      </c>
-      <c r="G3" s="20">
-        <f>E3*0.00006</f>
-        <v>2.6280000000000001</v>
-      </c>
-      <c r="H3" s="20">
-        <f>E3*0.00001</f>
-        <v>0.43800000000000006</v>
-      </c>
-      <c r="I3" s="20">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>6.3466200000000015</v>
-      </c>
-      <c r="J3" s="20">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>43897.012619999994</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="B4" s="25">
-        <f>(D3-D2)/D2</f>
-        <v>-8.7499999999999994E-2</v>
-      </c>
-      <c r="C4" s="22">
-        <f>SUM(C2:C3)</f>
-        <v>4200</v>
-      </c>
-      <c r="D4" s="65">
-        <f>E4/C4</f>
-        <v>39</v>
-      </c>
-      <c r="E4" s="22">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>163800</v>
-      </c>
-      <c r="F4" s="22">
-        <f t="shared" si="0"/>
-        <v>327.60000000000002</v>
-      </c>
-      <c r="G4" s="22">
-        <f t="shared" si="0"/>
-        <v>9.8279999999999994</v>
-      </c>
-      <c r="H4" s="22">
-        <f t="shared" si="0"/>
-        <v>1.6380000000000003</v>
-      </c>
-      <c r="I4" s="22">
-        <f t="shared" si="0"/>
-        <v>23.734620000000003</v>
-      </c>
-      <c r="J4" s="22">
-        <f t="shared" si="0"/>
-        <v>164162.80061999999</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB1EBAE-F735-42C2-8B12-15730D8F96F4}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5137,7 +4977,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -5523,7 +5363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5543,7 +5383,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1">
@@ -7068,7 +6908,7 @@
         <v>42720</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" s="16">
         <v>75000</v>
@@ -7180,7 +7020,7 @@
         <v>44351</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" s="16">
         <v>70000</v>
@@ -7697,7 +7537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -7720,7 +7560,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8140,7 +7980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8163,7 +8003,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8651,7 +8491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8674,7 +8514,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -10127,6 +9967,321 @@
       <c r="J40" s="20">
         <f>J39-J38</f>
         <v>4116.4531500000012</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>300</v>
+      </c>
+      <c r="D2" s="17">
+        <v>410</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>123000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>246</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>7.38</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.2300000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>17.822700000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>123272.4327</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1">
+      <c r="A3" s="39">
+        <v>44469</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>400</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>120000</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>240</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.388000000000002</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>120265.788</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439025E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>600</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>405</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>243000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>14.58</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.210700000000003</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>243538.22070000001</v>
+      </c>
+      <c r="L4" s="25"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="1:13" s="13" customFormat="1">
+      <c r="A5" s="39">
+        <v>44579</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>300</v>
+      </c>
+      <c r="D5" s="17">
+        <v>384</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>115200</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>230.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>6.9119999999999999</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>16.69248</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>115455.15647999999</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="7">
+        <f>(D5-D4)/D4</f>
+        <v>-5.185185185185185E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM(C4:C5)</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="71">
+        <f>E6/C6</f>
+        <v>398</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>358200</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>716.4</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>21.492000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5820000000000007</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>51.903180000000006</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>358993.37718000001</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="67">
+        <v>44579</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>300</v>
+      </c>
+      <c r="D7" s="11">
+        <v>382</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>114600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>229.20000000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>6.8760000000000003</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>16.605540000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>114853.82754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="25">
+        <f>(D7-D6)/D6</f>
+        <v>-4.0201005025125629E-2</v>
+      </c>
+      <c r="C8" s="22">
+        <f>SUM(C6:C7)</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="68">
+        <f>E8/C8</f>
+        <v>394</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>472800</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="2"/>
+        <v>945.6</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="2"/>
+        <v>28.368000000000002</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>4.7280000000000006</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="2"/>
+        <v>68.508720000000011</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="2"/>
+        <v>473847.20472000004</v>
       </c>
     </row>
   </sheetData>
@@ -11818,321 +11973,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>300</v>
-      </c>
-      <c r="D2" s="17">
-        <v>410</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="39">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>400</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" spans="1:13" s="13" customFormat="1">
-      <c r="A5" s="39">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>300</v>
-      </c>
-      <c r="D5" s="17">
-        <v>384</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="70"/>
-      <c r="B6" s="7">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="71">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="67">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>300</v>
-      </c>
-      <c r="D7" s="11">
-        <v>382</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>114600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>229.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.8760000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>16.605540000000001</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>114853.82754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="25">
-        <f>(D7-D6)/D6</f>
-        <v>-4.0201005025125629E-2</v>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="68">
-        <f>E8/C8</f>
-        <v>394</v>
-      </c>
-      <c r="E8" s="22">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>472800</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" si="2"/>
-        <v>945.6</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="2"/>
-        <v>28.368000000000002</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>4.7280000000000006</v>
-      </c>
-      <c r="I8" s="22">
-        <f t="shared" si="2"/>
-        <v>68.508720000000011</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="2"/>
-        <v>473847.20472000004</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12155,7 +11995,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -12360,7 +12200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12383,7 +12223,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -12901,7 +12741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -12924,7 +12764,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -14136,7 +13976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14159,7 +13999,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14377,7 +14217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14400,7 +14240,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14836,7 +14676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14859,7 +14699,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -15298,7 +15138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15324,7 +15164,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11101" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C59231-C952-4EF4-A3B7-FF26B688B366}"/>
+  <xr:revisionPtr revIDLastSave="11111" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BB61A42-5CD6-4D16-8057-21E13748EEB9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="22" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -34,11 +34,12 @@
     <sheet name="SCC" sheetId="152" r:id="rId19"/>
     <sheet name="SCCC" sheetId="177" r:id="rId20"/>
     <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
-    <sheet name="TMT" sheetId="145" r:id="rId24"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
-    <sheet name="WHART" sheetId="171" r:id="rId26"/>
+    <sheet name="SINGER" sheetId="201" r:id="rId22"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
+    <sheet name="TMT" sheetId="145" r:id="rId25"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
+    <sheet name="WHART" sheetId="171" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="36">
   <si>
     <t>KCE</t>
   </si>
@@ -148,6 +149,9 @@
   </si>
   <si>
     <t>SENA</t>
+  </si>
+  <si>
+    <t>SINGER</t>
   </si>
   <si>
     <t>SYNEX</t>
@@ -12742,6 +12746,243 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A37F3B0-D8F6-4080-95CB-3E133683EFC9}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44930</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D2" s="17">
+        <v>27.5</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>99000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>198</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>5.94</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>14.345100000000002</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>99219.275100000013</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="56"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="L3" s="24"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="12">
+      <c r="A4" s="50"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A5" s="56">
+        <v>44904</v>
+      </c>
+      <c r="C5" s="10">
+        <f>C2</f>
+        <v>3600</v>
+      </c>
+      <c r="D5" s="64">
+        <v>0.1003</v>
+      </c>
+      <c r="E5" s="60">
+        <v>0</v>
+      </c>
+      <c r="F5" s="32">
+        <v>0</v>
+      </c>
+      <c r="G5" s="60">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
+        <f>G5-E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="61">
+        <f>C5*D5</f>
+        <v>361.08</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1">
+      <c r="A6" s="56">
+        <v>44242</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10">
+        <f>C2</f>
+        <v>3600</v>
+      </c>
+      <c r="D6" s="11">
+        <f>D2</f>
+        <v>27.5</v>
+      </c>
+      <c r="E6" s="20">
+        <f>C6*D6</f>
+        <v>99000</v>
+      </c>
+      <c r="F6" s="20">
+        <f>E6*0.002</f>
+        <v>198</v>
+      </c>
+      <c r="G6" s="20">
+        <f>E6*0.00006</f>
+        <v>5.94</v>
+      </c>
+      <c r="H6" s="20">
+        <f>E6*0.00001</f>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="I6" s="20">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>14.345100000000002</v>
+      </c>
+      <c r="J6" s="20">
+        <f>E6+F6+I6+G6+H6</f>
+        <v>99219.275100000013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1">
+      <c r="A7" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="10">
+        <f>C6</f>
+        <v>3600</v>
+      </c>
+      <c r="D7" s="34">
+        <v>30</v>
+      </c>
+      <c r="E7" s="11">
+        <f>C7*D7</f>
+        <v>108000</v>
+      </c>
+      <c r="F7" s="35">
+        <f>E7*0.002</f>
+        <v>216</v>
+      </c>
+      <c r="G7" s="34">
+        <f>E7*0.000068</f>
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="H7" s="34">
+        <f>E7*0.00001</f>
+        <v>1.08</v>
+      </c>
+      <c r="I7" s="34">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>15.709680000000002</v>
+      </c>
+      <c r="J7" s="34">
+        <f>E7-F7-G7-H7-I7</f>
+        <v>107759.86632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1">
+      <c r="A8" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="20">
+        <f>E7-E6</f>
+        <v>9000</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20">
+        <f>J7-J6</f>
+        <v>8540.5912199999875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="12">
+      <c r="A9" s="50"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="47"/>
+      <c r="J9" s="53">
+        <f>J5+J8</f>
+        <v>8901.6712199999874</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -12764,7 +13005,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -13976,7 +14217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -13999,7 +14240,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14217,7 +14458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14240,7 +14481,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14676,7 +14917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14699,7 +14940,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -15138,7 +15379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15164,7 +15405,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,38 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11111" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BB61A42-5CD6-4D16-8057-21E13748EEB9}"/>
+  <xr:revisionPtr revIDLastSave="11138" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBCB0EB7-C860-4539-8CAA-F44B26FD1B45}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
     <sheet name="PTTGC" sheetId="42" r:id="rId2"/>
     <sheet name="STA" sheetId="197" r:id="rId3"/>
     <sheet name="ASP" sheetId="181" r:id="rId4"/>
-    <sheet name="BCH" sheetId="150" r:id="rId5"/>
-    <sheet name="CPNREIT" sheetId="194" r:id="rId6"/>
-    <sheet name="DCC" sheetId="185" r:id="rId7"/>
-    <sheet name="DIF" sheetId="57" r:id="rId8"/>
-    <sheet name="DOHOME" sheetId="170" r:id="rId9"/>
-    <sheet name="GVREIT" sheetId="195" r:id="rId10"/>
-    <sheet name="IVL" sheetId="196" r:id="rId11"/>
-    <sheet name="JASIF" sheetId="46" r:id="rId12"/>
-    <sheet name="JMART" sheetId="200" r:id="rId13"/>
-    <sheet name="MAKRO" sheetId="179" r:id="rId14"/>
-    <sheet name="MCS" sheetId="20" r:id="rId15"/>
-    <sheet name="NER" sheetId="117" r:id="rId16"/>
-    <sheet name="ORI" sheetId="184" r:id="rId17"/>
-    <sheet name="RCL" sheetId="161" r:id="rId18"/>
-    <sheet name="SCC" sheetId="152" r:id="rId19"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId20"/>
-    <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SINGER" sheetId="201" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
-    <sheet name="TMT" sheetId="145" r:id="rId25"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
-    <sheet name="WHART" sheetId="171" r:id="rId27"/>
+    <sheet name="BANPU" sheetId="202" r:id="rId5"/>
+    <sheet name="BCH" sheetId="150" r:id="rId6"/>
+    <sheet name="CPNREIT" sheetId="194" r:id="rId7"/>
+    <sheet name="DCC" sheetId="185" r:id="rId8"/>
+    <sheet name="DIF" sheetId="57" r:id="rId9"/>
+    <sheet name="DOHOME" sheetId="170" r:id="rId10"/>
+    <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
+    <sheet name="IVL" sheetId="196" r:id="rId12"/>
+    <sheet name="JASIF" sheetId="46" r:id="rId13"/>
+    <sheet name="JMART" sheetId="200" r:id="rId14"/>
+    <sheet name="MAKRO" sheetId="179" r:id="rId15"/>
+    <sheet name="MCS" sheetId="20" r:id="rId16"/>
+    <sheet name="NER" sheetId="117" r:id="rId17"/>
+    <sheet name="ORI" sheetId="184" r:id="rId18"/>
+    <sheet name="RCL" sheetId="161" r:id="rId19"/>
+    <sheet name="SCC" sheetId="152" r:id="rId20"/>
+    <sheet name="SCCC" sheetId="177" r:id="rId21"/>
+    <sheet name="SENA" sheetId="183" r:id="rId22"/>
+    <sheet name="SINGER" sheetId="201" r:id="rId23"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId25"/>
+    <sheet name="TMT" sheetId="145" r:id="rId26"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
+    <sheet name="WHART" sheetId="171" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -89,6 +90,9 @@
   </si>
   <si>
     <t>ASP</t>
+  </si>
+  <si>
+    <t>BANPU</t>
   </si>
   <si>
     <t>BCH</t>
@@ -2835,6 +2839,845 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29654F34-1A94-4023-9770-717C53C33E1B}">
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="19" customFormat="1" ht="16.5">
+      <c r="A2" s="49">
+        <v>44428</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>8000</v>
+      </c>
+      <c r="D2" s="41">
+        <v>25</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>200000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>400</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>12</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>28.980000000000004</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>200442.98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="78" customFormat="1">
+      <c r="A3" s="82">
+        <v>44566</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="84">
+        <v>4000</v>
+      </c>
+      <c r="D3" s="85">
+        <v>22.9</v>
+      </c>
+      <c r="E3" s="86">
+        <f>C3*D3</f>
+        <v>91600</v>
+      </c>
+      <c r="F3" s="86">
+        <f>E3*0.002</f>
+        <v>183.20000000000002</v>
+      </c>
+      <c r="G3" s="86">
+        <f>E3*0.000068</f>
+        <v>6.2287999999999997</v>
+      </c>
+      <c r="H3" s="86">
+        <f>E3*0.00001</f>
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="I3" s="86">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>13.324136000000003</v>
+      </c>
+      <c r="J3" s="86">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>91803.668935999987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="78" customFormat="1">
+      <c r="A4" s="82"/>
+      <c r="B4" s="87">
+        <f>(D3-D2)/D2</f>
+        <v>-8.4000000000000061E-2</v>
+      </c>
+      <c r="C4" s="84">
+        <f>SUM(C2:C3)</f>
+        <v>12000</v>
+      </c>
+      <c r="D4" s="85">
+        <f>E4/C4</f>
+        <v>24.3</v>
+      </c>
+      <c r="E4" s="84">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>291600</v>
+      </c>
+      <c r="F4" s="84">
+        <f t="shared" si="0"/>
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G4" s="84">
+        <f t="shared" si="0"/>
+        <v>18.2288</v>
+      </c>
+      <c r="H4" s="84">
+        <f t="shared" si="0"/>
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="I4" s="84">
+        <f t="shared" si="0"/>
+        <v>42.304136000000007</v>
+      </c>
+      <c r="J4" s="84">
+        <f t="shared" si="0"/>
+        <v>292246.64893600001</v>
+      </c>
+      <c r="K4" s="81"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="54">
+        <v>44624</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="51">
+        <f>C4*6/5</f>
+        <v>14400</v>
+      </c>
+      <c r="D5" s="52">
+        <f>E5/C5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E5" s="55">
+        <v>291600</v>
+      </c>
+      <c r="F5" s="55">
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G5" s="55">
+        <v>18.2288</v>
+      </c>
+      <c r="H5" s="55">
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="I5" s="55">
+        <v>42.304136000000007</v>
+      </c>
+      <c r="J5" s="55">
+        <v>292246.64893600001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="13" customFormat="1">
+      <c r="A6" s="49">
+        <v>44630</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="16">
+        <v>4800</v>
+      </c>
+      <c r="D6" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="E6" s="17">
+        <f>C6*D6</f>
+        <v>108000</v>
+      </c>
+      <c r="F6" s="27">
+        <f>E6*0.002</f>
+        <v>216</v>
+      </c>
+      <c r="G6" s="26">
+        <f>E6*0.000068</f>
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="H6" s="26">
+        <f>E6*0.00001</f>
+        <v>1.08</v>
+      </c>
+      <c r="I6" s="26">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>15.709680000000002</v>
+      </c>
+      <c r="J6" s="26">
+        <f>E6-F6-G6-H6-I6</f>
+        <v>107759.86632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="78" customFormat="1">
+      <c r="A7" s="82">
+        <v>44630</v>
+      </c>
+      <c r="B7" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="84">
+        <v>9600</v>
+      </c>
+      <c r="D7" s="85">
+        <f>D5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E7" s="86">
+        <f>C7*D7</f>
+        <v>194400</v>
+      </c>
+      <c r="F7" s="86">
+        <f>E7*0.002</f>
+        <v>388.8</v>
+      </c>
+      <c r="G7" s="86">
+        <f>E7*0.000068</f>
+        <v>13.219200000000001</v>
+      </c>
+      <c r="H7" s="86">
+        <f>E7*0.00001</f>
+        <v>1.9440000000000002</v>
+      </c>
+      <c r="I7" s="86">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>28.277424000000003</v>
+      </c>
+      <c r="J7" s="86">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>194832.24062399997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="78" customFormat="1">
+      <c r="A8" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B8" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="84">
+        <v>7200</v>
+      </c>
+      <c r="D8" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E8" s="86">
+        <f>C8*D8</f>
+        <v>145800</v>
+      </c>
+      <c r="F8" s="86">
+        <f>E8*0.002</f>
+        <v>291.60000000000002</v>
+      </c>
+      <c r="G8" s="86">
+        <f>E8*0.000068</f>
+        <v>9.9144000000000005</v>
+      </c>
+      <c r="H8" s="86">
+        <f>E8*0.00001</f>
+        <v>1.4580000000000002</v>
+      </c>
+      <c r="I8" s="86">
+        <f>(F8+G8+H8)*0.07</f>
+        <v>21.208068000000004</v>
+      </c>
+      <c r="J8" s="86">
+        <f>E8+F8+I8+G8+H8</f>
+        <v>146124.18046800004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="78" customFormat="1" ht="12.75">
+      <c r="A9" s="82">
+        <v>44880</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="84">
+        <v>4800</v>
+      </c>
+      <c r="D9" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E9" s="86">
+        <f>C9*D9</f>
+        <v>97200</v>
+      </c>
+      <c r="F9" s="86">
+        <f>E9*0.002</f>
+        <v>194.4</v>
+      </c>
+      <c r="G9" s="86">
+        <f>E9*0.000068</f>
+        <v>6.6096000000000004</v>
+      </c>
+      <c r="H9" s="86">
+        <f>E9*0.00001</f>
+        <v>0.97200000000000009</v>
+      </c>
+      <c r="I9" s="86">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>14.138712000000002</v>
+      </c>
+      <c r="J9" s="86">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>97416.120311999985</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="78" customFormat="1" ht="12.75">
+      <c r="A10" s="82">
+        <v>44886</v>
+      </c>
+      <c r="B10" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D10" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E10" s="86">
+        <f>C10*D10</f>
+        <v>48600</v>
+      </c>
+      <c r="F10" s="86">
+        <f>E10*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G10" s="86">
+        <f>E10*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H10" s="86">
+        <f>E10*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I10" s="86">
+        <f>(F10+G10+H10)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J10" s="86">
+        <f>E10+F10+I10+G10+H10</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="78" customFormat="1" ht="12.75">
+      <c r="A11" s="77"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+    </row>
+    <row r="12" spans="1:13" s="78" customFormat="1" ht="12.75">
+      <c r="A12" s="77"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="81"/>
+    </row>
+    <row r="13" spans="1:13" s="78" customFormat="1">
+      <c r="A13" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D13" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E13" s="86">
+        <f>C13*D13</f>
+        <v>48600</v>
+      </c>
+      <c r="F13" s="86">
+        <f>E13*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G13" s="86">
+        <f>E13*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H13" s="86">
+        <f>E13*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I13" s="86">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J13" s="86">
+        <f>E13+F13+I13+G13+H13</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="13" customFormat="1">
+      <c r="A14" s="49">
+        <v>44886</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="16">
+        <f>C13</f>
+        <v>2400</v>
+      </c>
+      <c r="D14" s="26">
+        <v>14.2</v>
+      </c>
+      <c r="E14" s="17">
+        <f>C14*D14</f>
+        <v>34080</v>
+      </c>
+      <c r="F14" s="27">
+        <f>E14*0.002</f>
+        <v>68.16</v>
+      </c>
+      <c r="G14" s="26">
+        <f>E14*0.000068</f>
+        <v>2.3174399999999999</v>
+      </c>
+      <c r="H14" s="26">
+        <f>E14*0.00001</f>
+        <v>0.34080000000000005</v>
+      </c>
+      <c r="I14" s="26">
+        <f>(F14+G14+H14)*0.07</f>
+        <v>4.9572768000000007</v>
+      </c>
+      <c r="J14" s="26">
+        <f>E14-F14-G14-H14-I14</f>
+        <v>34004.2244832</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A15" s="28">
+        <f>DAYS360(A13,A14)</f>
+        <v>191</v>
+      </c>
+      <c r="B15" s="30">
+        <f>(D14-D13)/D13</f>
+        <v>-0.29876543209876549</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18">
+        <f>E14-E13</f>
+        <v>-14520</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18">
+        <f>J14-J13</f>
+        <v>-14703.835672799993</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" s="13" customFormat="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+    </row>
+    <row r="17" spans="1:13" s="78" customFormat="1">
+      <c r="A17" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D17" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E17" s="86">
+        <f>C17*D17</f>
+        <v>48600</v>
+      </c>
+      <c r="F17" s="86">
+        <f>E17*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G17" s="86">
+        <f>E17*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H17" s="86">
+        <f>E17*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I17" s="86">
+        <f>(F17+G17+H17)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J17" s="86">
+        <f>E17+F17+I17+G17+H17</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="13" customFormat="1">
+      <c r="A18" s="49">
+        <v>44880</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="16">
+        <f>C17</f>
+        <v>2400</v>
+      </c>
+      <c r="D18" s="26">
+        <v>13.7</v>
+      </c>
+      <c r="E18" s="17">
+        <f>C18*D18</f>
+        <v>32880</v>
+      </c>
+      <c r="F18" s="27">
+        <f>E18*0.002</f>
+        <v>65.760000000000005</v>
+      </c>
+      <c r="G18" s="26">
+        <f>E18*0.000068</f>
+        <v>2.23584</v>
+      </c>
+      <c r="H18" s="26">
+        <f>E18*0.00001</f>
+        <v>0.32880000000000004</v>
+      </c>
+      <c r="I18" s="26">
+        <f>(F18+G18+H18)*0.07</f>
+        <v>4.7827248000000004</v>
+      </c>
+      <c r="J18" s="26">
+        <f>E18-F18-G18-H18-I18</f>
+        <v>32806.892635199991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A19" s="28">
+        <f>DAYS360(A17,A18)</f>
+        <v>185</v>
+      </c>
+      <c r="B19" s="30">
+        <f>(D18-D17)/D17</f>
+        <v>-0.32345679012345685</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18">
+        <f>E18-E17</f>
+        <v>-15720</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18">
+        <f>J18-J17</f>
+        <v>-15901.167520800002</v>
+      </c>
+      <c r="K19" s="32"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" s="13" customFormat="1" ht="12.75">
+      <c r="A20" s="49"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:13" s="78" customFormat="1">
+      <c r="A21" s="82">
+        <v>44644</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D21" s="85">
+        <v>21.3</v>
+      </c>
+      <c r="E21" s="86">
+        <f>C21*D21</f>
+        <v>51120</v>
+      </c>
+      <c r="F21" s="86">
+        <f>E21*0.002</f>
+        <v>102.24000000000001</v>
+      </c>
+      <c r="G21" s="86">
+        <f>E21*0.000068</f>
+        <v>3.4761600000000001</v>
+      </c>
+      <c r="H21" s="86">
+        <f>E21*0.00001</f>
+        <v>0.51119999999999999</v>
+      </c>
+      <c r="I21" s="86">
+        <f>(F21+G21+H21)*0.07</f>
+        <v>7.4359152000000011</v>
+      </c>
+      <c r="J21" s="86">
+        <f>E21+F21+I21+G21+H21</f>
+        <v>51233.6632752</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="13" customFormat="1">
+      <c r="A22" s="49">
+        <v>44671</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16">
+        <f>C21</f>
+        <v>2400</v>
+      </c>
+      <c r="D22" s="26">
+        <v>22.4</v>
+      </c>
+      <c r="E22" s="17">
+        <f>C22*D22</f>
+        <v>53760</v>
+      </c>
+      <c r="F22" s="27">
+        <f>E22*0.002</f>
+        <v>107.52</v>
+      </c>
+      <c r="G22" s="26">
+        <f>E22*0.000068</f>
+        <v>3.6556799999999998</v>
+      </c>
+      <c r="H22" s="26">
+        <f>E22*0.00001</f>
+        <v>0.53760000000000008</v>
+      </c>
+      <c r="I22" s="26">
+        <f>(F22+G22+H22)*0.07</f>
+        <v>7.8199296000000009</v>
+      </c>
+      <c r="J22" s="26">
+        <f>E22-F22-G22-H22-I22</f>
+        <v>53640.466790399994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A23" s="28">
+        <f>DAYS360(A21,A22)</f>
+        <v>26</v>
+      </c>
+      <c r="B23" s="30">
+        <f>(D22-D21)/D21</f>
+        <v>5.164319248826281E-2</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18">
+        <f>E22-E21</f>
+        <v>2640</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18">
+        <f>J22-J21</f>
+        <v>2406.8035151999939</v>
+      </c>
+      <c r="K23" s="32"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" spans="1:13" s="21" customFormat="1">
+      <c r="A24" s="49">
+        <v>44538</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="16">
+        <f>C5/3</f>
+        <v>4800</v>
+      </c>
+      <c r="D24" s="17">
+        <f>D5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E24" s="18">
+        <f>C24*D24</f>
+        <v>97200</v>
+      </c>
+      <c r="F24" s="18">
+        <f>E24*0.002</f>
+        <v>194.4</v>
+      </c>
+      <c r="G24" s="18">
+        <f>E24*0.000068</f>
+        <v>6.6096000000000004</v>
+      </c>
+      <c r="H24" s="18">
+        <f>E24*0.00001</f>
+        <v>0.97200000000000009</v>
+      </c>
+      <c r="I24" s="18">
+        <f>(F24+G24+H24)*0.07</f>
+        <v>14.138712000000002</v>
+      </c>
+      <c r="J24" s="18">
+        <f>E24+F24+I24+G24+H24</f>
+        <v>97416.120311999985</v>
+      </c>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="1:13" s="13" customFormat="1">
+      <c r="A25" s="49">
+        <v>44630</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="16">
+        <f>C24</f>
+        <v>4800</v>
+      </c>
+      <c r="D25" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="E25" s="17">
+        <f>C25*D25</f>
+        <v>108000</v>
+      </c>
+      <c r="F25" s="27">
+        <f>E25*0.002</f>
+        <v>216</v>
+      </c>
+      <c r="G25" s="26">
+        <f>E25*0.000068</f>
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="H25" s="26">
+        <f>E25*0.00001</f>
+        <v>1.08</v>
+      </c>
+      <c r="I25" s="26">
+        <f>(F25+G25+H25)*0.07</f>
+        <v>15.709680000000002</v>
+      </c>
+      <c r="J25" s="26">
+        <f>E25-F25-G25-H25-I25</f>
+        <v>107759.86632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A26" s="28">
+        <f>DAYS360(A24,A25)</f>
+        <v>92</v>
+      </c>
+      <c r="B26" s="30">
+        <f>(D25-D24)/D24</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18">
+        <f>E25-E24</f>
+        <v>10800</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18">
+        <f>J25-J24</f>
+        <v>10343.746008000016</v>
+      </c>
+      <c r="K26" s="32"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4115D497-67E5-4755-A37C-D801F1CE1CC8}">
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -2854,7 +3697,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
@@ -3301,9 +4144,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECE484-9DAC-4EE9-A8FE-27A01698073E}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -3321,7 +4164,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
@@ -3362,48 +4205,84 @@
         <v>105833.89343999999</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="54"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
+    <row r="3" spans="1:14" s="13" customFormat="1" ht="12.75">
+      <c r="A3" s="67">
+        <v>44473</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2400</v>
+      </c>
+      <c r="D3" s="11">
+        <v>37</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3*D3</f>
+        <v>88800</v>
+      </c>
+      <c r="F3" s="20">
+        <f>E3*0.002</f>
+        <v>177.6</v>
+      </c>
+      <c r="G3" s="20">
+        <f>E3*0.00006</f>
+        <v>5.3280000000000003</v>
+      </c>
+      <c r="H3" s="20">
+        <f>E3*0.00001</f>
+        <v>0.88800000000000012</v>
+      </c>
+      <c r="I3" s="20">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>12.867120000000002</v>
+      </c>
+      <c r="J3" s="20">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>88996.683120000002</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A4" s="56">
-        <v>44799</v>
+      <c r="A4" s="56"/>
+      <c r="B4" s="76">
+        <f>(D3-D2)/D2</f>
+        <v>-0.15909090909090909</v>
       </c>
       <c r="C4" s="10">
-        <f>C2</f>
-        <v>2400</v>
+        <f>SUM(C2:C3)</f>
+        <v>4800</v>
       </c>
       <c r="D4" s="64">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="60">
-        <v>0</v>
-      </c>
-      <c r="F4" s="32">
-        <v>0</v>
-      </c>
-      <c r="G4" s="60">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11">
-        <f>G4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
-        <v>0</v>
-      </c>
-      <c r="J4" s="61">
-        <f>C4*D4*0.9</f>
-        <v>864</v>
+        <f>E4/C4</f>
+        <v>40.5</v>
+      </c>
+      <c r="E4" s="10">
+        <f>SUM(E2:E3)</f>
+        <v>194400</v>
+      </c>
+      <c r="F4" s="10">
+        <f>SUM(F2:F3)</f>
+        <v>388.8</v>
+      </c>
+      <c r="G4" s="10">
+        <f>SUM(G2:G3)</f>
+        <v>11.664000000000001</v>
+      </c>
+      <c r="H4" s="10">
+        <f>SUM(H2:H3)</f>
+        <v>1.9440000000000002</v>
+      </c>
+      <c r="I4" s="10">
+        <f>SUM(I2:I3)</f>
+        <v>28.168560000000006</v>
+      </c>
+      <c r="J4" s="10">
+        <f>SUM(J2:J3)</f>
+        <v>194830.57655999999</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="13"/>
@@ -3411,177 +4290,200 @@
       <c r="N4" s="62"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="56">
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+    </row>
+    <row r="6" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A6" s="56">
+        <v>44799</v>
+      </c>
+      <c r="C6" s="10">
+        <f>C2</f>
+        <v>2400</v>
+      </c>
+      <c r="D6" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="60">
+        <v>0</v>
+      </c>
+      <c r="F6" s="32">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="61">
+        <f>C6*D6*0.9</f>
+        <v>864</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="56">
         <v>44242</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
-        <f>C4</f>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <f>C6</f>
         <v>2400</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D7" s="46">
         <f>D2</f>
         <v>44</v>
       </c>
-      <c r="E5" s="20">
-        <f>C5*D5</f>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
         <v>105600</v>
       </c>
-      <c r="F5" s="20">
-        <f>E5*0.002</f>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
         <v>211.20000000000002</v>
       </c>
-      <c r="G5" s="20">
-        <f>E5*0.00006</f>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
         <v>6.3360000000000003</v>
       </c>
-      <c r="H5" s="20">
-        <f>E5*0.00001</f>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
         <v>1.056</v>
       </c>
-      <c r="I5" s="20">
-        <f>(F5+G5+H5)*0.07</f>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
         <v>15.301440000000005</v>
       </c>
-      <c r="J5" s="20">
-        <f>E5+F5+I5+G5+H5</f>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
         <v>105833.89343999999</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="56">
+    <row r="8" spans="1:14">
+      <c r="A8" s="56">
         <v>44277</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="10">
-        <f>C5</f>
+      <c r="C8" s="10">
+        <f>C7</f>
         <v>2400</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D8" s="34">
         <v>45</v>
       </c>
-      <c r="E6" s="11">
-        <f>C6*D6</f>
+      <c r="E8" s="11">
+        <f>C8*D8</f>
         <v>108000</v>
       </c>
-      <c r="F6" s="35">
-        <f>E6*0.002</f>
+      <c r="F8" s="35">
+        <f>E8*0.002</f>
         <v>216</v>
       </c>
-      <c r="G6" s="34">
-        <f>E6*0.000068</f>
+      <c r="G8" s="34">
+        <f>E8*0.000068</f>
         <v>7.3440000000000003</v>
       </c>
-      <c r="H6" s="34">
-        <f>E6*0.00001</f>
+      <c r="H8" s="34">
+        <f>E8*0.00001</f>
         <v>1.08</v>
       </c>
-      <c r="I6" s="34">
-        <f>(F6+G6+H6)*0.07</f>
+      <c r="I8" s="34">
+        <f>(F8+G8+H8)*0.07</f>
         <v>15.709680000000002</v>
       </c>
-      <c r="J6" s="34">
-        <f>E6-F6-G6-H6-I6</f>
+      <c r="J8" s="34">
+        <f>E8-F8-G8-H8-I8</f>
         <v>107759.86632</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="56" t="s">
+    <row r="9" spans="1:14">
+      <c r="A9" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="20">
-        <f>E6-E5</f>
+      <c r="B9" s="13"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="20">
+        <f>E8-E7</f>
         <v>2400</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20">
-        <f>J6-J5</f>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20">
+        <f>J8-J7</f>
         <v>1925.9728800000157</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="J8" s="53">
-        <f>J4+J7</f>
+    <row r="10" spans="1:14">
+      <c r="J10" s="53">
+        <f>J6+J9</f>
         <v>2789.9728800000157</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="78" customFormat="1">
-      <c r="A9" s="82"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-    </row>
-    <row r="10" spans="1:14" s="13" customFormat="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-    </row>
-    <row r="11" spans="1:14" s="31" customFormat="1" ht="18.75">
-      <c r="A11" s="28"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" s="21" customFormat="1">
+    <row r="11" spans="1:14" s="78" customFormat="1">
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+    </row>
+    <row r="12" spans="1:14" s="13" customFormat="1">
       <c r="A12" s="49"/>
       <c r="B12" s="15"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="L12" s="25"/>
-    </row>
-    <row r="13" spans="1:14" s="13" customFormat="1">
-      <c r="A13" s="49"/>
-      <c r="B13" s="15"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+    </row>
+    <row r="13" spans="1:14" s="31" customFormat="1" ht="18.75">
+      <c r="A13" s="28"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-    </row>
-    <row r="14" spans="1:14" s="31" customFormat="1" ht="18.75">
-      <c r="A14" s="28"/>
-      <c r="B14" s="30"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" s="21" customFormat="1">
+      <c r="A14" s="49"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="16"/>
       <c r="D14" s="17"/>
       <c r="E14" s="18"/>
@@ -3590,12 +4492,38 @@
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" ht="12"/>
-    <row r="16" spans="1:14" ht="12"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="1:14" s="13" customFormat="1">
+      <c r="A15" s="49"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+    </row>
+    <row r="16" spans="1:14" s="31" customFormat="1" ht="18.75">
+      <c r="A16" s="28"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" ht="12"/>
+    <row r="18" ht="12"/>
+    <row r="19" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -3604,7 +4532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -3624,7 +4552,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -4802,7 +5730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C56F41-4A4D-49E3-9DEE-4D1E17C59DB3}">
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -4825,7 +5753,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -4958,7 +5886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB1EBAE-F735-42C2-8B12-15730D8F96F4}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -4981,7 +5909,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -5367,7 +6295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5387,7 +6315,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1">
@@ -6912,7 +7840,7 @@
         <v>42720</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" s="16">
         <v>75000</v>
@@ -7024,7 +7952,7 @@
         <v>44351</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C50" s="16">
         <v>70000</v>
@@ -7541,7 +8469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -7564,7 +8492,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -7984,7 +8912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8007,7 +8935,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8495,7 +9423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8518,7 +9446,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -9971,321 +10899,6 @@
       <c r="J40" s="20">
         <f>J39-J38</f>
         <v>4116.4531500000012</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>300</v>
-      </c>
-      <c r="D2" s="17">
-        <v>410</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="39">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>400</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" spans="1:13" s="13" customFormat="1">
-      <c r="A5" s="39">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>300</v>
-      </c>
-      <c r="D5" s="17">
-        <v>384</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="70"/>
-      <c r="B6" s="7">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="71">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="67">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>300</v>
-      </c>
-      <c r="D7" s="11">
-        <v>382</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>114600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>229.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.8760000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>16.605540000000001</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>114853.82754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="25">
-        <f>(D7-D6)/D6</f>
-        <v>-4.0201005025125629E-2</v>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="68">
-        <f>E8/C8</f>
-        <v>394</v>
-      </c>
-      <c r="E8" s="22">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>472800</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" si="2"/>
-        <v>945.6</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="2"/>
-        <v>28.368000000000002</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>4.7280000000000006</v>
-      </c>
-      <c r="I8" s="22">
-        <f t="shared" si="2"/>
-        <v>68.508720000000011</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="2"/>
-        <v>473847.20472000004</v>
       </c>
     </row>
   </sheetData>
@@ -11977,6 +12590,321 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>300</v>
+      </c>
+      <c r="D2" s="17">
+        <v>410</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>123000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>246</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>7.38</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.2300000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>17.822700000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>123272.4327</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1">
+      <c r="A3" s="39">
+        <v>44469</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>400</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>120000</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>240</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.388000000000002</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>120265.788</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439025E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>600</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>405</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>243000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>14.58</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.210700000000003</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>243538.22070000001</v>
+      </c>
+      <c r="L4" s="25"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="1:13" s="13" customFormat="1">
+      <c r="A5" s="39">
+        <v>44579</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>300</v>
+      </c>
+      <c r="D5" s="17">
+        <v>384</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>115200</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>230.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>6.9119999999999999</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>16.69248</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>115455.15647999999</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="7">
+        <f>(D5-D4)/D4</f>
+        <v>-5.185185185185185E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM(C4:C5)</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="71">
+        <f>E6/C6</f>
+        <v>398</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>358200</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>716.4</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>21.492000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5820000000000007</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>51.903180000000006</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>358993.37718000001</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="67">
+        <v>44579</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>300</v>
+      </c>
+      <c r="D7" s="11">
+        <v>382</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>114600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>229.20000000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>6.8760000000000003</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>16.605540000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>114853.82754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="25">
+        <f>(D7-D6)/D6</f>
+        <v>-4.0201005025125629E-2</v>
+      </c>
+      <c r="C8" s="22">
+        <f>SUM(C6:C7)</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="68">
+        <f>E8/C8</f>
+        <v>394</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>472800</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="2"/>
+        <v>945.6</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="2"/>
+        <v>28.368000000000002</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>4.7280000000000006</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="2"/>
+        <v>68.508720000000011</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="2"/>
+        <v>473847.20472000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -11999,7 +12927,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -12204,7 +13132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12227,7 +13155,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -12745,7 +13673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A37F3B0-D8F6-4080-95CB-3E133683EFC9}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -12768,7 +13696,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -12982,7 +13910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13005,7 +13933,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -14217,7 +15145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14240,7 +15168,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14458,7 +15386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14481,7 +15409,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14917,7 +15845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14940,7 +15868,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -15379,7 +16307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15405,7 +16333,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -18505,6 +19433,405 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FBE3BD-D1CD-48BE-9C86-B7AFE096597B}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="5.625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1">
+      <c r="A2" s="49">
+        <v>44932</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>12000</v>
+      </c>
+      <c r="D2" s="41">
+        <v>12.3</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>147600</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>295.2</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>8.8559999999999999</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.4760000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>21.387240000000002</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>147926.91924000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="13" customFormat="1">
+      <c r="A3" s="67">
+        <v>44473</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>6000</v>
+      </c>
+      <c r="D3" s="11">
+        <v>12</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3*D3</f>
+        <v>72000</v>
+      </c>
+      <c r="F3" s="20">
+        <f>E3*0.002</f>
+        <v>144</v>
+      </c>
+      <c r="G3" s="20">
+        <f>E3*0.00006</f>
+        <v>4.32</v>
+      </c>
+      <c r="H3" s="20">
+        <f>E3*0.00001</f>
+        <v>0.72000000000000008</v>
+      </c>
+      <c r="I3" s="20">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>10.4328</v>
+      </c>
+      <c r="J3" s="20">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>72159.472800000003</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A4" s="56"/>
+      <c r="B4" s="76">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439081E-2</v>
+      </c>
+      <c r="C4" s="10">
+        <f>SUM(C2:C3)</f>
+        <v>18000</v>
+      </c>
+      <c r="D4" s="64">
+        <f>E4/C4</f>
+        <v>12.2</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>219600</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="0"/>
+        <v>439.2</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" si="0"/>
+        <v>13.176</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" si="0"/>
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" si="0"/>
+        <v>31.820040000000002</v>
+      </c>
+      <c r="J4" s="10">
+        <f t="shared" si="0"/>
+        <v>220086.39204000001</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+    </row>
+    <row r="6" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A6" s="56">
+        <v>44630</v>
+      </c>
+      <c r="C6" s="10">
+        <f>C2</f>
+        <v>12000</v>
+      </c>
+      <c r="D6" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="60">
+        <v>0</v>
+      </c>
+      <c r="F6" s="32">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="61">
+        <f>C6*D6</f>
+        <v>2400</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1">
+      <c r="A7" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <f>C6</f>
+        <v>12000</v>
+      </c>
+      <c r="D7" s="46">
+        <f>D2</f>
+        <v>12.3</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>147600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>295.2</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>8.8559999999999999</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.4760000000000002</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>21.387240000000002</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>147926.91924000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1">
+      <c r="A8" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="10">
+        <f>C7</f>
+        <v>12000</v>
+      </c>
+      <c r="D8" s="34">
+        <v>13</v>
+      </c>
+      <c r="E8" s="11">
+        <f>C8*D8</f>
+        <v>156000</v>
+      </c>
+      <c r="F8" s="35">
+        <f>E8*0.002</f>
+        <v>312</v>
+      </c>
+      <c r="G8" s="34">
+        <f>E8*0.000068</f>
+        <v>10.608000000000001</v>
+      </c>
+      <c r="H8" s="34">
+        <f>E8*0.00001</f>
+        <v>1.56</v>
+      </c>
+      <c r="I8" s="34">
+        <f>(F8+G8+H8)*0.07</f>
+        <v>22.691760000000002</v>
+      </c>
+      <c r="J8" s="34">
+        <f>E8-F8-G8-H8-I8</f>
+        <v>155653.14024000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1">
+      <c r="A9" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12">
+        <f>(D8-D7)/D7</f>
+        <v>5.6910569105690999E-2</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="20">
+        <f>E8-E7</f>
+        <v>8400</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20">
+        <f>J8-J7</f>
+        <v>7726.2209999999905</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="12">
+      <c r="A10" s="50"/>
+      <c r="D10" s="47"/>
+      <c r="J10" s="53">
+        <f>J6+J9</f>
+        <v>10126.22099999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1">
+      <c r="A12" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10">
+        <v>30000</v>
+      </c>
+      <c r="D12" s="46">
+        <v>3.8</v>
+      </c>
+      <c r="E12" s="20">
+        <f>C12*D12</f>
+        <v>114000</v>
+      </c>
+      <c r="F12" s="20">
+        <f>E12*0.002</f>
+        <v>228</v>
+      </c>
+      <c r="G12" s="20">
+        <f>E12*0.00006</f>
+        <v>6.84</v>
+      </c>
+      <c r="H12" s="20">
+        <f>E12*0.00001</f>
+        <v>1.1400000000000001</v>
+      </c>
+      <c r="I12" s="20">
+        <f>(F12+G12+H12)*0.07</f>
+        <v>16.518599999999999</v>
+      </c>
+      <c r="J12" s="20">
+        <f>E12+F12+I12+G12+H12</f>
+        <v>114252.49859999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1">
+      <c r="A13" s="56">
+        <v>44633</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="10">
+        <f>C12</f>
+        <v>30000</v>
+      </c>
+      <c r="D13" s="34">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="E13" s="11">
+        <f>C13*D13</f>
+        <v>120599.99999999999</v>
+      </c>
+      <c r="F13" s="35">
+        <f>E13*0.002</f>
+        <v>241.2</v>
+      </c>
+      <c r="G13" s="34">
+        <f>E13*0.000068</f>
+        <v>8.2007999999999992</v>
+      </c>
+      <c r="H13" s="34">
+        <f>E13*0.00001</f>
+        <v>1.206</v>
+      </c>
+      <c r="I13" s="34">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>17.542476000000001</v>
+      </c>
+      <c r="J13" s="34">
+        <f>E13-F13-G13-H13-I13</f>
+        <v>120331.85072399997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1">
+      <c r="A14" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="20">
+        <f>E13-E12</f>
+        <v>6599.9999999999854</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20">
+        <f>J13-J12</f>
+        <v>6079.3521239999827</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9557670-D125-4921-A689-63714DB07995}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -18524,7 +19851,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="19" customFormat="1" ht="16.5">
@@ -19033,7 +20360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB529E6-7221-4171-9EDF-80891E84F736}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -19053,7 +20380,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
@@ -19457,7 +20784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3BFEDEB-1A70-4EC2-83C3-E7387031DF06}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -19477,7 +20804,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
@@ -19837,7 +21164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -19857,7 +21184,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -20303,7 +21630,7 @@
         <v>43600</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="16">
         <v>40000</v>
@@ -21517,843 +22844,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29654F34-1A94-4023-9770-717C53C33E1B}">
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="19" customFormat="1" ht="16.5">
-      <c r="A2" s="49">
-        <v>44428</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>8000</v>
-      </c>
-      <c r="D2" s="41">
-        <v>25</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>200000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>400</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>12</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>2</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>28.980000000000004</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>200442.98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="78" customFormat="1">
-      <c r="A3" s="82">
-        <v>44566</v>
-      </c>
-      <c r="B3" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="84">
-        <v>4000</v>
-      </c>
-      <c r="D3" s="85">
-        <v>22.9</v>
-      </c>
-      <c r="E3" s="86">
-        <f>C3*D3</f>
-        <v>91600</v>
-      </c>
-      <c r="F3" s="86">
-        <f>E3*0.002</f>
-        <v>183.20000000000002</v>
-      </c>
-      <c r="G3" s="86">
-        <f>E3*0.000068</f>
-        <v>6.2287999999999997</v>
-      </c>
-      <c r="H3" s="86">
-        <f>E3*0.00001</f>
-        <v>0.91600000000000004</v>
-      </c>
-      <c r="I3" s="86">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>13.324136000000003</v>
-      </c>
-      <c r="J3" s="86">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>91803.668935999987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="78" customFormat="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="87">
-        <f>(D3-D2)/D2</f>
-        <v>-8.4000000000000061E-2</v>
-      </c>
-      <c r="C4" s="84">
-        <f>SUM(C2:C3)</f>
-        <v>12000</v>
-      </c>
-      <c r="D4" s="85">
-        <f>E4/C4</f>
-        <v>24.3</v>
-      </c>
-      <c r="E4" s="84">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>291600</v>
-      </c>
-      <c r="F4" s="84">
-        <f t="shared" si="0"/>
-        <v>583.20000000000005</v>
-      </c>
-      <c r="G4" s="84">
-        <f t="shared" si="0"/>
-        <v>18.2288</v>
-      </c>
-      <c r="H4" s="84">
-        <f t="shared" si="0"/>
-        <v>2.9159999999999999</v>
-      </c>
-      <c r="I4" s="84">
-        <f t="shared" si="0"/>
-        <v>42.304136000000007</v>
-      </c>
-      <c r="J4" s="84">
-        <f t="shared" si="0"/>
-        <v>292246.64893600001</v>
-      </c>
-      <c r="K4" s="81"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="54">
-        <v>44624</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="51">
-        <f>C4*6/5</f>
-        <v>14400</v>
-      </c>
-      <c r="D5" s="52">
-        <f>E5/C5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E5" s="55">
-        <v>291600</v>
-      </c>
-      <c r="F5" s="55">
-        <v>583.20000000000005</v>
-      </c>
-      <c r="G5" s="55">
-        <v>18.2288</v>
-      </c>
-      <c r="H5" s="55">
-        <v>2.9159999999999999</v>
-      </c>
-      <c r="I5" s="55">
-        <v>42.304136000000007</v>
-      </c>
-      <c r="J5" s="55">
-        <v>292246.64893600001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="13" customFormat="1">
-      <c r="A6" s="49">
-        <v>44630</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16">
-        <v>4800</v>
-      </c>
-      <c r="D6" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="E6" s="17">
-        <f>C6*D6</f>
-        <v>108000</v>
-      </c>
-      <c r="F6" s="27">
-        <f>E6*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G6" s="26">
-        <f>E6*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H6" s="26">
-        <f>E6*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I6" s="26">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J6" s="26">
-        <f>E6-F6-G6-H6-I6</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="78" customFormat="1">
-      <c r="A7" s="82">
-        <v>44630</v>
-      </c>
-      <c r="B7" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="84">
-        <v>9600</v>
-      </c>
-      <c r="D7" s="85">
-        <f>D5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E7" s="86">
-        <f>C7*D7</f>
-        <v>194400</v>
-      </c>
-      <c r="F7" s="86">
-        <f>E7*0.002</f>
-        <v>388.8</v>
-      </c>
-      <c r="G7" s="86">
-        <f>E7*0.000068</f>
-        <v>13.219200000000001</v>
-      </c>
-      <c r="H7" s="86">
-        <f>E7*0.00001</f>
-        <v>1.9440000000000002</v>
-      </c>
-      <c r="I7" s="86">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>28.277424000000003</v>
-      </c>
-      <c r="J7" s="86">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>194832.24062399997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="78" customFormat="1">
-      <c r="A8" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B8" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="84">
-        <v>7200</v>
-      </c>
-      <c r="D8" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E8" s="86">
-        <f>C8*D8</f>
-        <v>145800</v>
-      </c>
-      <c r="F8" s="86">
-        <f>E8*0.002</f>
-        <v>291.60000000000002</v>
-      </c>
-      <c r="G8" s="86">
-        <f>E8*0.000068</f>
-        <v>9.9144000000000005</v>
-      </c>
-      <c r="H8" s="86">
-        <f>E8*0.00001</f>
-        <v>1.4580000000000002</v>
-      </c>
-      <c r="I8" s="86">
-        <f>(F8+G8+H8)*0.07</f>
-        <v>21.208068000000004</v>
-      </c>
-      <c r="J8" s="86">
-        <f>E8+F8+I8+G8+H8</f>
-        <v>146124.18046800004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="78" customFormat="1" ht="12.75">
-      <c r="A9" s="82">
-        <v>44880</v>
-      </c>
-      <c r="B9" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="84">
-        <v>4800</v>
-      </c>
-      <c r="D9" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E9" s="86">
-        <f>C9*D9</f>
-        <v>97200</v>
-      </c>
-      <c r="F9" s="86">
-        <f>E9*0.002</f>
-        <v>194.4</v>
-      </c>
-      <c r="G9" s="86">
-        <f>E9*0.000068</f>
-        <v>6.6096000000000004</v>
-      </c>
-      <c r="H9" s="86">
-        <f>E9*0.00001</f>
-        <v>0.97200000000000009</v>
-      </c>
-      <c r="I9" s="86">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>14.138712000000002</v>
-      </c>
-      <c r="J9" s="86">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>97416.120311999985</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="78" customFormat="1" ht="12.75">
-      <c r="A10" s="82">
-        <v>44886</v>
-      </c>
-      <c r="B10" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D10" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E10" s="86">
-        <f>C10*D10</f>
-        <v>48600</v>
-      </c>
-      <c r="F10" s="86">
-        <f>E10*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G10" s="86">
-        <f>E10*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H10" s="86">
-        <f>E10*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I10" s="86">
-        <f>(F10+G10+H10)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J10" s="86">
-        <f>E10+F10+I10+G10+H10</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="78" customFormat="1" ht="12.75">
-      <c r="A11" s="77"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-    </row>
-    <row r="12" spans="1:13" s="78" customFormat="1" ht="12.75">
-      <c r="A12" s="77"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="81"/>
-    </row>
-    <row r="13" spans="1:13" s="78" customFormat="1">
-      <c r="A13" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B13" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D13" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E13" s="86">
-        <f>C13*D13</f>
-        <v>48600</v>
-      </c>
-      <c r="F13" s="86">
-        <f>E13*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G13" s="86">
-        <f>E13*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H13" s="86">
-        <f>E13*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I13" s="86">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J13" s="86">
-        <f>E13+F13+I13+G13+H13</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="13" customFormat="1">
-      <c r="A14" s="49">
-        <v>44886</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="16">
-        <f>C13</f>
-        <v>2400</v>
-      </c>
-      <c r="D14" s="26">
-        <v>14.2</v>
-      </c>
-      <c r="E14" s="17">
-        <f>C14*D14</f>
-        <v>34080</v>
-      </c>
-      <c r="F14" s="27">
-        <f>E14*0.002</f>
-        <v>68.16</v>
-      </c>
-      <c r="G14" s="26">
-        <f>E14*0.000068</f>
-        <v>2.3174399999999999</v>
-      </c>
-      <c r="H14" s="26">
-        <f>E14*0.00001</f>
-        <v>0.34080000000000005</v>
-      </c>
-      <c r="I14" s="26">
-        <f>(F14+G14+H14)*0.07</f>
-        <v>4.9572768000000007</v>
-      </c>
-      <c r="J14" s="26">
-        <f>E14-F14-G14-H14-I14</f>
-        <v>34004.2244832</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A15" s="28">
-        <f>DAYS360(A13,A14)</f>
-        <v>191</v>
-      </c>
-      <c r="B15" s="30">
-        <f>(D14-D13)/D13</f>
-        <v>-0.29876543209876549</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18">
-        <f>E14-E13</f>
-        <v>-14520</v>
-      </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18">
-        <f>J14-J13</f>
-        <v>-14703.835672799993</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" spans="1:13" s="13" customFormat="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-    </row>
-    <row r="17" spans="1:13" s="78" customFormat="1">
-      <c r="A17" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B17" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D17" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E17" s="86">
-        <f>C17*D17</f>
-        <v>48600</v>
-      </c>
-      <c r="F17" s="86">
-        <f>E17*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G17" s="86">
-        <f>E17*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H17" s="86">
-        <f>E17*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I17" s="86">
-        <f>(F17+G17+H17)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J17" s="86">
-        <f>E17+F17+I17+G17+H17</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="13" customFormat="1">
-      <c r="A18" s="49">
-        <v>44880</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="16">
-        <f>C17</f>
-        <v>2400</v>
-      </c>
-      <c r="D18" s="26">
-        <v>13.7</v>
-      </c>
-      <c r="E18" s="17">
-        <f>C18*D18</f>
-        <v>32880</v>
-      </c>
-      <c r="F18" s="27">
-        <f>E18*0.002</f>
-        <v>65.760000000000005</v>
-      </c>
-      <c r="G18" s="26">
-        <f>E18*0.000068</f>
-        <v>2.23584</v>
-      </c>
-      <c r="H18" s="26">
-        <f>E18*0.00001</f>
-        <v>0.32880000000000004</v>
-      </c>
-      <c r="I18" s="26">
-        <f>(F18+G18+H18)*0.07</f>
-        <v>4.7827248000000004</v>
-      </c>
-      <c r="J18" s="26">
-        <f>E18-F18-G18-H18-I18</f>
-        <v>32806.892635199991</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A19" s="28">
-        <f>DAYS360(A17,A18)</f>
-        <v>185</v>
-      </c>
-      <c r="B19" s="30">
-        <f>(D18-D17)/D17</f>
-        <v>-0.32345679012345685</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18">
-        <f>E18-E17</f>
-        <v>-15720</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18">
-        <f>J18-J17</f>
-        <v>-15901.167520800002</v>
-      </c>
-      <c r="K19" s="32"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" spans="1:13" s="13" customFormat="1" ht="12.75">
-      <c r="A20" s="49"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" spans="1:13" s="78" customFormat="1">
-      <c r="A21" s="82">
-        <v>44644</v>
-      </c>
-      <c r="B21" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D21" s="85">
-        <v>21.3</v>
-      </c>
-      <c r="E21" s="86">
-        <f>C21*D21</f>
-        <v>51120</v>
-      </c>
-      <c r="F21" s="86">
-        <f>E21*0.002</f>
-        <v>102.24000000000001</v>
-      </c>
-      <c r="G21" s="86">
-        <f>E21*0.000068</f>
-        <v>3.4761600000000001</v>
-      </c>
-      <c r="H21" s="86">
-        <f>E21*0.00001</f>
-        <v>0.51119999999999999</v>
-      </c>
-      <c r="I21" s="86">
-        <f>(F21+G21+H21)*0.07</f>
-        <v>7.4359152000000011</v>
-      </c>
-      <c r="J21" s="86">
-        <f>E21+F21+I21+G21+H21</f>
-        <v>51233.6632752</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="13" customFormat="1">
-      <c r="A22" s="49">
-        <v>44671</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="16">
-        <f>C21</f>
-        <v>2400</v>
-      </c>
-      <c r="D22" s="26">
-        <v>22.4</v>
-      </c>
-      <c r="E22" s="17">
-        <f>C22*D22</f>
-        <v>53760</v>
-      </c>
-      <c r="F22" s="27">
-        <f>E22*0.002</f>
-        <v>107.52</v>
-      </c>
-      <c r="G22" s="26">
-        <f>E22*0.000068</f>
-        <v>3.6556799999999998</v>
-      </c>
-      <c r="H22" s="26">
-        <f>E22*0.00001</f>
-        <v>0.53760000000000008</v>
-      </c>
-      <c r="I22" s="26">
-        <f>(F22+G22+H22)*0.07</f>
-        <v>7.8199296000000009</v>
-      </c>
-      <c r="J22" s="26">
-        <f>E22-F22-G22-H22-I22</f>
-        <v>53640.466790399994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A23" s="28">
-        <f>DAYS360(A21,A22)</f>
-        <v>26</v>
-      </c>
-      <c r="B23" s="30">
-        <f>(D22-D21)/D21</f>
-        <v>5.164319248826281E-2</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18">
-        <f>E22-E21</f>
-        <v>2640</v>
-      </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18">
-        <f>J22-J21</f>
-        <v>2406.8035151999939</v>
-      </c>
-      <c r="K23" s="32"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-    </row>
-    <row r="24" spans="1:13" s="21" customFormat="1">
-      <c r="A24" s="49">
-        <v>44538</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16">
-        <f>C5/3</f>
-        <v>4800</v>
-      </c>
-      <c r="D24" s="17">
-        <f>D5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E24" s="18">
-        <f>C24*D24</f>
-        <v>97200</v>
-      </c>
-      <c r="F24" s="18">
-        <f>E24*0.002</f>
-        <v>194.4</v>
-      </c>
-      <c r="G24" s="18">
-        <f>E24*0.000068</f>
-        <v>6.6096000000000004</v>
-      </c>
-      <c r="H24" s="18">
-        <f>E24*0.00001</f>
-        <v>0.97200000000000009</v>
-      </c>
-      <c r="I24" s="18">
-        <f>(F24+G24+H24)*0.07</f>
-        <v>14.138712000000002</v>
-      </c>
-      <c r="J24" s="18">
-        <f>E24+F24+I24+G24+H24</f>
-        <v>97416.120311999985</v>
-      </c>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="1:13" s="13" customFormat="1">
-      <c r="A25" s="49">
-        <v>44630</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="16">
-        <f>C24</f>
-        <v>4800</v>
-      </c>
-      <c r="D25" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="E25" s="17">
-        <f>C25*D25</f>
-        <v>108000</v>
-      </c>
-      <c r="F25" s="27">
-        <f>E25*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G25" s="26">
-        <f>E25*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H25" s="26">
-        <f>E25*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I25" s="26">
-        <f>(F25+G25+H25)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J25" s="26">
-        <f>E25-F25-G25-H25-I25</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A26" s="28">
-        <f>DAYS360(A24,A25)</f>
-        <v>92</v>
-      </c>
-      <c r="B26" s="30">
-        <f>(D25-D24)/D24</f>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18">
-        <f>E25-E24</f>
-        <v>10800</v>
-      </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18">
-        <f>J25-J24</f>
-        <v>10343.746008000016</v>
-      </c>
-      <c r="K26" s="32"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11138" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBCB0EB7-C860-4539-8CAA-F44B26FD1B45}"/>
+  <xr:revisionPtr revIDLastSave="11154" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FAEEA83-C032-46B3-B59A-978825DF2B4F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="11" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -13740,23 +13740,81 @@
       <c r="L2" s="17"/>
       <c r="M2" s="30"/>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="56"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="L3" s="24"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="12">
-      <c r="A4" s="50"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="47"/>
+    <row r="3" spans="1:14" ht="14.25">
+      <c r="A3" s="67">
+        <v>44693</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="64">
+        <v>25.5</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3*D3</f>
+        <v>30600</v>
+      </c>
+      <c r="F3" s="20">
+        <f>E3*0.002</f>
+        <v>61.2</v>
+      </c>
+      <c r="G3" s="20">
+        <f>E3*0.00006</f>
+        <v>1.8360000000000001</v>
+      </c>
+      <c r="H3" s="20">
+        <f>E3*0.00001</f>
+        <v>0.30600000000000005</v>
+      </c>
+      <c r="I3" s="20">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>4.4339400000000007</v>
+      </c>
+      <c r="J3" s="20">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>30667.77594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="14.25">
+      <c r="B4" s="25">
+        <f>(D3-D2)/D2</f>
+        <v>-7.2727272727272724E-2</v>
+      </c>
+      <c r="C4" s="22">
+        <f>SUM(C2:C3)</f>
+        <v>4800</v>
+      </c>
+      <c r="D4" s="65">
+        <f>E4/C4</f>
+        <v>27</v>
+      </c>
+      <c r="E4" s="22">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>129600</v>
+      </c>
+      <c r="F4" s="22">
+        <f t="shared" si="0"/>
+        <v>259.2</v>
+      </c>
+      <c r="G4" s="22">
+        <f t="shared" si="0"/>
+        <v>7.7760000000000007</v>
+      </c>
+      <c r="H4" s="22">
+        <f t="shared" si="0"/>
+        <v>1.2960000000000003</v>
+      </c>
+      <c r="I4" s="22">
+        <f t="shared" si="0"/>
+        <v>18.779040000000002</v>
+      </c>
+      <c r="J4" s="22">
+        <f t="shared" si="0"/>
+        <v>129887.05104000002</v>
+      </c>
     </row>
     <row r="5" spans="1:14" s="63" customFormat="1" ht="21.75">
       <c r="A5" s="56">
@@ -20588,38 +20646,38 @@
         <v>10000</v>
       </c>
       <c r="D7" s="80">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="E7" s="94">
         <f>C7*D7</f>
-        <v>183000</v>
+        <v>192000</v>
       </c>
       <c r="F7" s="94">
         <f>E7*0.002</f>
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="G7" s="94">
         <f>E7*0.000068</f>
-        <v>12.443999999999999</v>
+        <v>13.055999999999999</v>
       </c>
       <c r="H7" s="94">
         <f>E7*0.00001</f>
-        <v>1.83</v>
+        <v>1.9200000000000002</v>
       </c>
       <c r="I7" s="94">
         <f>(F7+G7+H7)*0.07</f>
-        <v>26.619180000000004</v>
+        <v>27.928320000000003</v>
       </c>
       <c r="J7" s="94">
         <f>E7+F7+I7+G7+H7</f>
-        <v>183406.89317999998</v>
+        <v>192426.90432000003</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
       <c r="A8" s="77"/>
       <c r="B8" s="81">
         <f>(D7-D6)/D6</f>
-        <v>-3.1746031746031633E-2</v>
+        <v>1.587301587301591E-2</v>
       </c>
       <c r="C8" s="79">
         <f>SUM(C6:C7)</f>
@@ -20627,31 +20685,31 @@
       </c>
       <c r="D8" s="80">
         <f>E8/C8</f>
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="E8" s="79">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>561000</v>
+        <v>570000</v>
       </c>
       <c r="F8" s="79">
         <f t="shared" si="2"/>
-        <v>1122</v>
+        <v>1140</v>
       </c>
       <c r="G8" s="79">
         <f t="shared" si="2"/>
-        <v>37.372</v>
+        <v>37.984000000000002</v>
       </c>
       <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>5.61</v>
+        <v>5.7</v>
       </c>
       <c r="I8" s="79">
         <f t="shared" si="2"/>
-        <v>81.548740000000009</v>
+        <v>82.857880000000009</v>
       </c>
       <c r="J8" s="79">
         <f t="shared" si="2"/>
-        <v>562246.53073999996</v>
+        <v>571266.54188000003</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="13"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11154" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FAEEA83-C032-46B3-B59A-978825DF2B4F}"/>
+  <xr:revisionPtr revIDLastSave="11157" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7E8F9E-64BD-40D2-8B13-845047E7188D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="11" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -26,21 +26,19 @@
     <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
     <sheet name="IVL" sheetId="196" r:id="rId12"/>
     <sheet name="JASIF" sheetId="46" r:id="rId13"/>
-    <sheet name="JMART" sheetId="200" r:id="rId14"/>
-    <sheet name="MAKRO" sheetId="179" r:id="rId15"/>
-    <sheet name="MCS" sheetId="20" r:id="rId16"/>
-    <sheet name="NER" sheetId="117" r:id="rId17"/>
-    <sheet name="ORI" sheetId="184" r:id="rId18"/>
-    <sheet name="RCL" sheetId="161" r:id="rId19"/>
-    <sheet name="SCC" sheetId="152" r:id="rId20"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId21"/>
-    <sheet name="SENA" sheetId="183" r:id="rId22"/>
-    <sheet name="SINGER" sheetId="201" r:id="rId23"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId25"/>
-    <sheet name="TMT" sheetId="145" r:id="rId26"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
-    <sheet name="WHART" sheetId="171" r:id="rId28"/>
+    <sheet name="MAKRO" sheetId="179" r:id="rId14"/>
+    <sheet name="MCS" sheetId="20" r:id="rId15"/>
+    <sheet name="NER" sheetId="117" r:id="rId16"/>
+    <sheet name="ORI" sheetId="184" r:id="rId17"/>
+    <sheet name="RCL" sheetId="161" r:id="rId18"/>
+    <sheet name="SCC" sheetId="152" r:id="rId19"/>
+    <sheet name="SCCC" sheetId="177" r:id="rId20"/>
+    <sheet name="SENA" sheetId="183" r:id="rId21"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
+    <sheet name="TMT" sheetId="145" r:id="rId24"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
+    <sheet name="WHART" sheetId="171" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -60,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -125,9 +123,6 @@
     <t>JASIF</t>
   </si>
   <si>
-    <t>JMART</t>
-  </si>
-  <si>
     <t>MAKRO</t>
   </si>
   <si>
@@ -153,9 +148,6 @@
   </si>
   <si>
     <t>SENA</t>
-  </si>
-  <si>
-    <t>SINGER</t>
   </si>
   <si>
     <t>SYNEX</t>
@@ -5731,162 +5723,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C56F41-4A4D-49E3-9DEE-4D1E17C59DB3}">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="65" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44915</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>3000</v>
-      </c>
-      <c r="D2" s="40">
-        <v>40</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>120000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="67">
-        <v>44656</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="64">
-        <v>36.5</v>
-      </c>
-      <c r="E3" s="20">
-        <f>C3*D3</f>
-        <v>43800</v>
-      </c>
-      <c r="F3" s="20">
-        <f>E3*0.002</f>
-        <v>87.600000000000009</v>
-      </c>
-      <c r="G3" s="20">
-        <f>E3*0.00006</f>
-        <v>2.6280000000000001</v>
-      </c>
-      <c r="H3" s="20">
-        <f>E3*0.00001</f>
-        <v>0.43800000000000006</v>
-      </c>
-      <c r="I3" s="20">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>6.3466200000000015</v>
-      </c>
-      <c r="J3" s="20">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>43897.012619999994</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="B4" s="25">
-        <f>(D3-D2)/D2</f>
-        <v>-8.7499999999999994E-2</v>
-      </c>
-      <c r="C4" s="22">
-        <f>SUM(C2:C3)</f>
-        <v>4200</v>
-      </c>
-      <c r="D4" s="65">
-        <f>E4/C4</f>
-        <v>39</v>
-      </c>
-      <c r="E4" s="22">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>163800</v>
-      </c>
-      <c r="F4" s="22">
-        <f t="shared" si="0"/>
-        <v>327.60000000000002</v>
-      </c>
-      <c r="G4" s="22">
-        <f t="shared" si="0"/>
-        <v>9.8279999999999994</v>
-      </c>
-      <c r="H4" s="22">
-        <f t="shared" si="0"/>
-        <v>1.6380000000000003</v>
-      </c>
-      <c r="I4" s="22">
-        <f t="shared" si="0"/>
-        <v>23.734620000000003</v>
-      </c>
-      <c r="J4" s="22">
-        <f t="shared" si="0"/>
-        <v>164162.80061999999</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB1EBAE-F735-42C2-8B12-15730D8F96F4}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5909,7 +5745,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -6295,7 +6131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -6315,7 +6151,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1">
@@ -7840,7 +7676,7 @@
         <v>42720</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" s="16">
         <v>75000</v>
@@ -7952,7 +7788,7 @@
         <v>44351</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" s="16">
         <v>70000</v>
@@ -8469,7 +8305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8492,7 +8328,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8912,7 +8748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8935,7 +8771,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -9423,7 +9259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -9446,7 +9282,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -10899,6 +10735,321 @@
       <c r="J40" s="20">
         <f>J39-J38</f>
         <v>4116.4531500000012</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>300</v>
+      </c>
+      <c r="D2" s="17">
+        <v>410</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>123000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>246</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>7.38</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.2300000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>17.822700000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>123272.4327</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1">
+      <c r="A3" s="39">
+        <v>44469</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>400</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>120000</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>240</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.388000000000002</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>120265.788</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439025E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>600</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>405</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>243000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>14.58</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.210700000000003</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>243538.22070000001</v>
+      </c>
+      <c r="L4" s="25"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="1:13" s="13" customFormat="1">
+      <c r="A5" s="39">
+        <v>44579</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>300</v>
+      </c>
+      <c r="D5" s="17">
+        <v>384</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>115200</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>230.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>6.9119999999999999</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>16.69248</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>115455.15647999999</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="7">
+        <f>(D5-D4)/D4</f>
+        <v>-5.185185185185185E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM(C4:C5)</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="71">
+        <f>E6/C6</f>
+        <v>398</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>358200</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>716.4</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>21.492000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5820000000000007</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>51.903180000000006</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>358993.37718000001</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="67">
+        <v>44579</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>300</v>
+      </c>
+      <c r="D7" s="11">
+        <v>382</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>114600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>229.20000000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>6.8760000000000003</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>16.605540000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>114853.82754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="25">
+        <f>(D7-D6)/D6</f>
+        <v>-4.0201005025125629E-2</v>
+      </c>
+      <c r="C8" s="22">
+        <f>SUM(C6:C7)</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="68">
+        <f>E8/C8</f>
+        <v>394</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>472800</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="2"/>
+        <v>945.6</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="2"/>
+        <v>28.368000000000002</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>4.7280000000000006</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="2"/>
+        <v>68.508720000000011</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="2"/>
+        <v>473847.20472000004</v>
       </c>
     </row>
   </sheetData>
@@ -12590,321 +12741,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>300</v>
-      </c>
-      <c r="D2" s="17">
-        <v>410</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="39">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>400</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" spans="1:13" s="13" customFormat="1">
-      <c r="A5" s="39">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>300</v>
-      </c>
-      <c r="D5" s="17">
-        <v>384</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="70"/>
-      <c r="B6" s="7">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="71">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="67">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>300</v>
-      </c>
-      <c r="D7" s="11">
-        <v>382</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>114600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>229.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.8760000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>16.605540000000001</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>114853.82754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="25">
-        <f>(D7-D6)/D6</f>
-        <v>-4.0201005025125629E-2</v>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="68">
-        <f>E8/C8</f>
-        <v>394</v>
-      </c>
-      <c r="E8" s="22">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>472800</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" si="2"/>
-        <v>945.6</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="2"/>
-        <v>28.368000000000002</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>4.7280000000000006</v>
-      </c>
-      <c r="I8" s="22">
-        <f t="shared" si="2"/>
-        <v>68.508720000000011</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="2"/>
-        <v>473847.20472000004</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12927,7 +12763,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -13132,7 +12968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -13155,7 +12991,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -13673,302 +13509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A37F3B0-D8F6-4080-95CB-3E133683EFC9}">
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="B1" s="21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44930</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>3600</v>
-      </c>
-      <c r="D2" s="17">
-        <v>27.5</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>99000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>198</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>5.94</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>0.9900000000000001</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>14.345100000000002</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>99219.275100000013</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:14" ht="14.25">
-      <c r="A3" s="67">
-        <v>44693</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="64">
-        <v>25.5</v>
-      </c>
-      <c r="E3" s="20">
-        <f>C3*D3</f>
-        <v>30600</v>
-      </c>
-      <c r="F3" s="20">
-        <f>E3*0.002</f>
-        <v>61.2</v>
-      </c>
-      <c r="G3" s="20">
-        <f>E3*0.00006</f>
-        <v>1.8360000000000001</v>
-      </c>
-      <c r="H3" s="20">
-        <f>E3*0.00001</f>
-        <v>0.30600000000000005</v>
-      </c>
-      <c r="I3" s="20">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>4.4339400000000007</v>
-      </c>
-      <c r="J3" s="20">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>30667.77594</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="14.25">
-      <c r="B4" s="25">
-        <f>(D3-D2)/D2</f>
-        <v>-7.2727272727272724E-2</v>
-      </c>
-      <c r="C4" s="22">
-        <f>SUM(C2:C3)</f>
-        <v>4800</v>
-      </c>
-      <c r="D4" s="65">
-        <f>E4/C4</f>
-        <v>27</v>
-      </c>
-      <c r="E4" s="22">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>129600</v>
-      </c>
-      <c r="F4" s="22">
-        <f t="shared" si="0"/>
-        <v>259.2</v>
-      </c>
-      <c r="G4" s="22">
-        <f t="shared" si="0"/>
-        <v>7.7760000000000007</v>
-      </c>
-      <c r="H4" s="22">
-        <f t="shared" si="0"/>
-        <v>1.2960000000000003</v>
-      </c>
-      <c r="I4" s="22">
-        <f t="shared" si="0"/>
-        <v>18.779040000000002</v>
-      </c>
-      <c r="J4" s="22">
-        <f t="shared" si="0"/>
-        <v>129887.05104000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A5" s="56">
-        <v>44904</v>
-      </c>
-      <c r="C5" s="10">
-        <f>C2</f>
-        <v>3600</v>
-      </c>
-      <c r="D5" s="64">
-        <v>0.1003</v>
-      </c>
-      <c r="E5" s="60">
-        <v>0</v>
-      </c>
-      <c r="F5" s="32">
-        <v>0</v>
-      </c>
-      <c r="G5" s="60">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11">
-        <f>G5-E5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <v>0</v>
-      </c>
-      <c r="J5" s="61">
-        <f>C5*D5</f>
-        <v>361.08</v>
-      </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1">
-      <c r="A6" s="56">
-        <v>44242</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10">
-        <f>C2</f>
-        <v>3600</v>
-      </c>
-      <c r="D6" s="11">
-        <f>D2</f>
-        <v>27.5</v>
-      </c>
-      <c r="E6" s="20">
-        <f>C6*D6</f>
-        <v>99000</v>
-      </c>
-      <c r="F6" s="20">
-        <f>E6*0.002</f>
-        <v>198</v>
-      </c>
-      <c r="G6" s="20">
-        <f>E6*0.00006</f>
-        <v>5.94</v>
-      </c>
-      <c r="H6" s="20">
-        <f>E6*0.00001</f>
-        <v>0.9900000000000001</v>
-      </c>
-      <c r="I6" s="20">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>14.345100000000002</v>
-      </c>
-      <c r="J6" s="20">
-        <f>E6+F6+I6+G6+H6</f>
-        <v>99219.275100000013</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1">
-      <c r="A7" s="56">
-        <v>44277</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10">
-        <f>C6</f>
-        <v>3600</v>
-      </c>
-      <c r="D7" s="34">
-        <v>30</v>
-      </c>
-      <c r="E7" s="11">
-        <f>C7*D7</f>
-        <v>108000</v>
-      </c>
-      <c r="F7" s="35">
-        <f>E7*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G7" s="34">
-        <f>E7*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H7" s="34">
-        <f>E7*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I7" s="34">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J7" s="34">
-        <f>E7-F7-G7-H7-I7</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1">
-      <c r="A8" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="20">
-        <f>E7-E6</f>
-        <v>9000</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20">
-        <f>J7-J6</f>
-        <v>8540.5912199999875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="12">
-      <c r="A9" s="50"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="47"/>
-      <c r="J9" s="53">
-        <f>J5+J8</f>
-        <v>8901.6712199999874</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13991,7 +13532,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -15203,7 +14744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15226,7 +14767,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15444,7 +14985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15467,7 +15008,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15903,7 +15444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15926,7 +15467,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -16365,7 +15906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16391,7 +15932,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11157" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7E8F9E-64BD-40D2-8B13-845047E7188D}"/>
+  <xr:revisionPtr revIDLastSave="11161" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{812235DD-90B8-40E8-A7BE-82AD5E6FC68F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -20187,38 +20187,38 @@
         <v>10000</v>
       </c>
       <c r="D7" s="80">
-        <v>19.2</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E7" s="94">
         <f>C7*D7</f>
-        <v>192000</v>
+        <v>189000</v>
       </c>
       <c r="F7" s="94">
         <f>E7*0.002</f>
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="G7" s="94">
         <f>E7*0.000068</f>
-        <v>13.055999999999999</v>
+        <v>12.852</v>
       </c>
       <c r="H7" s="94">
         <f>E7*0.00001</f>
-        <v>1.9200000000000002</v>
+        <v>1.8900000000000001</v>
       </c>
       <c r="I7" s="94">
         <f>(F7+G7+H7)*0.07</f>
-        <v>27.928320000000003</v>
+        <v>27.49194</v>
       </c>
       <c r="J7" s="94">
         <f>E7+F7+I7+G7+H7</f>
-        <v>192426.90432000003</v>
+        <v>189420.23394000003</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
       <c r="A8" s="77"/>
       <c r="B8" s="81">
         <f>(D7-D6)/D6</f>
-        <v>1.587301587301591E-2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="79">
         <f>SUM(C6:C7)</f>
@@ -20226,31 +20226,31 @@
       </c>
       <c r="D8" s="80">
         <f>E8/C8</f>
-        <v>19</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E8" s="79">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>570000</v>
+        <v>567000</v>
       </c>
       <c r="F8" s="79">
         <f t="shared" si="2"/>
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="G8" s="79">
         <f t="shared" si="2"/>
-        <v>37.984000000000002</v>
+        <v>37.78</v>
       </c>
       <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="I8" s="79">
         <f t="shared" si="2"/>
-        <v>82.857880000000009</v>
+        <v>82.421500000000009</v>
       </c>
       <c r="J8" s="79">
         <f t="shared" si="2"/>
-        <v>571266.54188000003</v>
+        <v>568259.87150000001</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="13"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26111"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11161" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{812235DD-90B8-40E8-A7BE-82AD5E6FC68F}"/>
+  <xr:revisionPtr revIDLastSave="11192" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44422035-125B-4C58-BF2C-5497A67D5724}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -3671,7 +3671,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4115D497-67E5-4755-A37C-D801F1CE1CC8}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -3810,78 +3810,78 @@
       <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:14" s="21" customFormat="1" ht="12.75">
-      <c r="A5" s="8">
-        <v>44860</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="A5" s="14">
+        <v>44943</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
         <v>10000</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="17">
         <v>8.9</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="18">
         <f>C5*D5</f>
         <v>89000</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <f>E5*0.002</f>
         <v>178</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="18">
         <f>E5*0.000068</f>
         <v>6.0519999999999996</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="18">
         <f>E5*0.00001</f>
         <v>0.89000000000000012</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="18">
         <f>(F5+G5+H5)*0.07</f>
         <v>12.94594</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="18">
         <f>E5+F5+I5+G5+H5</f>
         <v>89197.887940000001</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="21" customFormat="1" ht="12.75">
-      <c r="A6" s="44"/>
-      <c r="B6" s="25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="7">
         <f>(D5-D4)/D4</f>
         <v>0</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="5">
         <f>SUM(C4:C5)</f>
         <v>30000</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="66">
         <f>E6/C6</f>
         <v>8.9</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="5">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
         <v>267000</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
         <v>534</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
         <v>17.423999999999999</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
         <v>2.6700000000000004</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="5">
         <f t="shared" si="1"/>
         <v>38.786580000000001</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="5">
         <f t="shared" si="1"/>
         <v>267592.88058</v>
       </c>
@@ -3889,245 +3889,403 @@
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:14" s="21" customFormat="1" ht="12.75">
-      <c r="A7" s="44"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
-    </row>
-    <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A8" s="56">
+      <c r="A7" s="14">
+        <v>44944</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="16">
+        <v>10000</v>
+      </c>
+      <c r="D7" s="17">
+        <v>8.9</v>
+      </c>
+      <c r="E7" s="18">
+        <f>C7*D7</f>
+        <v>89000</v>
+      </c>
+      <c r="F7" s="18">
+        <f>E7*0.002</f>
+        <v>178</v>
+      </c>
+      <c r="G7" s="18">
+        <f>E7*0.000068</f>
+        <v>6.0519999999999996</v>
+      </c>
+      <c r="H7" s="18">
+        <f>E7*0.00001</f>
+        <v>0.89000000000000012</v>
+      </c>
+      <c r="I7" s="18">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>12.94594</v>
+      </c>
+      <c r="J7" s="18">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>89197.887940000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A8" s="42"/>
+      <c r="B8" s="7">
+        <f>(D7-D6)/D6</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <f>SUM(C6:C7)</f>
+        <v>40000</v>
+      </c>
+      <c r="D8" s="66">
+        <f>E8/C8</f>
+        <v>8.9</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>356000</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="2"/>
+        <v>712</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="2"/>
+        <v>23.475999999999999</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="2"/>
+        <v>3.5600000000000005</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="2"/>
+        <v>51.732520000000001</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="2"/>
+        <v>356790.76851999998</v>
+      </c>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A9" s="8">
+        <v>44944</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="11">
+        <v>8.4</v>
+      </c>
+      <c r="E9" s="20">
+        <f>C9*D9</f>
+        <v>84000</v>
+      </c>
+      <c r="F9" s="20">
+        <f>E9*0.002</f>
+        <v>168</v>
+      </c>
+      <c r="G9" s="20">
+        <f>E9*0.000068</f>
+        <v>5.7119999999999997</v>
+      </c>
+      <c r="H9" s="20">
+        <f>E9*0.00001</f>
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="I9" s="20">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>12.218640000000001</v>
+      </c>
+      <c r="J9" s="20">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>84186.770640000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A10" s="44"/>
+      <c r="B10" s="25">
+        <f>(D9-D8)/D8</f>
+        <v>-5.6179775280898875E-2</v>
+      </c>
+      <c r="C10" s="22">
+        <f>SUM(C8:C9)</f>
+        <v>50000</v>
+      </c>
+      <c r="D10" s="65">
+        <f>E10/C10</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E10" s="22">
+        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
+        <v>440000</v>
+      </c>
+      <c r="F10" s="22">
+        <f t="shared" si="3"/>
+        <v>880</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="3"/>
+        <v>29.187999999999999</v>
+      </c>
+      <c r="H10" s="22">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I10" s="22">
+        <f t="shared" si="3"/>
+        <v>63.951160000000002</v>
+      </c>
+      <c r="J10" s="22">
+        <f t="shared" si="3"/>
+        <v>440977.53915999999</v>
+      </c>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A11" s="44"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A12" s="56">
         <v>44799</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C12" s="10">
         <f>C4</f>
         <v>20000</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D12" s="64">
         <v>0.19109999999999999</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E12" s="60">
         <v>0</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F12" s="32">
         <v>0</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G12" s="60">
         <v>0</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8-E8</f>
+      <c r="H12" s="11">
+        <f>G12-E12</f>
         <v>0</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I12" s="12">
         <v>0</v>
       </c>
-      <c r="J8" s="61">
-        <f>C8*D8*0.9</f>
+      <c r="J12" s="61">
+        <f>C12*D12*0.9</f>
         <v>3439.8</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="56">
+      <c r="K12" s="11"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="56">
         <v>44242</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="B13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10">
         <f>C4</f>
         <v>20000</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D13" s="46">
         <f>D4</f>
         <v>8.9</v>
       </c>
-      <c r="E9" s="20">
-        <f>C9*D9</f>
+      <c r="E13" s="20">
+        <f>C13*D13</f>
         <v>178000</v>
       </c>
-      <c r="F9" s="20">
-        <f>E9*0.002</f>
+      <c r="F13" s="20">
+        <f>E13*0.002</f>
         <v>356</v>
       </c>
-      <c r="G9" s="20">
-        <f>E9*0.00006</f>
+      <c r="G13" s="20">
+        <f>E13*0.00006</f>
         <v>10.68</v>
       </c>
-      <c r="H9" s="20">
-        <f>E9*0.00001</f>
+      <c r="H13" s="20">
+        <f>E13*0.00001</f>
         <v>1.7800000000000002</v>
       </c>
-      <c r="I9" s="20">
-        <f>(F9+G9+H9)*0.07</f>
+      <c r="I13" s="20">
+        <f>(F13+G13+H13)*0.07</f>
         <v>25.792200000000001</v>
       </c>
-      <c r="J9" s="20">
-        <f>E9+F9+I9+G9+H9</f>
+      <c r="J13" s="20">
+        <f>E13+F13+I13+G13+H13</f>
         <v>178394.25219999999</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="56">
+    <row r="14" spans="1:14">
+      <c r="A14" s="56">
         <v>44277</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="10">
-        <f>C9</f>
+      <c r="C14" s="10">
+        <f>C13</f>
         <v>20000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D14" s="34">
         <v>8.9499999999999993</v>
       </c>
-      <c r="E10" s="11">
-        <f>C10*D10</f>
+      <c r="E14" s="11">
+        <f>C14*D14</f>
         <v>179000</v>
       </c>
-      <c r="F10" s="35">
-        <f>E10*0.002</f>
+      <c r="F14" s="35">
+        <f>E14*0.002</f>
         <v>358</v>
       </c>
-      <c r="G10" s="34">
-        <f>E10*0.000068</f>
+      <c r="G14" s="34">
+        <f>E14*0.000068</f>
         <v>12.172000000000001</v>
       </c>
-      <c r="H10" s="34">
-        <f>E10*0.00001</f>
+      <c r="H14" s="34">
+        <f>E14*0.00001</f>
         <v>1.79</v>
       </c>
-      <c r="I10" s="34">
-        <f>(F10+G10+H10)*0.07</f>
+      <c r="I14" s="34">
+        <f>(F14+G14+H14)*0.07</f>
         <v>26.037340000000004</v>
       </c>
-      <c r="J10" s="34">
-        <f>E10-F10-G10-H10-I10</f>
+      <c r="J14" s="34">
+        <f>E14-F14-G14-H14-I14</f>
         <v>178602.00065999999</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="12.75">
-      <c r="A11" s="56" t="s">
+    <row r="15" spans="1:14" ht="12.75">
+      <c r="A15" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="25">
-        <f>(D10-D9)/D9</f>
+      <c r="B15" s="25">
+        <f>(D14-D13)/D13</f>
         <v>5.6179775280897678E-3</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="20">
-        <f>E10-E9</f>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="20">
+        <f>E14-E13</f>
         <v>1000</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20">
-        <f>J10-J9</f>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20">
+        <f>J14-J13</f>
         <v>207.74846000000252</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="J12" s="53">
-        <f>J8+J11</f>
+    <row r="16" spans="1:14">
+      <c r="J16" s="53">
+        <f>J12+J15</f>
         <v>3647.5484600000027</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="78" customFormat="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-    </row>
-    <row r="14" spans="1:14" s="13" customFormat="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-    </row>
-    <row r="15" spans="1:14" s="31" customFormat="1" ht="18.75">
-      <c r="A15" s="28"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" s="21" customFormat="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="L16" s="25"/>
-    </row>
-    <row r="17" spans="1:13" s="13" customFormat="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-    </row>
-    <row r="18" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A18" s="28"/>
-      <c r="B18" s="30"/>
+    <row r="17" spans="1:13" s="78" customFormat="1">
+      <c r="A17" s="82"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+    </row>
+    <row r="18" spans="1:13" s="13" customFormat="1">
+      <c r="A18" s="49"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" spans="1:13" ht="12"/>
-    <row r="20" spans="1:13" ht="12"/>
-    <row r="21" spans="1:13" ht="12"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+    </row>
+    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A19" s="28"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" s="21" customFormat="1">
+      <c r="A20" s="49"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="L20" s="25"/>
+    </row>
+    <row r="21" spans="1:13" s="13" customFormat="1">
+      <c r="A21" s="49"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+    </row>
+    <row r="22" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A22" s="28"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+    </row>
+    <row r="23" spans="1:13" ht="12"/>
+    <row r="24" spans="1:13" ht="12"/>
+    <row r="25" spans="1:13" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -11065,7 +11223,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="50" customWidth="1"/>
@@ -11665,7 +11823,7 @@
       </c>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" spans="1:12" s="13" customFormat="1">
+    <row r="17" spans="1:15" s="13" customFormat="1">
       <c r="A17" s="90"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5">
@@ -11702,7 +11860,7 @@
       </c>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" spans="1:12" s="21" customFormat="1">
+    <row r="18" spans="1:15" s="21" customFormat="1">
       <c r="A18" s="49">
         <v>44538</v>
       </c>
@@ -11741,7 +11899,7 @@
       </c>
       <c r="K18" s="25"/>
     </row>
-    <row r="19" spans="1:12" s="21" customFormat="1">
+    <row r="19" spans="1:15" s="21" customFormat="1">
       <c r="A19" s="49">
         <v>44557</v>
       </c>
@@ -11781,7 +11939,7 @@
       <c r="K19" s="25"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" s="21" customFormat="1">
+    <row r="20" spans="1:15" s="21" customFormat="1">
       <c r="A20" s="49">
         <v>44560</v>
       </c>
@@ -11821,7 +11979,7 @@
       <c r="K20" s="25"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" s="13" customFormat="1">
+    <row r="21" spans="1:15" s="13" customFormat="1">
       <c r="A21" s="49">
         <v>44578</v>
       </c>
@@ -11861,7 +12019,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" s="21" customFormat="1">
+    <row r="22" spans="1:15" s="21" customFormat="1">
       <c r="A22" s="90"/>
       <c r="B22" s="7">
         <f>(D21-D20)/D20</f>
@@ -11901,7 +12059,7 @@
       </c>
       <c r="L22" s="25"/>
     </row>
-    <row r="23" spans="1:12" s="13" customFormat="1">
+    <row r="23" spans="1:15" s="13" customFormat="1">
       <c r="A23" s="49">
         <v>44615</v>
       </c>
@@ -11941,394 +12099,363 @@
       <c r="K23" s="11"/>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" s="21" customFormat="1">
-      <c r="A24" s="90"/>
-      <c r="B24" s="7">
-        <f>(D23-D22)/D22</f>
-        <v>-0.16216216216216217</v>
-      </c>
-      <c r="C24" s="5">
-        <f>SUM(C22:C23)</f>
+    <row r="24" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="A24" s="49">
+        <v>44943</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16">
+        <f>C23</f>
+        <v>3000</v>
+      </c>
+      <c r="D24" s="26">
+        <v>50.75</v>
+      </c>
+      <c r="E24" s="17">
+        <f>C24*D24</f>
+        <v>152250</v>
+      </c>
+      <c r="F24" s="27">
+        <f>E24*0.002</f>
+        <v>304.5</v>
+      </c>
+      <c r="G24" s="26">
+        <f>E24*0.000068</f>
+        <v>10.353</v>
+      </c>
+      <c r="H24" s="26">
+        <f>E24*0.00001</f>
+        <v>1.5225000000000002</v>
+      </c>
+      <c r="I24" s="26">
+        <f>(F24+G24+H24)*0.07</f>
+        <v>22.146285000000002</v>
+      </c>
+      <c r="J24" s="26">
+        <f>E24-F24-G24-H24-I24</f>
+        <v>151911.47821500001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A25" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="7">
+        <f>(D24-D23)/D23</f>
+        <v>-6.4516129032258063E-2</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18">
+        <f>E24-E23</f>
+        <v>-10500</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18">
+        <f>J24-J23</f>
+        <v>-11198.996760000009</v>
+      </c>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:15" s="21" customFormat="1" ht="12.75">
+      <c r="A26" s="49">
+        <v>44943</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6000</v>
+      </c>
+      <c r="D26" s="71">
+        <v>64.75</v>
+      </c>
+      <c r="E26" s="5">
+        <v>388500</v>
+      </c>
+      <c r="F26" s="5">
+        <v>777</v>
+      </c>
+      <c r="G26" s="5">
+        <v>25.659599999999998</v>
+      </c>
+      <c r="H26" s="5">
+        <v>3.8850000000000002</v>
+      </c>
+      <c r="I26" s="5">
+        <v>56.458122000000003</v>
+      </c>
+      <c r="J26" s="5">
+        <v>389363.002722</v>
+      </c>
+      <c r="L26" s="25"/>
+    </row>
+    <row r="27" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A27" s="56">
+        <v>44543</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10">
+        <v>3000</v>
+      </c>
+      <c r="D27" s="46">
+        <v>48.25</v>
+      </c>
+      <c r="E27" s="20">
+        <f>C27*D27</f>
+        <v>144750</v>
+      </c>
+      <c r="F27" s="20">
+        <f>E27*0.002</f>
+        <v>289.5</v>
+      </c>
+      <c r="G27" s="20">
+        <f>E27*0.00006</f>
+        <v>8.6850000000000005</v>
+      </c>
+      <c r="H27" s="20">
+        <f>E27*0.00001</f>
+        <v>1.4475</v>
+      </c>
+      <c r="I27" s="20">
+        <f>(F27+G27+H27)*0.07</f>
+        <v>20.974275000000002</v>
+      </c>
+      <c r="J27" s="20">
+        <f>E27+F27+I27+G27+H27</f>
+        <v>145070.60677499999</v>
+      </c>
+      <c r="K27" s="57"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+    </row>
+    <row r="28" spans="1:15" ht="12.75">
+      <c r="B28" s="3">
+        <f>(D27-D26)/D26</f>
+        <v>-0.25482625482625482</v>
+      </c>
+      <c r="C28" s="2">
+        <f>SUM(C26:C27)</f>
         <v>9000</v>
       </c>
-      <c r="D24" s="71">
-        <f>E24/C24</f>
-        <v>61.25</v>
-      </c>
-      <c r="E24" s="5">
-        <f t="shared" ref="E24:J24" si="11">SUM(E22:E23)</f>
-        <v>551250</v>
-      </c>
-      <c r="F24" s="5">
+      <c r="D28" s="47">
+        <f>E28/C28</f>
+        <v>59.25</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" ref="E28:J28" si="11">SUM(E26:E27)</f>
+        <v>533250</v>
+      </c>
+      <c r="F28" s="2">
         <f t="shared" si="11"/>
-        <v>1102.5</v>
-      </c>
-      <c r="G24" s="5">
+        <v>1066.5</v>
+      </c>
+      <c r="G28" s="2">
         <f t="shared" si="11"/>
-        <v>35.424599999999998</v>
-      </c>
-      <c r="H24" s="5">
+        <v>34.3446</v>
+      </c>
+      <c r="H28" s="2">
         <f t="shared" si="11"/>
-        <v>5.5125000000000002</v>
-      </c>
-      <c r="I24" s="5">
+        <v>5.3325000000000005</v>
+      </c>
+      <c r="I28" s="2">
         <f t="shared" si="11"/>
-        <v>80.040597000000005</v>
-      </c>
-      <c r="J24" s="5">
+        <v>77.432397000000009</v>
+      </c>
+      <c r="J28" s="2">
         <f t="shared" si="11"/>
-        <v>552473.47769700002</v>
-      </c>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="1:12" s="13" customFormat="1" ht="12.75">
-      <c r="A25" s="56">
+        <v>534433.609497</v>
+      </c>
+      <c r="K28" s="57"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+    </row>
+    <row r="29" spans="1:15" s="21" customFormat="1" ht="12.75">
+      <c r="A29" s="90"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="L29" s="25"/>
+    </row>
+    <row r="30" spans="1:15" s="21" customFormat="1" ht="12.75">
+      <c r="A30" s="90"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="L30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" s="13" customFormat="1">
+      <c r="A31" s="49">
         <v>44623</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="10">
+      <c r="B31" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16">
         <v>3000</v>
       </c>
-      <c r="D25" s="62">
-        <v>41.25</v>
-      </c>
-      <c r="E25" s="20">
-        <f>C25*D25</f>
-        <v>123750</v>
-      </c>
-      <c r="F25" s="20">
-        <f>E25*0.002</f>
-        <v>247.5</v>
-      </c>
-      <c r="G25" s="20">
-        <f>E25*0.00006</f>
-        <v>7.4249999999999998</v>
-      </c>
-      <c r="H25" s="20">
-        <f>E25*0.00001</f>
-        <v>1.2375</v>
-      </c>
-      <c r="I25" s="20">
-        <f>(F25+G25+H25)*0.07</f>
-        <v>17.931375000000003</v>
-      </c>
-      <c r="J25" s="20">
-        <f>E25+F25+I25+G25+H25</f>
-        <v>124024.09387500001</v>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="1:12" s="21" customFormat="1" ht="12.75">
-      <c r="A26" s="89"/>
-      <c r="B26" s="25">
-        <f>(D25-D24)/D24</f>
-        <v>-0.32653061224489793</v>
-      </c>
-      <c r="C26" s="22">
-        <f>SUM(C24:C25)</f>
-        <v>12000</v>
-      </c>
-      <c r="D26" s="68">
-        <f>E26/C26</f>
-        <v>56.25</v>
-      </c>
-      <c r="E26" s="22">
-        <f t="shared" ref="E26:J26" si="12">SUM(E24:E25)</f>
-        <v>675000</v>
-      </c>
-      <c r="F26" s="22">
-        <f t="shared" si="12"/>
-        <v>1350</v>
-      </c>
-      <c r="G26" s="22">
-        <f t="shared" si="12"/>
-        <v>42.849599999999995</v>
-      </c>
-      <c r="H26" s="22">
-        <f t="shared" si="12"/>
-        <v>6.75</v>
-      </c>
-      <c r="I26" s="22">
-        <f t="shared" si="12"/>
-        <v>97.971972000000008</v>
-      </c>
-      <c r="J26" s="22">
-        <f t="shared" si="12"/>
-        <v>676497.57157200004</v>
-      </c>
-      <c r="L26" s="25"/>
-    </row>
-    <row r="27" spans="1:12" s="21" customFormat="1" ht="12.75">
-      <c r="A27" s="90"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="L27" s="25"/>
-    </row>
-    <row r="28" spans="1:12" s="13" customFormat="1">
-      <c r="A28" s="49">
-        <v>44623</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="16">
+      <c r="D31" s="69">
+        <v>51.25</v>
+      </c>
+      <c r="E31" s="18">
+        <f>C31*D31</f>
+        <v>153750</v>
+      </c>
+      <c r="F31" s="18">
+        <f>E31*0.002</f>
+        <v>307.5</v>
+      </c>
+      <c r="G31" s="18">
+        <f>E31*0.00006</f>
+        <v>9.2249999999999996</v>
+      </c>
+      <c r="H31" s="18">
+        <f>E31*0.00001</f>
+        <v>1.5375000000000001</v>
+      </c>
+      <c r="I31" s="18">
+        <f>(F31+G31+H31)*0.07</f>
+        <v>22.278375000000004</v>
+      </c>
+      <c r="J31" s="18">
+        <f>E31+F31+I31+G31+H31</f>
+        <v>154090.54087500001</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="A32" s="49">
+        <v>44865</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="16">
+        <f>C31</f>
         <v>3000</v>
       </c>
-      <c r="D28" s="69">
-        <v>51.25</v>
-      </c>
-      <c r="E28" s="18">
-        <f>C28*D28</f>
-        <v>153750</v>
-      </c>
-      <c r="F28" s="18">
-        <f>E28*0.002</f>
-        <v>307.5</v>
-      </c>
-      <c r="G28" s="18">
-        <f>E28*0.00006</f>
-        <v>9.2249999999999996</v>
-      </c>
-      <c r="H28" s="18">
-        <f>E28*0.00001</f>
-        <v>1.5375000000000001</v>
-      </c>
-      <c r="I28" s="18">
-        <f>(F28+G28+H28)*0.07</f>
-        <v>22.278375000000004</v>
-      </c>
-      <c r="J28" s="18">
-        <f>E28+F28+I28+G28+H28</f>
-        <v>154090.54087500001</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" spans="1:12" s="13" customFormat="1" ht="12.75">
-      <c r="A29" s="49">
-        <v>44865</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="16">
-        <f>C28</f>
+      <c r="D32" s="26">
+        <v>43.5</v>
+      </c>
+      <c r="E32" s="17">
+        <f>C32*D32</f>
+        <v>130500</v>
+      </c>
+      <c r="F32" s="27">
+        <f>E32*0.002</f>
+        <v>261</v>
+      </c>
+      <c r="G32" s="26">
+        <f>E32*0.000068</f>
+        <v>8.8740000000000006</v>
+      </c>
+      <c r="H32" s="26">
+        <f>E32*0.00001</f>
+        <v>1.3050000000000002</v>
+      </c>
+      <c r="I32" s="26">
+        <f>(F32+G32+H32)*0.07</f>
+        <v>18.982530000000004</v>
+      </c>
+      <c r="J32" s="26">
+        <f>E32-F32-G32-H32-I32</f>
+        <v>130209.83847000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A33" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7">
+        <f>(D32-D31)/D31</f>
+        <v>-0.15121951219512195</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18">
+        <f>E32-E31</f>
+        <v>-23250</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18">
+        <f>J32-J31</f>
+        <v>-23880.702404999989</v>
+      </c>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="50">
+        <v>44620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="19" customFormat="1" ht="16.5">
+      <c r="A36" s="56">
+        <v>44619</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="16">
         <v>3000</v>
       </c>
-      <c r="D29" s="26">
-        <v>43.5</v>
-      </c>
-      <c r="E29" s="17">
-        <f>C29*D29</f>
-        <v>130500</v>
-      </c>
-      <c r="F29" s="27">
-        <f>E29*0.002</f>
-        <v>261</v>
-      </c>
-      <c r="G29" s="26">
-        <f>E29*0.000068</f>
-        <v>8.8740000000000006</v>
-      </c>
-      <c r="H29" s="26">
-        <f>E29*0.00001</f>
-        <v>1.3050000000000002</v>
-      </c>
-      <c r="I29" s="26">
-        <f>(F29+G29+H29)*0.07</f>
-        <v>18.982530000000004</v>
-      </c>
-      <c r="J29" s="26">
-        <f>E29-F29-G29-H29-I29</f>
-        <v>130209.83847000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="31" customFormat="1" ht="18.75">
-      <c r="A30" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="7">
-        <f>(D29-D28)/D28</f>
-        <v>-0.15121951219512195</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18">
-        <f>E29-E28</f>
-        <v>-23250</v>
-      </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18">
-        <f>J29-J28</f>
-        <v>-23880.702404999989</v>
-      </c>
-      <c r="K30" s="12"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="50">
-        <v>44620</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" s="19" customFormat="1" ht="16.5">
-      <c r="A33" s="56">
-        <v>44619</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="16">
-        <v>3000</v>
-      </c>
-      <c r="D33" s="46">
+      <c r="D36" s="46">
         <v>54.25</v>
-      </c>
-      <c r="E33" s="20">
-        <f>C33*D33</f>
-        <v>162750</v>
-      </c>
-      <c r="F33" s="20">
-        <f>E33*0.002</f>
-        <v>325.5</v>
-      </c>
-      <c r="G33" s="20">
-        <f>E33*0.00006</f>
-        <v>9.7650000000000006</v>
-      </c>
-      <c r="H33" s="20">
-        <f>E33*0.00001</f>
-        <v>1.6275000000000002</v>
-      </c>
-      <c r="I33" s="20">
-        <f>(F33+G33+H33)*0.07</f>
-        <v>23.582475000000002</v>
-      </c>
-      <c r="J33" s="20">
-        <f>E33+F33+I33+G33+H33</f>
-        <v>163110.47497500002</v>
-      </c>
-      <c r="K33" s="57"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-    </row>
-    <row r="34" spans="1:15" s="13" customFormat="1">
-      <c r="A34" s="56">
-        <v>44524</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="10">
-        <f>C33</f>
-        <v>3000</v>
-      </c>
-      <c r="D34" s="26">
-        <v>58</v>
-      </c>
-      <c r="E34" s="11">
-        <f>C34*D34</f>
-        <v>174000</v>
-      </c>
-      <c r="F34" s="35">
-        <f>E34*0.002</f>
-        <v>348</v>
-      </c>
-      <c r="G34" s="34">
-        <f>E34*0.000068</f>
-        <v>11.832000000000001</v>
-      </c>
-      <c r="H34" s="34">
-        <f>E34*0.00001</f>
-        <v>1.7400000000000002</v>
-      </c>
-      <c r="I34" s="34">
-        <f>(F34+G34+H34)*0.07</f>
-        <v>25.310040000000004</v>
-      </c>
-      <c r="J34" s="34">
-        <f>E34-F34-G34-H34-I34</f>
-        <v>173613.11796</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A35" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="25">
-        <f>(D34-D33)/D33</f>
-        <v>6.9124423963133647E-2</v>
-      </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="20">
-        <f>E34-E33</f>
-        <v>11250</v>
-      </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="18">
-        <f>J34-J33</f>
-        <v>10502.642984999984</v>
-      </c>
-      <c r="K35" s="12"/>
-    </row>
-    <row r="36" spans="1:15" s="19" customFormat="1" ht="16.5">
-      <c r="A36" s="49">
-        <v>44578</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="16">
-        <v>1600</v>
-      </c>
-      <c r="D36" s="46">
-        <v>59.25</v>
       </c>
       <c r="E36" s="20">
         <f>C36*D36</f>
-        <v>94800</v>
+        <v>162750</v>
       </c>
       <c r="F36" s="20">
         <f>E36*0.002</f>
-        <v>189.6</v>
+        <v>325.5</v>
       </c>
       <c r="G36" s="20">
         <f>E36*0.00006</f>
-        <v>5.6879999999999997</v>
+        <v>9.7650000000000006</v>
       </c>
       <c r="H36" s="20">
         <f>E36*0.00001</f>
-        <v>0.94800000000000006</v>
+        <v>1.6275000000000002</v>
       </c>
       <c r="I36" s="20">
         <f>(F36+G36+H36)*0.07</f>
-        <v>13.736520000000001</v>
+        <v>23.582475000000002</v>
       </c>
       <c r="J36" s="20">
         <f>E36+F36+I36+G36+H36</f>
-        <v>95009.97252000001</v>
+        <v>163110.47497500002</v>
       </c>
       <c r="K36" s="57"/>
       <c r="L36" s="58"/>
@@ -12345,34 +12472,34 @@
       </c>
       <c r="C37" s="10">
         <f>C36</f>
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="D37" s="26">
         <v>58</v>
       </c>
       <c r="E37" s="11">
         <f>C37*D37</f>
-        <v>92800</v>
+        <v>174000</v>
       </c>
       <c r="F37" s="35">
         <f>E37*0.002</f>
-        <v>185.6</v>
+        <v>348</v>
       </c>
       <c r="G37" s="34">
         <f>E37*0.000068</f>
-        <v>6.3103999999999996</v>
+        <v>11.832000000000001</v>
       </c>
       <c r="H37" s="34">
         <f>E37*0.00001</f>
-        <v>0.92800000000000005</v>
+        <v>1.7400000000000002</v>
       </c>
       <c r="I37" s="34">
         <f>(F37+G37+H37)*0.07</f>
-        <v>13.498688</v>
+        <v>25.310040000000004</v>
       </c>
       <c r="J37" s="34">
         <f>E37-F37-G37-H37-I37</f>
-        <v>92593.662911999985</v>
+        <v>173613.11796</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="31" customFormat="1" ht="18.75">
@@ -12381,13 +12508,13 @@
       </c>
       <c r="B38" s="25">
         <f>(D37-D36)/D36</f>
-        <v>-2.1097046413502109E-2</v>
+        <v>6.9124423963133647E-2</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="11"/>
       <c r="E38" s="20">
         <f>E37-E36</f>
-        <v>-2000</v>
+        <v>11250</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
@@ -12395,49 +12522,46 @@
       <c r="I38" s="20"/>
       <c r="J38" s="18">
         <f>J37-J36</f>
-        <v>-2416.309608000025</v>
-      </c>
-      <c r="K38" s="20">
-        <f>J35+J38</f>
-        <v>8086.333376999959</v>
-      </c>
+        <v>10502.642984999984</v>
+      </c>
+      <c r="K38" s="12"/>
     </row>
     <row r="39" spans="1:15" s="19" customFormat="1" ht="16.5">
-      <c r="A39" s="56">
-        <v>44295</v>
+      <c r="A39" s="49">
+        <v>44578</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C39" s="16">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="D39" s="46">
-        <v>66.75</v>
+        <v>59.25</v>
       </c>
       <c r="E39" s="20">
         <f>C39*D39</f>
-        <v>66750</v>
+        <v>94800</v>
       </c>
       <c r="F39" s="20">
         <f>E39*0.002</f>
-        <v>133.5</v>
+        <v>189.6</v>
       </c>
       <c r="G39" s="20">
         <f>E39*0.00006</f>
-        <v>4.0049999999999999</v>
+        <v>5.6879999999999997</v>
       </c>
       <c r="H39" s="20">
         <f>E39*0.00001</f>
-        <v>0.66750000000000009</v>
+        <v>0.94800000000000006</v>
       </c>
       <c r="I39" s="20">
         <f>(F39+G39+H39)*0.07</f>
-        <v>9.6720749999999995</v>
+        <v>13.736520000000001</v>
       </c>
       <c r="J39" s="20">
         <f>E39+F39+I39+G39+H39</f>
-        <v>66897.844574999996</v>
+        <v>95009.97252000001</v>
       </c>
       <c r="K39" s="57"/>
       <c r="L39" s="58"/>
@@ -12454,35 +12578,34 @@
       </c>
       <c r="C40" s="10">
         <f>C39</f>
-        <v>1000</v>
-      </c>
-      <c r="D40" s="34">
-        <f>D37</f>
+        <v>1600</v>
+      </c>
+      <c r="D40" s="26">
         <v>58</v>
       </c>
       <c r="E40" s="11">
         <f>C40*D40</f>
-        <v>58000</v>
+        <v>92800</v>
       </c>
       <c r="F40" s="35">
         <f>E40*0.002</f>
-        <v>116</v>
+        <v>185.6</v>
       </c>
       <c r="G40" s="34">
         <f>E40*0.000068</f>
-        <v>3.944</v>
+        <v>6.3103999999999996</v>
       </c>
       <c r="H40" s="34">
         <f>E40*0.00001</f>
-        <v>0.58000000000000007</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="I40" s="34">
         <f>(F40+G40+H40)*0.07</f>
-        <v>8.4366800000000008</v>
+        <v>13.498688</v>
       </c>
       <c r="J40" s="34">
         <f>E40-F40-G40-H40-I40</f>
-        <v>57871.039319999996</v>
+        <v>92593.662911999985</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="31" customFormat="1" ht="18.75">
@@ -12491,13 +12614,13 @@
       </c>
       <c r="B41" s="25">
         <f>(D40-D39)/D39</f>
-        <v>-0.13108614232209737</v>
+        <v>-2.1097046413502109E-2</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="11"/>
       <c r="E41" s="20">
         <f>E40-E39</f>
-        <v>-8750</v>
+        <v>-2000</v>
       </c>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
@@ -12505,49 +12628,49 @@
       <c r="I41" s="20"/>
       <c r="J41" s="18">
         <f>J40-J39</f>
-        <v>-9026.8052549999993</v>
+        <v>-2416.309608000025</v>
       </c>
       <c r="K41" s="20">
-        <f>K38+J41</f>
-        <v>-940.47187800004031</v>
+        <f>J38+J41</f>
+        <v>8086.333376999959</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A42" s="56">
-        <v>44274</v>
+        <v>44295</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="16">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D42" s="46">
         <v>66.75</v>
       </c>
       <c r="E42" s="20">
         <f>C42*D42</f>
-        <v>133500</v>
+        <v>66750</v>
       </c>
       <c r="F42" s="20">
         <f>E42*0.002</f>
-        <v>267</v>
+        <v>133.5</v>
       </c>
       <c r="G42" s="20">
         <f>E42*0.00006</f>
-        <v>8.01</v>
+        <v>4.0049999999999999</v>
       </c>
       <c r="H42" s="20">
         <f>E42*0.00001</f>
-        <v>1.3350000000000002</v>
+        <v>0.66750000000000009</v>
       </c>
       <c r="I42" s="20">
         <f>(F42+G42+H42)*0.07</f>
-        <v>19.344149999999999</v>
+        <v>9.6720749999999995</v>
       </c>
       <c r="J42" s="20">
         <f>E42+F42+I42+G42+H42</f>
-        <v>133795.68914999999</v>
+        <v>66897.844574999996</v>
       </c>
       <c r="K42" s="57"/>
       <c r="L42" s="58"/>
@@ -12564,35 +12687,35 @@
       </c>
       <c r="C43" s="10">
         <f>C42</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="34">
-        <f>D37</f>
+        <f>D40</f>
         <v>58</v>
       </c>
       <c r="E43" s="11">
         <f>C43*D43</f>
-        <v>116000</v>
+        <v>58000</v>
       </c>
       <c r="F43" s="35">
         <f>E43*0.002</f>
-        <v>232</v>
+        <v>116</v>
       </c>
       <c r="G43" s="34">
         <f>E43*0.000068</f>
-        <v>7.8879999999999999</v>
+        <v>3.944</v>
       </c>
       <c r="H43" s="34">
         <f>E43*0.00001</f>
-        <v>1.1600000000000001</v>
+        <v>0.58000000000000007</v>
       </c>
       <c r="I43" s="34">
         <f>(F43+G43+H43)*0.07</f>
-        <v>16.873360000000002</v>
+        <v>8.4366800000000008</v>
       </c>
       <c r="J43" s="34">
         <f>E43-F43-G43-H43-I43</f>
-        <v>115742.07863999999</v>
+        <v>57871.039319999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" s="31" customFormat="1" ht="18.75">
@@ -12607,7 +12730,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="20">
         <f>E43-E42</f>
-        <v>-17500</v>
+        <v>-8750</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="20"/>
@@ -12615,49 +12738,49 @@
       <c r="I44" s="20"/>
       <c r="J44" s="18">
         <f>J43-J42</f>
-        <v>-18053.610509999999</v>
+        <v>-9026.8052549999993</v>
       </c>
       <c r="K44" s="20">
         <f>K41+J44</f>
-        <v>-18994.082388000039</v>
+        <v>-940.47187800004031</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A45" s="56">
-        <v>44272</v>
+        <v>44274</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C45" s="16">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D45" s="46">
         <v>66.75</v>
       </c>
       <c r="E45" s="20">
         <f>C45*D45</f>
-        <v>93450</v>
+        <v>133500</v>
       </c>
       <c r="F45" s="20">
         <f>E45*0.002</f>
-        <v>186.9</v>
+        <v>267</v>
       </c>
       <c r="G45" s="20">
         <f>E45*0.00006</f>
-        <v>5.6070000000000002</v>
+        <v>8.01</v>
       </c>
       <c r="H45" s="20">
         <f>E45*0.00001</f>
-        <v>0.93450000000000011</v>
+        <v>1.3350000000000002</v>
       </c>
       <c r="I45" s="20">
         <f>(F45+G45+H45)*0.07</f>
-        <v>13.540905000000002</v>
+        <v>19.344149999999999</v>
       </c>
       <c r="J45" s="20">
         <f>E45+F45+I45+G45+H45</f>
-        <v>93656.982405000002</v>
+        <v>133795.68914999999</v>
       </c>
       <c r="K45" s="57"/>
       <c r="L45" s="58"/>
@@ -12674,35 +12797,35 @@
       </c>
       <c r="C46" s="10">
         <f>C45</f>
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D46" s="34">
-        <f>D37</f>
+        <f>D40</f>
         <v>58</v>
       </c>
       <c r="E46" s="11">
         <f>C46*D46</f>
-        <v>81200</v>
+        <v>116000</v>
       </c>
       <c r="F46" s="35">
         <f>E46*0.002</f>
-        <v>162.4</v>
+        <v>232</v>
       </c>
       <c r="G46" s="34">
         <f>E46*0.000068</f>
-        <v>5.5216000000000003</v>
+        <v>7.8879999999999999</v>
       </c>
       <c r="H46" s="34">
         <f>E46*0.00001</f>
-        <v>0.81200000000000006</v>
+        <v>1.1600000000000001</v>
       </c>
       <c r="I46" s="34">
         <f>(F46+G46+H46)*0.07</f>
-        <v>11.811352000000003</v>
+        <v>16.873360000000002</v>
       </c>
       <c r="J46" s="34">
         <f>E46-F46-G46-H46-I46</f>
-        <v>81019.455048000003</v>
+        <v>115742.07863999999</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="31" customFormat="1" ht="18.75">
@@ -12717,7 +12840,7 @@
       <c r="D47" s="11"/>
       <c r="E47" s="20">
         <f>E46-E45</f>
-        <v>-12250</v>
+        <v>-17500</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
@@ -12725,10 +12848,120 @@
       <c r="I47" s="20"/>
       <c r="J47" s="18">
         <f>J46-J45</f>
-        <v>-12637.527356999999</v>
+        <v>-18053.610509999999</v>
       </c>
       <c r="K47" s="20">
         <f>K44+J47</f>
+        <v>-18994.082388000039</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" s="19" customFormat="1" ht="16.5">
+      <c r="A48" s="56">
+        <v>44272</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="16">
+        <v>1400</v>
+      </c>
+      <c r="D48" s="46">
+        <v>66.75</v>
+      </c>
+      <c r="E48" s="20">
+        <f>C48*D48</f>
+        <v>93450</v>
+      </c>
+      <c r="F48" s="20">
+        <f>E48*0.002</f>
+        <v>186.9</v>
+      </c>
+      <c r="G48" s="20">
+        <f>E48*0.00006</f>
+        <v>5.6070000000000002</v>
+      </c>
+      <c r="H48" s="20">
+        <f>E48*0.00001</f>
+        <v>0.93450000000000011</v>
+      </c>
+      <c r="I48" s="20">
+        <f>(F48+G48+H48)*0.07</f>
+        <v>13.540905000000002</v>
+      </c>
+      <c r="J48" s="20">
+        <f>E48+F48+I48+G48+H48</f>
+        <v>93656.982405000002</v>
+      </c>
+      <c r="K48" s="57"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+    </row>
+    <row r="49" spans="1:11" s="13" customFormat="1">
+      <c r="A49" s="56">
+        <v>44524</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="10">
+        <f>C48</f>
+        <v>1400</v>
+      </c>
+      <c r="D49" s="34">
+        <f>D40</f>
+        <v>58</v>
+      </c>
+      <c r="E49" s="11">
+        <f>C49*D49</f>
+        <v>81200</v>
+      </c>
+      <c r="F49" s="35">
+        <f>E49*0.002</f>
+        <v>162.4</v>
+      </c>
+      <c r="G49" s="34">
+        <f>E49*0.000068</f>
+        <v>5.5216000000000003</v>
+      </c>
+      <c r="H49" s="34">
+        <f>E49*0.00001</f>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="I49" s="34">
+        <f>(F49+G49+H49)*0.07</f>
+        <v>11.811352000000003</v>
+      </c>
+      <c r="J49" s="34">
+        <f>E49-F49-G49-H49-I49</f>
+        <v>81019.455048000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="31" customFormat="1" ht="18.75">
+      <c r="A50" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="25">
+        <f>(D49-D48)/D48</f>
+        <v>-0.13108614232209737</v>
+      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="20">
+        <f>E49-E48</f>
+        <v>-12250</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="18">
+        <f>J49-J48</f>
+        <v>-12637.527356999999</v>
+      </c>
+      <c r="K50" s="20">
+        <f>K47+J50</f>
         <v>-31631.609745000038</v>
       </c>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11192" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44422035-125B-4C58-BF2C-5497A67D5724}"/>
+  <xr:revisionPtr revIDLastSave="11243" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAE95D6E-85FC-4364-9007-FA0B27F14007}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="10" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -34,11 +34,12 @@
     <sheet name="SCC" sheetId="152" r:id="rId19"/>
     <sheet name="SCCC" sheetId="177" r:id="rId20"/>
     <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
-    <sheet name="TMT" sheetId="145" r:id="rId24"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
-    <sheet name="WHART" sheetId="171" r:id="rId26"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
+    <sheet name="TMT" sheetId="145" r:id="rId25"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
+    <sheet name="WHART" sheetId="171" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="36">
   <si>
     <t>KCE</t>
   </si>
@@ -148,6 +149,9 @@
   </si>
   <si>
     <t>SENA</t>
+  </si>
+  <si>
+    <t>SINGER</t>
   </si>
   <si>
     <t>SYNEX</t>
@@ -13743,6 +13747,194 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44945</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D2" s="17">
+        <v>28</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>100800</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>201.6</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>6.048</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.008</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>14.605920000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>101023.26192</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1">
+      <c r="A3" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10">
+        <f>C2</f>
+        <v>3600</v>
+      </c>
+      <c r="D3" s="34">
+        <v>29.5</v>
+      </c>
+      <c r="E3" s="11">
+        <f>C3*D3</f>
+        <v>106200</v>
+      </c>
+      <c r="F3" s="35">
+        <f>E3*0.002</f>
+        <v>212.4</v>
+      </c>
+      <c r="G3" s="34">
+        <f>E3*0.000068</f>
+        <v>7.2215999999999996</v>
+      </c>
+      <c r="H3" s="34">
+        <f>E3*0.00001</f>
+        <v>1.0620000000000001</v>
+      </c>
+      <c r="I3" s="34">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>15.447852000000003</v>
+      </c>
+      <c r="J3" s="34">
+        <f>E3-F3-G3-H3-I3</f>
+        <v>105963.868548</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1">
+      <c r="A4" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="12">
+        <f>(D3-D2)/D2</f>
+        <v>5.3571428571428568E-2</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="20">
+        <f>E3-E2</f>
+        <v>5400</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20">
+        <f>J3-J2</f>
+        <v>4940.6066279999941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
+      <c r="A5" s="50"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="47"/>
+      <c r="J5" s="53">
+        <f>J1+J4</f>
+        <v>4940.6066279999941</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1">
+      <c r="A6" s="56"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1">
+      <c r="A7" s="56"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
+      <c r="A9" s="50"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="47"/>
+      <c r="J9" s="53"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13765,7 +13957,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -14977,7 +15169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15000,7 +15192,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15218,7 +15410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15241,7 +15433,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15677,7 +15869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15700,7 +15892,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -16139,7 +16331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16165,7 +16357,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -16670,7 +16862,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="89" customWidth="1"/>
@@ -17124,130 +17316,93 @@
       <c r="N11" s="58"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" ht="14.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="74">
-        <f>(D11-D10)/D10</f>
-        <v>-0.12080536912751678</v>
-      </c>
-      <c r="C12" s="51">
-        <f>SUM(C10:C11)</f>
-        <v>15000</v>
-      </c>
-      <c r="D12" s="52">
-        <f>E12/C12</f>
-        <v>36.5</v>
-      </c>
-      <c r="E12" s="51">
-        <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
-        <v>547500</v>
-      </c>
-      <c r="F12" s="51">
-        <f t="shared" si="4"/>
-        <v>1095</v>
-      </c>
-      <c r="G12" s="51">
-        <f t="shared" si="4"/>
-        <v>32.85</v>
-      </c>
-      <c r="H12" s="51">
-        <f t="shared" si="4"/>
-        <v>5.4749999999999996</v>
-      </c>
-      <c r="I12" s="51">
-        <f t="shared" si="4"/>
-        <v>79.332750000000004</v>
-      </c>
-      <c r="J12" s="51">
-        <f t="shared" si="4"/>
-        <v>548712.65775000001</v>
-      </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="59"/>
-      <c r="O12" s="59"/>
-    </row>
-    <row r="13" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A13" s="56">
-        <v>44543</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10">
+    <row r="12" spans="1:15" s="1" customFormat="1">
+      <c r="A12" s="49">
+        <v>44945</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="16">
+        <f>C11</f>
         <v>2500</v>
       </c>
-      <c r="D13" s="46">
-        <v>19</v>
-      </c>
-      <c r="E13" s="20">
-        <f>C13*D13</f>
-        <v>47500</v>
-      </c>
-      <c r="F13" s="20">
-        <f>E13*0.002</f>
-        <v>95</v>
-      </c>
-      <c r="G13" s="20">
-        <f>E13*0.00006</f>
-        <v>2.85</v>
-      </c>
-      <c r="H13" s="20">
-        <f>E13*0.00001</f>
-        <v>0.47500000000000003</v>
-      </c>
-      <c r="I13" s="20">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>6.8827499999999997</v>
-      </c>
-      <c r="J13" s="20">
-        <f>E13+F13+I13+G13+H13</f>
-        <v>47605.207749999994</v>
-      </c>
-      <c r="K13" s="57"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1">
+      <c r="D12" s="26">
+        <v>21.2</v>
+      </c>
+      <c r="E12" s="17">
+        <f>C12*D12</f>
+        <v>53000</v>
+      </c>
+      <c r="F12" s="27">
+        <f>E12*0.002</f>
+        <v>106</v>
+      </c>
+      <c r="G12" s="26">
+        <f>E12*0.000068</f>
+        <v>3.6040000000000001</v>
+      </c>
+      <c r="H12" s="26">
+        <f>E12*0.00001</f>
+        <v>0.53</v>
+      </c>
+      <c r="I12" s="26">
+        <f>(F12+G12+H12)*0.07</f>
+        <v>7.7093800000000003</v>
+      </c>
+      <c r="J12" s="26">
+        <f>E12-F12-G12-H12-I12</f>
+        <v>52882.156620000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="1" customFormat="1">
+      <c r="A13" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18">
+        <f>E12-E11</f>
+        <v>-28875</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18">
+        <f>J12-J11</f>
+        <v>-29174.188317500004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="1" customFormat="1" ht="14.25">
       <c r="A14" s="50"/>
-      <c r="B14" s="3">
-        <f>(D13-D12)/D12</f>
-        <v>-0.47945205479452052</v>
-      </c>
-      <c r="C14" s="2">
-        <f>SUM(C12:C13)</f>
-        <v>17500</v>
-      </c>
-      <c r="D14" s="47">
-        <f>E14/C14</f>
-        <v>34</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" ref="E14:J14" si="5">SUM(E12:E13)</f>
-        <v>595000</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="5"/>
-        <v>1190</v>
-      </c>
-      <c r="G14" s="2">
-        <f t="shared" si="5"/>
-        <v>35.700000000000003</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="5"/>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="I14" s="2">
-        <f t="shared" si="5"/>
-        <v>86.215500000000006</v>
-      </c>
-      <c r="J14" s="2">
-        <f t="shared" si="5"/>
-        <v>596317.86549999996</v>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="51">
+        <v>12500</v>
+      </c>
+      <c r="D14" s="52">
+        <v>37.25</v>
+      </c>
+      <c r="E14" s="51">
+        <v>465625</v>
+      </c>
+      <c r="F14" s="51">
+        <v>931.25</v>
+      </c>
+      <c r="G14" s="51">
+        <v>27.937500000000004</v>
+      </c>
+      <c r="H14" s="51">
+        <v>4.65625</v>
+      </c>
+      <c r="I14" s="51">
+        <v>67.469062500000007</v>
+      </c>
+      <c r="J14" s="51">
+        <v>466656.31281250005</v>
       </c>
       <c r="K14" s="57"/>
       <c r="L14" s="58"/>
@@ -17255,1608 +17410,1692 @@
       <c r="N14" s="59"/>
       <c r="O14" s="59"/>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1">
-      <c r="A15" s="50"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="59"/>
-    </row>
-    <row r="16" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A16" s="49">
+    <row r="15" spans="1:15" s="13" customFormat="1" ht="14.25">
+      <c r="A15" s="67">
+        <v>44473</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D15" s="11">
+        <v>18</v>
+      </c>
+      <c r="E15" s="20">
+        <f>C15*D15</f>
+        <v>45000</v>
+      </c>
+      <c r="F15" s="20">
+        <f>E15*0.002</f>
+        <v>90</v>
+      </c>
+      <c r="G15" s="20">
+        <f>E15*0.00006</f>
+        <v>2.7</v>
+      </c>
+      <c r="H15" s="20">
+        <f>E15*0.00001</f>
+        <v>0.45</v>
+      </c>
+      <c r="I15" s="20">
+        <f>(F15+G15+H15)*0.07</f>
+        <v>6.5205000000000011</v>
+      </c>
+      <c r="J15" s="20">
+        <f>E15+F15+I15+G15+H15</f>
+        <v>45099.670499999993</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:15" s="63" customFormat="1" ht="21.75">
+      <c r="A16" s="56"/>
+      <c r="B16" s="76">
+        <f>(D15-D14)/D14</f>
+        <v>-0.51677852348993292</v>
+      </c>
+      <c r="C16" s="10">
+        <f>SUM(C14:C15)</f>
+        <v>15000</v>
+      </c>
+      <c r="D16" s="64">
+        <f>E16/C16</f>
+        <v>34.041666666666664</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" ref="E16:J16" si="4">SUM(E14:E15)</f>
+        <v>510625</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="4"/>
+        <v>1021.25</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="4"/>
+        <v>30.637500000000003</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="4"/>
+        <v>5.1062500000000002</v>
+      </c>
+      <c r="I16" s="10">
+        <f t="shared" si="4"/>
+        <v>73.989562500000005</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="4"/>
+        <v>511755.98331250006</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1">
+      <c r="A17" s="50"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="59"/>
+    </row>
+    <row r="18" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A18" s="49">
         <v>44543</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="16">
+      <c r="B18" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="16">
         <v>2500</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D18" s="41">
         <v>29.5</v>
       </c>
-      <c r="E16" s="18">
-        <f>C16*D16</f>
+      <c r="E18" s="18">
+        <f>C18*D18</f>
         <v>73750</v>
       </c>
-      <c r="F16" s="18">
-        <f>E16*0.002</f>
+      <c r="F18" s="18">
+        <f>E18*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G16" s="18">
-        <f>E16*0.00006</f>
+      <c r="G18" s="18">
+        <f>E18*0.00006</f>
         <v>4.4249999999999998</v>
       </c>
-      <c r="H16" s="18">
-        <f>E16*0.00001</f>
+      <c r="H18" s="18">
+        <f>E18*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I16" s="18">
-        <f>(F16+G16+H16)*0.07</f>
+      <c r="I18" s="18">
+        <f>(F18+G18+H18)*0.07</f>
         <v>10.686375000000002</v>
       </c>
-      <c r="J16" s="18">
-        <f>E16+F16+I16+G16+H16</f>
+      <c r="J18" s="18">
+        <f>E18+F18+I18+G18+H18</f>
         <v>73913.348875000011</v>
       </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1">
-      <c r="A17" s="49">
+      <c r="K18" s="57"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+    </row>
+    <row r="19" spans="1:15" s="1" customFormat="1">
+      <c r="A19" s="49">
         <v>44923</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B19" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="16">
-        <f>C16</f>
+      <c r="C19" s="16">
+        <f>C18</f>
         <v>2500</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D19" s="26">
         <v>20.3</v>
       </c>
-      <c r="E17" s="17">
-        <f>C17*D17</f>
+      <c r="E19" s="17">
+        <f>C19*D19</f>
         <v>50750</v>
       </c>
-      <c r="F17" s="27">
-        <f>E17*0.002</f>
+      <c r="F19" s="27">
+        <f>E19*0.002</f>
         <v>101.5</v>
       </c>
-      <c r="G17" s="26">
-        <f>E17*0.000068</f>
+      <c r="G19" s="26">
+        <f>E19*0.000068</f>
         <v>3.4510000000000001</v>
       </c>
-      <c r="H17" s="26">
-        <f>E17*0.00001</f>
+      <c r="H19" s="26">
+        <f>E19*0.00001</f>
         <v>0.50750000000000006</v>
       </c>
-      <c r="I17" s="26">
-        <f>(F17+G17+H17)*0.07</f>
+      <c r="I19" s="26">
+        <f>(F19+G19+H19)*0.07</f>
         <v>7.3820949999999996</v>
       </c>
-      <c r="J17" s="26">
-        <f>E17-F17-G17-H17-I17</f>
+      <c r="J19" s="26">
+        <f>E19-F19-G19-H19-I19</f>
         <v>50637.159404999999</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1">
-      <c r="A18" s="49" t="s">
+    <row r="20" spans="1:15" s="1" customFormat="1">
+      <c r="A20" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18">
-        <f>E17-E16</f>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18">
+        <f>E19-E18</f>
         <v>-23000</v>
       </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18">
-        <f>J17-J16</f>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18">
+        <f>J19-J18</f>
         <v>-23276.189470000012</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" ht="14.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
-    </row>
-    <row r="20" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A20" s="49">
+    <row r="21" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A21" s="54"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="59"/>
+    </row>
+    <row r="22" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A22" s="49">
         <v>44550</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="16">
+      <c r="B22" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16">
         <v>2500</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D22" s="41">
         <v>29.5</v>
       </c>
-      <c r="E20" s="18">
-        <f>C20*D20</f>
+      <c r="E22" s="18">
+        <f>C22*D22</f>
         <v>73750</v>
       </c>
-      <c r="F20" s="18">
-        <f>E20*0.002</f>
+      <c r="F22" s="18">
+        <f>E22*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G20" s="18">
-        <f>E20*0.00006</f>
+      <c r="G22" s="18">
+        <f>E22*0.00006</f>
         <v>4.4249999999999998</v>
       </c>
-      <c r="H20" s="18">
-        <f>E20*0.00001</f>
+      <c r="H22" s="18">
+        <f>E22*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I20" s="18">
-        <f>(F20+G20+H20)*0.07</f>
+      <c r="I22" s="18">
+        <f>(F22+G22+H22)*0.07</f>
         <v>10.686375000000002</v>
       </c>
-      <c r="J20" s="18">
-        <f>E20+F20+I20+G20+H20</f>
+      <c r="J22" s="18">
+        <f>E22+F22+I22+G22+H22</f>
         <v>73913.348875000011</v>
       </c>
-      <c r="K20" s="57"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-    </row>
-    <row r="21" spans="1:15" s="1" customFormat="1">
-      <c r="A21" s="49">
+      <c r="K22" s="57"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+    </row>
+    <row r="23" spans="1:15" s="1" customFormat="1">
+      <c r="A23" s="49">
         <v>44922</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B23" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="16">
-        <f>C20</f>
+      <c r="C23" s="16">
+        <f>C22</f>
         <v>2500</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D23" s="26">
         <v>19.7</v>
       </c>
-      <c r="E21" s="17">
-        <f>C21*D21</f>
+      <c r="E23" s="17">
+        <f>C23*D23</f>
         <v>49250</v>
       </c>
-      <c r="F21" s="27">
-        <f>E21*0.002</f>
+      <c r="F23" s="27">
+        <f>E23*0.002</f>
         <v>98.5</v>
       </c>
-      <c r="G21" s="26">
-        <f>E21*0.000068</f>
+      <c r="G23" s="26">
+        <f>E23*0.000068</f>
         <v>3.3489999999999998</v>
       </c>
-      <c r="H21" s="26">
-        <f>E21*0.00001</f>
+      <c r="H23" s="26">
+        <f>E23*0.00001</f>
         <v>0.49250000000000005</v>
       </c>
-      <c r="I21" s="26">
-        <f>(F21+G21+H21)*0.07</f>
+      <c r="I23" s="26">
+        <f>(F23+G23+H23)*0.07</f>
         <v>7.1639050000000015</v>
       </c>
-      <c r="J21" s="26">
-        <f>E21-F21-G21-H21-I21</f>
+      <c r="J23" s="26">
+        <f>E23-F23-G23-H23-I23</f>
         <v>49140.494594999996</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1">
-      <c r="A22" s="49" t="s">
+    <row r="24" spans="1:15" s="1" customFormat="1">
+      <c r="A24" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18">
-        <f>E21-E20</f>
+      <c r="B24" s="15"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18">
+        <f>E23-E22</f>
         <v>-24500</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18">
-        <f>J21-J20</f>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18">
+        <f>J23-J22</f>
         <v>-24772.854280000014</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-    </row>
-    <row r="24" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A24" s="49">
+    <row r="25" spans="1:15" s="1" customFormat="1">
+      <c r="A25" s="50"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+    </row>
+    <row r="26" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A26" s="49">
         <v>44624</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16">
+      <c r="B26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16">
         <v>2500</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D26" s="41">
         <v>25.75</v>
       </c>
-      <c r="E24" s="18">
-        <f>C24*D24</f>
+      <c r="E26" s="18">
+        <f>C26*D26</f>
         <v>64375</v>
       </c>
-      <c r="F24" s="18">
-        <f>E24*0.002</f>
+      <c r="F26" s="18">
+        <f>E26*0.002</f>
         <v>128.75</v>
       </c>
-      <c r="G24" s="18">
-        <f>E24*0.00006</f>
+      <c r="G26" s="18">
+        <f>E26*0.00006</f>
         <v>3.8625000000000003</v>
       </c>
-      <c r="H24" s="18">
-        <f>E24*0.00001</f>
+      <c r="H26" s="18">
+        <f>E26*0.00001</f>
         <v>0.64375000000000004</v>
       </c>
-      <c r="I24" s="18">
-        <f>(F24+G24+H24)*0.07</f>
+      <c r="I26" s="18">
+        <f>(F26+G26+H26)*0.07</f>
         <v>9.3279375000000027</v>
       </c>
-      <c r="J24" s="18">
-        <f>E24+F24+I24+G24+H24</f>
+      <c r="J26" s="18">
+        <f>E26+F26+I26+G26+H26</f>
         <v>64517.584187500004</v>
       </c>
-      <c r="K24" s="57"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-    </row>
-    <row r="25" spans="1:15" s="1" customFormat="1">
-      <c r="A25" s="49">
+      <c r="K26" s="57"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1">
+      <c r="A27" s="49">
         <v>44866</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B27" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="16">
-        <f>C24</f>
+      <c r="C27" s="16">
+        <f>C26</f>
         <v>2500</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D27" s="26">
         <v>19.2</v>
       </c>
-      <c r="E25" s="17">
-        <f>C25*D25</f>
+      <c r="E27" s="17">
+        <f>C27*D27</f>
         <v>48000</v>
       </c>
-      <c r="F25" s="27">
-        <f>E25*0.002</f>
+      <c r="F27" s="27">
+        <f>E27*0.002</f>
         <v>96</v>
       </c>
-      <c r="G25" s="26">
-        <f>E25*0.000068</f>
+      <c r="G27" s="26">
+        <f>E27*0.000068</f>
         <v>3.2639999999999998</v>
       </c>
-      <c r="H25" s="26">
-        <f>E25*0.00001</f>
+      <c r="H27" s="26">
+        <f>E27*0.00001</f>
         <v>0.48000000000000004</v>
       </c>
-      <c r="I25" s="26">
-        <f>(F25+G25+H25)*0.07</f>
+      <c r="I27" s="26">
+        <f>(F27+G27+H27)*0.07</f>
         <v>6.9820800000000007</v>
       </c>
-      <c r="J25" s="26">
-        <f>E25-F25-G25-H25-I25</f>
+      <c r="J27" s="26">
+        <f>E27-F27-G27-H27-I27</f>
         <v>47893.273919999992</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1">
-      <c r="A26" s="49" t="s">
+    <row r="28" spans="1:15" s="1" customFormat="1">
+      <c r="A28" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18">
-        <f>E25-E24</f>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18">
+        <f>E27-E26</f>
         <v>-16375</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18">
-        <f>J25-J24</f>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18">
+        <f>J27-J26</f>
         <v>-16624.310267500012</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1">
-      <c r="A27" s="56"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1">
-      <c r="A28" s="56">
+    <row r="29" spans="1:15" s="1" customFormat="1">
+      <c r="A29" s="56"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1">
+      <c r="A30" s="56">
         <v>44627</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10">
+      <c r="B30" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="10">
         <v>2500</v>
       </c>
-      <c r="D28" s="46">
+      <c r="D30" s="46">
         <v>25.75</v>
       </c>
-      <c r="E28" s="20">
-        <f>C28*D28</f>
+      <c r="E30" s="20">
+        <f>C30*D30</f>
         <v>64375</v>
       </c>
-      <c r="F28" s="20">
-        <f>E28*0.002</f>
+      <c r="F30" s="20">
+        <f>E30*0.002</f>
         <v>128.75</v>
       </c>
-      <c r="G28" s="20">
-        <f>E28*0.00006</f>
+      <c r="G30" s="20">
+        <f>E30*0.00006</f>
         <v>3.8625000000000003</v>
       </c>
-      <c r="H28" s="20">
-        <f>E28*0.00001</f>
+      <c r="H30" s="20">
+        <f>E30*0.00001</f>
         <v>0.64375000000000004</v>
       </c>
-      <c r="I28" s="20">
-        <f>(F28+G28+H28)*0.07</f>
+      <c r="I30" s="20">
+        <f>(F30+G30+H30)*0.07</f>
         <v>9.3279375000000027</v>
       </c>
-      <c r="J28" s="20">
-        <f>E28+F28+I28+G28+H28</f>
+      <c r="J30" s="20">
+        <f>E30+F30+I30+G30+H30</f>
         <v>64517.584187500004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1">
-      <c r="A29" s="56">
-        <v>44634</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="10">
-        <f>C28</f>
-        <v>2500</v>
-      </c>
-      <c r="D29" s="34">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="E29" s="11">
-        <f>C29*D29</f>
-        <v>50250</v>
-      </c>
-      <c r="F29" s="35">
-        <f>E29*0.002</f>
-        <v>100.5</v>
-      </c>
-      <c r="G29" s="34">
-        <f>E29*0.000068</f>
-        <v>3.4169999999999998</v>
-      </c>
-      <c r="H29" s="34">
-        <f>E29*0.00001</f>
-        <v>0.50250000000000006</v>
-      </c>
-      <c r="I29" s="34">
-        <f>(F29+G29+H29)*0.07</f>
-        <v>7.3093650000000006</v>
-      </c>
-      <c r="J29" s="34">
-        <f>E29-F29-G29-H29-I29</f>
-        <v>50138.271134999995</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1">
-      <c r="A30" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="20">
-        <f>E29-E28</f>
-        <v>-14125</v>
-      </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20">
-        <f>J29-J28</f>
-        <v>-14379.313052500009</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="1" customFormat="1">
       <c r="A31" s="56">
+        <v>44634</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="10">
+        <f>C30</f>
+        <v>2500</v>
+      </c>
+      <c r="D31" s="34">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E31" s="11">
+        <f>C31*D31</f>
+        <v>50250</v>
+      </c>
+      <c r="F31" s="35">
+        <f>E31*0.002</f>
+        <v>100.5</v>
+      </c>
+      <c r="G31" s="34">
+        <f>E31*0.000068</f>
+        <v>3.4169999999999998</v>
+      </c>
+      <c r="H31" s="34">
+        <f>E31*0.00001</f>
+        <v>0.50250000000000006</v>
+      </c>
+      <c r="I31" s="34">
+        <f>(F31+G31+H31)*0.07</f>
+        <v>7.3093650000000006</v>
+      </c>
+      <c r="J31" s="34">
+        <f>E31-F31-G31-H31-I31</f>
+        <v>50138.271134999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1">
+      <c r="A32" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="20">
+        <f>E31-E30</f>
+        <v>-14125</v>
+      </c>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20">
+        <f>J31-J30</f>
+        <v>-14379.313052500009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="1" customFormat="1">
+      <c r="A33" s="56">
         <v>44627</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="10">
+      <c r="B33" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="10">
         <v>2500</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D33" s="46">
         <v>19</v>
       </c>
-      <c r="E31" s="20">
-        <f>C31*D31</f>
+      <c r="E33" s="20">
+        <f>C33*D33</f>
         <v>47500</v>
       </c>
-      <c r="F31" s="20">
-        <f>E31*0.002</f>
+      <c r="F33" s="20">
+        <f>E33*0.002</f>
         <v>95</v>
       </c>
-      <c r="G31" s="20">
-        <f>E31*0.00006</f>
+      <c r="G33" s="20">
+        <f>E33*0.00006</f>
         <v>2.85</v>
       </c>
-      <c r="H31" s="20">
-        <f>E31*0.00001</f>
+      <c r="H33" s="20">
+        <f>E33*0.00001</f>
         <v>0.47500000000000003</v>
       </c>
-      <c r="I31" s="20">
-        <f>(F31+G31+H31)*0.07</f>
+      <c r="I33" s="20">
+        <f>(F33+G33+H33)*0.07</f>
         <v>6.8827499999999997</v>
       </c>
-      <c r="J31" s="20">
-        <f>E31+F31+I31+G31+H31</f>
+      <c r="J33" s="20">
+        <f>E33+F33+I33+G33+H33</f>
         <v>47605.207749999994</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="1" customFormat="1">
-      <c r="A32" s="56">
+    <row r="34" spans="1:15" s="1" customFormat="1">
+      <c r="A34" s="56">
         <v>44634</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="10">
-        <f>C31</f>
+      <c r="C34" s="10">
+        <f>C33</f>
         <v>2500</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D34" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="E32" s="11">
-        <f>C32*D32</f>
+      <c r="E34" s="11">
+        <f>C34*D34</f>
         <v>50250</v>
       </c>
-      <c r="F32" s="35">
-        <f>E32*0.002</f>
+      <c r="F34" s="35">
+        <f>E34*0.002</f>
         <v>100.5</v>
       </c>
-      <c r="G32" s="34">
-        <f>E32*0.000068</f>
+      <c r="G34" s="34">
+        <f>E34*0.000068</f>
         <v>3.4169999999999998</v>
       </c>
-      <c r="H32" s="34">
-        <f>E32*0.00001</f>
+      <c r="H34" s="34">
+        <f>E34*0.00001</f>
         <v>0.50250000000000006</v>
       </c>
-      <c r="I32" s="34">
-        <f>(F32+G32+H32)*0.07</f>
+      <c r="I34" s="34">
+        <f>(F34+G34+H34)*0.07</f>
         <v>7.3093650000000006</v>
       </c>
-      <c r="J32" s="34">
-        <f>E32-F32-G32-H32-I32</f>
+      <c r="J34" s="34">
+        <f>E34-F34-G34-H34-I34</f>
         <v>50138.271134999995</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="1" customFormat="1">
-      <c r="A33" s="56" t="s">
+    <row r="35" spans="1:15" s="1" customFormat="1">
+      <c r="A35" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="12">
-        <f>(D32-D31)/D31</f>
+      <c r="B35" s="12">
+        <f>(D34-D33)/D33</f>
         <v>5.7894736842105339E-2</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="20">
-        <f>E32-E31</f>
+      <c r="C35" s="10"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="20">
+        <f>E34-E33</f>
         <v>2750</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20">
-        <f>J32-J31</f>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20">
+        <f>J34-J33</f>
         <v>2533.0633850000013</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" ht="12">
-      <c r="A34" s="50"/>
-      <c r="D34" s="47"/>
-      <c r="J34" s="53"/>
-    </row>
-    <row r="35" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A35" s="56">
+    <row r="36" spans="1:15" s="1" customFormat="1" ht="12">
+      <c r="A36" s="50"/>
+      <c r="D36" s="47"/>
+      <c r="J36" s="53"/>
+    </row>
+    <row r="37" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A37" s="56">
         <v>44624</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="16">
+      <c r="B37" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="16">
         <v>2500</v>
       </c>
-      <c r="D35" s="46">
+      <c r="D37" s="46">
         <v>25.75</v>
       </c>
-      <c r="E35" s="20">
-        <f>C35*D35</f>
+      <c r="E37" s="20">
+        <f>C37*D37</f>
         <v>64375</v>
       </c>
-      <c r="F35" s="20">
-        <f>E35*0.002</f>
+      <c r="F37" s="20">
+        <f>E37*0.002</f>
         <v>128.75</v>
       </c>
-      <c r="G35" s="20">
-        <f>E35*0.00006</f>
+      <c r="G37" s="20">
+        <f>E37*0.00006</f>
         <v>3.8625000000000003</v>
       </c>
-      <c r="H35" s="20">
-        <f>E35*0.00001</f>
+      <c r="H37" s="20">
+        <f>E37*0.00001</f>
         <v>0.64375000000000004</v>
       </c>
-      <c r="I35" s="20">
-        <f>(F35+G35+H35)*0.07</f>
+      <c r="I37" s="20">
+        <f>(F37+G37+H37)*0.07</f>
         <v>9.3279375000000027</v>
       </c>
-      <c r="J35" s="20">
-        <f>E35+F35+I35+G35+H35</f>
+      <c r="J37" s="20">
+        <f>E37+F37+I37+G37+H37</f>
         <v>64517.584187500004</v>
       </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
-      <c r="O35" s="58"/>
-    </row>
-    <row r="36" spans="1:15" s="13" customFormat="1">
-      <c r="A36" s="56" t="e">
+      <c r="K37" s="57"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+    </row>
+    <row r="38" spans="1:15" s="13" customFormat="1">
+      <c r="A38" s="56" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="10">
-        <f>C35</f>
+      <c r="C38" s="10">
+        <f>C37</f>
         <v>2500</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D38" s="26">
         <v>29.5</v>
       </c>
-      <c r="E36" s="11">
-        <f>C36*D36</f>
-        <v>73750</v>
-      </c>
-      <c r="F36" s="35">
-        <f>E36*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G36" s="34">
-        <f>E36*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H36" s="34">
-        <f>E36*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I36" s="34">
-        <f>(F36+G36+H36)*0.07</f>
-        <v>10.727675000000001</v>
-      </c>
-      <c r="J36" s="34">
-        <f>E36-F36-G36-H36-I36</f>
-        <v>73586.019824999996</v>
-      </c>
-      <c r="K36" s="10">
-        <f>C36</f>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A37" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="25">
-        <f>(D36-D35)/D35</f>
-        <v>0.14563106796116504</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="20">
-        <f>E36-E35</f>
-        <v>9375</v>
-      </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20">
-        <f>J36-J35</f>
-        <v>9068.4356374999916</v>
-      </c>
-      <c r="K37" s="20">
-        <f>J37</f>
-        <v>9068.4356374999916</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A38" s="49">
-        <v>44550</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D38" s="46">
-        <v>29.5</v>
-      </c>
-      <c r="E38" s="20">
+      <c r="E38" s="11">
         <f>C38*D38</f>
         <v>73750</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="35">
         <f>E38*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G38" s="20">
-        <f>E38*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H38" s="20">
+      <c r="G38" s="34">
+        <f>E38*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H38" s="34">
         <f>E38*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="34">
         <f>(F38+G38+H38)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J38" s="20">
-        <f>E38+F38+I38+G38+H38</f>
-        <v>73913.348875000011</v>
-      </c>
-      <c r="K38" s="57"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="58"/>
-      <c r="O38" s="58"/>
-    </row>
-    <row r="39" spans="1:15" s="13" customFormat="1">
-      <c r="A39" s="56" t="e">
-        <f>A36</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="10">
+        <v>10.727675000000001</v>
+      </c>
+      <c r="J38" s="34">
+        <f>E38-F38-G38-H38-I38</f>
+        <v>73586.019824999996</v>
+      </c>
+      <c r="K38" s="10">
         <f>C38</f>
         <v>2500</v>
       </c>
-      <c r="D39" s="34">
-        <f>D36</f>
+    </row>
+    <row r="39" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A39" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="25">
+        <f>(D38-D37)/D37</f>
+        <v>0.14563106796116504</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="20">
+        <f>E38-E37</f>
+        <v>9375</v>
+      </c>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20">
+        <f>J38-J37</f>
+        <v>9068.4356374999916</v>
+      </c>
+      <c r="K39" s="20">
+        <f>J39</f>
+        <v>9068.4356374999916</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A40" s="49">
+        <v>44550</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D40" s="46">
         <v>29.5</v>
       </c>
-      <c r="E39" s="11">
-        <f>C39*D39</f>
+      <c r="E40" s="20">
+        <f>C40*D40</f>
         <v>73750</v>
       </c>
-      <c r="F39" s="35">
-        <f>E39*0.002</f>
+      <c r="F40" s="20">
+        <f>E40*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G39" s="34">
-        <f>E39*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H39" s="34">
-        <f>E39*0.00001</f>
+      <c r="G40" s="20">
+        <f>E40*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H40" s="20">
+        <f>E40*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I39" s="34">
-        <f>(F39+G39+H39)*0.07</f>
-        <v>10.727675000000001</v>
-      </c>
-      <c r="J39" s="34">
-        <f>E39-F39-G39-H39-I39</f>
-        <v>73586.019824999996</v>
-      </c>
-      <c r="K39" s="10">
-        <f>K36+C39</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A40" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="25">
-        <f>(D39-D38)/D38</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="20">
-        <f>E39-E38</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
+      <c r="I40" s="20">
+        <f>(F40+G40+H40)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
       <c r="J40" s="20">
-        <f>J39-J38</f>
-        <v>-327.32905000001483</v>
-      </c>
-      <c r="K40" s="20">
-        <f>K37+J40</f>
-        <v>8741.1065874999767</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A41" s="56">
-        <v>44543</v>
+        <f>E40+F40+I40+G40+H40</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K40" s="57"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+    </row>
+    <row r="41" spans="1:15" s="13" customFormat="1">
+      <c r="A41" s="56" t="e">
+        <f>A38</f>
+        <v>#REF!</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="16">
+        <v>3</v>
+      </c>
+      <c r="C41" s="10">
+        <f>C40</f>
         <v>2500</v>
       </c>
-      <c r="D41" s="46">
+      <c r="D41" s="34">
+        <f>D38</f>
         <v>29.5</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="11">
         <f>C41*D41</f>
         <v>73750</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="35">
         <f>E41*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G41" s="20">
-        <f>E41*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H41" s="20">
+      <c r="G41" s="34">
+        <f>E41*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H41" s="34">
         <f>E41*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="34">
         <f>(F41+G41+H41)*0.07</f>
+        <v>10.727675000000001</v>
+      </c>
+      <c r="J41" s="34">
+        <f>E41-F41-G41-H41-I41</f>
+        <v>73586.019824999996</v>
+      </c>
+      <c r="K41" s="10">
+        <f>K38+C41</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A42" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="25">
+        <f>(D41-D40)/D40</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="20">
+        <f>E41-E40</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20">
+        <f>J41-J40</f>
+        <v>-327.32905000001483</v>
+      </c>
+      <c r="K42" s="20">
+        <f>K39+J42</f>
+        <v>8741.1065874999767</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A43" s="56">
+        <v>44543</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D43" s="46">
+        <v>29.5</v>
+      </c>
+      <c r="E43" s="20">
+        <f>C43*D43</f>
+        <v>73750</v>
+      </c>
+      <c r="F43" s="20">
+        <f>E43*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G43" s="20">
+        <f>E43*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H43" s="20">
+        <f>E43*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I43" s="20">
+        <f>(F43+G43+H43)*0.07</f>
         <v>10.686375000000002</v>
       </c>
-      <c r="J41" s="20">
-        <f>E41+F41+I41+G41+H41</f>
+      <c r="J43" s="20">
+        <f>E43+F43+I43+G43+H43</f>
         <v>73913.348875000011</v>
       </c>
-      <c r="K41" s="57"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-    </row>
-    <row r="42" spans="1:15" s="13" customFormat="1">
-      <c r="A42" s="56" t="e">
-        <f>A39</f>
+      <c r="K43" s="57"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+    </row>
+    <row r="44" spans="1:15" s="13" customFormat="1">
+      <c r="A44" s="56" t="e">
+        <f>A41</f>
         <v>#REF!</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B44" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="10">
-        <f>C41</f>
+      <c r="C44" s="10">
+        <f>C43</f>
         <v>2500</v>
       </c>
-      <c r="D42" s="34">
-        <f>D39</f>
+      <c r="D44" s="34">
+        <f>D41</f>
         <v>29.5</v>
       </c>
-      <c r="E42" s="11">
-        <f>C42*D42</f>
+      <c r="E44" s="11">
+        <f>C44*D44</f>
         <v>73750</v>
       </c>
-      <c r="F42" s="35">
-        <f>E42*0.002</f>
+      <c r="F44" s="35">
+        <f>E44*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G42" s="34">
-        <f>E42*0.000068</f>
+      <c r="G44" s="34">
+        <f>E44*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H42" s="34">
-        <f>E42*0.00001</f>
+      <c r="H44" s="34">
+        <f>E44*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I42" s="34">
-        <f>(F42+G42+H42)*0.07</f>
+      <c r="I44" s="34">
+        <f>(F44+G44+H44)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J42" s="34">
-        <f>E42-F42-G42-H42-I42</f>
+      <c r="J44" s="34">
+        <f>E44-F44-G44-H44-I44</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K42" s="10">
-        <f>K39+C42</f>
+      <c r="K44" s="10">
+        <f>K41+C44</f>
         <v>7500</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A43" s="56" t="s">
+    <row r="45" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A45" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="25">
-        <f>(D42-D41)/D41</f>
+      <c r="B45" s="25">
+        <f>(D44-D43)/D43</f>
         <v>0</v>
       </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="20">
-        <f>E42-E41</f>
+      <c r="C45" s="10"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="20">
+        <f>E44-E43</f>
         <v>0</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20">
-        <f>J42-J41</f>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20">
+        <f>J44-J43</f>
         <v>-327.32905000001483</v>
       </c>
-      <c r="K43" s="20">
-        <f>K40+J43</f>
+      <c r="K45" s="20">
+        <f>K42+J45</f>
         <v>8413.7775374999619</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A44" s="56">
+    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A46" s="56">
         <v>44496</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="16">
+      <c r="B46" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="16">
         <v>2500</v>
       </c>
-      <c r="D44" s="46">
+      <c r="D46" s="46">
         <v>32.75</v>
       </c>
-      <c r="E44" s="20">
-        <f>C44*D44</f>
+      <c r="E46" s="20">
+        <f>C46*D46</f>
         <v>81875</v>
       </c>
-      <c r="F44" s="20">
-        <f>E44*0.002</f>
+      <c r="F46" s="20">
+        <f>E46*0.002</f>
         <v>163.75</v>
       </c>
-      <c r="G44" s="20">
-        <f>E44*0.00006</f>
+      <c r="G46" s="20">
+        <f>E46*0.00006</f>
         <v>4.9125000000000005</v>
       </c>
-      <c r="H44" s="20">
-        <f>E44*0.00001</f>
+      <c r="H46" s="20">
+        <f>E46*0.00001</f>
         <v>0.81875000000000009</v>
       </c>
-      <c r="I44" s="20">
-        <f>(F44+G44+H44)*0.07</f>
+      <c r="I46" s="20">
+        <f>(F46+G46+H46)*0.07</f>
         <v>11.863687500000001</v>
       </c>
-      <c r="J44" s="20">
-        <f>E44+F44+I44+G44+H44</f>
+      <c r="J46" s="20">
+        <f>E46+F46+I46+G46+H46</f>
         <v>82056.344937500005</v>
       </c>
-      <c r="K44" s="57"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="58"/>
-    </row>
-    <row r="45" spans="1:15" s="13" customFormat="1">
-      <c r="A45" s="56" t="e">
-        <f>A42</f>
+      <c r="K46" s="57"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+    </row>
+    <row r="47" spans="1:15" s="13" customFormat="1">
+      <c r="A47" s="56" t="e">
+        <f>A44</f>
         <v>#REF!</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B47" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="10">
-        <f>C44</f>
+      <c r="C47" s="10">
+        <f>C46</f>
         <v>2500</v>
       </c>
-      <c r="D45" s="34">
-        <f>D39</f>
+      <c r="D47" s="34">
+        <f>D41</f>
         <v>29.5</v>
       </c>
-      <c r="E45" s="11">
-        <f>C45*D45</f>
+      <c r="E47" s="11">
+        <f>C47*D47</f>
         <v>73750</v>
       </c>
-      <c r="F45" s="35">
-        <f>E45*0.002</f>
+      <c r="F47" s="35">
+        <f>E47*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G45" s="34">
-        <f>E45*0.000068</f>
+      <c r="G47" s="34">
+        <f>E47*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H45" s="34">
-        <f>E45*0.00001</f>
+      <c r="H47" s="34">
+        <f>E47*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I45" s="34">
-        <f>(F45+G45+H45)*0.07</f>
+      <c r="I47" s="34">
+        <f>(F47+G47+H47)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J45" s="34">
-        <f>E45-F45-G45-H45-I45</f>
+      <c r="J47" s="34">
+        <f>E47-F47-G47-H47-I47</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K45" s="10">
-        <f>K42+C45</f>
+      <c r="K47" s="10">
+        <f>K44+C47</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A46" s="56" t="s">
+    <row r="48" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A48" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="25">
-        <f>(D45-D44)/D44</f>
+      <c r="B48" s="25">
+        <f>(D47-D46)/D46</f>
         <v>-9.9236641221374045E-2</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="20">
-        <f>E45-E44</f>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="20">
+        <f>E47-E46</f>
         <v>-8125</v>
       </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20">
-        <f>J45-J44</f>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20">
+        <f>J47-J46</f>
         <v>-8470.3251125000097</v>
       </c>
-      <c r="K46" s="20">
-        <f>K43+J46</f>
+      <c r="K48" s="20">
+        <f>K45+J48</f>
         <v>-56.5475750000478</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A47" s="56">
+    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A49" s="56">
         <v>44462</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="16">
+      <c r="B49" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="16">
         <v>2500</v>
       </c>
-      <c r="D47" s="46">
+      <c r="D49" s="46">
         <v>33.25</v>
       </c>
-      <c r="E47" s="20">
-        <f>C47*D47</f>
+      <c r="E49" s="20">
+        <f>C49*D49</f>
         <v>83125</v>
       </c>
-      <c r="F47" s="20">
-        <f>E47*0.002</f>
+      <c r="F49" s="20">
+        <f>E49*0.002</f>
         <v>166.25</v>
       </c>
-      <c r="G47" s="20">
-        <f>E47*0.00006</f>
+      <c r="G49" s="20">
+        <f>E49*0.00006</f>
         <v>4.9874999999999998</v>
       </c>
-      <c r="H47" s="20">
-        <f>E47*0.00001</f>
+      <c r="H49" s="20">
+        <f>E49*0.00001</f>
         <v>0.83125000000000004</v>
       </c>
-      <c r="I47" s="20">
-        <f>(F47+G47+H47)*0.07</f>
+      <c r="I49" s="20">
+        <f>(F49+G49+H49)*0.07</f>
         <v>12.044812500000003</v>
       </c>
-      <c r="J47" s="20">
-        <f>E47+F47+I47+G47+H47</f>
+      <c r="J49" s="20">
+        <f>E49+F49+I49+G49+H49</f>
         <v>83309.113562500002</v>
       </c>
-      <c r="K47" s="57"/>
-      <c r="L47" s="58"/>
-      <c r="M47" s="58"/>
-      <c r="N47" s="58"/>
-      <c r="O47" s="58"/>
-    </row>
-    <row r="48" spans="1:15" s="13" customFormat="1">
-      <c r="A48" s="56" t="e">
-        <f>A45</f>
+      <c r="K49" s="57"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+    </row>
+    <row r="50" spans="1:15" s="13" customFormat="1">
+      <c r="A50" s="56" t="e">
+        <f>A47</f>
         <v>#REF!</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B50" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="10">
-        <f>C47</f>
+      <c r="C50" s="10">
+        <f>C49</f>
         <v>2500</v>
       </c>
-      <c r="D48" s="34">
-        <f>D39</f>
+      <c r="D50" s="34">
+        <f>D41</f>
         <v>29.5</v>
       </c>
-      <c r="E48" s="11">
-        <f>C48*D48</f>
+      <c r="E50" s="11">
+        <f>C50*D50</f>
         <v>73750</v>
       </c>
-      <c r="F48" s="35">
-        <f>E48*0.002</f>
+      <c r="F50" s="35">
+        <f>E50*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G48" s="34">
-        <f>E48*0.000068</f>
+      <c r="G50" s="34">
+        <f>E50*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H48" s="34">
-        <f>E48*0.00001</f>
+      <c r="H50" s="34">
+        <f>E50*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I48" s="34">
-        <f>(F48+G48+H48)*0.07</f>
+      <c r="I50" s="34">
+        <f>(F50+G50+H50)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J48" s="34">
-        <f>E48-F48-G48-H48-I48</f>
+      <c r="J50" s="34">
+        <f>E50-F50-G50-H50-I50</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K48" s="10">
-        <f>K45+C48</f>
+      <c r="K50" s="10">
+        <f>K47+C50</f>
         <v>12500</v>
       </c>
     </row>
-    <row r="49" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A49" s="56" t="s">
+    <row r="51" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A51" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="25">
-        <f>(D48-D47)/D47</f>
+      <c r="B51" s="25">
+        <f>(D50-D49)/D49</f>
         <v>-0.11278195488721804</v>
       </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="20">
-        <f>E48-E47</f>
+      <c r="C51" s="10"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="20">
+        <f>E50-E49</f>
         <v>-9375</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20">
-        <f>J48-J47</f>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20">
+        <f>J50-J49</f>
         <v>-9723.0937375000067</v>
       </c>
-      <c r="K49" s="20">
-        <f>K46+J49</f>
+      <c r="K51" s="20">
+        <f>K48+J51</f>
         <v>-9779.6413125000545</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A50" s="56">
+    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A52" s="56">
         <v>44452</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="16">
+      <c r="B52" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="16">
         <v>2500</v>
       </c>
-      <c r="D50" s="46">
+      <c r="D52" s="46">
         <v>35.25</v>
       </c>
-      <c r="E50" s="20">
-        <f>C50*D50</f>
+      <c r="E52" s="20">
+        <f>C52*D52</f>
         <v>88125</v>
       </c>
-      <c r="F50" s="20">
-        <f>E50*0.002</f>
+      <c r="F52" s="20">
+        <f>E52*0.002</f>
         <v>176.25</v>
       </c>
-      <c r="G50" s="20">
-        <f>E50*0.00006</f>
+      <c r="G52" s="20">
+        <f>E52*0.00006</f>
         <v>5.2875000000000005</v>
       </c>
-      <c r="H50" s="20">
-        <f>E50*0.00001</f>
+      <c r="H52" s="20">
+        <f>E52*0.00001</f>
         <v>0.88125000000000009</v>
       </c>
-      <c r="I50" s="20">
-        <f>(F50+G50+H50)*0.07</f>
+      <c r="I52" s="20">
+        <f>(F52+G52+H52)*0.07</f>
         <v>12.7693125</v>
       </c>
-      <c r="J50" s="20">
-        <f>E50+F50+I50+G50+H50</f>
+      <c r="J52" s="20">
+        <f>E52+F52+I52+G52+H52</f>
         <v>88320.188062500005</v>
       </c>
-      <c r="K50" s="57"/>
-      <c r="L50" s="58"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="58"/>
-      <c r="O50" s="58"/>
-    </row>
-    <row r="51" spans="1:15" s="13" customFormat="1">
-      <c r="A51" s="56" t="e">
-        <f>A48</f>
+      <c r="K52" s="57"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+    </row>
+    <row r="53" spans="1:15" s="13" customFormat="1">
+      <c r="A53" s="56" t="e">
+        <f>A50</f>
         <v>#REF!</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B53" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="10">
-        <f>C50</f>
+      <c r="C53" s="10">
+        <f>C52</f>
         <v>2500</v>
       </c>
-      <c r="D51" s="34">
-        <f>D39</f>
+      <c r="D53" s="34">
+        <f>D41</f>
         <v>29.5</v>
       </c>
-      <c r="E51" s="11">
-        <f>C51*D51</f>
+      <c r="E53" s="11">
+        <f>C53*D53</f>
         <v>73750</v>
       </c>
-      <c r="F51" s="35">
-        <f>E51*0.002</f>
+      <c r="F53" s="35">
+        <f>E53*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G51" s="34">
-        <f>E51*0.000068</f>
+      <c r="G53" s="34">
+        <f>E53*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H51" s="34">
-        <f>E51*0.00001</f>
+      <c r="H53" s="34">
+        <f>E53*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I51" s="34">
-        <f>(F51+G51+H51)*0.07</f>
+      <c r="I53" s="34">
+        <f>(F53+G53+H53)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J51" s="34">
-        <f>E51-F51-G51-H51-I51</f>
+      <c r="J53" s="34">
+        <f>E53-F53-G53-H53-I53</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K51" s="91">
-        <f>K48+C51</f>
+      <c r="K53" s="91">
+        <f>K50+C53</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A52" s="56" t="s">
+    <row r="54" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A54" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="25">
-        <f>(D51-D50)/D50</f>
+      <c r="B54" s="25">
+        <f>(D53-D52)/D52</f>
         <v>-0.16312056737588654</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="20">
-        <f>E51-E50</f>
+      <c r="C54" s="10"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="20">
+        <f>E53-E52</f>
         <v>-14375</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20">
-        <f>J51-J50</f>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20">
+        <f>J53-J52</f>
         <v>-14734.168237500009</v>
       </c>
-      <c r="K52" s="20">
-        <f>K49+J52</f>
+      <c r="K54" s="20">
+        <f>K51+J54</f>
         <v>-24513.809550000064</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A53" s="56">
+    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A55" s="56">
         <v>44398</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="16">
+      <c r="B55" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="16">
         <v>2500</v>
       </c>
-      <c r="D53" s="46">
+      <c r="D55" s="46">
         <v>37.75</v>
       </c>
-      <c r="E53" s="20">
-        <f>C53*D53</f>
+      <c r="E55" s="20">
+        <f>C55*D55</f>
         <v>94375</v>
       </c>
-      <c r="F53" s="20">
-        <f>E53*0.002</f>
+      <c r="F55" s="20">
+        <f>E55*0.002</f>
         <v>188.75</v>
       </c>
-      <c r="G53" s="20">
-        <f>E53*0.00006</f>
+      <c r="G55" s="20">
+        <f>E55*0.00006</f>
         <v>5.6625000000000005</v>
       </c>
-      <c r="H53" s="20">
-        <f>E53*0.00001</f>
+      <c r="H55" s="20">
+        <f>E55*0.00001</f>
         <v>0.94375000000000009</v>
       </c>
-      <c r="I53" s="20">
-        <f>(F53+G53+H53)*0.07</f>
+      <c r="I55" s="20">
+        <f>(F55+G55+H55)*0.07</f>
         <v>13.6749375</v>
       </c>
-      <c r="J53" s="20">
-        <f>E53+F53+I53+G53+H53</f>
+      <c r="J55" s="20">
+        <f>E55+F55+I55+G55+H55</f>
         <v>94584.031187500019</v>
       </c>
-      <c r="K53" s="57"/>
-      <c r="L53" s="58"/>
-      <c r="M53" s="58"/>
-      <c r="N53" s="58"/>
-      <c r="O53" s="58"/>
-    </row>
-    <row r="54" spans="1:15" s="13" customFormat="1">
-      <c r="A54" s="56" t="e">
-        <f>A51</f>
+      <c r="K55" s="57"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+    </row>
+    <row r="56" spans="1:15" s="13" customFormat="1">
+      <c r="A56" s="56" t="e">
+        <f>A53</f>
         <v>#REF!</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B56" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="10">
-        <f>C53</f>
+      <c r="C56" s="10">
+        <f>C55</f>
         <v>2500</v>
       </c>
-      <c r="D54" s="34">
-        <f>D39</f>
+      <c r="D56" s="34">
+        <f>D41</f>
         <v>29.5</v>
       </c>
-      <c r="E54" s="11">
-        <f>C54*D54</f>
+      <c r="E56" s="11">
+        <f>C56*D56</f>
         <v>73750</v>
       </c>
-      <c r="F54" s="35">
-        <f>E54*0.002</f>
+      <c r="F56" s="35">
+        <f>E56*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G54" s="34">
-        <f>E54*0.000068</f>
+      <c r="G56" s="34">
+        <f>E56*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H54" s="34">
-        <f>E54*0.00001</f>
+      <c r="H56" s="34">
+        <f>E56*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I54" s="34">
-        <f>(F54+G54+H54)*0.07</f>
+      <c r="I56" s="34">
+        <f>(F56+G56+H56)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J54" s="34">
-        <f>E54-F54-G54-H54-I54</f>
+      <c r="J56" s="34">
+        <f>E56-F56-G56-H56-I56</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K54" s="10">
-        <f>K51+C54</f>
+      <c r="K56" s="10">
+        <f>K53+C56</f>
         <v>17500</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A55" s="56" t="s">
+    <row r="57" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A57" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="25">
-        <f>(D54-D53)/D53</f>
+      <c r="B57" s="25">
+        <f>(D56-D55)/D55</f>
         <v>-0.2185430463576159</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="20">
-        <f>E54-E53</f>
+      <c r="C57" s="10"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="20">
+        <f>E56-E55</f>
         <v>-20625</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20">
-        <f>J54-J53</f>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20">
+        <f>J56-J55</f>
         <v>-20998.011362500023</v>
       </c>
-      <c r="K55" s="20">
-        <f>K52+J55</f>
+      <c r="K57" s="20">
+        <f>K54+J57</f>
         <v>-45511.820912500087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A56" s="56">
+    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A58" s="56">
         <v>44368</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="16">
+      <c r="B58" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="16">
         <v>2500</v>
       </c>
-      <c r="D56" s="46">
+      <c r="D58" s="46">
         <v>40</v>
       </c>
-      <c r="E56" s="20">
-        <f>C56*D56</f>
+      <c r="E58" s="20">
+        <f>C58*D58</f>
         <v>100000</v>
       </c>
-      <c r="F56" s="20">
-        <f>E56*0.002</f>
+      <c r="F58" s="20">
+        <f>E58*0.002</f>
         <v>200</v>
       </c>
-      <c r="G56" s="20">
-        <f>E56*0.00006</f>
+      <c r="G58" s="20">
+        <f>E58*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H56" s="20">
-        <f>E56*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I56" s="20">
-        <f>(F56+G56+H56)*0.07</f>
+      <c r="H58" s="20">
+        <f>E58*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I58" s="20">
+        <f>(F58+G58+H58)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J56" s="20">
-        <f>E56+F56+I56+G56+H56</f>
+      <c r="J58" s="20">
+        <f>E58+F58+I58+G58+H58</f>
         <v>100221.49</v>
       </c>
-      <c r="K56" s="57"/>
-      <c r="L56" s="58"/>
-      <c r="M56" s="58"/>
-      <c r="N56" s="58"/>
-      <c r="O56" s="58"/>
-    </row>
-    <row r="57" spans="1:15" s="13" customFormat="1">
-      <c r="A57" s="56" t="e">
-        <f>A54</f>
+      <c r="K58" s="57"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+    </row>
+    <row r="59" spans="1:15" s="13" customFormat="1">
+      <c r="A59" s="56" t="e">
+        <f>A56</f>
         <v>#REF!</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B59" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="10">
-        <f>C56</f>
+      <c r="C59" s="10">
+        <f>C58</f>
         <v>2500</v>
       </c>
-      <c r="D57" s="34">
-        <f>D42</f>
+      <c r="D59" s="34">
+        <f>D44</f>
         <v>29.5</v>
       </c>
-      <c r="E57" s="11">
-        <f>C57*D57</f>
+      <c r="E59" s="11">
+        <f>C59*D59</f>
         <v>73750</v>
       </c>
-      <c r="F57" s="35">
-        <f>E57*0.002</f>
+      <c r="F59" s="35">
+        <f>E59*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G57" s="34">
-        <f>E57*0.000068</f>
+      <c r="G59" s="34">
+        <f>E59*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H57" s="34">
-        <f>E57*0.00001</f>
+      <c r="H59" s="34">
+        <f>E59*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I57" s="34">
-        <f>(F57+G57+H57)*0.07</f>
+      <c r="I59" s="34">
+        <f>(F59+G59+H59)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J57" s="34">
-        <f>E57-F57-G57-H57-I57</f>
+      <c r="J59" s="34">
+        <f>E59-F59-G59-H59-I59</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K57" s="10">
-        <f>K54+C57</f>
+      <c r="K59" s="10">
+        <f>K56+C59</f>
         <v>20000</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A58" s="56" t="s">
+    <row r="60" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A60" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="25">
-        <f>(D57-D56)/D56</f>
+      <c r="B60" s="25">
+        <f>(D59-D58)/D58</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="20">
-        <f>E57-E56</f>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="20">
+        <f>E59-E58</f>
         <v>-26250</v>
       </c>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20">
-        <f>J57-J56</f>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20">
+        <f>J59-J58</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K58" s="20">
-        <f>K55+J58</f>
+      <c r="K60" s="20">
+        <f>K57+J60</f>
         <v>-72147.291087500096</v>
       </c>
     </row>
-    <row r="59" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A59" s="56">
+    <row r="61" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A61" s="56">
         <v>44368</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="16">
+      <c r="B61" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="16">
         <v>2500</v>
       </c>
-      <c r="D59" s="46">
+      <c r="D61" s="46">
         <v>40</v>
       </c>
-      <c r="E59" s="20">
-        <f>C59*D59</f>
+      <c r="E61" s="20">
+        <f>C61*D61</f>
         <v>100000</v>
       </c>
-      <c r="F59" s="20">
-        <f>E59*0.002</f>
+      <c r="F61" s="20">
+        <f>E61*0.002</f>
         <v>200</v>
       </c>
-      <c r="G59" s="20">
-        <f>E59*0.00006</f>
+      <c r="G61" s="20">
+        <f>E61*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H59" s="20">
-        <f>E59*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I59" s="20">
-        <f>(F59+G59+H59)*0.07</f>
+      <c r="H61" s="20">
+        <f>E61*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I61" s="20">
+        <f>(F61+G61+H61)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J59" s="20">
-        <f>E59+F59+I59+G59+H59</f>
+      <c r="J61" s="20">
+        <f>E61+F61+I61+G61+H61</f>
         <v>100221.49</v>
       </c>
-      <c r="K59" s="57"/>
-      <c r="L59" s="58"/>
-      <c r="M59" s="58"/>
-      <c r="N59" s="58"/>
-      <c r="O59" s="58"/>
-    </row>
-    <row r="60" spans="1:15" s="13" customFormat="1">
-      <c r="A60" s="56" t="e">
-        <f>A57</f>
+      <c r="K61" s="57"/>
+      <c r="L61" s="58"/>
+      <c r="M61" s="58"/>
+      <c r="N61" s="58"/>
+      <c r="O61" s="58"/>
+    </row>
+    <row r="62" spans="1:15" s="13" customFormat="1">
+      <c r="A62" s="56" t="e">
+        <f>A59</f>
         <v>#REF!</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="10">
-        <f>C59</f>
+      <c r="C62" s="10">
+        <f>C61</f>
         <v>2500</v>
       </c>
-      <c r="D60" s="34">
-        <f>D45</f>
+      <c r="D62" s="34">
+        <f>D47</f>
         <v>29.5</v>
       </c>
-      <c r="E60" s="11">
-        <f>C60*D60</f>
+      <c r="E62" s="11">
+        <f>C62*D62</f>
         <v>73750</v>
       </c>
-      <c r="F60" s="35">
-        <f>E60*0.002</f>
+      <c r="F62" s="35">
+        <f>E62*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G60" s="34">
-        <f>E60*0.000068</f>
+      <c r="G62" s="34">
+        <f>E62*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H60" s="34">
-        <f>E60*0.00001</f>
+      <c r="H62" s="34">
+        <f>E62*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I60" s="34">
-        <f>(F60+G60+H60)*0.07</f>
+      <c r="I62" s="34">
+        <f>(F62+G62+H62)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J60" s="34">
-        <f>E60-F60-G60-H60-I60</f>
+      <c r="J62" s="34">
+        <f>E62-F62-G62-H62-I62</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K60" s="10">
-        <f>K57+C60</f>
+      <c r="K62" s="10">
+        <f>K59+C62</f>
         <v>22500</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A61" s="56" t="s">
+    <row r="63" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A63" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="25">
-        <f>(D60-D59)/D59</f>
+      <c r="B63" s="25">
+        <f>(D62-D61)/D61</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="20">
-        <f>E60-E59</f>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="20">
+        <f>E62-E61</f>
         <v>-26250</v>
       </c>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20">
-        <f>J60-J59</f>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20">
+        <f>J62-J61</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K61" s="20">
-        <f>K58+J61</f>
+      <c r="K63" s="20">
+        <f>K60+J63</f>
         <v>-98782.761262500106</v>
       </c>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11243" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAE95D6E-85FC-4364-9007-FA0B27F14007}"/>
+  <xr:revisionPtr revIDLastSave="11274" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C1AC8AD-701F-4456-937B-805D307A0E9C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="10" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -34,12 +34,13 @@
     <sheet name="SCC" sheetId="152" r:id="rId19"/>
     <sheet name="SCCC" sheetId="177" r:id="rId20"/>
     <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
-    <sheet name="TMT" sheetId="145" r:id="rId25"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
-    <sheet name="WHART" sheetId="171" r:id="rId27"/>
+    <sheet name="JMART" sheetId="204" r:id="rId22"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId23"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId25"/>
+    <sheet name="TMT" sheetId="145" r:id="rId26"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
+    <sheet name="WHART" sheetId="171" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -149,6 +150,9 @@
   </si>
   <si>
     <t>SENA</t>
+  </si>
+  <si>
+    <t>JMART</t>
   </si>
   <si>
     <t>SINGER</t>
@@ -13747,7 +13751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
@@ -13774,7 +13778,7 @@
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
       <c r="A2" s="39">
-        <v>44945</v>
+        <v>44946</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>1</v>
@@ -13783,31 +13787,31 @@
         <v>3600</v>
       </c>
       <c r="D2" s="17">
-        <v>28</v>
+        <v>39.5</v>
       </c>
       <c r="E2" s="18">
         <f>C2*D2</f>
-        <v>100800</v>
+        <v>142200</v>
       </c>
       <c r="F2" s="18">
         <f>E2*0.002</f>
-        <v>201.6</v>
+        <v>284.40000000000003</v>
       </c>
       <c r="G2" s="18">
         <f>E2*0.00006</f>
-        <v>6.048</v>
+        <v>8.532</v>
       </c>
       <c r="H2" s="18">
         <f>E2*0.00001</f>
-        <v>1.008</v>
+        <v>1.4220000000000002</v>
       </c>
       <c r="I2" s="18">
         <f>(F2+G2+H2)*0.07</f>
-        <v>14.605920000000001</v>
+        <v>20.604780000000005</v>
       </c>
       <c r="J2" s="18">
         <f>E2+F2+I2+G2+H2</f>
-        <v>101023.26192</v>
+        <v>142514.95877999999</v>
       </c>
       <c r="K2" s="29"/>
       <c r="L2" s="17"/>
@@ -13825,31 +13829,31 @@
         <v>3600</v>
       </c>
       <c r="D3" s="34">
-        <v>29.5</v>
+        <v>41.5</v>
       </c>
       <c r="E3" s="11">
         <f>C3*D3</f>
-        <v>106200</v>
+        <v>149400</v>
       </c>
       <c r="F3" s="35">
         <f>E3*0.002</f>
-        <v>212.4</v>
+        <v>298.8</v>
       </c>
       <c r="G3" s="34">
         <f>E3*0.000068</f>
-        <v>7.2215999999999996</v>
+        <v>10.1592</v>
       </c>
       <c r="H3" s="34">
         <f>E3*0.00001</f>
-        <v>1.0620000000000001</v>
+        <v>1.4940000000000002</v>
       </c>
       <c r="I3" s="34">
         <f>(F3+G3+H3)*0.07</f>
-        <v>15.447852000000003</v>
+        <v>21.731724000000003</v>
       </c>
       <c r="J3" s="34">
         <f>E3-F3-G3-H3-I3</f>
-        <v>105963.868548</v>
+        <v>149067.815076</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1">
@@ -13858,13 +13862,13 @@
       </c>
       <c r="B4" s="12">
         <f>(D3-D2)/D2</f>
-        <v>5.3571428571428568E-2</v>
+        <v>5.0632911392405063E-2</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
       <c r="E4" s="20">
         <f>E3-E2</f>
-        <v>5400</v>
+        <v>7200</v>
       </c>
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
@@ -13872,7 +13876,7 @@
       <c r="I4" s="20"/>
       <c r="J4" s="20">
         <f>J3-J2</f>
-        <v>4940.6066279999941</v>
+        <v>6552.8562960000127</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
@@ -13881,44 +13885,126 @@
       <c r="D5" s="47"/>
       <c r="J5" s="53">
         <f>J1+J4</f>
-        <v>4940.6066279999941</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="56"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1">
+        <v>6552.8562960000127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="13" customFormat="1">
+      <c r="A6" s="39">
+        <v>44946</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D6" s="17">
+        <v>39.5</v>
+      </c>
+      <c r="E6" s="18">
+        <f>C6*D6</f>
+        <v>142200</v>
+      </c>
+      <c r="F6" s="18">
+        <f>E6*0.002</f>
+        <v>284.40000000000003</v>
+      </c>
+      <c r="G6" s="18">
+        <f>E6*0.00006</f>
+        <v>8.532</v>
+      </c>
+      <c r="H6" s="18">
+        <f>E6*0.00001</f>
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="I6" s="18">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>20.604780000000005</v>
+      </c>
+      <c r="J6" s="18">
+        <f>E6+F6+I6+G6+H6</f>
+        <v>142514.95877999999</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="30"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A7" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>2400</v>
+      </c>
+      <c r="D7" s="46">
+        <v>38.25</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>91800</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>183.6</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>5.508</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>13.301820000000003</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>92003.327820000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="56"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="B8" s="12">
+        <f>(D7-D6)/D6</f>
+        <v>-3.1645569620253167E-2</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C6:C7)</f>
+        <v>6000</v>
+      </c>
+      <c r="D8" s="11">
+        <f>E8/C8</f>
+        <v>39</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
+        <v>234000</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>468</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>14.04</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>2.3400000000000003</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>33.906600000000012</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>234518.28659999999</v>
+      </c>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
       <c r="A9" s="50"/>
@@ -13935,6 +14021,426 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44945</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D2" s="17">
+        <v>28</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>100800</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>201.6</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>6.048</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.008</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>14.605920000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>101023.26192</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1">
+      <c r="A3" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10">
+        <f>C2</f>
+        <v>3600</v>
+      </c>
+      <c r="D3" s="34">
+        <v>29.5</v>
+      </c>
+      <c r="E3" s="11">
+        <f>C3*D3</f>
+        <v>106200</v>
+      </c>
+      <c r="F3" s="35">
+        <f>E3*0.002</f>
+        <v>212.4</v>
+      </c>
+      <c r="G3" s="34">
+        <f>E3*0.000068</f>
+        <v>7.2215999999999996</v>
+      </c>
+      <c r="H3" s="34">
+        <f>E3*0.00001</f>
+        <v>1.0620000000000001</v>
+      </c>
+      <c r="I3" s="34">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>15.447852000000003</v>
+      </c>
+      <c r="J3" s="34">
+        <f>E3-F3-G3-H3-I3</f>
+        <v>105963.868548</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1">
+      <c r="A4" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="12">
+        <f>(D3-D2)/D2</f>
+        <v>5.3571428571428568E-2</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="20">
+        <f>E3-E2</f>
+        <v>5400</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20">
+        <f>J3-J2</f>
+        <v>4940.6066279999941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
+      <c r="A5" s="50"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="47"/>
+      <c r="J5" s="53">
+        <f>J1+J4</f>
+        <v>4940.6066279999941</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="13" customFormat="1">
+      <c r="A6" s="39">
+        <f>A2</f>
+        <v>44945</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D6" s="17">
+        <f>D2</f>
+        <v>28</v>
+      </c>
+      <c r="E6" s="18">
+        <f>C6*D6</f>
+        <v>100800</v>
+      </c>
+      <c r="F6" s="18">
+        <f>E6*0.002</f>
+        <v>201.6</v>
+      </c>
+      <c r="G6" s="18">
+        <f>E6*0.00006</f>
+        <v>6.048</v>
+      </c>
+      <c r="H6" s="18">
+        <f>E6*0.00001</f>
+        <v>1.008</v>
+      </c>
+      <c r="I6" s="18">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>14.605920000000001</v>
+      </c>
+      <c r="J6" s="18">
+        <f>E6+F6+I6+G6+H6</f>
+        <v>101023.26192</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="30"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A7" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="46">
+        <v>27</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>32400</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>64.8</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>1.944</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>4.6947600000000005</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>32471.762759999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A8" s="56"/>
+      <c r="B8" s="12">
+        <f>(D7-D6)/D6</f>
+        <v>-3.5714285714285712E-2</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C6:C7)</f>
+        <v>4800</v>
+      </c>
+      <c r="D8" s="11">
+        <f>E8/C8</f>
+        <v>27.75</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
+        <v>133200</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>266.39999999999998</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>7.992</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>1.3320000000000001</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>19.30068</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>133495.02468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A9" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="46">
+        <v>26.5</v>
+      </c>
+      <c r="E9" s="20">
+        <f>C9*D9</f>
+        <v>31800</v>
+      </c>
+      <c r="F9" s="20">
+        <f>E9*0.002</f>
+        <v>63.6</v>
+      </c>
+      <c r="G9" s="20">
+        <f>E9*0.00006</f>
+        <v>1.9080000000000001</v>
+      </c>
+      <c r="H9" s="20">
+        <f>E9*0.00001</f>
+        <v>0.318</v>
+      </c>
+      <c r="I9" s="20">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>4.6078200000000002</v>
+      </c>
+      <c r="J9" s="20">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>31870.433819999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="12">
+        <f>(D9-D8)/D8</f>
+        <v>-4.5045045045045043E-2</v>
+      </c>
+      <c r="C10" s="10">
+        <f>SUM(C8:C9)</f>
+        <v>6000</v>
+      </c>
+      <c r="D10" s="11">
+        <f>E10/C10</f>
+        <v>27.5</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" ref="E10:J10" si="1">SUM(E8:E9)</f>
+        <v>165000</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="1"/>
+        <v>9.9</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="1"/>
+        <v>23.9085</v>
+      </c>
+      <c r="J10" s="10">
+        <f t="shared" si="1"/>
+        <v>165365.45850000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A11" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D11" s="46">
+        <v>26</v>
+      </c>
+      <c r="E11" s="20">
+        <f>C11*D11</f>
+        <v>31200</v>
+      </c>
+      <c r="F11" s="20">
+        <f>E11*0.002</f>
+        <v>62.4</v>
+      </c>
+      <c r="G11" s="20">
+        <f>E11*0.00006</f>
+        <v>1.8720000000000001</v>
+      </c>
+      <c r="H11" s="20">
+        <f>E11*0.00001</f>
+        <v>0.312</v>
+      </c>
+      <c r="I11" s="20">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>4.5208800000000009</v>
+      </c>
+      <c r="J11" s="20">
+        <f>E11+F11+I11+G11+H11</f>
+        <v>31269.104880000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A12" s="56"/>
+      <c r="B12" s="12">
+        <f>(D11-D10)/D10</f>
+        <v>-5.4545454545454543E-2</v>
+      </c>
+      <c r="C12" s="10">
+        <f>SUM(C10:C11)</f>
+        <v>7200</v>
+      </c>
+      <c r="D12" s="11">
+        <f>E12/C12</f>
+        <v>27.25</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" ref="E12:J12" si="2">SUM(E10:E11)</f>
+        <v>196200</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="2"/>
+        <v>392.4</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="2"/>
+        <v>11.772</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="2"/>
+        <v>1.9620000000000002</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="2"/>
+        <v>28.429380000000002</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" si="2"/>
+        <v>196634.56338000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13957,7 +14463,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -15169,7 +15675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15192,7 +15698,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15410,7 +15916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15433,7 +15939,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15869,7 +16375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15892,7 +16398,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -16256,38 +16762,38 @@
         <v>10000</v>
       </c>
       <c r="D11" s="46">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="E11" s="20">
         <f>C11*D11</f>
-        <v>72000</v>
+        <v>77000</v>
       </c>
       <c r="F11" s="20">
         <f>E11*0.002</f>
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G11" s="20">
         <f>E11*0.000068</f>
-        <v>4.8959999999999999</v>
+        <v>5.2359999999999998</v>
       </c>
       <c r="H11" s="20">
         <f>E11*0.00001</f>
-        <v>0.72000000000000008</v>
+        <v>0.77</v>
       </c>
       <c r="I11" s="20">
         <f>(F11+G11+H11)*0.07</f>
-        <v>10.47312</v>
+        <v>11.200420000000001</v>
       </c>
       <c r="J11" s="20">
         <f>E11+F11+I11+G11+H11</f>
-        <v>72160.08911999999</v>
+        <v>77171.206420000002</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="21" customFormat="1">
       <c r="A12" s="44"/>
       <c r="B12" s="74">
         <f>(D11-D10)/D10</f>
-        <v>-0.19553072625698315</v>
+        <v>-0.13966480446927365</v>
       </c>
       <c r="C12" s="22">
         <f>C10+C11</f>
@@ -16295,31 +16801,31 @@
       </c>
       <c r="D12" s="33">
         <f>E12/C12</f>
-        <v>8.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E12" s="22">
         <f>E10+E11</f>
-        <v>430000</v>
+        <v>435000</v>
       </c>
       <c r="F12" s="22">
         <f>F10+F11</f>
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="G12" s="22">
         <f>G10+G11</f>
-        <v>28.512</v>
+        <v>28.852</v>
       </c>
       <c r="H12" s="22">
         <f>H10+H11</f>
-        <v>4.3000000000000007</v>
+        <v>4.3500000000000005</v>
       </c>
       <c r="I12" s="22">
         <f>I10+I11</f>
-        <v>62.496840000000006</v>
+        <v>63.224140000000006</v>
       </c>
       <c r="J12" s="22">
         <f>J10+J11</f>
-        <v>430955.30883999995</v>
+        <v>435966.42614</v>
       </c>
       <c r="K12" s="25"/>
     </row>
@@ -16331,7 +16837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16357,7 +16863,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11274" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C1AC8AD-701F-4456-937B-805D307A0E9C}"/>
+  <xr:revisionPtr revIDLastSave="11279" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C77AB42-2B96-4A87-8A65-1E2CCC3CC648}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -21165,38 +21165,38 @@
         <v>10000</v>
       </c>
       <c r="D7" s="80">
-        <v>18.899999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="94">
         <f>C7*D7</f>
-        <v>189000</v>
+        <v>195000</v>
       </c>
       <c r="F7" s="94">
         <f>E7*0.002</f>
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="G7" s="94">
         <f>E7*0.000068</f>
-        <v>12.852</v>
+        <v>13.26</v>
       </c>
       <c r="H7" s="94">
         <f>E7*0.00001</f>
-        <v>1.8900000000000001</v>
+        <v>1.9500000000000002</v>
       </c>
       <c r="I7" s="94">
         <f>(F7+G7+H7)*0.07</f>
-        <v>27.49194</v>
+        <v>28.364700000000003</v>
       </c>
       <c r="J7" s="94">
         <f>E7+F7+I7+G7+H7</f>
-        <v>189420.23394000003</v>
+        <v>195433.57470000003</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
       <c r="A8" s="77"/>
       <c r="B8" s="81">
         <f>(D7-D6)/D6</f>
-        <v>0</v>
+        <v>3.1746031746031821E-2</v>
       </c>
       <c r="C8" s="79">
         <f>SUM(C6:C7)</f>
@@ -21204,31 +21204,31 @@
       </c>
       <c r="D8" s="80">
         <f>E8/C8</f>
-        <v>18.899999999999999</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="E8" s="79">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>567000</v>
+        <v>573000</v>
       </c>
       <c r="F8" s="79">
         <f t="shared" si="2"/>
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="G8" s="79">
         <f t="shared" si="2"/>
-        <v>37.78</v>
+        <v>38.188000000000002</v>
       </c>
       <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>5.67</v>
+        <v>5.73</v>
       </c>
       <c r="I8" s="79">
         <f t="shared" si="2"/>
-        <v>82.421500000000009</v>
+        <v>83.294260000000008</v>
       </c>
       <c r="J8" s="79">
         <f t="shared" si="2"/>
-        <v>568259.87150000001</v>
+        <v>574273.21226000006</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="13"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11279" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C77AB42-2B96-4A87-8A65-1E2CCC3CC648}"/>
+  <xr:revisionPtr revIDLastSave="11292" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF60989-9033-42E9-82D5-BF9FBE6A6B4A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -26,21 +26,20 @@
     <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
     <sheet name="IVL" sheetId="196" r:id="rId12"/>
     <sheet name="JASIF" sheetId="46" r:id="rId13"/>
-    <sheet name="MAKRO" sheetId="179" r:id="rId14"/>
-    <sheet name="MCS" sheetId="20" r:id="rId15"/>
-    <sheet name="NER" sheetId="117" r:id="rId16"/>
-    <sheet name="ORI" sheetId="184" r:id="rId17"/>
-    <sheet name="RCL" sheetId="161" r:id="rId18"/>
-    <sheet name="SCC" sheetId="152" r:id="rId19"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId20"/>
-    <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="JMART" sheetId="204" r:id="rId22"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId23"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId25"/>
-    <sheet name="TMT" sheetId="145" r:id="rId26"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
-    <sheet name="WHART" sheetId="171" r:id="rId28"/>
+    <sheet name="MCS" sheetId="20" r:id="rId14"/>
+    <sheet name="NER" sheetId="117" r:id="rId15"/>
+    <sheet name="ORI" sheetId="184" r:id="rId16"/>
+    <sheet name="RCL" sheetId="161" r:id="rId17"/>
+    <sheet name="SCC" sheetId="152" r:id="rId18"/>
+    <sheet name="SCCC" sheetId="177" r:id="rId19"/>
+    <sheet name="SENA" sheetId="183" r:id="rId20"/>
+    <sheet name="JMART" sheetId="204" r:id="rId21"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
+    <sheet name="TMT" sheetId="145" r:id="rId25"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
+    <sheet name="WHART" sheetId="171" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="36">
   <si>
     <t>KCE</t>
   </si>
@@ -123,9 +122,6 @@
   </si>
   <si>
     <t>JASIF</t>
-  </si>
-  <si>
-    <t>MAKRO</t>
   </si>
   <si>
     <t>MCS</t>
@@ -5889,415 +5885,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB1EBAE-F735-42C2-8B12-15730D8F96F4}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="5.625" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1">
-      <c r="A2" s="49">
-        <v>44616</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>3000</v>
-      </c>
-      <c r="D2" s="41">
-        <v>42</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>126000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>252</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.26</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>18.257400000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>126279.07739999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="49">
-        <v>44624</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>1500</v>
-      </c>
-      <c r="D3" s="41">
-        <v>42</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>63000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>126</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>9.1287000000000003</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>63139.538699999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="30">
-        <f>(D3-D2)/D2</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="16">
-        <f>SUM(C2:C3)</f>
-        <v>4500</v>
-      </c>
-      <c r="D4" s="17">
-        <f>E4/C4</f>
-        <v>42</v>
-      </c>
-      <c r="E4" s="16">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>189000</v>
-      </c>
-      <c r="F4" s="16">
-        <f t="shared" si="0"/>
-        <v>378</v>
-      </c>
-      <c r="G4" s="16">
-        <f t="shared" si="0"/>
-        <v>11.34</v>
-      </c>
-      <c r="H4" s="16">
-        <f t="shared" si="0"/>
-        <v>1.8900000000000001</v>
-      </c>
-      <c r="I4" s="16">
-        <f t="shared" si="0"/>
-        <v>27.386099999999999</v>
-      </c>
-      <c r="J4" s="16">
-        <f t="shared" si="0"/>
-        <v>189418.61609999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1">
-      <c r="A5" s="49">
-        <v>44663</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>1500</v>
-      </c>
-      <c r="D5" s="41">
-        <v>39</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>58500</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>117</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>3.5100000000000002</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>0.58500000000000008</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>8.4766500000000011</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>58629.571649999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="49"/>
-      <c r="B6" s="30">
-        <f>(D5-D4)/D4</f>
-        <v>-7.1428571428571425E-2</v>
-      </c>
-      <c r="C6" s="16">
-        <f>SUM(C4:C5)</f>
-        <v>6000</v>
-      </c>
-      <c r="D6" s="17">
-        <f>E6/C6</f>
-        <v>41.25</v>
-      </c>
-      <c r="E6" s="16">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>247500</v>
-      </c>
-      <c r="F6" s="16">
-        <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="G6" s="16">
-        <f t="shared" si="1"/>
-        <v>14.85</v>
-      </c>
-      <c r="H6" s="16">
-        <f t="shared" si="1"/>
-        <v>2.4750000000000001</v>
-      </c>
-      <c r="I6" s="16">
-        <f t="shared" si="1"/>
-        <v>35.862749999999998</v>
-      </c>
-      <c r="J6" s="16">
-        <f t="shared" si="1"/>
-        <v>248048.18774999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1">
-      <c r="A7" s="49">
-        <v>44684</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="16">
-        <v>1500</v>
-      </c>
-      <c r="D7" s="41">
-        <v>37</v>
-      </c>
-      <c r="E7" s="18">
-        <f>C7*D7</f>
-        <v>55500</v>
-      </c>
-      <c r="F7" s="18">
-        <f>E7*0.002</f>
-        <v>111</v>
-      </c>
-      <c r="G7" s="18">
-        <f>E7*0.00006</f>
-        <v>3.33</v>
-      </c>
-      <c r="H7" s="18">
-        <f>E7*0.00001</f>
-        <v>0.55500000000000005</v>
-      </c>
-      <c r="I7" s="18">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>8.0419500000000017</v>
-      </c>
-      <c r="J7" s="18">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>55622.926950000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="30">
-        <f>(D7-D6)/D6</f>
-        <v>-0.10303030303030303</v>
-      </c>
-      <c r="C8" s="16">
-        <f>SUM(C6:C7)</f>
-        <v>7500</v>
-      </c>
-      <c r="D8" s="17">
-        <f>E8/C8</f>
-        <v>40.4</v>
-      </c>
-      <c r="E8" s="16">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>303000</v>
-      </c>
-      <c r="F8" s="16">
-        <f t="shared" si="2"/>
-        <v>606</v>
-      </c>
-      <c r="G8" s="16">
-        <f t="shared" si="2"/>
-        <v>18.18</v>
-      </c>
-      <c r="H8" s="16">
-        <f t="shared" si="2"/>
-        <v>3.0300000000000002</v>
-      </c>
-      <c r="I8" s="16">
-        <f t="shared" si="2"/>
-        <v>43.904699999999998</v>
-      </c>
-      <c r="J8" s="16">
-        <f t="shared" si="2"/>
-        <v>303671.11469999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="56">
-        <v>44607</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="10">
-        <v>7500</v>
-      </c>
-      <c r="D10" s="11">
-        <v>40.4</v>
-      </c>
-      <c r="E10" s="20">
-        <f>C10*D10</f>
-        <v>303000</v>
-      </c>
-      <c r="F10" s="20">
-        <f>E10*0.002</f>
-        <v>606</v>
-      </c>
-      <c r="G10" s="20">
-        <f>E10*0.000068</f>
-        <v>20.603999999999999</v>
-      </c>
-      <c r="H10" s="20">
-        <f>E10*0.00001</f>
-        <v>3.0300000000000002</v>
-      </c>
-      <c r="I10" s="20">
-        <f>(F10+G10+H10)*0.07</f>
-        <v>44.074380000000005</v>
-      </c>
-      <c r="J10" s="20">
-        <f>E10+F10+I10+G10+H10</f>
-        <v>303673.70838000003</v>
-      </c>
-      <c r="L10" s="25"/>
-      <c r="M10" s="21"/>
-    </row>
-    <row r="11" spans="1:13" s="13" customFormat="1">
-      <c r="A11" s="56">
-        <v>44560</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="10">
-        <f>C10</f>
-        <v>7500</v>
-      </c>
-      <c r="D11" s="34">
-        <v>42.5</v>
-      </c>
-      <c r="E11" s="11">
-        <f>C11*D11</f>
-        <v>318750</v>
-      </c>
-      <c r="F11" s="35">
-        <f>E11*0.002</f>
-        <v>637.5</v>
-      </c>
-      <c r="G11" s="34">
-        <f>E11*0.000068</f>
-        <v>21.675000000000001</v>
-      </c>
-      <c r="H11" s="34">
-        <f>E11*0.00001</f>
-        <v>3.1875000000000004</v>
-      </c>
-      <c r="I11" s="34">
-        <f>(F11+G11+H11)*0.07</f>
-        <v>46.365375</v>
-      </c>
-      <c r="J11" s="34">
-        <f>E11-F11-G11-H11-I11</f>
-        <v>318041.27212500002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A12" s="9">
-        <f>DAYS360(A10,A11)</f>
-        <v>-45</v>
-      </c>
-      <c r="B12" s="12">
-        <f>(D11-D10)/D10</f>
-        <v>5.1980198019802019E-2</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="20">
-        <f>E11-E10</f>
-        <v>15750</v>
-      </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20">
-        <f>J11-J10</f>
-        <v>14367.563744999992</v>
-      </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -6317,7 +5904,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1">
@@ -7842,7 +7429,7 @@
         <v>42720</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" s="16">
         <v>75000</v>
@@ -7954,7 +7541,7 @@
         <v>44351</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" s="16">
         <v>70000</v>
@@ -8471,7 +8058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8494,7 +8081,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8914,7 +8501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8937,7 +8524,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -9425,7 +9012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -9448,7 +9035,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -10911,7 +10498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -10934,7 +10521,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -11216,6 +10803,234 @@
       <c r="J8" s="22">
         <f t="shared" si="2"/>
         <v>473847.20472000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>900</v>
+      </c>
+      <c r="D2" s="17">
+        <v>174.5</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>157050</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>314.10000000000002</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>9.423</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.5705000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>22.756545000000003</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>157397.85004500003</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="39">
+        <v>44616</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>160.5</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>48150</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>96.3</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>2.8890000000000002</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>0.48150000000000004</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>6.9769350000000001</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>48256.647435000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-8.0229226361031525E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>1200</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>171</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>205200</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>410.40000000000003</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>12.312000000000001</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0520000000000005</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>29.733480000000004</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>205654.49748000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="67">
+        <v>44616</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>300</v>
+      </c>
+      <c r="D5" s="11">
+        <v>148.5</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5*D5</f>
+        <v>44550</v>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*0.002</f>
+        <v>89.100000000000009</v>
+      </c>
+      <c r="G5" s="20">
+        <f>E5*0.00006</f>
+        <v>2.673</v>
+      </c>
+      <c r="H5" s="20">
+        <f>E5*0.00001</f>
+        <v>0.44550000000000006</v>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>6.4552950000000013</v>
+      </c>
+      <c r="J5" s="20">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>44648.673795000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="25">
+        <f>(D5-D4)/D4</f>
+        <v>-0.13157894736842105</v>
+      </c>
+      <c r="C6" s="22">
+        <f>SUM(C4:C5)</f>
+        <v>1500</v>
+      </c>
+      <c r="D6" s="68">
+        <f>E6/C6</f>
+        <v>166.5</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>249750</v>
+      </c>
+      <c r="F6" s="22">
+        <f t="shared" si="1"/>
+        <v>499.50000000000006</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" si="1"/>
+        <v>14.985000000000001</v>
+      </c>
+      <c r="H6" s="22">
+        <f t="shared" si="1"/>
+        <v>2.4975000000000005</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" si="1"/>
+        <v>36.188775000000007</v>
+      </c>
+      <c r="J6" s="22">
+        <f t="shared" si="1"/>
+        <v>250303.17127500003</v>
       </c>
     </row>
   </sheetData>
@@ -12982,234 +12797,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>900</v>
-      </c>
-      <c r="D2" s="17">
-        <v>174.5</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>157050</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>314.10000000000002</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>9.423</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.5705000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>22.756545000000003</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>157397.85004500003</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="39">
-        <v>44616</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>160.5</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>48150</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>96.3</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>2.8890000000000002</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>0.48150000000000004</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>6.9769350000000001</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>48256.647435000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-8.0229226361031525E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>1200</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>171</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>205200</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>410.40000000000003</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>12.312000000000001</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0520000000000005</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>29.733480000000004</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>205654.49748000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="67">
-        <v>44616</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
-        <v>300</v>
-      </c>
-      <c r="D5" s="11">
-        <v>148.5</v>
-      </c>
-      <c r="E5" s="20">
-        <f>C5*D5</f>
-        <v>44550</v>
-      </c>
-      <c r="F5" s="20">
-        <f>E5*0.002</f>
-        <v>89.100000000000009</v>
-      </c>
-      <c r="G5" s="20">
-        <f>E5*0.00006</f>
-        <v>2.673</v>
-      </c>
-      <c r="H5" s="20">
-        <f>E5*0.00001</f>
-        <v>0.44550000000000006</v>
-      </c>
-      <c r="I5" s="20">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>6.4552950000000013</v>
-      </c>
-      <c r="J5" s="20">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>44648.673795000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="25">
-        <f>(D5-D4)/D4</f>
-        <v>-0.13157894736842105</v>
-      </c>
-      <c r="C6" s="22">
-        <f>SUM(C4:C5)</f>
-        <v>1500</v>
-      </c>
-      <c r="D6" s="68">
-        <f>E6/C6</f>
-        <v>166.5</v>
-      </c>
-      <c r="E6" s="22">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>249750</v>
-      </c>
-      <c r="F6" s="22">
-        <f t="shared" si="1"/>
-        <v>499.50000000000006</v>
-      </c>
-      <c r="G6" s="22">
-        <f t="shared" si="1"/>
-        <v>14.985000000000001</v>
-      </c>
-      <c r="H6" s="22">
-        <f t="shared" si="1"/>
-        <v>2.4975000000000005</v>
-      </c>
-      <c r="I6" s="22">
-        <f t="shared" si="1"/>
-        <v>36.188775000000007</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="1"/>
-        <v>250303.17127500003</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -13232,7 +12819,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -13750,7 +13337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13773,7 +13360,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -14020,7 +13607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -14043,7 +13630,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -14440,7 +14027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -14463,7 +14050,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -15675,7 +15262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15698,7 +15285,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15916,7 +15503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15939,7 +15526,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -16375,7 +15962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16398,7 +15985,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -16837,7 +16424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16863,7 +16450,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -21155,78 +20742,78 @@
       <c r="K6" s="81"/>
     </row>
     <row r="7" spans="1:14" ht="12.75">
-      <c r="A7" s="77">
-        <v>44880</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="79">
+      <c r="A7" s="82">
+        <v>44950</v>
+      </c>
+      <c r="B7" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="84">
         <v>10000</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="85">
         <v>19.5</v>
       </c>
-      <c r="E7" s="94">
+      <c r="E7" s="86">
         <f>C7*D7</f>
         <v>195000</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="86">
         <f>E7*0.002</f>
         <v>390</v>
       </c>
-      <c r="G7" s="94">
+      <c r="G7" s="86">
         <f>E7*0.000068</f>
         <v>13.26</v>
       </c>
-      <c r="H7" s="94">
+      <c r="H7" s="86">
         <f>E7*0.00001</f>
         <v>1.9500000000000002</v>
       </c>
-      <c r="I7" s="94">
+      <c r="I7" s="86">
         <f>(F7+G7+H7)*0.07</f>
         <v>28.364700000000003</v>
       </c>
-      <c r="J7" s="94">
+      <c r="J7" s="86">
         <f>E7+F7+I7+G7+H7</f>
         <v>195433.57470000003</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A8" s="77"/>
-      <c r="B8" s="81">
+      <c r="A8" s="82"/>
+      <c r="B8" s="87">
         <f>(D7-D6)/D6</f>
         <v>3.1746031746031821E-2</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="84">
         <f>SUM(C6:C7)</f>
         <v>30000</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="85">
         <f>E8/C8</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="E8" s="79">
+      <c r="E8" s="84">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
         <v>573000</v>
       </c>
-      <c r="F8" s="79">
+      <c r="F8" s="84">
         <f t="shared" si="2"/>
         <v>1146</v>
       </c>
-      <c r="G8" s="79">
+      <c r="G8" s="84">
         <f t="shared" si="2"/>
         <v>38.188000000000002</v>
       </c>
-      <c r="H8" s="79">
+      <c r="H8" s="84">
         <f t="shared" si="2"/>
         <v>5.73</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="84">
         <f t="shared" si="2"/>
         <v>83.294260000000008</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="84">
         <f t="shared" si="2"/>
         <v>574273.21226000006</v>
       </c>
@@ -21235,29 +20822,82 @@
       <c r="M8" s="62"/>
       <c r="N8" s="62"/>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="56"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="56"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
+    <row r="9" spans="1:14" ht="12.75">
+      <c r="A9" s="77">
+        <v>44950</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="80">
+        <v>18.7</v>
+      </c>
+      <c r="E9" s="94">
+        <f>C9*D9</f>
+        <v>187000</v>
+      </c>
+      <c r="F9" s="94">
+        <f>E9*0.002</f>
+        <v>374</v>
+      </c>
+      <c r="G9" s="94">
+        <f>E9*0.000068</f>
+        <v>12.715999999999999</v>
+      </c>
+      <c r="H9" s="94">
+        <f>E9*0.00001</f>
+        <v>1.87</v>
+      </c>
+      <c r="I9" s="94">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>27.201020000000003</v>
+      </c>
+      <c r="J9" s="94">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>187415.78701999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="12.75">
+      <c r="A10" s="77"/>
+      <c r="B10" s="81">
+        <f>(D9-D8)/D8</f>
+        <v>-2.094240837696346E-2</v>
+      </c>
+      <c r="C10" s="79">
+        <f>SUM(C8:C9)</f>
+        <v>40000</v>
+      </c>
+      <c r="D10" s="80">
+        <f>E10/C10</f>
+        <v>19</v>
+      </c>
+      <c r="E10" s="79">
+        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
+        <v>760000</v>
+      </c>
+      <c r="F10" s="79">
+        <f t="shared" si="3"/>
+        <v>1520</v>
+      </c>
+      <c r="G10" s="79">
+        <f t="shared" si="3"/>
+        <v>50.904000000000003</v>
+      </c>
+      <c r="H10" s="79">
+        <f t="shared" si="3"/>
+        <v>7.6000000000000005</v>
+      </c>
+      <c r="I10" s="79">
+        <f t="shared" si="3"/>
+        <v>110.49528000000001</v>
+      </c>
+      <c r="J10" s="79">
+        <f t="shared" si="3"/>
+        <v>761688.99928000011</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="56"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11292" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF60989-9033-42E9-82D5-BF9FBE6A6B4A}"/>
+  <xr:revisionPtr revIDLastSave="11378" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A644BB5-6C75-4745-A7DA-5DBFD1AB224E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -26,20 +26,21 @@
     <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
     <sheet name="IVL" sheetId="196" r:id="rId12"/>
     <sheet name="JASIF" sheetId="46" r:id="rId13"/>
-    <sheet name="MCS" sheetId="20" r:id="rId14"/>
-    <sheet name="NER" sheetId="117" r:id="rId15"/>
-    <sheet name="ORI" sheetId="184" r:id="rId16"/>
-    <sheet name="RCL" sheetId="161" r:id="rId17"/>
-    <sheet name="SCC" sheetId="152" r:id="rId18"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId19"/>
-    <sheet name="SENA" sheetId="183" r:id="rId20"/>
-    <sheet name="JMART" sheetId="204" r:id="rId21"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
-    <sheet name="TMT" sheetId="145" r:id="rId25"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
-    <sheet name="WHART" sheetId="171" r:id="rId27"/>
+    <sheet name="JMART" sheetId="204" r:id="rId14"/>
+    <sheet name="JMT" sheetId="205" r:id="rId15"/>
+    <sheet name="MCS" sheetId="20" r:id="rId16"/>
+    <sheet name="NER" sheetId="117" r:id="rId17"/>
+    <sheet name="ORI" sheetId="184" r:id="rId18"/>
+    <sheet name="RCL" sheetId="161" r:id="rId19"/>
+    <sheet name="SCC" sheetId="152" r:id="rId20"/>
+    <sheet name="SCCC" sheetId="177" r:id="rId21"/>
+    <sheet name="SENA" sheetId="183" r:id="rId22"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId23"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId25"/>
+    <sheet name="TMT" sheetId="145" r:id="rId26"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
+    <sheet name="WHART" sheetId="171" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -124,6 +125,12 @@
     <t>JASIF</t>
   </si>
   <si>
+    <t>JMART</t>
+  </si>
+  <si>
+    <t>JMT</t>
+  </si>
+  <si>
     <t>MCS</t>
   </si>
   <si>
@@ -146,9 +153,6 @@
   </si>
   <si>
     <t>SENA</t>
-  </si>
-  <si>
-    <t>JMART</t>
   </si>
   <si>
     <t>SINGER</t>
@@ -4300,7 +4304,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECE484-9DAC-4EE9-A8FE-27A01698073E}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -4360,131 +4364,167 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="13" customFormat="1" ht="12.75">
-      <c r="A3" s="67">
-        <v>44473</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="A3" s="39">
+        <v>44952</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
         <v>2400</v>
       </c>
-      <c r="D3" s="11">
-        <v>37</v>
-      </c>
-      <c r="E3" s="20">
+      <c r="D3" s="17">
+        <v>40</v>
+      </c>
+      <c r="E3" s="18">
         <f>C3*D3</f>
-        <v>88800</v>
-      </c>
-      <c r="F3" s="20">
+        <v>96000</v>
+      </c>
+      <c r="F3" s="18">
         <f>E3*0.002</f>
-        <v>177.6</v>
-      </c>
-      <c r="G3" s="20">
+        <v>192</v>
+      </c>
+      <c r="G3" s="18">
         <f>E3*0.00006</f>
-        <v>5.3280000000000003</v>
-      </c>
-      <c r="H3" s="20">
+        <v>5.76</v>
+      </c>
+      <c r="H3" s="18">
         <f>E3*0.00001</f>
-        <v>0.88800000000000012</v>
-      </c>
-      <c r="I3" s="20">
+        <v>0.96000000000000008</v>
+      </c>
+      <c r="I3" s="18">
         <f>(F3+G3+H3)*0.07</f>
-        <v>12.867120000000002</v>
-      </c>
-      <c r="J3" s="20">
+        <v>13.910400000000001</v>
+      </c>
+      <c r="J3" s="18">
         <f>E3+F3+I3+G3+H3</f>
-        <v>88996.683120000002</v>
+        <v>96212.630399999995</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="11"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A4" s="56"/>
-      <c r="B4" s="76">
+      <c r="A4" s="49"/>
+      <c r="B4" s="75">
         <f>(D3-D2)/D2</f>
-        <v>-0.15909090909090909</v>
-      </c>
-      <c r="C4" s="10">
+        <v>-9.0909090909090912E-2</v>
+      </c>
+      <c r="C4" s="16">
         <f>SUM(C2:C3)</f>
         <v>4800</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="40">
         <f>E4/C4</f>
-        <v>40.5</v>
-      </c>
-      <c r="E4" s="10">
+        <v>42</v>
+      </c>
+      <c r="E4" s="16">
         <f>SUM(E2:E3)</f>
-        <v>194400</v>
-      </c>
-      <c r="F4" s="10">
+        <v>201600</v>
+      </c>
+      <c r="F4" s="16">
         <f>SUM(F2:F3)</f>
-        <v>388.8</v>
-      </c>
-      <c r="G4" s="10">
+        <v>403.20000000000005</v>
+      </c>
+      <c r="G4" s="16">
         <f>SUM(G2:G3)</f>
-        <v>11.664000000000001</v>
-      </c>
-      <c r="H4" s="10">
+        <v>12.096</v>
+      </c>
+      <c r="H4" s="16">
         <f>SUM(H2:H3)</f>
-        <v>1.9440000000000002</v>
-      </c>
-      <c r="I4" s="10">
+        <v>2.016</v>
+      </c>
+      <c r="I4" s="16">
         <f>SUM(I2:I3)</f>
-        <v>28.168560000000006</v>
-      </c>
-      <c r="J4" s="10">
+        <v>29.211840000000006</v>
+      </c>
+      <c r="J4" s="16">
         <f>SUM(J2:J3)</f>
-        <v>194830.57655999999</v>
+        <v>202046.52383999998</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="13"/>
       <c r="M4" s="62"/>
       <c r="N4" s="62"/>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
+    <row r="5" spans="1:14" s="13" customFormat="1" ht="12.75">
+      <c r="A5" s="67">
+        <v>44952</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2400</v>
+      </c>
+      <c r="D5" s="11">
+        <v>36</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5*D5</f>
+        <v>86400</v>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*0.002</f>
+        <v>172.8</v>
+      </c>
+      <c r="G5" s="20">
+        <f>E5*0.00006</f>
+        <v>5.1840000000000002</v>
+      </c>
+      <c r="H5" s="20">
+        <f>E5*0.00001</f>
+        <v>0.8640000000000001</v>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>12.519360000000002</v>
+      </c>
+      <c r="J5" s="20">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>86591.367360000004</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A6" s="56">
-        <v>44799</v>
+      <c r="A6" s="56"/>
+      <c r="B6" s="76">
+        <f>(D5-D4)/D4</f>
+        <v>-0.14285714285714285</v>
       </c>
       <c r="C6" s="10">
-        <f>C2</f>
-        <v>2400</v>
+        <f>SUM(C4:C5)</f>
+        <v>7200</v>
       </c>
       <c r="D6" s="64">
-        <v>0.4</v>
-      </c>
-      <c r="E6" s="60">
-        <v>0</v>
-      </c>
-      <c r="F6" s="32">
-        <v>0</v>
-      </c>
-      <c r="G6" s="60">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
-        <f>G6-E6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0</v>
-      </c>
-      <c r="J6" s="61">
-        <f>C6*D6*0.9</f>
-        <v>864</v>
+        <f>E6/C6</f>
+        <v>40</v>
+      </c>
+      <c r="E6" s="10">
+        <f>SUM(E4:E5)</f>
+        <v>288000</v>
+      </c>
+      <c r="F6" s="10">
+        <f>SUM(F4:F5)</f>
+        <v>576</v>
+      </c>
+      <c r="G6" s="10">
+        <f>SUM(G4:G5)</f>
+        <v>17.28</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(H4:H5)</f>
+        <v>2.88</v>
+      </c>
+      <c r="I6" s="10">
+        <f>SUM(I4:I5)</f>
+        <v>41.731200000000008</v>
+      </c>
+      <c r="J6" s="10">
+        <f>SUM(J4:J5)</f>
+        <v>288637.89119999995</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="13"/>
@@ -4492,161 +4532,184 @@
       <c r="N6" s="62"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="56">
+      <c r="A7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="54"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+    </row>
+    <row r="9" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A9" s="56">
+        <v>44799</v>
+      </c>
+      <c r="C9" s="10">
+        <f>C2</f>
+        <v>2400</v>
+      </c>
+      <c r="D9" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="60">
+        <v>0</v>
+      </c>
+      <c r="F9" s="32">
+        <v>0</v>
+      </c>
+      <c r="G9" s="60">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <f>G9-E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
+      <c r="J9" s="61">
+        <f>C9*D9*0.9</f>
+        <v>864</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="56">
         <v>44242</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <f>C6</f>
-        <v>2400</v>
-      </c>
-      <c r="D7" s="46">
-        <f>D2</f>
-        <v>44</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>105600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>211.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.3360000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.056</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>15.301440000000005</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>105833.89343999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="56">
+      <c r="B10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10">
+        <f>C4</f>
+        <v>4800</v>
+      </c>
+      <c r="D10" s="46">
+        <f>D4</f>
+        <v>42</v>
+      </c>
+      <c r="E10" s="20">
+        <f>C10*D10</f>
+        <v>201600</v>
+      </c>
+      <c r="F10" s="20">
+        <f>E10*0.002</f>
+        <v>403.2</v>
+      </c>
+      <c r="G10" s="20">
+        <f>E10*0.00006</f>
+        <v>12.096</v>
+      </c>
+      <c r="H10" s="20">
+        <f>E10*0.00001</f>
+        <v>2.016</v>
+      </c>
+      <c r="I10" s="20">
+        <f>(F10+G10+H10)*0.07</f>
+        <v>29.211840000000002</v>
+      </c>
+      <c r="J10" s="20">
+        <f>E10+F10+I10+G10+H10</f>
+        <v>202046.52384000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="56">
         <v>44277</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10">
-        <f>C7</f>
-        <v>2400</v>
-      </c>
-      <c r="D8" s="34">
-        <v>45</v>
-      </c>
-      <c r="E8" s="11">
-        <f>C8*D8</f>
-        <v>108000</v>
-      </c>
-      <c r="F8" s="35">
-        <f>E8*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G8" s="34">
-        <f>E8*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H8" s="34">
-        <f>E8*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I8" s="34">
-        <f>(F8+G8+H8)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J8" s="34">
-        <f>E8-F8-G8-H8-I8</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="56" t="s">
+      <c r="C11" s="10">
+        <f>C10</f>
+        <v>4800</v>
+      </c>
+      <c r="D11" s="34">
+        <v>44.5</v>
+      </c>
+      <c r="E11" s="11">
+        <f>C11*D11</f>
+        <v>213600</v>
+      </c>
+      <c r="F11" s="35">
+        <f>E11*0.002</f>
+        <v>427.2</v>
+      </c>
+      <c r="G11" s="34">
+        <f>E11*0.000068</f>
+        <v>14.524799999999999</v>
+      </c>
+      <c r="H11" s="34">
+        <f>E11*0.00001</f>
+        <v>2.1360000000000001</v>
+      </c>
+      <c r="I11" s="34">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>31.070256000000001</v>
+      </c>
+      <c r="J11" s="34">
+        <f>E11-F11-G11-H11-I11</f>
+        <v>213125.06894399997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.75">
+      <c r="A12" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="20">
-        <f>E8-E7</f>
-        <v>2400</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20">
-        <f>J8-J7</f>
-        <v>1925.9728800000157</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="J10" s="53">
-        <f>J6+J9</f>
-        <v>2789.9728800000157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="78" customFormat="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-    </row>
-    <row r="12" spans="1:14" s="13" customFormat="1">
-      <c r="A12" s="49"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-    </row>
-    <row r="13" spans="1:14" s="31" customFormat="1" ht="18.75">
-      <c r="A13" s="28"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" s="21" customFormat="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="L14" s="25"/>
+      <c r="B12" s="76">
+        <f>(D11-D10)/D10</f>
+        <v>5.9523809523809521E-2</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="20">
+        <f>E11-E10</f>
+        <v>12000</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20">
+        <f>J11-J10</f>
+        <v>11078.545103999961</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="J13" s="53">
+        <f>J9+J12</f>
+        <v>11942.545103999961</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="78" customFormat="1">
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
     </row>
     <row r="15" spans="1:14" s="13" customFormat="1">
       <c r="A15" s="49"/>
@@ -4675,9 +4738,49 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" ht="12"/>
-    <row r="18" ht="12"/>
-    <row r="19" ht="12"/>
+    <row r="17" spans="1:13" s="21" customFormat="1">
+      <c r="A17" s="49"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="L17" s="25"/>
+    </row>
+    <row r="18" spans="1:13" s="13" customFormat="1">
+      <c r="A18" s="49"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+    </row>
+    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A19" s="28"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" ht="12"/>
+    <row r="21" spans="1:13" ht="12"/>
+    <row r="22" spans="1:13" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -5885,6 +5988,505 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44946</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D2" s="17">
+        <v>39.5</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>142200</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>284.40000000000003</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>8.532</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>20.604780000000005</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>142514.95877999999</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1">
+      <c r="A3" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10">
+        <f>C2</f>
+        <v>3600</v>
+      </c>
+      <c r="D3" s="34">
+        <v>41.5</v>
+      </c>
+      <c r="E3" s="11">
+        <f>C3*D3</f>
+        <v>149400</v>
+      </c>
+      <c r="F3" s="35">
+        <f>E3*0.002</f>
+        <v>298.8</v>
+      </c>
+      <c r="G3" s="34">
+        <f>E3*0.000068</f>
+        <v>10.1592</v>
+      </c>
+      <c r="H3" s="34">
+        <f>E3*0.00001</f>
+        <v>1.4940000000000002</v>
+      </c>
+      <c r="I3" s="34">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>21.731724000000003</v>
+      </c>
+      <c r="J3" s="34">
+        <f>E3-F3-G3-H3-I3</f>
+        <v>149067.815076</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1">
+      <c r="A4" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="12">
+        <f>(D3-D2)/D2</f>
+        <v>5.0632911392405063E-2</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="20">
+        <f>E3-E2</f>
+        <v>7200</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20">
+        <f>J3-J2</f>
+        <v>6552.8562960000127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
+      <c r="A5" s="50"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="47"/>
+      <c r="J5" s="53">
+        <f>J1+J4</f>
+        <v>6552.8562960000127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="13" customFormat="1">
+      <c r="A6" s="39">
+        <v>44946</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3600</v>
+      </c>
+      <c r="D6" s="17">
+        <v>39.5</v>
+      </c>
+      <c r="E6" s="18">
+        <f>C6*D6</f>
+        <v>142200</v>
+      </c>
+      <c r="F6" s="18">
+        <f>E6*0.002</f>
+        <v>284.40000000000003</v>
+      </c>
+      <c r="G6" s="18">
+        <f>E6*0.00006</f>
+        <v>8.532</v>
+      </c>
+      <c r="H6" s="18">
+        <f>E6*0.00001</f>
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="I6" s="18">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>20.604780000000005</v>
+      </c>
+      <c r="J6" s="18">
+        <f>E6+F6+I6+G6+H6</f>
+        <v>142514.95877999999</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="30"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A7" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="46">
+        <v>33.5</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>40200</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>80.400000000000006</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>2.4119999999999999</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>5.8249800000000018</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>40289.038979999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
+      <c r="A8" s="56"/>
+      <c r="B8" s="12">
+        <f>(D7-D6)/D6</f>
+        <v>-0.15189873417721519</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C6:C7)</f>
+        <v>4800</v>
+      </c>
+      <c r="D8" s="11">
+        <f>E8/C8</f>
+        <v>38</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
+        <v>182400</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>364.80000000000007</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>10.943999999999999</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>1.8240000000000003</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>26.429760000000009</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="0"/>
+        <v>182803.99776</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
+      <c r="A9" s="50"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="47"/>
+      <c r="J9" s="53"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF9A6BF-841A-4E49-8659-89A8DE11562A}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="68" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="68" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44946</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>2400</v>
+      </c>
+      <c r="D2" s="17">
+        <v>58.5</v>
+      </c>
+      <c r="E2" s="69">
+        <f>C2*D2</f>
+        <v>140400</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>280.8</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>8.4239999999999995</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.4040000000000001</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>20.343960000000003</v>
+      </c>
+      <c r="J2" s="69">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>140710.97196</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1">
+      <c r="A3" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>900</v>
+      </c>
+      <c r="D3" s="46">
+        <v>53</v>
+      </c>
+      <c r="E3" s="62">
+        <f>C3*D3</f>
+        <v>47700</v>
+      </c>
+      <c r="F3" s="20">
+        <f>E3*0.002</f>
+        <v>95.4</v>
+      </c>
+      <c r="G3" s="20">
+        <f>E3*0.00006</f>
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="H3" s="20">
+        <f>E3*0.00001</f>
+        <v>0.47700000000000004</v>
+      </c>
+      <c r="I3" s="20">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>6.9117300000000013</v>
+      </c>
+      <c r="J3" s="62">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>47805.650730000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="12">
+        <f>(D3-D2)/D2</f>
+        <v>-9.4017094017094016E-2</v>
+      </c>
+      <c r="C4" s="10">
+        <f>SUM(C2:C3)</f>
+        <v>3300</v>
+      </c>
+      <c r="D4" s="11">
+        <f>E4/C4</f>
+        <v>57</v>
+      </c>
+      <c r="E4" s="62">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>188100</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="0"/>
+        <v>376.20000000000005</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" si="0"/>
+        <v>11.286</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" si="0"/>
+        <v>1.8810000000000002</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" si="0"/>
+        <v>27.255690000000005</v>
+      </c>
+      <c r="J4" s="62">
+        <f t="shared" si="0"/>
+        <v>188516.62268999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1">
+      <c r="A5" s="56">
+        <v>44676</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>900</v>
+      </c>
+      <c r="D5" s="46">
+        <v>50</v>
+      </c>
+      <c r="E5" s="62">
+        <f>C5*D5</f>
+        <v>45000</v>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*0.002</f>
+        <v>90</v>
+      </c>
+      <c r="G5" s="20">
+        <f>E5*0.00006</f>
+        <v>2.7</v>
+      </c>
+      <c r="H5" s="20">
+        <f>E5*0.00001</f>
+        <v>0.45</v>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>6.5205000000000011</v>
+      </c>
+      <c r="J5" s="62">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>45099.670499999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1">
+      <c r="A6" s="56"/>
+      <c r="B6" s="12">
+        <f>(D5-D4)/D4</f>
+        <v>-0.12280701754385964</v>
+      </c>
+      <c r="C6" s="10">
+        <f>SUM(C4:C5)</f>
+        <v>4200</v>
+      </c>
+      <c r="D6" s="11">
+        <f>E6/C6</f>
+        <v>55.5</v>
+      </c>
+      <c r="E6" s="62">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>233100</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>466.20000000000005</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="1"/>
+        <v>13.986000000000001</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="1"/>
+        <v>2.3310000000000004</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>33.776190000000007</v>
+      </c>
+      <c r="J6" s="62">
+        <f t="shared" si="1"/>
+        <v>233616.29319</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5904,7 +6506,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="15" customFormat="1">
@@ -7429,7 +8031,7 @@
         <v>42720</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C47" s="16">
         <v>75000</v>
@@ -7541,7 +8143,7 @@
         <v>44351</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C50" s="16">
         <v>70000</v>
@@ -8058,7 +8660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8081,7 +8683,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -8501,7 +9103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8524,7 +9126,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -9012,7 +9614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -9035,7 +9637,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -10488,549 +11090,6 @@
       <c r="J40" s="20">
         <f>J39-J38</f>
         <v>4116.4531500000012</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>300</v>
-      </c>
-      <c r="D2" s="17">
-        <v>410</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="39">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>400</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" spans="1:13" s="13" customFormat="1">
-      <c r="A5" s="39">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>300</v>
-      </c>
-      <c r="D5" s="17">
-        <v>384</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="70"/>
-      <c r="B6" s="7">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="71">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="67">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>300</v>
-      </c>
-      <c r="D7" s="11">
-        <v>382</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>114600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>229.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.8760000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>16.605540000000001</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>114853.82754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="25">
-        <f>(D7-D6)/D6</f>
-        <v>-4.0201005025125629E-2</v>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="68">
-        <f>E8/C8</f>
-        <v>394</v>
-      </c>
-      <c r="E8" s="22">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>472800</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" si="2"/>
-        <v>945.6</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="2"/>
-        <v>28.368000000000002</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>4.7280000000000006</v>
-      </c>
-      <c r="I8" s="22">
-        <f t="shared" si="2"/>
-        <v>68.508720000000011</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="2"/>
-        <v>473847.20472000004</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>900</v>
-      </c>
-      <c r="D2" s="17">
-        <v>174.5</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>157050</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>314.10000000000002</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>9.423</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.5705000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>22.756545000000003</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>157397.85004500003</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="39">
-        <v>44616</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>160.5</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>48150</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>96.3</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>2.8890000000000002</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>0.48150000000000004</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>6.9769350000000001</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>48256.647435000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-8.0229226361031525E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>1200</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>171</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>205200</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>410.40000000000003</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>12.312000000000001</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0520000000000005</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>29.733480000000004</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>205654.49748000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="67">
-        <v>44616</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
-        <v>300</v>
-      </c>
-      <c r="D5" s="11">
-        <v>148.5</v>
-      </c>
-      <c r="E5" s="20">
-        <f>C5*D5</f>
-        <v>44550</v>
-      </c>
-      <c r="F5" s="20">
-        <f>E5*0.002</f>
-        <v>89.100000000000009</v>
-      </c>
-      <c r="G5" s="20">
-        <f>E5*0.00006</f>
-        <v>2.673</v>
-      </c>
-      <c r="H5" s="20">
-        <f>E5*0.00001</f>
-        <v>0.44550000000000006</v>
-      </c>
-      <c r="I5" s="20">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>6.4552950000000013</v>
-      </c>
-      <c r="J5" s="20">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>44648.673795000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="25">
-        <f>(D5-D4)/D4</f>
-        <v>-0.13157894736842105</v>
-      </c>
-      <c r="C6" s="22">
-        <f>SUM(C4:C5)</f>
-        <v>1500</v>
-      </c>
-      <c r="D6" s="68">
-        <f>E6/C6</f>
-        <v>166.5</v>
-      </c>
-      <c r="E6" s="22">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>249750</v>
-      </c>
-      <c r="F6" s="22">
-        <f t="shared" si="1"/>
-        <v>499.50000000000006</v>
-      </c>
-      <c r="G6" s="22">
-        <f t="shared" si="1"/>
-        <v>14.985000000000001</v>
-      </c>
-      <c r="H6" s="22">
-        <f t="shared" si="1"/>
-        <v>2.4975000000000005</v>
-      </c>
-      <c r="I6" s="22">
-        <f t="shared" si="1"/>
-        <v>36.188775000000007</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="1"/>
-        <v>250303.17127500003</v>
       </c>
     </row>
   </sheetData>
@@ -12797,6 +12856,549 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>300</v>
+      </c>
+      <c r="D2" s="17">
+        <v>410</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>123000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>246</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>7.38</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.2300000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>17.822700000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>123272.4327</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1">
+      <c r="A3" s="39">
+        <v>44469</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>400</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>120000</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>240</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.388000000000002</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>120265.788</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439025E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>600</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>405</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>243000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>14.58</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.210700000000003</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>243538.22070000001</v>
+      </c>
+      <c r="L4" s="25"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="1:13" s="13" customFormat="1">
+      <c r="A5" s="39">
+        <v>44579</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>300</v>
+      </c>
+      <c r="D5" s="17">
+        <v>384</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>115200</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>230.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>6.9119999999999999</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>16.69248</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>115455.15647999999</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="7">
+        <f>(D5-D4)/D4</f>
+        <v>-5.185185185185185E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM(C4:C5)</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="71">
+        <f>E6/C6</f>
+        <v>398</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>358200</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>716.4</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>21.492000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5820000000000007</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>51.903180000000006</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>358993.37718000001</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="67">
+        <v>44579</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>300</v>
+      </c>
+      <c r="D7" s="11">
+        <v>382</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>114600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>229.20000000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>6.8760000000000003</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>16.605540000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>114853.82754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="25">
+        <f>(D7-D6)/D6</f>
+        <v>-4.0201005025125629E-2</v>
+      </c>
+      <c r="C8" s="22">
+        <f>SUM(C6:C7)</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="68">
+        <f>E8/C8</f>
+        <v>394</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>472800</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="2"/>
+        <v>945.6</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="2"/>
+        <v>28.368000000000002</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>4.7280000000000006</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="2"/>
+        <v>68.508720000000011</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="2"/>
+        <v>473847.20472000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>900</v>
+      </c>
+      <c r="D2" s="17">
+        <v>174.5</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>157050</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>314.10000000000002</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>9.423</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.5705000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>22.756545000000003</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>157397.85004500003</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="39">
+        <v>44616</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>160.5</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>48150</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>96.3</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>2.8890000000000002</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>0.48150000000000004</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>6.9769350000000001</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>48256.647435000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-8.0229226361031525E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>1200</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>171</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>205200</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>410.40000000000003</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>12.312000000000001</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0520000000000005</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>29.733480000000004</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>205654.49748000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="67">
+        <v>44616</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>300</v>
+      </c>
+      <c r="D5" s="11">
+        <v>148.5</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5*D5</f>
+        <v>44550</v>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*0.002</f>
+        <v>89.100000000000009</v>
+      </c>
+      <c r="G5" s="20">
+        <f>E5*0.00006</f>
+        <v>2.673</v>
+      </c>
+      <c r="H5" s="20">
+        <f>E5*0.00001</f>
+        <v>0.44550000000000006</v>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>6.4552950000000013</v>
+      </c>
+      <c r="J5" s="20">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>44648.673795000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="25">
+        <f>(D5-D4)/D4</f>
+        <v>-0.13157894736842105</v>
+      </c>
+      <c r="C6" s="22">
+        <f>SUM(C4:C5)</f>
+        <v>1500</v>
+      </c>
+      <c r="D6" s="68">
+        <f>E6/C6</f>
+        <v>166.5</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>249750</v>
+      </c>
+      <c r="F6" s="22">
+        <f t="shared" si="1"/>
+        <v>499.50000000000006</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" si="1"/>
+        <v>14.985000000000001</v>
+      </c>
+      <c r="H6" s="22">
+        <f t="shared" si="1"/>
+        <v>2.4975000000000005</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" si="1"/>
+        <v>36.188775000000007</v>
+      </c>
+      <c r="J6" s="22">
+        <f t="shared" si="1"/>
+        <v>250303.17127500003</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12819,7 +13421,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -13337,277 +13939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44946</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>3600</v>
-      </c>
-      <c r="D2" s="17">
-        <v>39.5</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>142200</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>284.40000000000003</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>8.532</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.4220000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>20.604780000000005</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>142514.95877999999</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="56">
-        <v>44277</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <f>C2</f>
-        <v>3600</v>
-      </c>
-      <c r="D3" s="34">
-        <v>41.5</v>
-      </c>
-      <c r="E3" s="11">
-        <f>C3*D3</f>
-        <v>149400</v>
-      </c>
-      <c r="F3" s="35">
-        <f>E3*0.002</f>
-        <v>298.8</v>
-      </c>
-      <c r="G3" s="34">
-        <f>E3*0.000068</f>
-        <v>10.1592</v>
-      </c>
-      <c r="H3" s="34">
-        <f>E3*0.00001</f>
-        <v>1.4940000000000002</v>
-      </c>
-      <c r="I3" s="34">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>21.731724000000003</v>
-      </c>
-      <c r="J3" s="34">
-        <f>E3-F3-G3-H3-I3</f>
-        <v>149067.815076</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="12">
-        <f>(D3-D2)/D2</f>
-        <v>5.0632911392405063E-2</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="20">
-        <f>E3-E2</f>
-        <v>7200</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20">
-        <f>J3-J2</f>
-        <v>6552.8562960000127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
-      <c r="A5" s="50"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="47"/>
-      <c r="J5" s="53">
-        <f>J1+J4</f>
-        <v>6552.8562960000127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="13" customFormat="1">
-      <c r="A6" s="39">
-        <v>44946</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16">
-        <v>3600</v>
-      </c>
-      <c r="D6" s="17">
-        <v>39.5</v>
-      </c>
-      <c r="E6" s="18">
-        <f>C6*D6</f>
-        <v>142200</v>
-      </c>
-      <c r="F6" s="18">
-        <f>E6*0.002</f>
-        <v>284.40000000000003</v>
-      </c>
-      <c r="G6" s="18">
-        <f>E6*0.00006</f>
-        <v>8.532</v>
-      </c>
-      <c r="H6" s="18">
-        <f>E6*0.00001</f>
-        <v>1.4220000000000002</v>
-      </c>
-      <c r="I6" s="18">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>20.604780000000005</v>
-      </c>
-      <c r="J6" s="18">
-        <f>E6+F6+I6+G6+H6</f>
-        <v>142514.95877999999</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="30"/>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A7" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>2400</v>
-      </c>
-      <c r="D7" s="46">
-        <v>38.25</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>91800</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>183.6</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>5.508</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>13.301820000000003</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>92003.327820000006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A8" s="56"/>
-      <c r="B8" s="12">
-        <f>(D7-D6)/D6</f>
-        <v>-3.1645569620253167E-2</v>
-      </c>
-      <c r="C8" s="10">
-        <f>SUM(C6:C7)</f>
-        <v>6000</v>
-      </c>
-      <c r="D8" s="11">
-        <f>E8/C8</f>
-        <v>39</v>
-      </c>
-      <c r="E8" s="10">
-        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
-        <v>234000</v>
-      </c>
-      <c r="F8" s="10">
-        <f t="shared" si="0"/>
-        <v>468</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" si="0"/>
-        <v>14.04</v>
-      </c>
-      <c r="H8" s="10">
-        <f t="shared" si="0"/>
-        <v>2.3400000000000003</v>
-      </c>
-      <c r="I8" s="10">
-        <f t="shared" si="0"/>
-        <v>33.906600000000012</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="0"/>
-        <v>234518.28659999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
-      <c r="A9" s="50"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="47"/>
-      <c r="J9" s="53"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13630,7 +13962,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -14027,7 +14359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -14050,7 +14382,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -15262,7 +15594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15285,7 +15617,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15503,7 +15835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15526,7 +15858,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15962,7 +16294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15985,7 +16317,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
@@ -16424,7 +16756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16450,7 +16782,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -16955,7 +17287,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="89" customWidth="1"/>
@@ -17503,327 +17835,307 @@
       <c r="N14" s="59"/>
       <c r="O14" s="59"/>
     </row>
-    <row r="15" spans="1:15" s="13" customFormat="1" ht="14.25">
-      <c r="A15" s="67">
-        <v>44473</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="10">
+    <row r="15" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A15" s="50">
+        <v>44462</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="51">
         <v>2500</v>
       </c>
-      <c r="D15" s="11">
-        <v>18</v>
-      </c>
-      <c r="E15" s="20">
-        <f>C15*D15</f>
-        <v>45000</v>
-      </c>
-      <c r="F15" s="20">
-        <f>E15*0.002</f>
-        <v>90</v>
-      </c>
-      <c r="G15" s="20">
-        <f>E15*0.00006</f>
-        <v>2.7</v>
-      </c>
-      <c r="H15" s="20">
-        <f>E15*0.00001</f>
-        <v>0.45</v>
-      </c>
-      <c r="I15" s="20">
-        <f>(F15+G15+H15)*0.07</f>
-        <v>6.5205000000000011</v>
-      </c>
-      <c r="J15" s="20">
-        <f>E15+F15+I15+G15+H15</f>
-        <v>45099.670499999993</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" spans="1:15" s="63" customFormat="1" ht="21.75">
-      <c r="A16" s="56"/>
-      <c r="B16" s="76">
-        <f>(D15-D14)/D14</f>
-        <v>-0.51677852348993292</v>
-      </c>
-      <c r="C16" s="10">
-        <f>SUM(C14:C15)</f>
-        <v>15000</v>
-      </c>
-      <c r="D16" s="64">
-        <f>E16/C16</f>
-        <v>34.041666666666664</v>
-      </c>
-      <c r="E16" s="10">
-        <f t="shared" ref="E16:J16" si="4">SUM(E14:E15)</f>
-        <v>510625</v>
-      </c>
-      <c r="F16" s="10">
-        <f t="shared" si="4"/>
-        <v>1021.25</v>
-      </c>
-      <c r="G16" s="10">
-        <f t="shared" si="4"/>
-        <v>30.637500000000003</v>
-      </c>
-      <c r="H16" s="10">
-        <f t="shared" si="4"/>
-        <v>5.1062500000000002</v>
-      </c>
-      <c r="I16" s="10">
-        <f t="shared" si="4"/>
-        <v>73.989562500000005</v>
-      </c>
-      <c r="J16" s="10">
-        <f t="shared" si="4"/>
-        <v>511755.98331250006</v>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="62"/>
+      <c r="D15" s="52">
+        <v>33.25</v>
+      </c>
+      <c r="E15" s="51">
+        <v>83125</v>
+      </c>
+      <c r="F15" s="51">
+        <v>166.25</v>
+      </c>
+      <c r="G15" s="51">
+        <v>4.9874999999999998</v>
+      </c>
+      <c r="H15" s="51">
+        <v>0.83125000000000004</v>
+      </c>
+      <c r="I15" s="51">
+        <v>12.044812500000003</v>
+      </c>
+      <c r="J15" s="51">
+        <v>83309.113562500002</v>
+      </c>
+      <c r="K15" s="57"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="59"/>
+    </row>
+    <row r="16" spans="1:15" s="1" customFormat="1">
+      <c r="A16" s="49">
+        <v>44951</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D16" s="26">
+        <v>21.4</v>
+      </c>
+      <c r="E16" s="17">
+        <f>C16*D16</f>
+        <v>53500</v>
+      </c>
+      <c r="F16" s="27">
+        <f>E16*0.002</f>
+        <v>107</v>
+      </c>
+      <c r="G16" s="26">
+        <f>E16*0.000068</f>
+        <v>3.6379999999999999</v>
+      </c>
+      <c r="H16" s="26">
+        <f>E16*0.00001</f>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I16" s="26">
+        <f>(F16+G16+H16)*0.07</f>
+        <v>7.7821100000000012</v>
+      </c>
+      <c r="J16" s="26">
+        <f>E16-F16-G16-H16-I16</f>
+        <v>53381.044889999997</v>
+      </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1">
-      <c r="A17" s="50"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="59"/>
-    </row>
-    <row r="18" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A18" s="49">
-        <v>44543</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D18" s="41">
-        <v>29.5</v>
-      </c>
-      <c r="E18" s="18">
-        <f>C18*D18</f>
-        <v>73750</v>
-      </c>
-      <c r="F18" s="18">
-        <f>E18*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G18" s="18">
-        <f>E18*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H18" s="18">
-        <f>E18*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I18" s="18">
-        <f>(F18+G18+H18)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J18" s="18">
-        <f>E18+F18+I18+G18+H18</f>
-        <v>73913.348875000011</v>
+      <c r="A17" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18">
+        <f>E16-E15</f>
+        <v>-29625</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18">
+        <f>J16-J15</f>
+        <v>-29928.068672500005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A18" s="50"/>
+      <c r="B18" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="51">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="52">
+        <v>38.25</v>
+      </c>
+      <c r="E18" s="51">
+        <v>382500</v>
+      </c>
+      <c r="F18" s="51">
+        <v>765</v>
+      </c>
+      <c r="G18" s="51">
+        <v>22.950000000000003</v>
+      </c>
+      <c r="H18" s="51">
+        <v>3.8250000000000002</v>
+      </c>
+      <c r="I18" s="51">
+        <v>55.424250000000001</v>
+      </c>
+      <c r="J18" s="51">
+        <v>383347.19925000006</v>
       </c>
       <c r="K18" s="57"/>
       <c r="L18" s="58"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-    </row>
-    <row r="19" spans="1:15" s="1" customFormat="1">
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
+    </row>
+    <row r="19" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A19" s="49">
-        <v>44923</v>
+        <v>44452</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D19" s="41">
+        <v>35.25</v>
+      </c>
+      <c r="E19" s="18">
+        <f>C19*D19</f>
+        <v>88125</v>
+      </c>
+      <c r="F19" s="18">
+        <f>E19*0.002</f>
+        <v>176.25</v>
+      </c>
+      <c r="G19" s="18">
+        <f>E19*0.00006</f>
+        <v>5.2875000000000005</v>
+      </c>
+      <c r="H19" s="18">
+        <f>E19*0.00001</f>
+        <v>0.88125000000000009</v>
+      </c>
+      <c r="I19" s="18">
+        <f>(F19+G19+H19)*0.07</f>
+        <v>12.7693125</v>
+      </c>
+      <c r="J19" s="18">
+        <f>E19+F19+I19+G19+H19</f>
+        <v>88320.188062500005</v>
+      </c>
+      <c r="K19" s="57"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+    </row>
+    <row r="20" spans="1:15" s="1" customFormat="1">
+      <c r="A20" s="49">
+        <v>44951</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="16">
-        <f>C18</f>
+      <c r="C20" s="16">
         <v>2500</v>
       </c>
-      <c r="D19" s="26">
-        <v>20.3</v>
-      </c>
-      <c r="E19" s="17">
-        <f>C19*D19</f>
-        <v>50750</v>
-      </c>
-      <c r="F19" s="27">
-        <f>E19*0.002</f>
-        <v>101.5</v>
-      </c>
-      <c r="G19" s="26">
-        <f>E19*0.000068</f>
-        <v>3.4510000000000001</v>
-      </c>
-      <c r="H19" s="26">
-        <f>E19*0.00001</f>
-        <v>0.50750000000000006</v>
-      </c>
-      <c r="I19" s="26">
-        <f>(F19+G19+H19)*0.07</f>
-        <v>7.3820949999999996</v>
-      </c>
-      <c r="J19" s="26">
-        <f>E19-F19-G19-H19-I19</f>
-        <v>50637.159404999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="1" customFormat="1">
-      <c r="A20" s="49" t="s">
+      <c r="D20" s="26">
+        <v>21.9</v>
+      </c>
+      <c r="E20" s="17">
+        <f>C20*D20</f>
+        <v>54750</v>
+      </c>
+      <c r="F20" s="27">
+        <f>E20*0.002</f>
+        <v>109.5</v>
+      </c>
+      <c r="G20" s="26">
+        <f>E20*0.000068</f>
+        <v>3.7229999999999999</v>
+      </c>
+      <c r="H20" s="26">
+        <f>E20*0.00001</f>
+        <v>0.5475000000000001</v>
+      </c>
+      <c r="I20" s="26">
+        <f>(F20+G20+H20)*0.07</f>
+        <v>7.9639350000000002</v>
+      </c>
+      <c r="J20" s="26">
+        <f>E20-F20-G20-H20-I20</f>
+        <v>54628.265565000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="1" customFormat="1">
+      <c r="A21" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18">
-        <f>E19-E18</f>
-        <v>-23000</v>
-      </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18">
-        <f>J19-J18</f>
-        <v>-23276.189470000012</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" ht="14.25">
-      <c r="A21" s="54"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-    </row>
-    <row r="22" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="B21" s="15"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18">
+        <f>E20-E19</f>
+        <v>-33375</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18">
+        <f>J20-J19</f>
+        <v>-33691.922497500003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="1" customFormat="1" ht="14.25">
       <c r="A22" s="49">
-        <v>44550</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D22" s="41">
-        <v>29.5</v>
-      </c>
-      <c r="E22" s="18">
-        <f>C22*D22</f>
-        <v>73750</v>
-      </c>
-      <c r="F22" s="18">
-        <f>E22*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G22" s="18">
-        <f>E22*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H22" s="18">
-        <f>E22*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I22" s="18">
-        <f>(F22+G22+H22)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J22" s="18">
-        <f>E22+F22+I22+G22+H22</f>
-        <v>73913.348875000011</v>
+        <v>44951</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="51">
+        <v>7500</v>
+      </c>
+      <c r="D22" s="52">
+        <v>39.25</v>
+      </c>
+      <c r="E22" s="51">
+        <v>294375</v>
+      </c>
+      <c r="F22" s="51">
+        <v>588.75</v>
+      </c>
+      <c r="G22" s="51">
+        <v>17.662500000000001</v>
+      </c>
+      <c r="H22" s="51">
+        <v>2.9437500000000001</v>
+      </c>
+      <c r="I22" s="51">
+        <v>42.654937500000003</v>
+      </c>
+      <c r="J22" s="51">
+        <v>295027.01118750003</v>
       </c>
       <c r="K22" s="57"/>
       <c r="L22" s="58"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
     </row>
     <row r="23" spans="1:15" s="1" customFormat="1">
-      <c r="A23" s="49">
-        <v>44922</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="16">
-        <f>C22</f>
-        <v>2500</v>
-      </c>
-      <c r="D23" s="26">
-        <v>19.7</v>
-      </c>
-      <c r="E23" s="17">
-        <f>C23*D23</f>
-        <v>49250</v>
-      </c>
-      <c r="F23" s="27">
-        <f>E23*0.002</f>
-        <v>98.5</v>
-      </c>
-      <c r="G23" s="26">
-        <f>E23*0.000068</f>
-        <v>3.3489999999999998</v>
-      </c>
-      <c r="H23" s="26">
-        <f>E23*0.00001</f>
-        <v>0.49250000000000005</v>
-      </c>
-      <c r="I23" s="26">
-        <f>(F23+G23+H23)*0.07</f>
-        <v>7.1639050000000015</v>
-      </c>
-      <c r="J23" s="26">
-        <f>E23-F23-G23-H23-I23</f>
-        <v>49140.494594999996</v>
-      </c>
+      <c r="A23" s="50"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
     </row>
     <row r="24" spans="1:15" s="1" customFormat="1">
-      <c r="A24" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18">
-        <f>E23-E22</f>
-        <v>-24500</v>
-      </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18">
-        <f>J23-J22</f>
-        <v>-24772.854280000014</v>
-      </c>
+      <c r="A24" s="50"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="59"/>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1">
       <c r="A25" s="50"/>
@@ -17844,7 +18156,7 @@
     </row>
     <row r="26" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A26" s="49">
-        <v>44624</v>
+        <v>44543</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>1</v>
@@ -17853,31 +18165,31 @@
         <v>2500</v>
       </c>
       <c r="D26" s="41">
-        <v>25.75</v>
+        <v>29.5</v>
       </c>
       <c r="E26" s="18">
         <f>C26*D26</f>
-        <v>64375</v>
+        <v>73750</v>
       </c>
       <c r="F26" s="18">
         <f>E26*0.002</f>
-        <v>128.75</v>
+        <v>147.5</v>
       </c>
       <c r="G26" s="18">
         <f>E26*0.00006</f>
-        <v>3.8625000000000003</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="H26" s="18">
         <f>E26*0.00001</f>
-        <v>0.64375000000000004</v>
+        <v>0.73750000000000004</v>
       </c>
       <c r="I26" s="18">
         <f>(F26+G26+H26)*0.07</f>
-        <v>9.3279375000000027</v>
+        <v>10.686375000000002</v>
       </c>
       <c r="J26" s="18">
         <f>E26+F26+I26+G26+H26</f>
-        <v>64517.584187500004</v>
+        <v>73913.348875000011</v>
       </c>
       <c r="K26" s="57"/>
       <c r="L26" s="58"/>
@@ -17887,7 +18199,7 @@
     </row>
     <row r="27" spans="1:15" s="1" customFormat="1">
       <c r="A27" s="49">
-        <v>44866</v>
+        <v>44923</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>3</v>
@@ -17897,31 +18209,31 @@
         <v>2500</v>
       </c>
       <c r="D27" s="26">
-        <v>19.2</v>
+        <v>20.3</v>
       </c>
       <c r="E27" s="17">
         <f>C27*D27</f>
-        <v>48000</v>
+        <v>50750</v>
       </c>
       <c r="F27" s="27">
         <f>E27*0.002</f>
-        <v>96</v>
+        <v>101.5</v>
       </c>
       <c r="G27" s="26">
         <f>E27*0.000068</f>
-        <v>3.2639999999999998</v>
+        <v>3.4510000000000001</v>
       </c>
       <c r="H27" s="26">
         <f>E27*0.00001</f>
-        <v>0.48000000000000004</v>
+        <v>0.50750000000000006</v>
       </c>
       <c r="I27" s="26">
         <f>(F27+G27+H27)*0.07</f>
-        <v>6.9820800000000007</v>
+        <v>7.3820949999999996</v>
       </c>
       <c r="J27" s="26">
         <f>E27-F27-G27-H27-I27</f>
-        <v>47893.273919999992</v>
+        <v>50637.159404999999</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="1" customFormat="1">
@@ -17933,7 +18245,7 @@
       <c r="D28" s="17"/>
       <c r="E28" s="18">
         <f>E27-E26</f>
-        <v>-16375</v>
+        <v>-23000</v>
       </c>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
@@ -17941,1254 +18253,1492 @@
       <c r="I28" s="18"/>
       <c r="J28" s="18">
         <f>J27-J26</f>
-        <v>-16624.310267500012</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1">
-      <c r="A29" s="56"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1">
-      <c r="A30" s="56">
-        <v>44627</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="10">
+        <v>-23276.189470000012</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A29" s="54"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+    </row>
+    <row r="30" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A30" s="49">
+        <v>44550</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="16">
         <v>2500</v>
       </c>
-      <c r="D30" s="46">
-        <v>25.75</v>
-      </c>
-      <c r="E30" s="20">
+      <c r="D30" s="41">
+        <v>29.5</v>
+      </c>
+      <c r="E30" s="18">
         <f>C30*D30</f>
-        <v>64375</v>
-      </c>
-      <c r="F30" s="20">
+        <v>73750</v>
+      </c>
+      <c r="F30" s="18">
         <f>E30*0.002</f>
-        <v>128.75</v>
-      </c>
-      <c r="G30" s="20">
+        <v>147.5</v>
+      </c>
+      <c r="G30" s="18">
         <f>E30*0.00006</f>
-        <v>3.8625000000000003</v>
-      </c>
-      <c r="H30" s="20">
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H30" s="18">
         <f>E30*0.00001</f>
-        <v>0.64375000000000004</v>
-      </c>
-      <c r="I30" s="20">
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I30" s="18">
         <f>(F30+G30+H30)*0.07</f>
-        <v>9.3279375000000027</v>
-      </c>
-      <c r="J30" s="20">
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J30" s="18">
         <f>E30+F30+I30+G30+H30</f>
-        <v>64517.584187500004</v>
-      </c>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K30" s="57"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
     </row>
     <row r="31" spans="1:15" s="1" customFormat="1">
-      <c r="A31" s="56">
-        <v>44634</v>
-      </c>
-      <c r="B31" s="13" t="s">
+      <c r="A31" s="49">
+        <v>44922</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="16">
         <f>C30</f>
         <v>2500</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="26">
+        <v>19.7</v>
+      </c>
+      <c r="E31" s="17">
+        <f>C31*D31</f>
+        <v>49250</v>
+      </c>
+      <c r="F31" s="27">
+        <f>E31*0.002</f>
+        <v>98.5</v>
+      </c>
+      <c r="G31" s="26">
+        <f>E31*0.000068</f>
+        <v>3.3489999999999998</v>
+      </c>
+      <c r="H31" s="26">
+        <f>E31*0.00001</f>
+        <v>0.49250000000000005</v>
+      </c>
+      <c r="I31" s="26">
+        <f>(F31+G31+H31)*0.07</f>
+        <v>7.1639050000000015</v>
+      </c>
+      <c r="J31" s="26">
+        <f>E31-F31-G31-H31-I31</f>
+        <v>49140.494594999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1">
+      <c r="A32" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18">
+        <f>E31-E30</f>
+        <v>-24500</v>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18">
+        <f>J31-J30</f>
+        <v>-24772.854280000014</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="1" customFormat="1">
+      <c r="A33" s="50"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="59"/>
+    </row>
+    <row r="34" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A34" s="49">
+        <v>44624</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D34" s="41">
+        <v>25.75</v>
+      </c>
+      <c r="E34" s="18">
+        <f>C34*D34</f>
+        <v>64375</v>
+      </c>
+      <c r="F34" s="18">
+        <f>E34*0.002</f>
+        <v>128.75</v>
+      </c>
+      <c r="G34" s="18">
+        <f>E34*0.00006</f>
+        <v>3.8625000000000003</v>
+      </c>
+      <c r="H34" s="18">
+        <f>E34*0.00001</f>
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="I34" s="18">
+        <f>(F34+G34+H34)*0.07</f>
+        <v>9.3279375000000027</v>
+      </c>
+      <c r="J34" s="18">
+        <f>E34+F34+I34+G34+H34</f>
+        <v>64517.584187500004</v>
+      </c>
+      <c r="K34" s="57"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+    </row>
+    <row r="35" spans="1:15" s="1" customFormat="1">
+      <c r="A35" s="49">
+        <v>44866</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="16">
+        <f>C34</f>
+        <v>2500</v>
+      </c>
+      <c r="D35" s="26">
+        <v>19.2</v>
+      </c>
+      <c r="E35" s="17">
+        <f>C35*D35</f>
+        <v>48000</v>
+      </c>
+      <c r="F35" s="27">
+        <f>E35*0.002</f>
+        <v>96</v>
+      </c>
+      <c r="G35" s="26">
+        <f>E35*0.000068</f>
+        <v>3.2639999999999998</v>
+      </c>
+      <c r="H35" s="26">
+        <f>E35*0.00001</f>
+        <v>0.48000000000000004</v>
+      </c>
+      <c r="I35" s="26">
+        <f>(F35+G35+H35)*0.07</f>
+        <v>6.9820800000000007</v>
+      </c>
+      <c r="J35" s="26">
+        <f>E35-F35-G35-H35-I35</f>
+        <v>47893.273919999992</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="1" customFormat="1">
+      <c r="A36" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="18">
+        <f>E35-E34</f>
+        <v>-16375</v>
+      </c>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18">
+        <f>J35-J34</f>
+        <v>-16624.310267500012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" s="1" customFormat="1">
+      <c r="A37" s="56"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="1:15" s="1" customFormat="1">
+      <c r="A38" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D38" s="46">
+        <v>25.75</v>
+      </c>
+      <c r="E38" s="20">
+        <f>C38*D38</f>
+        <v>64375</v>
+      </c>
+      <c r="F38" s="20">
+        <f>E38*0.002</f>
+        <v>128.75</v>
+      </c>
+      <c r="G38" s="20">
+        <f>E38*0.00006</f>
+        <v>3.8625000000000003</v>
+      </c>
+      <c r="H38" s="20">
+        <f>E38*0.00001</f>
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="I38" s="20">
+        <f>(F38+G38+H38)*0.07</f>
+        <v>9.3279375000000027</v>
+      </c>
+      <c r="J38" s="20">
+        <f>E38+F38+I38+G38+H38</f>
+        <v>64517.584187500004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" s="1" customFormat="1">
+      <c r="A39" s="56">
+        <v>44634</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="10">
+        <f>C38</f>
+        <v>2500</v>
+      </c>
+      <c r="D39" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="E31" s="11">
-        <f>C31*D31</f>
+      <c r="E39" s="11">
+        <f>C39*D39</f>
         <v>50250</v>
       </c>
-      <c r="F31" s="35">
-        <f>E31*0.002</f>
+      <c r="F39" s="35">
+        <f>E39*0.002</f>
         <v>100.5</v>
       </c>
-      <c r="G31" s="34">
-        <f>E31*0.000068</f>
+      <c r="G39" s="34">
+        <f>E39*0.000068</f>
         <v>3.4169999999999998</v>
       </c>
-      <c r="H31" s="34">
-        <f>E31*0.00001</f>
+      <c r="H39" s="34">
+        <f>E39*0.00001</f>
         <v>0.50250000000000006</v>
       </c>
-      <c r="I31" s="34">
-        <f>(F31+G31+H31)*0.07</f>
+      <c r="I39" s="34">
+        <f>(F39+G39+H39)*0.07</f>
         <v>7.3093650000000006</v>
       </c>
-      <c r="J31" s="34">
-        <f>E31-F31-G31-H31-I31</f>
+      <c r="J39" s="34">
+        <f>E39-F39-G39-H39-I39</f>
         <v>50138.271134999995</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="1" customFormat="1">
-      <c r="A32" s="56" t="s">
+    <row r="40" spans="1:15" s="1" customFormat="1">
+      <c r="A40" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="20">
-        <f>E31-E30</f>
+      <c r="B40" s="13"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="20">
+        <f>E39-E38</f>
         <v>-14125</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20">
-        <f>J31-J30</f>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20">
+        <f>J39-J38</f>
         <v>-14379.313052500009</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="1" customFormat="1">
-      <c r="A33" s="56">
+    <row r="41" spans="1:15" s="1" customFormat="1">
+      <c r="A41" s="56">
         <v>44627</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="10">
+      <c r="B41" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="10">
         <v>2500</v>
       </c>
-      <c r="D33" s="46">
+      <c r="D41" s="46">
         <v>19</v>
       </c>
-      <c r="E33" s="20">
-        <f>C33*D33</f>
+      <c r="E41" s="20">
+        <f>C41*D41</f>
         <v>47500</v>
       </c>
-      <c r="F33" s="20">
-        <f>E33*0.002</f>
+      <c r="F41" s="20">
+        <f>E41*0.002</f>
         <v>95</v>
       </c>
-      <c r="G33" s="20">
-        <f>E33*0.00006</f>
+      <c r="G41" s="20">
+        <f>E41*0.00006</f>
         <v>2.85</v>
       </c>
-      <c r="H33" s="20">
-        <f>E33*0.00001</f>
+      <c r="H41" s="20">
+        <f>E41*0.00001</f>
         <v>0.47500000000000003</v>
       </c>
-      <c r="I33" s="20">
-        <f>(F33+G33+H33)*0.07</f>
+      <c r="I41" s="20">
+        <f>(F41+G41+H41)*0.07</f>
         <v>6.8827499999999997</v>
       </c>
-      <c r="J33" s="20">
-        <f>E33+F33+I33+G33+H33</f>
+      <c r="J41" s="20">
+        <f>E41+F41+I41+G41+H41</f>
         <v>47605.207749999994</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1">
-      <c r="A34" s="56">
+    <row r="42" spans="1:15" s="1" customFormat="1">
+      <c r="A42" s="56">
         <v>44634</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B42" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="10">
-        <f>C33</f>
+      <c r="C42" s="10">
+        <f>C41</f>
         <v>2500</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D42" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="E34" s="11">
-        <f>C34*D34</f>
+      <c r="E42" s="11">
+        <f>C42*D42</f>
         <v>50250</v>
       </c>
-      <c r="F34" s="35">
-        <f>E34*0.002</f>
+      <c r="F42" s="35">
+        <f>E42*0.002</f>
         <v>100.5</v>
       </c>
-      <c r="G34" s="34">
-        <f>E34*0.000068</f>
+      <c r="G42" s="34">
+        <f>E42*0.000068</f>
         <v>3.4169999999999998</v>
       </c>
-      <c r="H34" s="34">
-        <f>E34*0.00001</f>
+      <c r="H42" s="34">
+        <f>E42*0.00001</f>
         <v>0.50250000000000006</v>
       </c>
-      <c r="I34" s="34">
-        <f>(F34+G34+H34)*0.07</f>
+      <c r="I42" s="34">
+        <f>(F42+G42+H42)*0.07</f>
         <v>7.3093650000000006</v>
       </c>
-      <c r="J34" s="34">
-        <f>E34-F34-G34-H34-I34</f>
+      <c r="J42" s="34">
+        <f>E42-F42-G42-H42-I42</f>
         <v>50138.271134999995</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="1" customFormat="1">
-      <c r="A35" s="56" t="s">
+    <row r="43" spans="1:15" s="1" customFormat="1">
+      <c r="A43" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="12">
-        <f>(D34-D33)/D33</f>
+      <c r="B43" s="12">
+        <f>(D42-D41)/D41</f>
         <v>5.7894736842105339E-2</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="20">
-        <f>E34-E33</f>
+      <c r="C43" s="10"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="20">
+        <f>E42-E41</f>
         <v>2750</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20">
-        <f>J34-J33</f>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20">
+        <f>J42-J41</f>
         <v>2533.0633850000013</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="1" customFormat="1" ht="12">
-      <c r="A36" s="50"/>
-      <c r="D36" s="47"/>
-      <c r="J36" s="53"/>
-    </row>
-    <row r="37" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A37" s="56">
+    <row r="44" spans="1:15" s="1" customFormat="1" ht="12">
+      <c r="A44" s="50"/>
+      <c r="D44" s="47"/>
+      <c r="J44" s="53"/>
+    </row>
+    <row r="45" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A45" s="56">
         <v>44624</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="16">
+      <c r="B45" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="16">
         <v>2500</v>
       </c>
-      <c r="D37" s="46">
+      <c r="D45" s="46">
         <v>25.75</v>
       </c>
-      <c r="E37" s="20">
-        <f>C37*D37</f>
+      <c r="E45" s="20">
+        <f>C45*D45</f>
         <v>64375</v>
       </c>
-      <c r="F37" s="20">
-        <f>E37*0.002</f>
+      <c r="F45" s="20">
+        <f>E45*0.002</f>
         <v>128.75</v>
       </c>
-      <c r="G37" s="20">
-        <f>E37*0.00006</f>
+      <c r="G45" s="20">
+        <f>E45*0.00006</f>
         <v>3.8625000000000003</v>
       </c>
-      <c r="H37" s="20">
-        <f>E37*0.00001</f>
+      <c r="H45" s="20">
+        <f>E45*0.00001</f>
         <v>0.64375000000000004</v>
       </c>
-      <c r="I37" s="20">
-        <f>(F37+G37+H37)*0.07</f>
+      <c r="I45" s="20">
+        <f>(F45+G45+H45)*0.07</f>
         <v>9.3279375000000027</v>
       </c>
-      <c r="J37" s="20">
-        <f>E37+F37+I37+G37+H37</f>
+      <c r="J45" s="20">
+        <f>E45+F45+I45+G45+H45</f>
         <v>64517.584187500004</v>
       </c>
-      <c r="K37" s="57"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="58"/>
-      <c r="N37" s="58"/>
-      <c r="O37" s="58"/>
-    </row>
-    <row r="38" spans="1:15" s="13" customFormat="1">
-      <c r="A38" s="56" t="e">
+      <c r="K45" s="57"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+    </row>
+    <row r="46" spans="1:15" s="13" customFormat="1">
+      <c r="A46" s="56" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="10">
-        <f>C37</f>
+      <c r="C46" s="10">
+        <f>C45</f>
         <v>2500</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D46" s="26">
         <v>29.5</v>
       </c>
-      <c r="E38" s="11">
-        <f>C38*D38</f>
+      <c r="E46" s="11">
+        <f>C46*D46</f>
         <v>73750</v>
       </c>
-      <c r="F38" s="35">
-        <f>E38*0.002</f>
+      <c r="F46" s="35">
+        <f>E46*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G38" s="34">
-        <f>E38*0.000068</f>
+      <c r="G46" s="34">
+        <f>E46*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H38" s="34">
-        <f>E38*0.00001</f>
+      <c r="H46" s="34">
+        <f>E46*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I38" s="34">
-        <f>(F38+G38+H38)*0.07</f>
+      <c r="I46" s="34">
+        <f>(F46+G46+H46)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J38" s="34">
-        <f>E38-F38-G38-H38-I38</f>
+      <c r="J46" s="34">
+        <f>E46-F46-G46-H46-I46</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K38" s="10">
-        <f>C38</f>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A39" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="25">
-        <f>(D38-D37)/D37</f>
-        <v>0.14563106796116504</v>
-      </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="20">
-        <f>E38-E37</f>
-        <v>9375</v>
-      </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20">
-        <f>J38-J37</f>
-        <v>9068.4356374999916</v>
-      </c>
-      <c r="K39" s="20">
-        <f>J39</f>
-        <v>9068.4356374999916</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A40" s="49">
-        <v>44550</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D40" s="46">
-        <v>29.5</v>
-      </c>
-      <c r="E40" s="20">
-        <f>C40*D40</f>
-        <v>73750</v>
-      </c>
-      <c r="F40" s="20">
-        <f>E40*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G40" s="20">
-        <f>E40*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H40" s="20">
-        <f>E40*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I40" s="20">
-        <f>(F40+G40+H40)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J40" s="20">
-        <f>E40+F40+I40+G40+H40</f>
-        <v>73913.348875000011</v>
-      </c>
-      <c r="K40" s="57"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
-    </row>
-    <row r="41" spans="1:15" s="13" customFormat="1">
-      <c r="A41" s="56" t="e">
-        <f>A38</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="10">
-        <f>C40</f>
-        <v>2500</v>
-      </c>
-      <c r="D41" s="34">
-        <f>D38</f>
-        <v>29.5</v>
-      </c>
-      <c r="E41" s="11">
-        <f>C41*D41</f>
-        <v>73750</v>
-      </c>
-      <c r="F41" s="35">
-        <f>E41*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G41" s="34">
-        <f>E41*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H41" s="34">
-        <f>E41*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I41" s="34">
-        <f>(F41+G41+H41)*0.07</f>
-        <v>10.727675000000001</v>
-      </c>
-      <c r="J41" s="34">
-        <f>E41-F41-G41-H41-I41</f>
-        <v>73586.019824999996</v>
-      </c>
-      <c r="K41" s="10">
-        <f>K38+C41</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A42" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="25">
-        <f>(D41-D40)/D40</f>
-        <v>0</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="20">
-        <f>E41-E40</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20">
-        <f>J41-J40</f>
-        <v>-327.32905000001483</v>
-      </c>
-      <c r="K42" s="20">
-        <f>K39+J42</f>
-        <v>8741.1065874999767</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A43" s="56">
-        <v>44543</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D43" s="46">
-        <v>29.5</v>
-      </c>
-      <c r="E43" s="20">
-        <f>C43*D43</f>
-        <v>73750</v>
-      </c>
-      <c r="F43" s="20">
-        <f>E43*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G43" s="20">
-        <f>E43*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H43" s="20">
-        <f>E43*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I43" s="20">
-        <f>(F43+G43+H43)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J43" s="20">
-        <f>E43+F43+I43+G43+H43</f>
-        <v>73913.348875000011</v>
-      </c>
-      <c r="K43" s="57"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="58"/>
-      <c r="N43" s="58"/>
-      <c r="O43" s="58"/>
-    </row>
-    <row r="44" spans="1:15" s="13" customFormat="1">
-      <c r="A44" s="56" t="e">
-        <f>A41</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="10">
-        <f>C43</f>
-        <v>2500</v>
-      </c>
-      <c r="D44" s="34">
-        <f>D41</f>
-        <v>29.5</v>
-      </c>
-      <c r="E44" s="11">
-        <f>C44*D44</f>
-        <v>73750</v>
-      </c>
-      <c r="F44" s="35">
-        <f>E44*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G44" s="34">
-        <f>E44*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H44" s="34">
-        <f>E44*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I44" s="34">
-        <f>(F44+G44+H44)*0.07</f>
-        <v>10.727675000000001</v>
-      </c>
-      <c r="J44" s="34">
-        <f>E44-F44-G44-H44-I44</f>
-        <v>73586.019824999996</v>
-      </c>
-      <c r="K44" s="10">
-        <f>K41+C44</f>
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A45" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="25">
-        <f>(D44-D43)/D43</f>
-        <v>0</v>
-      </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="20">
-        <f>E44-E43</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20">
-        <f>J44-J43</f>
-        <v>-327.32905000001483</v>
-      </c>
-      <c r="K45" s="20">
-        <f>K42+J45</f>
-        <v>8413.7775374999619</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A46" s="56">
-        <v>44496</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D46" s="46">
-        <v>32.75</v>
-      </c>
-      <c r="E46" s="20">
-        <f>C46*D46</f>
-        <v>81875</v>
-      </c>
-      <c r="F46" s="20">
-        <f>E46*0.002</f>
-        <v>163.75</v>
-      </c>
-      <c r="G46" s="20">
-        <f>E46*0.00006</f>
-        <v>4.9125000000000005</v>
-      </c>
-      <c r="H46" s="20">
-        <f>E46*0.00001</f>
-        <v>0.81875000000000009</v>
-      </c>
-      <c r="I46" s="20">
-        <f>(F46+G46+H46)*0.07</f>
-        <v>11.863687500000001</v>
-      </c>
-      <c r="J46" s="20">
-        <f>E46+F46+I46+G46+H46</f>
-        <v>82056.344937500005</v>
-      </c>
-      <c r="K46" s="57"/>
-      <c r="L46" s="58"/>
-      <c r="M46" s="58"/>
-      <c r="N46" s="58"/>
-      <c r="O46" s="58"/>
-    </row>
-    <row r="47" spans="1:15" s="13" customFormat="1">
-      <c r="A47" s="56" t="e">
-        <f>A44</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="10">
+      <c r="K46" s="10">
         <f>C46</f>
         <v>2500</v>
       </c>
-      <c r="D47" s="34">
-        <f>D41</f>
+    </row>
+    <row r="47" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A47" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="25">
+        <f>(D46-D45)/D45</f>
+        <v>0.14563106796116504</v>
+      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="20">
+        <f>E46-E45</f>
+        <v>9375</v>
+      </c>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20">
+        <f>J46-J45</f>
+        <v>9068.4356374999916</v>
+      </c>
+      <c r="K47" s="20">
+        <f>J47</f>
+        <v>9068.4356374999916</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A48" s="49">
+        <v>44550</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D48" s="46">
         <v>29.5</v>
       </c>
-      <c r="E47" s="11">
-        <f>C47*D47</f>
+      <c r="E48" s="20">
+        <f>C48*D48</f>
         <v>73750</v>
       </c>
-      <c r="F47" s="35">
-        <f>E47*0.002</f>
+      <c r="F48" s="20">
+        <f>E48*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G47" s="34">
-        <f>E47*0.000068</f>
+      <c r="G48" s="20">
+        <f>E48*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H48" s="20">
+        <f>E48*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I48" s="20">
+        <f>(F48+G48+H48)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J48" s="20">
+        <f>E48+F48+I48+G48+H48</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K48" s="57"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+    </row>
+    <row r="49" spans="1:15" s="13" customFormat="1">
+      <c r="A49" s="56" t="e">
+        <f>A46</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="10">
+        <f>C48</f>
+        <v>2500</v>
+      </c>
+      <c r="D49" s="34">
+        <f>D46</f>
+        <v>29.5</v>
+      </c>
+      <c r="E49" s="11">
+        <f>C49*D49</f>
+        <v>73750</v>
+      </c>
+      <c r="F49" s="35">
+        <f>E49*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G49" s="34">
+        <f>E49*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H47" s="34">
-        <f>E47*0.00001</f>
+      <c r="H49" s="34">
+        <f>E49*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I47" s="34">
-        <f>(F47+G47+H47)*0.07</f>
+      <c r="I49" s="34">
+        <f>(F49+G49+H49)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J47" s="34">
-        <f>E47-F47-G47-H47-I47</f>
+      <c r="J49" s="34">
+        <f>E49-F49-G49-H49-I49</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K47" s="10">
-        <f>K44+C47</f>
+      <c r="K49" s="10">
+        <f>K46+C49</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A50" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="25">
+        <f>(D49-D48)/D48</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="20">
+        <f>E49-E48</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20">
+        <f>J49-J48</f>
+        <v>-327.32905000001483</v>
+      </c>
+      <c r="K50" s="20">
+        <f>K47+J50</f>
+        <v>8741.1065874999767</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A51" s="56">
+        <v>44543</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D51" s="46">
+        <v>29.5</v>
+      </c>
+      <c r="E51" s="20">
+        <f>C51*D51</f>
+        <v>73750</v>
+      </c>
+      <c r="F51" s="20">
+        <f>E51*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G51" s="20">
+        <f>E51*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H51" s="20">
+        <f>E51*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I51" s="20">
+        <f>(F51+G51+H51)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J51" s="20">
+        <f>E51+F51+I51+G51+H51</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K51" s="57"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+    </row>
+    <row r="52" spans="1:15" s="13" customFormat="1">
+      <c r="A52" s="56" t="e">
+        <f>A49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="10">
+        <f>C51</f>
+        <v>2500</v>
+      </c>
+      <c r="D52" s="34">
+        <f>D49</f>
+        <v>29.5</v>
+      </c>
+      <c r="E52" s="11">
+        <f>C52*D52</f>
+        <v>73750</v>
+      </c>
+      <c r="F52" s="35">
+        <f>E52*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G52" s="34">
+        <f>E52*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H52" s="34">
+        <f>E52*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I52" s="34">
+        <f>(F52+G52+H52)*0.07</f>
+        <v>10.727675000000001</v>
+      </c>
+      <c r="J52" s="34">
+        <f>E52-F52-G52-H52-I52</f>
+        <v>73586.019824999996</v>
+      </c>
+      <c r="K52" s="10">
+        <f>K49+C52</f>
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A53" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="25">
+        <f>(D52-D51)/D51</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="20">
+        <f>E52-E51</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20">
+        <f>J52-J51</f>
+        <v>-327.32905000001483</v>
+      </c>
+      <c r="K53" s="20">
+        <f>K50+J53</f>
+        <v>8413.7775374999619</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A54" s="56">
+        <v>44496</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D54" s="46">
+        <v>32.75</v>
+      </c>
+      <c r="E54" s="20">
+        <f>C54*D54</f>
+        <v>81875</v>
+      </c>
+      <c r="F54" s="20">
+        <f>E54*0.002</f>
+        <v>163.75</v>
+      </c>
+      <c r="G54" s="20">
+        <f>E54*0.00006</f>
+        <v>4.9125000000000005</v>
+      </c>
+      <c r="H54" s="20">
+        <f>E54*0.00001</f>
+        <v>0.81875000000000009</v>
+      </c>
+      <c r="I54" s="20">
+        <f>(F54+G54+H54)*0.07</f>
+        <v>11.863687500000001</v>
+      </c>
+      <c r="J54" s="20">
+        <f>E54+F54+I54+G54+H54</f>
+        <v>82056.344937500005</v>
+      </c>
+      <c r="K54" s="57"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="58"/>
+      <c r="O54" s="58"/>
+    </row>
+    <row r="55" spans="1:15" s="13" customFormat="1">
+      <c r="A55" s="56" t="e">
+        <f>A52</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="10">
+        <f>C54</f>
+        <v>2500</v>
+      </c>
+      <c r="D55" s="34">
+        <f>D49</f>
+        <v>29.5</v>
+      </c>
+      <c r="E55" s="11">
+        <f>C55*D55</f>
+        <v>73750</v>
+      </c>
+      <c r="F55" s="35">
+        <f>E55*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G55" s="34">
+        <f>E55*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H55" s="34">
+        <f>E55*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I55" s="34">
+        <f>(F55+G55+H55)*0.07</f>
+        <v>10.727675000000001</v>
+      </c>
+      <c r="J55" s="34">
+        <f>E55-F55-G55-H55-I55</f>
+        <v>73586.019824999996</v>
+      </c>
+      <c r="K55" s="10">
+        <f>K52+C55</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="48" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A48" s="56" t="s">
+    <row r="56" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A56" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="25">
-        <f>(D47-D46)/D46</f>
+      <c r="B56" s="25">
+        <f>(D55-D54)/D54</f>
         <v>-9.9236641221374045E-2</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="20">
-        <f>E47-E46</f>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="20">
+        <f>E55-E54</f>
         <v>-8125</v>
       </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20">
-        <f>J47-J46</f>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20">
+        <f>J55-J54</f>
         <v>-8470.3251125000097</v>
       </c>
-      <c r="K48" s="20">
-        <f>K45+J48</f>
+      <c r="K56" s="20">
+        <f>K53+J56</f>
         <v>-56.5475750000478</v>
       </c>
     </row>
-    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A49" s="56">
+    <row r="57" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A57" s="56">
         <v>44462</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="16">
+      <c r="B57" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="16">
         <v>2500</v>
       </c>
-      <c r="D49" s="46">
+      <c r="D57" s="46">
         <v>33.25</v>
       </c>
-      <c r="E49" s="20">
-        <f>C49*D49</f>
+      <c r="E57" s="20">
+        <f>C57*D57</f>
         <v>83125</v>
       </c>
-      <c r="F49" s="20">
-        <f>E49*0.002</f>
+      <c r="F57" s="20">
+        <f>E57*0.002</f>
         <v>166.25</v>
       </c>
-      <c r="G49" s="20">
-        <f>E49*0.00006</f>
+      <c r="G57" s="20">
+        <f>E57*0.00006</f>
         <v>4.9874999999999998</v>
       </c>
-      <c r="H49" s="20">
-        <f>E49*0.00001</f>
+      <c r="H57" s="20">
+        <f>E57*0.00001</f>
         <v>0.83125000000000004</v>
       </c>
-      <c r="I49" s="20">
-        <f>(F49+G49+H49)*0.07</f>
+      <c r="I57" s="20">
+        <f>(F57+G57+H57)*0.07</f>
         <v>12.044812500000003</v>
       </c>
-      <c r="J49" s="20">
-        <f>E49+F49+I49+G49+H49</f>
+      <c r="J57" s="20">
+        <f>E57+F57+I57+G57+H57</f>
         <v>83309.113562500002</v>
       </c>
-      <c r="K49" s="57"/>
-      <c r="L49" s="58"/>
-      <c r="M49" s="58"/>
-      <c r="N49" s="58"/>
-      <c r="O49" s="58"/>
-    </row>
-    <row r="50" spans="1:15" s="13" customFormat="1">
-      <c r="A50" s="56" t="e">
-        <f>A47</f>
+      <c r="K57" s="57"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="58"/>
+      <c r="O57" s="58"/>
+    </row>
+    <row r="58" spans="1:15" s="13" customFormat="1">
+      <c r="A58" s="56" t="e">
+        <f>A55</f>
         <v>#REF!</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B58" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="10">
-        <f>C49</f>
+      <c r="C58" s="10">
+        <f>C57</f>
         <v>2500</v>
       </c>
-      <c r="D50" s="34">
-        <f>D41</f>
+      <c r="D58" s="34">
+        <f>D49</f>
         <v>29.5</v>
       </c>
-      <c r="E50" s="11">
-        <f>C50*D50</f>
+      <c r="E58" s="11">
+        <f>C58*D58</f>
         <v>73750</v>
       </c>
-      <c r="F50" s="35">
-        <f>E50*0.002</f>
+      <c r="F58" s="35">
+        <f>E58*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G50" s="34">
-        <f>E50*0.000068</f>
+      <c r="G58" s="34">
+        <f>E58*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H50" s="34">
-        <f>E50*0.00001</f>
+      <c r="H58" s="34">
+        <f>E58*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I50" s="34">
-        <f>(F50+G50+H50)*0.07</f>
+      <c r="I58" s="34">
+        <f>(F58+G58+H58)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J50" s="34">
-        <f>E50-F50-G50-H50-I50</f>
+      <c r="J58" s="34">
+        <f>E58-F58-G58-H58-I58</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K50" s="10">
-        <f>K47+C50</f>
+      <c r="K58" s="10">
+        <f>K55+C58</f>
         <v>12500</v>
       </c>
     </row>
-    <row r="51" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A51" s="56" t="s">
+    <row r="59" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A59" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="25">
-        <f>(D50-D49)/D49</f>
+      <c r="B59" s="25">
+        <f>(D58-D57)/D57</f>
         <v>-0.11278195488721804</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="20">
-        <f>E50-E49</f>
+      <c r="C59" s="10"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="20">
+        <f>E58-E57</f>
         <v>-9375</v>
       </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20">
-        <f>J50-J49</f>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20">
+        <f>J58-J57</f>
         <v>-9723.0937375000067</v>
       </c>
-      <c r="K51" s="20">
-        <f>K48+J51</f>
+      <c r="K59" s="20">
+        <f>K56+J59</f>
         <v>-9779.6413125000545</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A52" s="56">
+    <row r="60" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A60" s="56">
         <v>44452</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="16">
+      <c r="B60" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="16">
         <v>2500</v>
       </c>
-      <c r="D52" s="46">
+      <c r="D60" s="46">
         <v>35.25</v>
       </c>
-      <c r="E52" s="20">
-        <f>C52*D52</f>
+      <c r="E60" s="20">
+        <f>C60*D60</f>
         <v>88125</v>
       </c>
-      <c r="F52" s="20">
-        <f>E52*0.002</f>
+      <c r="F60" s="20">
+        <f>E60*0.002</f>
         <v>176.25</v>
       </c>
-      <c r="G52" s="20">
-        <f>E52*0.00006</f>
+      <c r="G60" s="20">
+        <f>E60*0.00006</f>
         <v>5.2875000000000005</v>
       </c>
-      <c r="H52" s="20">
-        <f>E52*0.00001</f>
+      <c r="H60" s="20">
+        <f>E60*0.00001</f>
         <v>0.88125000000000009</v>
       </c>
-      <c r="I52" s="20">
-        <f>(F52+G52+H52)*0.07</f>
+      <c r="I60" s="20">
+        <f>(F60+G60+H60)*0.07</f>
         <v>12.7693125</v>
       </c>
-      <c r="J52" s="20">
-        <f>E52+F52+I52+G52+H52</f>
+      <c r="J60" s="20">
+        <f>E60+F60+I60+G60+H60</f>
         <v>88320.188062500005</v>
       </c>
-      <c r="K52" s="57"/>
-      <c r="L52" s="58"/>
-      <c r="M52" s="58"/>
-      <c r="N52" s="58"/>
-      <c r="O52" s="58"/>
-    </row>
-    <row r="53" spans="1:15" s="13" customFormat="1">
-      <c r="A53" s="56" t="e">
-        <f>A50</f>
+      <c r="K60" s="57"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+    </row>
+    <row r="61" spans="1:15" s="13" customFormat="1">
+      <c r="A61" s="56" t="e">
+        <f>A58</f>
         <v>#REF!</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B61" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="10">
-        <f>C52</f>
+      <c r="C61" s="10">
+        <f>C60</f>
         <v>2500</v>
       </c>
-      <c r="D53" s="34">
-        <f>D41</f>
+      <c r="D61" s="34">
+        <f>D49</f>
         <v>29.5</v>
       </c>
-      <c r="E53" s="11">
-        <f>C53*D53</f>
+      <c r="E61" s="11">
+        <f>C61*D61</f>
         <v>73750</v>
       </c>
-      <c r="F53" s="35">
-        <f>E53*0.002</f>
+      <c r="F61" s="35">
+        <f>E61*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G53" s="34">
-        <f>E53*0.000068</f>
+      <c r="G61" s="34">
+        <f>E61*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H53" s="34">
-        <f>E53*0.00001</f>
+      <c r="H61" s="34">
+        <f>E61*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I53" s="34">
-        <f>(F53+G53+H53)*0.07</f>
+      <c r="I61" s="34">
+        <f>(F61+G61+H61)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J53" s="34">
-        <f>E53-F53-G53-H53-I53</f>
+      <c r="J61" s="34">
+        <f>E61-F61-G61-H61-I61</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K53" s="91">
-        <f>K50+C53</f>
+      <c r="K61" s="91">
+        <f>K58+C61</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A54" s="56" t="s">
+    <row r="62" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A62" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="25">
-        <f>(D53-D52)/D52</f>
+      <c r="B62" s="25">
+        <f>(D61-D60)/D60</f>
         <v>-0.16312056737588654</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="20">
-        <f>E53-E52</f>
+      <c r="C62" s="10"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="20">
+        <f>E61-E60</f>
         <v>-14375</v>
       </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20">
-        <f>J53-J52</f>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20">
+        <f>J61-J60</f>
         <v>-14734.168237500009</v>
       </c>
-      <c r="K54" s="20">
-        <f>K51+J54</f>
+      <c r="K62" s="20">
+        <f>K59+J62</f>
         <v>-24513.809550000064</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A55" s="56">
+    <row r="63" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A63" s="56">
         <v>44398</v>
       </c>
-      <c r="B55" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="16">
+      <c r="B63" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="16">
         <v>2500</v>
       </c>
-      <c r="D55" s="46">
+      <c r="D63" s="46">
         <v>37.75</v>
       </c>
-      <c r="E55" s="20">
-        <f>C55*D55</f>
+      <c r="E63" s="20">
+        <f>C63*D63</f>
         <v>94375</v>
       </c>
-      <c r="F55" s="20">
-        <f>E55*0.002</f>
+      <c r="F63" s="20">
+        <f>E63*0.002</f>
         <v>188.75</v>
       </c>
-      <c r="G55" s="20">
-        <f>E55*0.00006</f>
+      <c r="G63" s="20">
+        <f>E63*0.00006</f>
         <v>5.6625000000000005</v>
       </c>
-      <c r="H55" s="20">
-        <f>E55*0.00001</f>
+      <c r="H63" s="20">
+        <f>E63*0.00001</f>
         <v>0.94375000000000009</v>
       </c>
-      <c r="I55" s="20">
-        <f>(F55+G55+H55)*0.07</f>
+      <c r="I63" s="20">
+        <f>(F63+G63+H63)*0.07</f>
         <v>13.6749375</v>
       </c>
-      <c r="J55" s="20">
-        <f>E55+F55+I55+G55+H55</f>
+      <c r="J63" s="20">
+        <f>E63+F63+I63+G63+H63</f>
         <v>94584.031187500019</v>
       </c>
-      <c r="K55" s="57"/>
-      <c r="L55" s="58"/>
-      <c r="M55" s="58"/>
-      <c r="N55" s="58"/>
-      <c r="O55" s="58"/>
-    </row>
-    <row r="56" spans="1:15" s="13" customFormat="1">
-      <c r="A56" s="56" t="e">
-        <f>A53</f>
+      <c r="K63" s="57"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+    </row>
+    <row r="64" spans="1:15" s="13" customFormat="1">
+      <c r="A64" s="56" t="e">
+        <f>A61</f>
         <v>#REF!</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B64" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="10">
-        <f>C55</f>
+      <c r="C64" s="10">
+        <f>C63</f>
         <v>2500</v>
       </c>
-      <c r="D56" s="34">
-        <f>D41</f>
+      <c r="D64" s="34">
+        <f>D49</f>
         <v>29.5</v>
       </c>
-      <c r="E56" s="11">
-        <f>C56*D56</f>
+      <c r="E64" s="11">
+        <f>C64*D64</f>
         <v>73750</v>
       </c>
-      <c r="F56" s="35">
-        <f>E56*0.002</f>
+      <c r="F64" s="35">
+        <f>E64*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G56" s="34">
-        <f>E56*0.000068</f>
+      <c r="G64" s="34">
+        <f>E64*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H56" s="34">
-        <f>E56*0.00001</f>
+      <c r="H64" s="34">
+        <f>E64*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I56" s="34">
-        <f>(F56+G56+H56)*0.07</f>
+      <c r="I64" s="34">
+        <f>(F64+G64+H64)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J56" s="34">
-        <f>E56-F56-G56-H56-I56</f>
+      <c r="J64" s="34">
+        <f>E64-F64-G64-H64-I64</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K56" s="10">
-        <f>K53+C56</f>
+      <c r="K64" s="10">
+        <f>K61+C64</f>
         <v>17500</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A57" s="56" t="s">
+    <row r="65" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A65" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="25">
-        <f>(D56-D55)/D55</f>
+      <c r="B65" s="25">
+        <f>(D64-D63)/D63</f>
         <v>-0.2185430463576159</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="20">
-        <f>E56-E55</f>
+      <c r="C65" s="10"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="20">
+        <f>E64-E63</f>
         <v>-20625</v>
       </c>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20">
-        <f>J56-J55</f>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20">
+        <f>J64-J63</f>
         <v>-20998.011362500023</v>
       </c>
-      <c r="K57" s="20">
-        <f>K54+J57</f>
+      <c r="K65" s="20">
+        <f>K62+J65</f>
         <v>-45511.820912500087</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A58" s="56">
+    <row r="66" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A66" s="56">
         <v>44368</v>
       </c>
-      <c r="B58" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="16">
+      <c r="B66" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="16">
         <v>2500</v>
       </c>
-      <c r="D58" s="46">
+      <c r="D66" s="46">
         <v>40</v>
       </c>
-      <c r="E58" s="20">
-        <f>C58*D58</f>
+      <c r="E66" s="20">
+        <f>C66*D66</f>
         <v>100000</v>
       </c>
-      <c r="F58" s="20">
-        <f>E58*0.002</f>
+      <c r="F66" s="20">
+        <f>E66*0.002</f>
         <v>200</v>
       </c>
-      <c r="G58" s="20">
-        <f>E58*0.00006</f>
+      <c r="G66" s="20">
+        <f>E66*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H58" s="20">
-        <f>E58*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I58" s="20">
-        <f>(F58+G58+H58)*0.07</f>
+      <c r="H66" s="20">
+        <f>E66*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I66" s="20">
+        <f>(F66+G66+H66)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J58" s="20">
-        <f>E58+F58+I58+G58+H58</f>
+      <c r="J66" s="20">
+        <f>E66+F66+I66+G66+H66</f>
         <v>100221.49</v>
       </c>
-      <c r="K58" s="57"/>
-      <c r="L58" s="58"/>
-      <c r="M58" s="58"/>
-      <c r="N58" s="58"/>
-      <c r="O58" s="58"/>
-    </row>
-    <row r="59" spans="1:15" s="13" customFormat="1">
-      <c r="A59" s="56" t="e">
-        <f>A56</f>
+      <c r="K66" s="57"/>
+      <c r="L66" s="58"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="58"/>
+      <c r="O66" s="58"/>
+    </row>
+    <row r="67" spans="1:15" s="13" customFormat="1">
+      <c r="A67" s="56" t="e">
+        <f>A64</f>
         <v>#REF!</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B67" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="10">
-        <f>C58</f>
+      <c r="C67" s="10">
+        <f>C66</f>
         <v>2500</v>
       </c>
-      <c r="D59" s="34">
-        <f>D44</f>
+      <c r="D67" s="34">
+        <f>D52</f>
         <v>29.5</v>
       </c>
-      <c r="E59" s="11">
-        <f>C59*D59</f>
+      <c r="E67" s="11">
+        <f>C67*D67</f>
         <v>73750</v>
       </c>
-      <c r="F59" s="35">
-        <f>E59*0.002</f>
+      <c r="F67" s="35">
+        <f>E67*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G59" s="34">
-        <f>E59*0.000068</f>
+      <c r="G67" s="34">
+        <f>E67*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H59" s="34">
-        <f>E59*0.00001</f>
+      <c r="H67" s="34">
+        <f>E67*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I59" s="34">
-        <f>(F59+G59+H59)*0.07</f>
+      <c r="I67" s="34">
+        <f>(F67+G67+H67)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J59" s="34">
-        <f>E59-F59-G59-H59-I59</f>
+      <c r="J67" s="34">
+        <f>E67-F67-G67-H67-I67</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K59" s="10">
-        <f>K56+C59</f>
+      <c r="K67" s="10">
+        <f>K64+C67</f>
         <v>20000</v>
       </c>
     </row>
-    <row r="60" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A60" s="56" t="s">
+    <row r="68" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A68" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="25">
-        <f>(D59-D58)/D58</f>
+      <c r="B68" s="25">
+        <f>(D67-D66)/D66</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="20">
-        <f>E59-E58</f>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="20">
+        <f>E67-E66</f>
         <v>-26250</v>
       </c>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20">
-        <f>J59-J58</f>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20">
+        <f>J67-J66</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K60" s="20">
-        <f>K57+J60</f>
+      <c r="K68" s="20">
+        <f>K65+J68</f>
         <v>-72147.291087500096</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A61" s="56">
+    <row r="69" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A69" s="56">
         <v>44368</v>
       </c>
-      <c r="B61" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="16">
+      <c r="B69" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="16">
         <v>2500</v>
       </c>
-      <c r="D61" s="46">
+      <c r="D69" s="46">
         <v>40</v>
       </c>
-      <c r="E61" s="20">
-        <f>C61*D61</f>
+      <c r="E69" s="20">
+        <f>C69*D69</f>
         <v>100000</v>
       </c>
-      <c r="F61" s="20">
-        <f>E61*0.002</f>
+      <c r="F69" s="20">
+        <f>E69*0.002</f>
         <v>200</v>
       </c>
-      <c r="G61" s="20">
-        <f>E61*0.00006</f>
+      <c r="G69" s="20">
+        <f>E69*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H61" s="20">
-        <f>E61*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I61" s="20">
-        <f>(F61+G61+H61)*0.07</f>
+      <c r="H69" s="20">
+        <f>E69*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I69" s="20">
+        <f>(F69+G69+H69)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J61" s="20">
-        <f>E61+F61+I61+G61+H61</f>
+      <c r="J69" s="20">
+        <f>E69+F69+I69+G69+H69</f>
         <v>100221.49</v>
       </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="58"/>
-      <c r="M61" s="58"/>
-      <c r="N61" s="58"/>
-      <c r="O61" s="58"/>
-    </row>
-    <row r="62" spans="1:15" s="13" customFormat="1">
-      <c r="A62" s="56" t="e">
-        <f>A59</f>
+      <c r="K69" s="57"/>
+      <c r="L69" s="58"/>
+      <c r="M69" s="58"/>
+      <c r="N69" s="58"/>
+      <c r="O69" s="58"/>
+    </row>
+    <row r="70" spans="1:15" s="13" customFormat="1">
+      <c r="A70" s="56" t="e">
+        <f>A67</f>
         <v>#REF!</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B70" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="10">
-        <f>C61</f>
+      <c r="C70" s="10">
+        <f>C69</f>
         <v>2500</v>
       </c>
-      <c r="D62" s="34">
-        <f>D47</f>
+      <c r="D70" s="34">
+        <f>D55</f>
         <v>29.5</v>
       </c>
-      <c r="E62" s="11">
-        <f>C62*D62</f>
+      <c r="E70" s="11">
+        <f>C70*D70</f>
         <v>73750</v>
       </c>
-      <c r="F62" s="35">
-        <f>E62*0.002</f>
+      <c r="F70" s="35">
+        <f>E70*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G62" s="34">
-        <f>E62*0.000068</f>
+      <c r="G70" s="34">
+        <f>E70*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H62" s="34">
-        <f>E62*0.00001</f>
+      <c r="H70" s="34">
+        <f>E70*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I62" s="34">
-        <f>(F62+G62+H62)*0.07</f>
+      <c r="I70" s="34">
+        <f>(F70+G70+H70)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J62" s="34">
-        <f>E62-F62-G62-H62-I62</f>
+      <c r="J70" s="34">
+        <f>E70-F70-G70-H70-I70</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K62" s="10">
-        <f>K59+C62</f>
+      <c r="K70" s="10">
+        <f>K67+C70</f>
         <v>22500</v>
       </c>
     </row>
-    <row r="63" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A63" s="56" t="s">
+    <row r="71" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A71" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B63" s="25">
-        <f>(D62-D61)/D61</f>
+      <c r="B71" s="25">
+        <f>(D70-D69)/D69</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="20">
-        <f>E62-E61</f>
+      <c r="C71" s="10"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="20">
+        <f>E70-E69</f>
         <v>-26250</v>
       </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20">
-        <f>J62-J61</f>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20">
+        <f>J70-J69</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K63" s="20">
-        <f>K60+J63</f>
+      <c r="K71" s="20">
+        <f>K68+J71</f>
         <v>-98782.761262500106</v>
       </c>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11378" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A644BB5-6C75-4745-A7DA-5DBFD1AB224E}"/>
+  <xr:revisionPtr revIDLastSave="11444" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14430126-7C49-410D-B046-42168B99BBD9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="14" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="198" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -6325,78 +6325,78 @@
       <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="A3" s="49">
+        <v>44956</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
         <v>900</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="41">
         <v>53</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="69">
         <f>C3*D3</f>
         <v>47700</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="18">
         <f>E3*0.002</f>
         <v>95.4</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="18">
         <f>E3*0.00006</f>
         <v>2.8620000000000001</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="18">
         <f>E3*0.00001</f>
         <v>0.47700000000000004</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="18">
         <f>(F3+G3+H3)*0.07</f>
         <v>6.9117300000000013</v>
       </c>
-      <c r="J3" s="62">
+      <c r="J3" s="69">
         <f>E3+F3+I3+G3+H3</f>
         <v>47805.650730000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="12">
+      <c r="A4" s="49"/>
+      <c r="B4" s="30">
         <f>(D3-D2)/D2</f>
         <v>-9.4017094017094016E-2</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="16">
         <f>SUM(C2:C3)</f>
         <v>3300</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="17">
         <f>E4/C4</f>
         <v>57</v>
       </c>
-      <c r="E4" s="62">
+      <c r="E4" s="69">
         <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
         <v>188100</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="16">
         <f t="shared" si="0"/>
         <v>376.20000000000005</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="16">
         <f t="shared" si="0"/>
         <v>11.286</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="16">
         <f t="shared" si="0"/>
         <v>1.8810000000000002</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="16">
         <f t="shared" si="0"/>
         <v>27.255690000000005</v>
       </c>
-      <c r="J4" s="62">
+      <c r="J4" s="69">
         <f t="shared" si="0"/>
         <v>188516.62268999999</v>
       </c>
@@ -6409,73 +6409,73 @@
         <v>1</v>
       </c>
       <c r="C5" s="10">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="D5" s="46">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E5" s="62">
         <f>C5*D5</f>
-        <v>45000</v>
+        <v>79500</v>
       </c>
       <c r="F5" s="20">
         <f>E5*0.002</f>
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="G5" s="20">
         <f>E5*0.00006</f>
-        <v>2.7</v>
+        <v>4.7700000000000005</v>
       </c>
       <c r="H5" s="20">
         <f>E5*0.00001</f>
-        <v>0.45</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="I5" s="20">
         <f>(F5+G5+H5)*0.07</f>
-        <v>6.5205000000000011</v>
+        <v>11.519550000000001</v>
       </c>
       <c r="J5" s="62">
         <f>E5+F5+I5+G5+H5</f>
-        <v>45099.670499999993</v>
+        <v>79676.08455</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1">
       <c r="A6" s="56"/>
       <c r="B6" s="12">
         <f>(D5-D4)/D4</f>
-        <v>-0.12280701754385964</v>
+        <v>-7.0175438596491224E-2</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(C4:C5)</f>
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="D6" s="11">
         <f>E6/C6</f>
-        <v>55.5</v>
+        <v>55.75</v>
       </c>
       <c r="E6" s="62">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>233100</v>
+        <v>267600</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>466.20000000000005</v>
+        <v>535.20000000000005</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="1"/>
-        <v>13.986000000000001</v>
+        <v>16.056000000000001</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>2.3310000000000004</v>
+        <v>2.6760000000000002</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" si="1"/>
-        <v>33.776190000000007</v>
+        <v>38.775240000000004</v>
       </c>
       <c r="J6" s="62">
         <f t="shared" si="1"/>
-        <v>233616.29319</v>
+        <v>268192.70724000002</v>
       </c>
     </row>
   </sheetData>
@@ -16299,7 +16299,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -16310,17 +16310,17 @@
     <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="5.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
     <col min="11" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="19" customFormat="1" ht="16.5">
+    <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
       <c r="A2" s="49">
         <v>44466</v>
       </c>
@@ -16358,7 +16358,7 @@
         <v>91201.555900000007</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="21" customFormat="1">
+    <row r="3" spans="1:14" s="21" customFormat="1">
       <c r="A3" s="14">
         <v>44544</v>
       </c>
@@ -16396,7 +16396,7 @@
         <v>89197.887940000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="21" customFormat="1">
+    <row r="4" spans="1:14" s="21" customFormat="1">
       <c r="A4" s="42"/>
       <c r="B4" s="74">
         <f>(D3-D2)/D2</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" spans="1:11" s="21" customFormat="1">
+    <row r="5" spans="1:14" s="21" customFormat="1">
       <c r="A5" s="14">
         <v>44546</v>
       </c>
@@ -16474,7 +16474,7 @@
         <v>45235.355867099999</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="21" customFormat="1">
+    <row r="6" spans="1:14" s="21" customFormat="1">
       <c r="A6" s="42"/>
       <c r="B6" s="74">
         <f>(D5-D4)/D4</f>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="K6" s="25"/>
     </row>
-    <row r="7" spans="1:11" s="21" customFormat="1">
+    <row r="7" spans="1:14" s="21" customFormat="1">
       <c r="A7" s="14">
         <v>44547</v>
       </c>
@@ -16552,7 +16552,7 @@
         <v>43461.420342899997</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="21" customFormat="1">
+    <row r="8" spans="1:14" s="21" customFormat="1">
       <c r="A8" s="42"/>
       <c r="B8" s="74">
         <f>(D7-D6)/D6</f>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" spans="1:11" s="21" customFormat="1">
+    <row r="9" spans="1:14" s="21" customFormat="1">
       <c r="A9" s="14">
         <v>44620</v>
       </c>
@@ -16630,7 +16630,7 @@
         <v>89698.999670000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="21" customFormat="1">
+    <row r="10" spans="1:14" s="21" customFormat="1">
       <c r="A10" s="42"/>
       <c r="B10" s="74">
         <f>(D9-D8)/D8</f>
@@ -16670,83 +16670,296 @@
       </c>
       <c r="K10" s="25"/>
     </row>
-    <row r="11" spans="1:11" s="21" customFormat="1">
-      <c r="A11" s="8">
-        <v>44623</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10">
+    <row r="11" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A11" s="14">
+        <v>44956</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="16">
         <v>10000</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="41">
         <v>7.7</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="18">
         <f>C11*D11</f>
         <v>77000</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="18">
         <f>E11*0.002</f>
         <v>154</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="18">
         <f>E11*0.000068</f>
         <v>5.2359999999999998</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="18">
         <f>E11*0.00001</f>
         <v>0.77</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="18">
         <f>(F11+G11+H11)*0.07</f>
         <v>11.200420000000001</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="18">
         <f>E11+F11+I11+G11+H11</f>
         <v>77171.206420000002</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="21" customFormat="1">
-      <c r="A12" s="44"/>
+    <row r="12" spans="1:14" s="21" customFormat="1">
+      <c r="A12" s="42"/>
       <c r="B12" s="74">
         <f>(D11-D10)/D10</f>
         <v>-0.13966480446927365</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="5">
         <f>C10+C11</f>
         <v>50000</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="36">
         <f>E12/C12</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="5">
         <f>E10+E11</f>
         <v>435000</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="5">
         <f>F10+F11</f>
         <v>870</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="5">
         <f>G10+G11</f>
         <v>28.852</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="5">
         <f>H10+H11</f>
         <v>4.3500000000000005</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="5">
         <f>I10+I11</f>
         <v>63.224140000000006</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12" s="5">
         <f>J10+J11</f>
         <v>435966.42614</v>
       </c>
       <c r="K12" s="25"/>
+    </row>
+    <row r="13" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A13" s="8">
+        <v>44956</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10">
+        <v>10000</v>
+      </c>
+      <c r="D13" s="46">
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="20">
+        <f>C13*D13</f>
+        <v>75000</v>
+      </c>
+      <c r="F13" s="20">
+        <f>E13*0.002</f>
+        <v>150</v>
+      </c>
+      <c r="G13" s="20">
+        <f>E13*0.000068</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H13" s="20">
+        <f>E13*0.00001</f>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="I13" s="20">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>10.909500000000001</v>
+      </c>
+      <c r="J13" s="20">
+        <f>E13+F13+I13+G13+H13</f>
+        <v>75166.7595</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="21" customFormat="1" ht="12.75">
+      <c r="A14" s="44"/>
+      <c r="B14" s="3">
+        <f>(D13-D12)/D12</f>
+        <v>-0.13793103448275856</v>
+      </c>
+      <c r="C14" s="22">
+        <f>C12+C13</f>
+        <v>60000</v>
+      </c>
+      <c r="D14" s="33">
+        <f>E14/C14</f>
+        <v>8.5</v>
+      </c>
+      <c r="E14" s="22">
+        <f>E12+E13</f>
+        <v>510000</v>
+      </c>
+      <c r="F14" s="22">
+        <f>F12+F13</f>
+        <v>1020</v>
+      </c>
+      <c r="G14" s="22">
+        <f>G12+G13</f>
+        <v>33.951999999999998</v>
+      </c>
+      <c r="H14" s="22">
+        <f>H12+H13</f>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I14" s="22">
+        <f>I12+I13</f>
+        <v>74.133640000000014</v>
+      </c>
+      <c r="J14" s="22">
+        <f>J12+J13</f>
+        <v>511133.18563999998</v>
+      </c>
+      <c r="K14" s="25"/>
+    </row>
+    <row r="15" spans="1:14" ht="12"/>
+    <row r="16" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A16" s="56">
+        <v>44629</v>
+      </c>
+      <c r="C16" s="10">
+        <f>C13</f>
+        <v>10000</v>
+      </c>
+      <c r="D16" s="64">
+        <v>0.17380000000000001</v>
+      </c>
+      <c r="E16" s="60"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="61">
+        <f>C16*D16</f>
+        <v>1738</v>
+      </c>
+      <c r="J16" s="61">
+        <f>I16*0.9</f>
+        <v>1564.2</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="56">
+        <v>44242</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10">
+        <f>C13</f>
+        <v>10000</v>
+      </c>
+      <c r="D17" s="46">
+        <f>D12</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E17" s="20">
+        <f>C17*D17</f>
+        <v>87000</v>
+      </c>
+      <c r="F17" s="20">
+        <f>E17*0.002</f>
+        <v>174</v>
+      </c>
+      <c r="G17" s="20">
+        <f>E17*0.00006</f>
+        <v>5.22</v>
+      </c>
+      <c r="H17" s="20">
+        <f>E17*0.00001</f>
+        <v>0.87000000000000011</v>
+      </c>
+      <c r="I17" s="20">
+        <f>(F17+G17+H17)*0.07</f>
+        <v>12.606300000000001</v>
+      </c>
+      <c r="J17" s="20">
+        <f>E17+F17+I17+G17+H17</f>
+        <v>87192.696299999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="10">
+        <f>C17</f>
+        <v>10000</v>
+      </c>
+      <c r="D18" s="34">
+        <v>8.9</v>
+      </c>
+      <c r="E18" s="11">
+        <f>C18*D18</f>
+        <v>89000</v>
+      </c>
+      <c r="F18" s="35">
+        <f>E18*0.002</f>
+        <v>178</v>
+      </c>
+      <c r="G18" s="34">
+        <f>E18*0.000068</f>
+        <v>6.0519999999999996</v>
+      </c>
+      <c r="H18" s="34">
+        <f>E18*0.00001</f>
+        <v>0.89000000000000012</v>
+      </c>
+      <c r="I18" s="34">
+        <f>(F18+G18+H18)*0.07</f>
+        <v>12.94594</v>
+      </c>
+      <c r="J18" s="34">
+        <f>E18-F18-G18-H18-I18</f>
+        <v>88802.112059999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="20">
+        <f>E18-E17</f>
+        <v>2000</v>
+      </c>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20">
+        <f>J18-J17</f>
+        <v>1609.4157600000035</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="C20" s="2"/>
+      <c r="J20" s="53">
+        <f>J16+J19</f>
+        <v>3173.6157600000033</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11516" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D9008-9598-4539-A719-28DBAC6D7315}"/>
+  <xr:revisionPtr revIDLastSave="11544" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F09480-6FE9-4287-A285-82C68B4A87CB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE (2)" sheetId="206" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -324,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -421,6 +421,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="191" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -789,7 +793,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -1612,40 +1616,40 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25">
-      <c r="A22" s="54"/>
-      <c r="B22" s="74">
+      <c r="A22" s="96"/>
+      <c r="B22" s="97">
         <f>(D21-D28)/D28</f>
         <v>-0.12767624020887736</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="98">
         <f>SUM(C20:C21)</f>
         <v>12000</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="99">
         <f>E22/C22</f>
         <v>74.5625</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="98">
         <f t="shared" ref="E22:J22" si="7">SUM(E20:E21)</f>
         <v>894750</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="98">
         <f t="shared" si="7"/>
         <v>1789.5</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="98">
         <f t="shared" si="7"/>
         <v>53.684999999999995</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="98">
         <f t="shared" si="7"/>
         <v>8.9475000000000016</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="98">
         <f t="shared" si="7"/>
         <v>129.64927499999999</v>
       </c>
-      <c r="J22" s="51">
+      <c r="J22" s="98">
         <f t="shared" si="7"/>
         <v>896731.78177500004</v>
       </c>
@@ -1868,508 +1872,646 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="12.75">
-      <c r="A29" s="56">
+      <c r="A29" s="49">
         <v>44658</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="91">
+      <c r="B29" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="88">
         <v>1000</v>
       </c>
-      <c r="D29" s="46">
-        <v>50.5</v>
-      </c>
-      <c r="E29" s="20">
+      <c r="D29" s="41">
+        <v>62.75</v>
+      </c>
+      <c r="E29" s="18">
         <f>C29*D29</f>
-        <v>50500</v>
-      </c>
-      <c r="F29" s="20">
+        <v>62750</v>
+      </c>
+      <c r="F29" s="18">
         <f>E29*0.002</f>
-        <v>101</v>
-      </c>
-      <c r="G29" s="20">
+        <v>125.5</v>
+      </c>
+      <c r="G29" s="18">
         <f>E29*0.00006</f>
-        <v>3.0300000000000002</v>
-      </c>
-      <c r="H29" s="20">
+        <v>3.7650000000000001</v>
+      </c>
+      <c r="H29" s="18">
         <f>E29*0.00001</f>
-        <v>0.505</v>
-      </c>
-      <c r="I29" s="20">
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="I29" s="18">
         <f>(F29+G29+H29)*0.07</f>
-        <v>7.3174500000000009</v>
-      </c>
-      <c r="J29" s="20">
+        <v>9.0924750000000003</v>
+      </c>
+      <c r="J29" s="18">
         <f>E29+F29+I29+G29+H29</f>
-        <v>50611.852449999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="B30" s="3">
-        <f>(D29-D28)/D28</f>
-        <v>-0.31436031331592695</v>
-      </c>
-      <c r="C30" s="2">
-        <f>SUM(C28:C29)</f>
-        <v>14000</v>
-      </c>
-      <c r="D30" s="47">
-        <f>E30/C30</f>
-        <v>72</v>
-      </c>
-      <c r="E30" s="2">
-        <f t="shared" ref="E30:J30" si="9">SUM(E28:E29)</f>
-        <v>1008000</v>
-      </c>
-      <c r="F30" s="2">
+        <v>62888.984974999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="13" customFormat="1" ht="12.75">
+      <c r="A30" s="49">
+        <v>44958</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="16">
+        <f>C29</f>
+        <v>1000</v>
+      </c>
+      <c r="D30" s="26">
+        <v>56</v>
+      </c>
+      <c r="E30" s="17">
+        <f>C30*D30</f>
+        <v>56000</v>
+      </c>
+      <c r="F30" s="27">
+        <f>E30*0.002</f>
+        <v>112</v>
+      </c>
+      <c r="G30" s="26">
+        <f>E30*0.000068</f>
+        <v>3.8079999999999998</v>
+      </c>
+      <c r="H30" s="26">
+        <f>E30*0.00001</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I30" s="26">
+        <f>(F30+G30+H30)*0.07</f>
+        <v>8.145760000000001</v>
+      </c>
+      <c r="J30" s="26">
+        <f>E30-F30-G30-H30-I30</f>
+        <v>55875.486240000006</v>
+      </c>
+      <c r="K30" s="16">
+        <f>C30</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="31" customFormat="1" ht="18.75">
+      <c r="A31" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="7">
+        <f>(D30-D29)/D29</f>
+        <v>-0.10756972111553785</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="18">
+        <f>E30-E29</f>
+        <v>-6750</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18">
+        <f>J30-J29</f>
+        <v>-7013.4987349999938</v>
+      </c>
+      <c r="K31" s="18">
+        <f>J31</f>
+        <v>-7013.4987349999938</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.25">
+      <c r="A32" s="54"/>
+      <c r="B32" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="51">
+        <v>12000</v>
+      </c>
+      <c r="D32" s="52">
+        <v>74.5625</v>
+      </c>
+      <c r="E32" s="51">
+        <v>894750</v>
+      </c>
+      <c r="F32" s="51">
+        <v>1789.5</v>
+      </c>
+      <c r="G32" s="51">
+        <v>53.684999999999995</v>
+      </c>
+      <c r="H32" s="51">
+        <v>8.9475000000000016</v>
+      </c>
+      <c r="I32" s="51">
+        <v>129.64927499999999</v>
+      </c>
+      <c r="J32" s="51">
+        <v>896731.78177500004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="12.75">
+      <c r="A33" s="56">
+        <v>44658</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="91">
+        <v>1000</v>
+      </c>
+      <c r="D33" s="46">
+        <v>54.25</v>
+      </c>
+      <c r="E33" s="20">
+        <f>C33*D33</f>
+        <v>54250</v>
+      </c>
+      <c r="F33" s="20">
+        <f>E33*0.002</f>
+        <v>108.5</v>
+      </c>
+      <c r="G33" s="20">
+        <f>E33*0.00006</f>
+        <v>3.2549999999999999</v>
+      </c>
+      <c r="H33" s="20">
+        <f>E33*0.00001</f>
+        <v>0.54250000000000009</v>
+      </c>
+      <c r="I33" s="20">
+        <f>(F33+G33+H33)*0.07</f>
+        <v>7.8608250000000011</v>
+      </c>
+      <c r="J33" s="20">
+        <f>E33+F33+I33+G33+H33</f>
+        <v>54370.158325000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="B34" s="3">
+        <f>(D33-D32)/D32</f>
+        <v>-0.27242246437552387</v>
+      </c>
+      <c r="C34" s="2">
+        <f>SUM(C32:C33)</f>
+        <v>13000</v>
+      </c>
+      <c r="D34" s="47">
+        <f>E34/C34</f>
+        <v>73</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" ref="E34:J34" si="9">SUM(E32:E33)</f>
+        <v>949000</v>
+      </c>
+      <c r="F34" s="2">
         <f t="shared" si="9"/>
-        <v>2016</v>
-      </c>
-      <c r="G30" s="2">
+        <v>1898</v>
+      </c>
+      <c r="G34" s="2">
         <f t="shared" si="9"/>
-        <v>60.48</v>
-      </c>
-      <c r="H30" s="2">
+        <v>56.94</v>
+      </c>
+      <c r="H34" s="2">
         <f t="shared" si="9"/>
-        <v>10.080000000000002</v>
-      </c>
-      <c r="I30" s="2">
+        <v>9.490000000000002</v>
+      </c>
+      <c r="I34" s="2">
         <f t="shared" si="9"/>
-        <v>146.0592</v>
-      </c>
-      <c r="J30" s="2">
+        <v>137.51009999999999</v>
+      </c>
+      <c r="J34" s="2">
         <f t="shared" si="9"/>
-        <v>1010232.6192000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="14.25">
-      <c r="A31" s="54"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-    </row>
-    <row r="32" spans="1:11" ht="12.75">
-      <c r="A32" s="49">
+        <v>951101.94010000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="14.25">
+      <c r="A35" s="54"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+    </row>
+    <row r="36" spans="1:15" ht="12.75">
+      <c r="A36" s="49">
         <v>44634</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="88">
+      <c r="B36" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="88">
         <v>1000</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D36" s="41">
         <v>57.5</v>
       </c>
-      <c r="E32" s="18">
-        <f>C32*D32</f>
+      <c r="E36" s="18">
+        <f>C36*D36</f>
         <v>57500</v>
       </c>
-      <c r="F32" s="18">
-        <f>E32*0.002</f>
+      <c r="F36" s="18">
+        <f>E36*0.002</f>
         <v>115</v>
       </c>
-      <c r="G32" s="18">
-        <f>E32*0.00006</f>
+      <c r="G36" s="18">
+        <f>E36*0.00006</f>
         <v>3.45</v>
       </c>
-      <c r="H32" s="18">
-        <f>E32*0.00001</f>
+      <c r="H36" s="18">
+        <f>E36*0.00001</f>
         <v>0.57500000000000007</v>
       </c>
-      <c r="I32" s="18">
-        <f>(F32+G32+H32)*0.07</f>
+      <c r="I36" s="18">
+        <f>(F36+G36+H36)*0.07</f>
         <v>8.3317500000000013</v>
       </c>
-      <c r="J32" s="18">
-        <f>E32+F32+I32+G32+H32</f>
+      <c r="J36" s="18">
+        <f>E36+F36+I36+G36+H36</f>
         <v>57627.356749999992</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="13" customFormat="1" ht="12.75">
-      <c r="A33" s="49">
+    <row r="37" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="A37" s="49">
         <v>44866</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="16">
-        <f>C32</f>
+      <c r="C37" s="16">
+        <f>C36</f>
         <v>1000</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D37" s="26">
         <v>44.25</v>
       </c>
-      <c r="E33" s="17">
-        <f>C33*D33</f>
+      <c r="E37" s="17">
+        <f>C37*D37</f>
         <v>44250</v>
       </c>
-      <c r="F33" s="27">
-        <f>E33*0.002</f>
+      <c r="F37" s="27">
+        <f>E37*0.002</f>
         <v>88.5</v>
       </c>
-      <c r="G33" s="26">
-        <f>E33*0.000068</f>
+      <c r="G37" s="26">
+        <f>E37*0.000068</f>
         <v>3.0089999999999999</v>
       </c>
-      <c r="H33" s="26">
-        <f>E33*0.00001</f>
+      <c r="H37" s="26">
+        <f>E37*0.00001</f>
         <v>0.44250000000000006</v>
       </c>
-      <c r="I33" s="26">
-        <f>(F33+G33+H33)*0.07</f>
+      <c r="I37" s="26">
+        <f>(F37+G37+H37)*0.07</f>
         <v>6.4366050000000001</v>
       </c>
-      <c r="J33" s="26">
-        <f>E33-F33-G33-H33-I33</f>
+      <c r="J37" s="26">
+        <f>E37-F37-G37-H37-I37</f>
         <v>44151.611895000002</v>
       </c>
-      <c r="K33" s="16">
-        <f>C33</f>
+      <c r="K37" s="16">
+        <f>C37</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A34" s="49" t="s">
+    <row r="38" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A38" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="7">
-        <f>(D33-D32)/D32</f>
+      <c r="B38" s="7">
+        <f>(D37-D36)/D36</f>
         <v>-0.23043478260869565</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18">
-        <f>E33-E32</f>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="18">
+        <f>E37-E36</f>
         <v>-13250</v>
       </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18">
-        <f>J33-J32</f>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18">
+        <f>J37-J36</f>
         <v>-13475.74485499999</v>
       </c>
-      <c r="K34" s="18">
-        <f>J34</f>
+      <c r="K38" s="18">
+        <f>J38</f>
         <v>-13475.74485499999</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A35" s="56"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-    </row>
-    <row r="36" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A36" s="56"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="58"/>
-      <c r="O36" s="58"/>
-    </row>
-    <row r="37" spans="1:15" s="13" customFormat="1" ht="12.75">
-      <c r="A37" s="56"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A38" s="56"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-    </row>
-    <row r="39" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="39" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A39" s="56"/>
-      <c r="B39" s="13"/>
+      <c r="B39" s="25"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="46"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="58"/>
-      <c r="N39" s="58"/>
-      <c r="O39" s="58"/>
-    </row>
-    <row r="40" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K39" s="20"/>
+    </row>
+    <row r="40" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A40" s="56"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="10"/>
-    </row>
-    <row r="41" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D40" s="46"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+    </row>
+    <row r="41" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A41" s="56"/>
-      <c r="B41" s="25"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-    </row>
-    <row r="42" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="D41" s="34"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A42" s="56"/>
-      <c r="B42" s="13"/>
+      <c r="B42" s="25"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="46"/>
+      <c r="D42" s="11"/>
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="58"/>
-      <c r="N42" s="58"/>
-      <c r="O42" s="58"/>
-    </row>
-    <row r="43" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K42" s="20"/>
+    </row>
+    <row r="43" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A43" s="56"/>
+      <c r="B43" s="13"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D43" s="46"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+    </row>
+    <row r="44" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A44" s="56"/>
-      <c r="B44" s="25"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-    </row>
-    <row r="45" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="D44" s="34"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A45" s="56"/>
-      <c r="B45" s="13"/>
+      <c r="B45" s="25"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="46"/>
+      <c r="D45" s="11"/>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="58"/>
-      <c r="O45" s="58"/>
-    </row>
-    <row r="46" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K45" s="20"/>
+    </row>
+    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A46" s="56"/>
+      <c r="B46" s="13"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="10"/>
-    </row>
-    <row r="47" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D46" s="46"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="57"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+    </row>
+    <row r="47" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A47" s="56"/>
-      <c r="B47" s="25"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-    </row>
-    <row r="48" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="D47" s="34"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A48" s="56"/>
-      <c r="B48" s="13"/>
+      <c r="B48" s="25"/>
       <c r="C48" s="10"/>
-      <c r="D48" s="46"/>
+      <c r="D48" s="11"/>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
       <c r="J48" s="20"/>
-      <c r="K48" s="57"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
-    </row>
-    <row r="49" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K48" s="20"/>
+    </row>
+    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A49" s="56"/>
+      <c r="B49" s="13"/>
       <c r="C49" s="10"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="10"/>
-    </row>
-    <row r="50" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D49" s="46"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="57"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+    </row>
+    <row r="50" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A50" s="56"/>
-      <c r="B50" s="25"/>
       <c r="C50" s="10"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="92"/>
-    </row>
-    <row r="51" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="D50" s="34"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A51" s="56"/>
-      <c r="B51" s="13"/>
+      <c r="B51" s="25"/>
       <c r="C51" s="10"/>
-      <c r="D51" s="46"/>
+      <c r="D51" s="11"/>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="58"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="58"/>
-      <c r="O51" s="58"/>
-    </row>
-    <row r="52" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K51" s="20"/>
+    </row>
+    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A52" s="56"/>
+      <c r="B52" s="13"/>
       <c r="C52" s="10"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-    </row>
-    <row r="53" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D52" s="46"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+    </row>
+    <row r="53" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A53" s="56"/>
-      <c r="B53" s="25"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-    </row>
-    <row r="54" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="D53" s="34"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="10"/>
+    </row>
+    <row r="54" spans="1:15" s="31" customFormat="1" ht="18.75">
       <c r="A54" s="56"/>
-      <c r="B54" s="13"/>
+      <c r="B54" s="25"/>
       <c r="C54" s="10"/>
-      <c r="D54" s="46"/>
+      <c r="D54" s="11"/>
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
-      <c r="K54" s="57"/>
-      <c r="L54" s="58"/>
-      <c r="M54" s="58"/>
-      <c r="N54" s="58"/>
-      <c r="O54" s="58"/>
-    </row>
-    <row r="55" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="K54" s="92"/>
+    </row>
+    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A55" s="56"/>
+      <c r="B55" s="13"/>
       <c r="C55" s="10"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-    </row>
-    <row r="56" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="D55" s="46"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+    </row>
+    <row r="56" spans="1:15" s="13" customFormat="1" ht="12.75">
       <c r="A56" s="56"/>
-      <c r="B56" s="25"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="C57" s="2"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+    </row>
+    <row r="57" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A57" s="56"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
+    </row>
+    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A58" s="56"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+    </row>
+    <row r="59" spans="1:15" s="13" customFormat="1" ht="12.75">
+      <c r="A59" s="56"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+    </row>
+    <row r="60" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A60" s="56"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="C61" s="2"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -12894,7 +13036,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="89" customWidth="1"/>
@@ -14074,299 +14216,377 @@
       <c r="M30" s="21"/>
     </row>
     <row r="31" spans="1:13" ht="12.75">
-      <c r="A31" s="56">
-        <v>44876</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="10">
+      <c r="A31" s="49">
+        <v>44959</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16">
         <v>3000</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="17">
         <v>30.25</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="18">
         <f>C31*D31</f>
         <v>90750</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="18">
         <f>E31*0.002</f>
         <v>181.5</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="18">
         <f>E31*0.000068</f>
         <v>6.1710000000000003</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="18">
         <f>E31*0.00001</f>
         <v>0.90750000000000008</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="18">
         <f>(F31+G31+H31)*0.07</f>
         <v>13.200495</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="18">
         <f>E31+F31+I31+G31+H31</f>
         <v>90951.778995000001</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="12.75">
-      <c r="B32" s="25">
+      <c r="A32" s="90"/>
+      <c r="B32" s="7">
         <f>(D31-D30)/D30</f>
         <v>-0.24018838304552589</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="5">
         <f>SUM(C30:C31)</f>
         <v>27000</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="66">
         <f>E32/C32</f>
         <v>38.75</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="5">
         <f t="shared" ref="E32:J32" si="11">SUM(E30:E31)</f>
         <v>1046250</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="5">
         <f t="shared" si="11"/>
         <v>2092.5</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="5">
         <f t="shared" si="11"/>
         <v>71.14500000000001</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="5">
         <f t="shared" si="11"/>
         <v>10.4625</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="5">
         <f t="shared" si="11"/>
         <v>152.18752499999999</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="5">
         <f t="shared" si="11"/>
         <v>1048576.2950249999</v>
       </c>
       <c r="M32" s="21"/>
     </row>
-    <row r="33" spans="1:13" s="13" customFormat="1" ht="12.75">
-      <c r="A33" s="89"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-    </row>
-    <row r="34" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A34" s="49">
+    <row r="33" spans="1:13" ht="12.75">
+      <c r="A33" s="56">
+        <v>44959</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="10">
+        <v>3000</v>
+      </c>
+      <c r="D33" s="11">
+        <v>28.75</v>
+      </c>
+      <c r="E33" s="20">
+        <f>C33*D33</f>
+        <v>86250</v>
+      </c>
+      <c r="F33" s="20">
+        <f>E33*0.002</f>
+        <v>172.5</v>
+      </c>
+      <c r="G33" s="20">
+        <f>E33*0.000068</f>
+        <v>5.8650000000000002</v>
+      </c>
+      <c r="H33" s="20">
+        <f>E33*0.00001</f>
+        <v>0.86250000000000004</v>
+      </c>
+      <c r="I33" s="20">
+        <f>(F33+G33+H33)*0.07</f>
+        <v>12.545925000000002</v>
+      </c>
+      <c r="J33" s="20">
+        <f>E33+F33+I33+G33+H33</f>
+        <v>86441.773425000007</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="12.75">
+      <c r="B34" s="25">
+        <f>(D33-D32)/D32</f>
+        <v>-0.25806451612903225</v>
+      </c>
+      <c r="C34" s="22">
+        <f>SUM(C32:C33)</f>
+        <v>30000</v>
+      </c>
+      <c r="D34" s="65">
+        <f>E34/C34</f>
+        <v>37.75</v>
+      </c>
+      <c r="E34" s="22">
+        <f t="shared" ref="E34:J34" si="12">SUM(E32:E33)</f>
+        <v>1132500</v>
+      </c>
+      <c r="F34" s="22">
+        <f t="shared" si="12"/>
+        <v>2265</v>
+      </c>
+      <c r="G34" s="22">
+        <f t="shared" si="12"/>
+        <v>77.010000000000005</v>
+      </c>
+      <c r="H34" s="22">
+        <f t="shared" si="12"/>
+        <v>11.325000000000001</v>
+      </c>
+      <c r="I34" s="22">
+        <f t="shared" si="12"/>
+        <v>164.73345</v>
+      </c>
+      <c r="J34" s="22">
+        <f t="shared" si="12"/>
+        <v>1135018.0684499999</v>
+      </c>
+      <c r="M34" s="21"/>
+    </row>
+    <row r="35" spans="1:13" s="13" customFormat="1" ht="12.75">
+      <c r="A35" s="89"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A36" s="49">
         <v>44846</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="16">
+      <c r="B36" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="16">
         <v>3000</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D36" s="17">
         <v>27.75</v>
       </c>
-      <c r="E34" s="18">
-        <f>C34*D34</f>
+      <c r="E36" s="18">
+        <f>C36*D36</f>
         <v>83250</v>
       </c>
-      <c r="F34" s="18">
-        <f>E34*0.002</f>
+      <c r="F36" s="18">
+        <f>E36*0.002</f>
         <v>166.5</v>
       </c>
-      <c r="G34" s="18">
-        <f>E34*0.000068</f>
+      <c r="G36" s="18">
+        <f>E36*0.000068</f>
         <v>5.6609999999999996</v>
       </c>
-      <c r="H34" s="18">
-        <f>E34*0.00001</f>
+      <c r="H36" s="18">
+        <f>E36*0.00001</f>
         <v>0.83250000000000002</v>
       </c>
-      <c r="I34" s="18">
-        <f>(F34+G34+H34)*0.07</f>
+      <c r="I36" s="18">
+        <f>(F36+G36+H36)*0.07</f>
         <v>12.109545000000002</v>
       </c>
-      <c r="J34" s="18">
-        <f>E34+F34+I34+G34+H34</f>
+      <c r="J36" s="18">
+        <f>E36+F36+I36+G36+H36</f>
         <v>83435.103044999996</v>
       </c>
-      <c r="K34" s="32"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-    </row>
-    <row r="35" spans="1:13" ht="12.75">
-      <c r="A35" s="49">
+      <c r="K36" s="32"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+    </row>
+    <row r="37" spans="1:13" ht="12.75">
+      <c r="A37" s="49">
         <v>44853</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="16">
-        <f>C34</f>
+      <c r="C37" s="16">
+        <f>C36</f>
         <v>3000</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D37" s="26">
         <v>29.25</v>
       </c>
-      <c r="E35" s="17">
-        <f>C35*D35</f>
+      <c r="E37" s="17">
+        <f>C37*D37</f>
         <v>87750</v>
       </c>
-      <c r="F35" s="27">
-        <f>E35*0.002</f>
+      <c r="F37" s="27">
+        <f>E37*0.002</f>
         <v>175.5</v>
       </c>
-      <c r="G35" s="26">
-        <f>E35*0.000068</f>
+      <c r="G37" s="26">
+        <f>E37*0.000068</f>
         <v>5.9669999999999996</v>
       </c>
-      <c r="H35" s="26">
-        <f>E35*0.00001</f>
+      <c r="H37" s="26">
+        <f>E37*0.00001</f>
         <v>0.87750000000000006</v>
       </c>
-      <c r="I35" s="26">
-        <f>(F35+G35+H35)*0.07</f>
+      <c r="I37" s="26">
+        <f>(F37+G37+H37)*0.07</f>
         <v>12.764115000000002</v>
       </c>
-      <c r="J35" s="26">
-        <f>E35-F35-G35-H35-I35</f>
+      <c r="J37" s="26">
+        <f>E37-F37-G37-H37-I37</f>
         <v>87554.891384999995</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="12.75">
-      <c r="A36" s="49">
-        <f>DAYS360(A34,A35)</f>
+    <row r="38" spans="1:13" ht="12.75">
+      <c r="A38" s="49">
+        <f>DAYS360(A36,A37)</f>
         <v>7</v>
       </c>
-      <c r="B36" s="30">
-        <f>(D35-D34)/D34</f>
+      <c r="B38" s="30">
+        <f>(D37-D36)/D36</f>
         <v>5.4054054054054057E-2</v>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18">
-        <f>E35-E34</f>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="18">
+        <f>E37-E36</f>
         <v>4500</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18">
-        <f>J35-J34</f>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18">
+        <f>J37-J36</f>
         <v>4119.7883399999992</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A38" s="56">
+    <row r="40" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A40" s="56">
         <v>44846</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="10">
+      <c r="B40" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10">
         <v>3000</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D40" s="11">
         <v>28</v>
       </c>
-      <c r="E38" s="20">
-        <f>C38*D38</f>
+      <c r="E40" s="20">
+        <f>C40*D40</f>
         <v>84000</v>
       </c>
-      <c r="F38" s="20">
-        <f>E38*0.002</f>
+      <c r="F40" s="20">
+        <f>E40*0.002</f>
         <v>168</v>
       </c>
-      <c r="G38" s="20">
-        <f>E38*0.000068</f>
+      <c r="G40" s="20">
+        <f>E40*0.000068</f>
         <v>5.7119999999999997</v>
       </c>
-      <c r="H38" s="20">
-        <f>E38*0.00001</f>
+      <c r="H40" s="20">
+        <f>E40*0.00001</f>
         <v>0.84000000000000008</v>
       </c>
-      <c r="I38" s="20">
-        <f>(F38+G38+H38)*0.07</f>
+      <c r="I40" s="20">
+        <f>(F40+G40+H40)*0.07</f>
         <v>12.218640000000001</v>
       </c>
-      <c r="J38" s="20">
-        <f>E38+F38+I38+G38+H38</f>
+      <c r="J40" s="20">
+        <f>E40+F40+I40+G40+H40</f>
         <v>84186.770640000002</v>
       </c>
-      <c r="K38" s="32"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-    </row>
-    <row r="39" spans="1:13" ht="12.75">
-      <c r="A39" s="56">
+      <c r="K40" s="32"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+    </row>
+    <row r="41" spans="1:13" ht="12.75">
+      <c r="A41" s="56">
         <v>44853</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B41" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="10">
-        <f>C38</f>
+      <c r="C41" s="10">
+        <f>C40</f>
         <v>3000</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D41" s="34">
         <v>29.5</v>
       </c>
-      <c r="E39" s="11">
-        <f>C39*D39</f>
+      <c r="E41" s="11">
+        <f>C41*D41</f>
         <v>88500</v>
       </c>
-      <c r="F39" s="35">
-        <f>E39*0.002</f>
+      <c r="F41" s="35">
+        <f>E41*0.002</f>
         <v>177</v>
       </c>
-      <c r="G39" s="34">
-        <f>E39*0.000068</f>
+      <c r="G41" s="34">
+        <f>E41*0.000068</f>
         <v>6.0179999999999998</v>
       </c>
-      <c r="H39" s="34">
-        <f>E39*0.00001</f>
+      <c r="H41" s="34">
+        <f>E41*0.00001</f>
         <v>0.88500000000000012</v>
       </c>
-      <c r="I39" s="34">
-        <f>(F39+G39+H39)*0.07</f>
+      <c r="I41" s="34">
+        <f>(F41+G41+H41)*0.07</f>
         <v>12.87321</v>
       </c>
-      <c r="J39" s="34">
-        <f>E39-F39-G39-H39-I39</f>
+      <c r="J41" s="34">
+        <f>E41-F41-G41-H41-I41</f>
         <v>88303.223790000004</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="12.75">
-      <c r="A40" s="56">
-        <f>DAYS360(A38,A39)</f>
+    <row r="42" spans="1:13" ht="12.75">
+      <c r="A42" s="56">
+        <f>DAYS360(A40,A41)</f>
         <v>7</v>
       </c>
-      <c r="B40" s="12">
-        <f>(D39-D38)/D38</f>
+      <c r="B42" s="12">
+        <f>(D41-D40)/D40</f>
         <v>5.3571428571428568E-2</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="20">
-        <f>E39-E38</f>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="20">
+        <f>E41-E40</f>
         <v>4500</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20">
-        <f>J39-J38</f>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20">
+        <f>J41-J40</f>
         <v>4116.4531500000012</v>
       </c>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26202"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11544" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F09480-6FE9-4287-A285-82C68B4A87CB}"/>
+  <xr:revisionPtr revIDLastSave="11552" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41CB907D-114C-4410-BC75-BAD1177BF08C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE (2)" sheetId="206" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="37">
   <si>
     <t>KCE</t>
   </si>
@@ -25272,96 +25272,158 @@
       <c r="N8" s="62"/>
     </row>
     <row r="9" spans="1:14" ht="12.75">
-      <c r="A9" s="77">
-        <v>44950</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="79">
+      <c r="A9" s="82">
+        <v>44964</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="84">
         <v>10000</v>
       </c>
-      <c r="D9" s="80">
-        <v>18.7</v>
-      </c>
-      <c r="E9" s="94">
+      <c r="D9" s="85">
+        <v>18.3</v>
+      </c>
+      <c r="E9" s="86">
         <f>C9*D9</f>
-        <v>187000</v>
-      </c>
-      <c r="F9" s="94">
+        <v>183000</v>
+      </c>
+      <c r="F9" s="86">
         <f>E9*0.002</f>
-        <v>374</v>
-      </c>
-      <c r="G9" s="94">
+        <v>366</v>
+      </c>
+      <c r="G9" s="86">
         <f>E9*0.000068</f>
-        <v>12.715999999999999</v>
-      </c>
-      <c r="H9" s="94">
+        <v>12.443999999999999</v>
+      </c>
+      <c r="H9" s="86">
         <f>E9*0.00001</f>
-        <v>1.87</v>
-      </c>
-      <c r="I9" s="94">
+        <v>1.83</v>
+      </c>
+      <c r="I9" s="86">
         <f>(F9+G9+H9)*0.07</f>
-        <v>27.201020000000003</v>
-      </c>
-      <c r="J9" s="94">
+        <v>26.619180000000004</v>
+      </c>
+      <c r="J9" s="86">
         <f>E9+F9+I9+G9+H9</f>
-        <v>187415.78701999999</v>
+        <v>183406.89317999998</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="12.75">
-      <c r="A10" s="77"/>
-      <c r="B10" s="81">
+      <c r="A10" s="82"/>
+      <c r="B10" s="87">
         <f>(D9-D8)/D8</f>
-        <v>-2.094240837696346E-2</v>
-      </c>
-      <c r="C10" s="79">
+        <v>-4.1884816753926739E-2</v>
+      </c>
+      <c r="C10" s="84">
         <f>SUM(C8:C9)</f>
         <v>40000</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="85">
         <f>E10/C10</f>
-        <v>19</v>
-      </c>
-      <c r="E10" s="79">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E10" s="84">
         <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
-        <v>760000</v>
-      </c>
-      <c r="F10" s="79">
+        <v>756000</v>
+      </c>
+      <c r="F10" s="84">
         <f t="shared" si="3"/>
-        <v>1520</v>
-      </c>
-      <c r="G10" s="79">
+        <v>1512</v>
+      </c>
+      <c r="G10" s="84">
         <f t="shared" si="3"/>
-        <v>50.904000000000003</v>
-      </c>
-      <c r="H10" s="79">
+        <v>50.632000000000005</v>
+      </c>
+      <c r="H10" s="84">
         <f t="shared" si="3"/>
-        <v>7.6000000000000005</v>
-      </c>
-      <c r="I10" s="79">
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="I10" s="84">
         <f t="shared" si="3"/>
-        <v>110.49528000000001</v>
-      </c>
-      <c r="J10" s="79">
+        <v>109.91344000000001</v>
+      </c>
+      <c r="J10" s="84">
         <f t="shared" si="3"/>
-        <v>761688.99928000011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="56"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="J12" s="53"/>
+        <v>757680.10544000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="12.75">
+      <c r="A11" s="77">
+        <v>44964</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="80">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E11" s="94">
+        <f>C11*D11</f>
+        <v>179000</v>
+      </c>
+      <c r="F11" s="94">
+        <f>E11*0.002</f>
+        <v>358</v>
+      </c>
+      <c r="G11" s="94">
+        <f>E11*0.000068</f>
+        <v>12.172000000000001</v>
+      </c>
+      <c r="H11" s="94">
+        <f>E11*0.00001</f>
+        <v>1.79</v>
+      </c>
+      <c r="I11" s="94">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>26.037340000000004</v>
+      </c>
+      <c r="J11" s="94">
+        <f>E11+F11+I11+G11+H11</f>
+        <v>179397.99934000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="12.75">
+      <c r="A12" s="77"/>
+      <c r="B12" s="81">
+        <f>(D11-D10)/D10</f>
+        <v>-5.2910052910052914E-2</v>
+      </c>
+      <c r="C12" s="79">
+        <f>SUM(C10:C11)</f>
+        <v>50000</v>
+      </c>
+      <c r="D12" s="80">
+        <f>E12/C12</f>
+        <v>18.7</v>
+      </c>
+      <c r="E12" s="79">
+        <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
+        <v>935000</v>
+      </c>
+      <c r="F12" s="79">
+        <f t="shared" si="4"/>
+        <v>1870</v>
+      </c>
+      <c r="G12" s="79">
+        <f t="shared" si="4"/>
+        <v>62.804000000000002</v>
+      </c>
+      <c r="H12" s="79">
+        <f t="shared" si="4"/>
+        <v>9.3500000000000014</v>
+      </c>
+      <c r="I12" s="79">
+        <f t="shared" si="4"/>
+        <v>135.95078000000001</v>
+      </c>
+      <c r="J12" s="79">
+        <f t="shared" si="4"/>
+        <v>937078.10478000005</v>
+      </c>
     </row>
     <row r="13" spans="1:14" s="78" customFormat="1">
       <c r="A13" s="82"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11579" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96446A8B-3A1F-42DD-AAC6-561C22FAF6A7}"/>
+  <xr:revisionPtr revIDLastSave="11596" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A1F028-A2E9-4090-933D-7131335F7664}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="36">
   <si>
     <t>KCE</t>
   </si>
@@ -16539,7 +16539,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="89" customWidth="1"/>
@@ -17355,1642 +17355,1724 @@
       <c r="N22" s="59"/>
       <c r="O22" s="59"/>
     </row>
-    <row r="23" spans="1:15" s="1" customFormat="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+    <row r="23" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A23" s="49">
+        <v>44398</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D23" s="41">
+        <v>37.75</v>
+      </c>
+      <c r="E23" s="18">
+        <f>C23*D23</f>
+        <v>94375</v>
+      </c>
+      <c r="F23" s="18">
+        <f>E23*0.002</f>
+        <v>188.75</v>
+      </c>
+      <c r="G23" s="18">
+        <f>E23*0.00006</f>
+        <v>5.6625000000000005</v>
+      </c>
+      <c r="H23" s="18">
+        <f>E23*0.00001</f>
+        <v>0.94375000000000009</v>
+      </c>
+      <c r="I23" s="18">
+        <f>(F23+G23+H23)*0.07</f>
+        <v>13.6749375</v>
+      </c>
+      <c r="J23" s="18">
+        <f>E23+F23+I23+G23+H23</f>
+        <v>94584.031187500019</v>
+      </c>
       <c r="K23" s="57"/>
       <c r="L23" s="58"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
     </row>
     <row r="24" spans="1:15" s="1" customFormat="1">
-      <c r="A24" s="50"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="59"/>
+      <c r="A24" s="49">
+        <v>44951</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D24" s="26">
+        <v>24.1</v>
+      </c>
+      <c r="E24" s="17">
+        <f>C24*D24</f>
+        <v>60250</v>
+      </c>
+      <c r="F24" s="27">
+        <f>E24*0.002</f>
+        <v>120.5</v>
+      </c>
+      <c r="G24" s="26">
+        <f>E24*0.000068</f>
+        <v>4.0969999999999995</v>
+      </c>
+      <c r="H24" s="26">
+        <f>E24*0.00001</f>
+        <v>0.60250000000000004</v>
+      </c>
+      <c r="I24" s="26">
+        <f>(F24+G24+H24)*0.07</f>
+        <v>8.7639650000000007</v>
+      </c>
+      <c r="J24" s="26">
+        <f>E24-F24-G24-H24-I24</f>
+        <v>60116.036534999999</v>
+      </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-    </row>
-    <row r="26" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A26" s="49">
-        <v>44543</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D26" s="41">
-        <v>29.5</v>
-      </c>
-      <c r="E26" s="18">
-        <f>C26*D26</f>
-        <v>73750</v>
-      </c>
-      <c r="F26" s="18">
-        <f>E26*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G26" s="18">
-        <f>E26*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H26" s="18">
-        <f>E26*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I26" s="18">
-        <f>(F26+G26+H26)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J26" s="18">
-        <f>E26+F26+I26+G26+H26</f>
-        <v>73913.348875000011</v>
+      <c r="A25" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18">
+        <f>E24-E23</f>
+        <v>-34125</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18">
+        <f>J24-J23</f>
+        <v>-34467.99465250002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A26" s="54"/>
+      <c r="B26" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="51">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="52">
+        <v>40</v>
+      </c>
+      <c r="E26" s="51">
+        <v>200000</v>
+      </c>
+      <c r="F26" s="51">
+        <v>400</v>
+      </c>
+      <c r="G26" s="51">
+        <v>12</v>
+      </c>
+      <c r="H26" s="51">
+        <v>2</v>
+      </c>
+      <c r="I26" s="51">
+        <v>28.980000000000004</v>
+      </c>
+      <c r="J26" s="51">
+        <v>200442.98</v>
       </c>
       <c r="K26" s="57"/>
       <c r="L26" s="58"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1">
-      <c r="A27" s="49">
-        <v>44923</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="16">
-        <f>C26</f>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+    </row>
+    <row r="27" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A27" s="56">
+        <v>44462</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10">
         <v>2500</v>
       </c>
-      <c r="D27" s="26">
-        <v>20.3</v>
-      </c>
-      <c r="E27" s="17">
+      <c r="D27" s="46">
+        <v>19</v>
+      </c>
+      <c r="E27" s="20">
         <f>C27*D27</f>
-        <v>50750</v>
-      </c>
-      <c r="F27" s="27">
+        <v>47500</v>
+      </c>
+      <c r="F27" s="20">
         <f>E27*0.002</f>
-        <v>101.5</v>
-      </c>
-      <c r="G27" s="26">
-        <f>E27*0.000068</f>
-        <v>3.4510000000000001</v>
-      </c>
-      <c r="H27" s="26">
+        <v>95</v>
+      </c>
+      <c r="G27" s="20">
+        <f>E27*0.00006</f>
+        <v>2.85</v>
+      </c>
+      <c r="H27" s="20">
         <f>E27*0.00001</f>
-        <v>0.50750000000000006</v>
-      </c>
-      <c r="I27" s="26">
+        <v>0.47500000000000003</v>
+      </c>
+      <c r="I27" s="20">
         <f>(F27+G27+H27)*0.07</f>
-        <v>7.3820949999999996</v>
-      </c>
-      <c r="J27" s="26">
-        <f>E27-F27-G27-H27-I27</f>
-        <v>50637.159404999999</v>
-      </c>
+        <v>6.8827499999999997</v>
+      </c>
+      <c r="J27" s="20">
+        <f>E27+F27+I27+G27+H27</f>
+        <v>47605.207749999994</v>
+      </c>
+      <c r="K27" s="57"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
     </row>
     <row r="28" spans="1:15" s="1" customFormat="1">
-      <c r="A28" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18">
-        <f>E27-E26</f>
-        <v>-23000</v>
-      </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18">
-        <f>J27-J26</f>
-        <v>-23276.189470000012</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" ht="14.25">
-      <c r="A29" s="54"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="59"/>
-    </row>
-    <row r="30" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A30" s="49">
-        <v>44550</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D30" s="41">
-        <v>29.5</v>
-      </c>
-      <c r="E30" s="18">
-        <f>C30*D30</f>
-        <v>73750</v>
-      </c>
-      <c r="F30" s="18">
-        <f>E30*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G30" s="18">
-        <f>E30*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H30" s="18">
-        <f>E30*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I30" s="18">
-        <f>(F30+G30+H30)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J30" s="18">
-        <f>E30+F30+I30+G30+H30</f>
-        <v>73913.348875000011</v>
-      </c>
+      <c r="A28" s="50"/>
+      <c r="B28" s="3">
+        <f>(D27-D26)/D26</f>
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="C28" s="2">
+        <f>SUM(C26:C27)</f>
+        <v>7500</v>
+      </c>
+      <c r="D28" s="47">
+        <f>E28/C28</f>
+        <v>33</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" ref="E28:J28" si="4">SUM(E26:E27)</f>
+        <v>247500</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="4"/>
+        <v>495</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="4"/>
+        <v>14.85</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="4"/>
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="4"/>
+        <v>35.862750000000005</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="4"/>
+        <v>248048.18775000001</v>
+      </c>
+      <c r="K28" s="57"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+    </row>
+    <row r="29" spans="1:15" s="1" customFormat="1">
+      <c r="A29" s="49"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1" ht="14.25">
+      <c r="A30" s="54"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
       <c r="K30" s="57"/>
       <c r="L30" s="58"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-    </row>
-    <row r="31" spans="1:15" s="1" customFormat="1">
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+    </row>
+    <row r="31" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A31" s="49">
+        <v>44550</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D31" s="41">
+        <v>29.5</v>
+      </c>
+      <c r="E31" s="18">
+        <f>C31*D31</f>
+        <v>73750</v>
+      </c>
+      <c r="F31" s="18">
+        <f>E31*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G31" s="18">
+        <f>E31*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H31" s="18">
+        <f>E31*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I31" s="18">
+        <f>(F31+G31+H31)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J31" s="18">
+        <f>E31+F31+I31+G31+H31</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K31" s="57"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1">
+      <c r="A32" s="49">
         <v>44922</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B32" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="16">
-        <f>C30</f>
+      <c r="C32" s="16">
+        <f>C31</f>
         <v>2500</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D32" s="26">
         <v>19.7</v>
       </c>
-      <c r="E31" s="17">
-        <f>C31*D31</f>
+      <c r="E32" s="17">
+        <f>C32*D32</f>
         <v>49250</v>
       </c>
-      <c r="F31" s="27">
-        <f>E31*0.002</f>
+      <c r="F32" s="27">
+        <f>E32*0.002</f>
         <v>98.5</v>
       </c>
-      <c r="G31" s="26">
-        <f>E31*0.000068</f>
+      <c r="G32" s="26">
+        <f>E32*0.000068</f>
         <v>3.3489999999999998</v>
       </c>
-      <c r="H31" s="26">
-        <f>E31*0.00001</f>
+      <c r="H32" s="26">
+        <f>E32*0.00001</f>
         <v>0.49250000000000005</v>
       </c>
-      <c r="I31" s="26">
-        <f>(F31+G31+H31)*0.07</f>
+      <c r="I32" s="26">
+        <f>(F32+G32+H32)*0.07</f>
         <v>7.1639050000000015</v>
       </c>
-      <c r="J31" s="26">
-        <f>E31-F31-G31-H31-I31</f>
+      <c r="J32" s="26">
+        <f>E32-F32-G32-H32-I32</f>
         <v>49140.494594999996</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="1" customFormat="1">
-      <c r="A32" s="49" t="s">
+    <row r="33" spans="1:15" s="1" customFormat="1">
+      <c r="A33" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18">
-        <f>E31-E30</f>
+      <c r="B33" s="15"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18">
+        <f>E32-E31</f>
         <v>-24500</v>
       </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18">
-        <f>J31-J30</f>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18">
+        <f>J32-J31</f>
         <v>-24772.854280000014</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="1" customFormat="1">
-      <c r="A33" s="50"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="59"/>
-    </row>
-    <row r="34" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A34" s="49">
-        <v>44624</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="16">
-        <v>2500</v>
-      </c>
-      <c r="D34" s="41">
-        <v>25.75</v>
-      </c>
-      <c r="E34" s="18">
-        <f>C34*D34</f>
-        <v>64375</v>
-      </c>
-      <c r="F34" s="18">
-        <f>E34*0.002</f>
-        <v>128.75</v>
-      </c>
-      <c r="G34" s="18">
-        <f>E34*0.00006</f>
-        <v>3.8625000000000003</v>
-      </c>
-      <c r="H34" s="18">
-        <f>E34*0.00001</f>
-        <v>0.64375000000000004</v>
-      </c>
-      <c r="I34" s="18">
-        <f>(F34+G34+H34)*0.07</f>
-        <v>9.3279375000000027</v>
-      </c>
-      <c r="J34" s="18">
-        <f>E34+F34+I34+G34+H34</f>
-        <v>64517.584187500004</v>
-      </c>
+    <row r="34" spans="1:15" s="1" customFormat="1">
+      <c r="A34" s="50"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
       <c r="K34" s="57"/>
       <c r="L34" s="58"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="58"/>
-      <c r="O34" s="58"/>
-    </row>
-    <row r="35" spans="1:15" s="1" customFormat="1">
+      <c r="N34" s="59"/>
+      <c r="O34" s="59"/>
+    </row>
+    <row r="35" spans="1:15" s="19" customFormat="1" ht="15">
       <c r="A35" s="49">
+        <v>44624</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D35" s="41">
+        <v>25.75</v>
+      </c>
+      <c r="E35" s="18">
+        <f>C35*D35</f>
+        <v>64375</v>
+      </c>
+      <c r="F35" s="18">
+        <f>E35*0.002</f>
+        <v>128.75</v>
+      </c>
+      <c r="G35" s="18">
+        <f>E35*0.00006</f>
+        <v>3.8625000000000003</v>
+      </c>
+      <c r="H35" s="18">
+        <f>E35*0.00001</f>
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="I35" s="18">
+        <f>(F35+G35+H35)*0.07</f>
+        <v>9.3279375000000027</v>
+      </c>
+      <c r="J35" s="18">
+        <f>E35+F35+I35+G35+H35</f>
+        <v>64517.584187500004</v>
+      </c>
+      <c r="K35" s="57"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
+    </row>
+    <row r="36" spans="1:15" s="1" customFormat="1">
+      <c r="A36" s="49">
         <v>44866</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B36" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="16">
-        <f>C34</f>
+      <c r="C36" s="16">
+        <f>C35</f>
         <v>2500</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D36" s="26">
         <v>19.2</v>
       </c>
-      <c r="E35" s="17">
-        <f>C35*D35</f>
+      <c r="E36" s="17">
+        <f>C36*D36</f>
         <v>48000</v>
       </c>
-      <c r="F35" s="27">
-        <f>E35*0.002</f>
+      <c r="F36" s="27">
+        <f>E36*0.002</f>
         <v>96</v>
       </c>
-      <c r="G35" s="26">
-        <f>E35*0.000068</f>
+      <c r="G36" s="26">
+        <f>E36*0.000068</f>
         <v>3.2639999999999998</v>
       </c>
-      <c r="H35" s="26">
-        <f>E35*0.00001</f>
+      <c r="H36" s="26">
+        <f>E36*0.00001</f>
         <v>0.48000000000000004</v>
       </c>
-      <c r="I35" s="26">
-        <f>(F35+G35+H35)*0.07</f>
+      <c r="I36" s="26">
+        <f>(F36+G36+H36)*0.07</f>
         <v>6.9820800000000007</v>
       </c>
-      <c r="J35" s="26">
-        <f>E35-F35-G35-H35-I35</f>
+      <c r="J36" s="26">
+        <f>E36-F36-G36-H36-I36</f>
         <v>47893.273919999992</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="1" customFormat="1">
-      <c r="A36" s="49" t="s">
+    <row r="37" spans="1:15" s="1" customFormat="1">
+      <c r="A37" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18">
-        <f>E35-E34</f>
+      <c r="B37" s="15"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18">
+        <f>E36-E35</f>
         <v>-16375</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18">
-        <f>J35-J34</f>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18">
+        <f>J36-J35</f>
         <v>-16624.310267500012</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="1" customFormat="1">
-      <c r="A37" s="56"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-    </row>
     <row r="38" spans="1:15" s="1" customFormat="1">
-      <c r="A38" s="56">
-        <v>44627</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="10">
-        <v>2500</v>
-      </c>
-      <c r="D38" s="46">
-        <v>25.75</v>
-      </c>
-      <c r="E38" s="20">
-        <f>C38*D38</f>
-        <v>64375</v>
-      </c>
-      <c r="F38" s="20">
-        <f>E38*0.002</f>
-        <v>128.75</v>
-      </c>
-      <c r="G38" s="20">
-        <f>E38*0.00006</f>
-        <v>3.8625000000000003</v>
-      </c>
-      <c r="H38" s="20">
-        <f>E38*0.00001</f>
-        <v>0.64375000000000004</v>
-      </c>
-      <c r="I38" s="20">
-        <f>(F38+G38+H38)*0.07</f>
-        <v>9.3279375000000027</v>
-      </c>
-      <c r="J38" s="20">
-        <f>E38+F38+I38+G38+H38</f>
-        <v>64517.584187500004</v>
-      </c>
+      <c r="A38" s="56"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
     </row>
     <row r="39" spans="1:15" s="1" customFormat="1">
       <c r="A39" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D39" s="46">
+        <v>25.75</v>
+      </c>
+      <c r="E39" s="20">
+        <f>C39*D39</f>
+        <v>64375</v>
+      </c>
+      <c r="F39" s="20">
+        <f>E39*0.002</f>
+        <v>128.75</v>
+      </c>
+      <c r="G39" s="20">
+        <f>E39*0.00006</f>
+        <v>3.8625000000000003</v>
+      </c>
+      <c r="H39" s="20">
+        <f>E39*0.00001</f>
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="I39" s="20">
+        <f>(F39+G39+H39)*0.07</f>
+        <v>9.3279375000000027</v>
+      </c>
+      <c r="J39" s="20">
+        <f>E39+F39+I39+G39+H39</f>
+        <v>64517.584187500004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="1" customFormat="1">
+      <c r="A40" s="56">
         <v>44634</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B40" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="10">
-        <f>C38</f>
+      <c r="C40" s="10">
+        <f>C39</f>
         <v>2500</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D40" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="E39" s="11">
-        <f>C39*D39</f>
+      <c r="E40" s="11">
+        <f>C40*D40</f>
         <v>50250</v>
       </c>
-      <c r="F39" s="35">
-        <f>E39*0.002</f>
+      <c r="F40" s="35">
+        <f>E40*0.002</f>
         <v>100.5</v>
       </c>
-      <c r="G39" s="34">
-        <f>E39*0.000068</f>
+      <c r="G40" s="34">
+        <f>E40*0.000068</f>
         <v>3.4169999999999998</v>
       </c>
-      <c r="H39" s="34">
-        <f>E39*0.00001</f>
+      <c r="H40" s="34">
+        <f>E40*0.00001</f>
         <v>0.50250000000000006</v>
       </c>
-      <c r="I39" s="34">
-        <f>(F39+G39+H39)*0.07</f>
+      <c r="I40" s="34">
+        <f>(F40+G40+H40)*0.07</f>
         <v>7.3093650000000006</v>
       </c>
-      <c r="J39" s="34">
-        <f>E39-F39-G39-H39-I39</f>
+      <c r="J40" s="34">
+        <f>E40-F40-G40-H40-I40</f>
         <v>50138.271134999995</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="1" customFormat="1">
-      <c r="A40" s="56" t="s">
+    <row r="41" spans="1:15" s="1" customFormat="1">
+      <c r="A41" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="20">
-        <f>E39-E38</f>
+      <c r="B41" s="13"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="20">
+        <f>E40-E39</f>
         <v>-14125</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20">
-        <f>J39-J38</f>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20">
+        <f>J40-J39</f>
         <v>-14379.313052500009</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="1" customFormat="1">
-      <c r="A41" s="56">
-        <v>44627</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="10">
-        <v>2500</v>
-      </c>
-      <c r="D41" s="46">
-        <v>19</v>
-      </c>
-      <c r="E41" s="20">
-        <f>C41*D41</f>
-        <v>47500</v>
-      </c>
-      <c r="F41" s="20">
-        <f>E41*0.002</f>
-        <v>95</v>
-      </c>
-      <c r="G41" s="20">
-        <f>E41*0.00006</f>
-        <v>2.85</v>
-      </c>
-      <c r="H41" s="20">
-        <f>E41*0.00001</f>
-        <v>0.47500000000000003</v>
-      </c>
-      <c r="I41" s="20">
-        <f>(F41+G41+H41)*0.07</f>
-        <v>6.8827499999999997</v>
-      </c>
-      <c r="J41" s="20">
-        <f>E41+F41+I41+G41+H41</f>
-        <v>47605.207749999994</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="1" customFormat="1">
       <c r="A42" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D42" s="46">
+        <v>19</v>
+      </c>
+      <c r="E42" s="20">
+        <f>C42*D42</f>
+        <v>47500</v>
+      </c>
+      <c r="F42" s="20">
+        <f>E42*0.002</f>
+        <v>95</v>
+      </c>
+      <c r="G42" s="20">
+        <f>E42*0.00006</f>
+        <v>2.85</v>
+      </c>
+      <c r="H42" s="20">
+        <f>E42*0.00001</f>
+        <v>0.47500000000000003</v>
+      </c>
+      <c r="I42" s="20">
+        <f>(F42+G42+H42)*0.07</f>
+        <v>6.8827499999999997</v>
+      </c>
+      <c r="J42" s="20">
+        <f>E42+F42+I42+G42+H42</f>
+        <v>47605.207749999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" s="1" customFormat="1">
+      <c r="A43" s="56">
         <v>44634</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B43" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="10">
-        <f>C41</f>
+      <c r="C43" s="10">
+        <f>C42</f>
         <v>2500</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D43" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="E42" s="11">
-        <f>C42*D42</f>
+      <c r="E43" s="11">
+        <f>C43*D43</f>
         <v>50250</v>
       </c>
-      <c r="F42" s="35">
-        <f>E42*0.002</f>
+      <c r="F43" s="35">
+        <f>E43*0.002</f>
         <v>100.5</v>
       </c>
-      <c r="G42" s="34">
-        <f>E42*0.000068</f>
+      <c r="G43" s="34">
+        <f>E43*0.000068</f>
         <v>3.4169999999999998</v>
       </c>
-      <c r="H42" s="34">
-        <f>E42*0.00001</f>
+      <c r="H43" s="34">
+        <f>E43*0.00001</f>
         <v>0.50250000000000006</v>
       </c>
-      <c r="I42" s="34">
-        <f>(F42+G42+H42)*0.07</f>
+      <c r="I43" s="34">
+        <f>(F43+G43+H43)*0.07</f>
         <v>7.3093650000000006</v>
       </c>
-      <c r="J42" s="34">
-        <f>E42-F42-G42-H42-I42</f>
+      <c r="J43" s="34">
+        <f>E43-F43-G43-H43-I43</f>
         <v>50138.271134999995</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="1" customFormat="1">
-      <c r="A43" s="56" t="s">
+    <row r="44" spans="1:15" s="1" customFormat="1">
+      <c r="A44" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="12">
-        <f>(D42-D41)/D41</f>
+      <c r="B44" s="12">
+        <f>(D43-D42)/D42</f>
         <v>5.7894736842105339E-2</v>
       </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="20">
-        <f>E42-E41</f>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="20">
+        <f>E43-E42</f>
         <v>2750</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20">
-        <f>J42-J41</f>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20">
+        <f>J43-J42</f>
         <v>2533.0633850000013</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="1" customFormat="1" ht="12">
-      <c r="A44" s="50"/>
-      <c r="D44" s="47"/>
-      <c r="J44" s="53"/>
-    </row>
-    <row r="45" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A45" s="56">
+    <row r="45" spans="1:15" s="1" customFormat="1" ht="12">
+      <c r="A45" s="50"/>
+      <c r="D45" s="47"/>
+      <c r="J45" s="53"/>
+    </row>
+    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A46" s="56">
         <v>44624</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="16">
+      <c r="B46" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="16">
         <v>2500</v>
       </c>
-      <c r="D45" s="46">
+      <c r="D46" s="46">
         <v>25.75</v>
       </c>
-      <c r="E45" s="20">
-        <f>C45*D45</f>
+      <c r="E46" s="20">
+        <f>C46*D46</f>
         <v>64375</v>
       </c>
-      <c r="F45" s="20">
-        <f>E45*0.002</f>
+      <c r="F46" s="20">
+        <f>E46*0.002</f>
         <v>128.75</v>
       </c>
-      <c r="G45" s="20">
-        <f>E45*0.00006</f>
+      <c r="G46" s="20">
+        <f>E46*0.00006</f>
         <v>3.8625000000000003</v>
       </c>
-      <c r="H45" s="20">
-        <f>E45*0.00001</f>
+      <c r="H46" s="20">
+        <f>E46*0.00001</f>
         <v>0.64375000000000004</v>
       </c>
-      <c r="I45" s="20">
-        <f>(F45+G45+H45)*0.07</f>
+      <c r="I46" s="20">
+        <f>(F46+G46+H46)*0.07</f>
         <v>9.3279375000000027</v>
       </c>
-      <c r="J45" s="20">
-        <f>E45+F45+I45+G45+H45</f>
+      <c r="J46" s="20">
+        <f>E46+F46+I46+G46+H46</f>
         <v>64517.584187500004</v>
       </c>
-      <c r="K45" s="57"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="58"/>
-      <c r="O45" s="58"/>
-    </row>
-    <row r="46" spans="1:15" s="13" customFormat="1">
-      <c r="A46" s="56" t="e">
+      <c r="K46" s="57"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+    </row>
+    <row r="47" spans="1:15" s="13" customFormat="1">
+      <c r="A47" s="56" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B47" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="10">
-        <f>C45</f>
-        <v>2500</v>
-      </c>
-      <c r="D46" s="26">
-        <v>29.5</v>
-      </c>
-      <c r="E46" s="11">
-        <f>C46*D46</f>
-        <v>73750</v>
-      </c>
-      <c r="F46" s="35">
-        <f>E46*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G46" s="34">
-        <f>E46*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H46" s="34">
-        <f>E46*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I46" s="34">
-        <f>(F46+G46+H46)*0.07</f>
-        <v>10.727675000000001</v>
-      </c>
-      <c r="J46" s="34">
-        <f>E46-F46-G46-H46-I46</f>
-        <v>73586.019824999996</v>
-      </c>
-      <c r="K46" s="10">
+      <c r="C47" s="10">
         <f>C46</f>
         <v>2500</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A47" s="56" t="s">
+      <c r="D47" s="26">
+        <v>29.5</v>
+      </c>
+      <c r="E47" s="11">
+        <f>C47*D47</f>
+        <v>73750</v>
+      </c>
+      <c r="F47" s="35">
+        <f>E47*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G47" s="34">
+        <f>E47*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H47" s="34">
+        <f>E47*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I47" s="34">
+        <f>(F47+G47+H47)*0.07</f>
+        <v>10.727675000000001</v>
+      </c>
+      <c r="J47" s="34">
+        <f>E47-F47-G47-H47-I47</f>
+        <v>73586.019824999996</v>
+      </c>
+      <c r="K47" s="10">
+        <f>C47</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A48" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="25">
-        <f>(D46-D45)/D45</f>
+      <c r="B48" s="25">
+        <f>(D47-D46)/D46</f>
         <v>0.14563106796116504</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="20">
-        <f>E46-E45</f>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="20">
+        <f>E47-E46</f>
         <v>9375</v>
       </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20">
-        <f>J46-J45</f>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20">
+        <f>J47-J46</f>
         <v>9068.4356374999916</v>
       </c>
-      <c r="K47" s="20">
-        <f>J47</f>
+      <c r="K48" s="20">
+        <f>J48</f>
         <v>9068.4356374999916</v>
       </c>
     </row>
-    <row r="48" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A48" s="49">
+    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A49" s="49">
         <v>44550</v>
       </c>
-      <c r="B48" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="16">
+      <c r="B49" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="16">
         <v>2500</v>
       </c>
-      <c r="D48" s="46">
+      <c r="D49" s="46">
         <v>29.5</v>
       </c>
-      <c r="E48" s="20">
-        <f>C48*D48</f>
-        <v>73750</v>
-      </c>
-      <c r="F48" s="20">
-        <f>E48*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G48" s="20">
-        <f>E48*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H48" s="20">
-        <f>E48*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I48" s="20">
-        <f>(F48+G48+H48)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J48" s="20">
-        <f>E48+F48+I48+G48+H48</f>
-        <v>73913.348875000011</v>
-      </c>
-      <c r="K48" s="57"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
-    </row>
-    <row r="49" spans="1:15" s="13" customFormat="1">
-      <c r="A49" s="56" t="e">
-        <f>A46</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="10">
-        <f>C48</f>
-        <v>2500</v>
-      </c>
-      <c r="D49" s="34">
-        <f>D46</f>
-        <v>29.5</v>
-      </c>
-      <c r="E49" s="11">
+      <c r="E49" s="20">
         <f>C49*D49</f>
         <v>73750</v>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="20">
         <f>E49*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G49" s="34">
-        <f>E49*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H49" s="34">
+      <c r="G49" s="20">
+        <f>E49*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H49" s="20">
         <f>E49*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I49" s="34">
+      <c r="I49" s="20">
         <f>(F49+G49+H49)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J49" s="20">
+        <f>E49+F49+I49+G49+H49</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K49" s="57"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+    </row>
+    <row r="50" spans="1:15" s="13" customFormat="1">
+      <c r="A50" s="56" t="e">
+        <f>A47</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="10">
+        <f>C49</f>
+        <v>2500</v>
+      </c>
+      <c r="D50" s="34">
+        <f>D47</f>
+        <v>29.5</v>
+      </c>
+      <c r="E50" s="11">
+        <f>C50*D50</f>
+        <v>73750</v>
+      </c>
+      <c r="F50" s="35">
+        <f>E50*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G50" s="34">
+        <f>E50*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H50" s="34">
+        <f>E50*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I50" s="34">
+        <f>(F50+G50+H50)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J49" s="34">
-        <f>E49-F49-G49-H49-I49</f>
+      <c r="J50" s="34">
+        <f>E50-F50-G50-H50-I50</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K49" s="10">
-        <f>K46+C49</f>
+      <c r="K50" s="10">
+        <f>K47+C50</f>
         <v>5000</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A50" s="56" t="s">
+    <row r="51" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A51" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="25">
-        <f>(D49-D48)/D48</f>
+      <c r="B51" s="25">
+        <f>(D50-D49)/D49</f>
         <v>0</v>
       </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="20">
-        <f>E49-E48</f>
+      <c r="C51" s="10"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="20">
+        <f>E50-E49</f>
         <v>0</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20">
-        <f>J49-J48</f>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20">
+        <f>J50-J49</f>
         <v>-327.32905000001483</v>
       </c>
-      <c r="K50" s="20">
-        <f>K47+J50</f>
+      <c r="K51" s="20">
+        <f>K48+J51</f>
         <v>8741.1065874999767</v>
       </c>
     </row>
-    <row r="51" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A51" s="56">
+    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A52" s="56">
         <v>44543</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="16">
+      <c r="B52" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="16">
         <v>2500</v>
       </c>
-      <c r="D51" s="46">
+      <c r="D52" s="46">
         <v>29.5</v>
       </c>
-      <c r="E51" s="20">
-        <f>C51*D51</f>
-        <v>73750</v>
-      </c>
-      <c r="F51" s="20">
-        <f>E51*0.002</f>
-        <v>147.5</v>
-      </c>
-      <c r="G51" s="20">
-        <f>E51*0.00006</f>
-        <v>4.4249999999999998</v>
-      </c>
-      <c r="H51" s="20">
-        <f>E51*0.00001</f>
-        <v>0.73750000000000004</v>
-      </c>
-      <c r="I51" s="20">
-        <f>(F51+G51+H51)*0.07</f>
-        <v>10.686375000000002</v>
-      </c>
-      <c r="J51" s="20">
-        <f>E51+F51+I51+G51+H51</f>
-        <v>73913.348875000011</v>
-      </c>
-      <c r="K51" s="57"/>
-      <c r="L51" s="58"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="58"/>
-      <c r="O51" s="58"/>
-    </row>
-    <row r="52" spans="1:15" s="13" customFormat="1">
-      <c r="A52" s="56" t="e">
-        <f>A49</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="10">
-        <f>C51</f>
-        <v>2500</v>
-      </c>
-      <c r="D52" s="34">
-        <f>D49</f>
-        <v>29.5</v>
-      </c>
-      <c r="E52" s="11">
+      <c r="E52" s="20">
         <f>C52*D52</f>
         <v>73750</v>
       </c>
-      <c r="F52" s="35">
+      <c r="F52" s="20">
         <f>E52*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G52" s="34">
-        <f>E52*0.000068</f>
-        <v>5.0149999999999997</v>
-      </c>
-      <c r="H52" s="34">
+      <c r="G52" s="20">
+        <f>E52*0.00006</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="H52" s="20">
         <f>E52*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I52" s="34">
+      <c r="I52" s="20">
         <f>(F52+G52+H52)*0.07</f>
+        <v>10.686375000000002</v>
+      </c>
+      <c r="J52" s="20">
+        <f>E52+F52+I52+G52+H52</f>
+        <v>73913.348875000011</v>
+      </c>
+      <c r="K52" s="57"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+    </row>
+    <row r="53" spans="1:15" s="13" customFormat="1">
+      <c r="A53" s="56" t="e">
+        <f>A50</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="10">
+        <f>C52</f>
+        <v>2500</v>
+      </c>
+      <c r="D53" s="34">
+        <f>D50</f>
+        <v>29.5</v>
+      </c>
+      <c r="E53" s="11">
+        <f>C53*D53</f>
+        <v>73750</v>
+      </c>
+      <c r="F53" s="35">
+        <f>E53*0.002</f>
+        <v>147.5</v>
+      </c>
+      <c r="G53" s="34">
+        <f>E53*0.000068</f>
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="H53" s="34">
+        <f>E53*0.00001</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="I53" s="34">
+        <f>(F53+G53+H53)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J52" s="34">
-        <f>E52-F52-G52-H52-I52</f>
+      <c r="J53" s="34">
+        <f>E53-F53-G53-H53-I53</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K52" s="10">
-        <f>K49+C52</f>
+      <c r="K53" s="10">
+        <f>K50+C53</f>
         <v>7500</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A53" s="56" t="s">
+    <row r="54" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A54" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="25">
-        <f>(D52-D51)/D51</f>
+      <c r="B54" s="25">
+        <f>(D53-D52)/D52</f>
         <v>0</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="20">
-        <f>E52-E51</f>
+      <c r="C54" s="10"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="20">
+        <f>E53-E52</f>
         <v>0</v>
       </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20">
-        <f>J52-J51</f>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20">
+        <f>J53-J52</f>
         <v>-327.32905000001483</v>
       </c>
-      <c r="K53" s="20">
-        <f>K50+J53</f>
+      <c r="K54" s="20">
+        <f>K51+J54</f>
         <v>8413.7775374999619</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A54" s="56">
+    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A55" s="56">
         <v>44496</v>
       </c>
-      <c r="B54" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="16">
+      <c r="B55" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="16">
         <v>2500</v>
       </c>
-      <c r="D54" s="46">
+      <c r="D55" s="46">
         <v>32.75</v>
       </c>
-      <c r="E54" s="20">
-        <f>C54*D54</f>
+      <c r="E55" s="20">
+        <f>C55*D55</f>
         <v>81875</v>
       </c>
-      <c r="F54" s="20">
-        <f>E54*0.002</f>
+      <c r="F55" s="20">
+        <f>E55*0.002</f>
         <v>163.75</v>
       </c>
-      <c r="G54" s="20">
-        <f>E54*0.00006</f>
+      <c r="G55" s="20">
+        <f>E55*0.00006</f>
         <v>4.9125000000000005</v>
       </c>
-      <c r="H54" s="20">
-        <f>E54*0.00001</f>
+      <c r="H55" s="20">
+        <f>E55*0.00001</f>
         <v>0.81875000000000009</v>
       </c>
-      <c r="I54" s="20">
-        <f>(F54+G54+H54)*0.07</f>
+      <c r="I55" s="20">
+        <f>(F55+G55+H55)*0.07</f>
         <v>11.863687500000001</v>
       </c>
-      <c r="J54" s="20">
-        <f>E54+F54+I54+G54+H54</f>
+      <c r="J55" s="20">
+        <f>E55+F55+I55+G55+H55</f>
         <v>82056.344937500005</v>
       </c>
-      <c r="K54" s="57"/>
-      <c r="L54" s="58"/>
-      <c r="M54" s="58"/>
-      <c r="N54" s="58"/>
-      <c r="O54" s="58"/>
-    </row>
-    <row r="55" spans="1:15" s="13" customFormat="1">
-      <c r="A55" s="56" t="e">
-        <f>A52</f>
+      <c r="K55" s="57"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+    </row>
+    <row r="56" spans="1:15" s="13" customFormat="1">
+      <c r="A56" s="56" t="e">
+        <f>A53</f>
         <v>#REF!</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B56" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="10">
-        <f>C54</f>
+      <c r="C56" s="10">
+        <f>C55</f>
         <v>2500</v>
       </c>
-      <c r="D55" s="34">
-        <f>D49</f>
+      <c r="D56" s="34">
+        <f>D50</f>
         <v>29.5</v>
       </c>
-      <c r="E55" s="11">
-        <f>C55*D55</f>
+      <c r="E56" s="11">
+        <f>C56*D56</f>
         <v>73750</v>
       </c>
-      <c r="F55" s="35">
-        <f>E55*0.002</f>
+      <c r="F56" s="35">
+        <f>E56*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G55" s="34">
-        <f>E55*0.000068</f>
+      <c r="G56" s="34">
+        <f>E56*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H55" s="34">
-        <f>E55*0.00001</f>
+      <c r="H56" s="34">
+        <f>E56*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I55" s="34">
-        <f>(F55+G55+H55)*0.07</f>
+      <c r="I56" s="34">
+        <f>(F56+G56+H56)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J55" s="34">
-        <f>E55-F55-G55-H55-I55</f>
+      <c r="J56" s="34">
+        <f>E56-F56-G56-H56-I56</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K55" s="10">
-        <f>K52+C55</f>
+      <c r="K56" s="10">
+        <f>K53+C56</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A56" s="56" t="s">
+    <row r="57" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A57" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="25">
-        <f>(D55-D54)/D54</f>
+      <c r="B57" s="25">
+        <f>(D56-D55)/D55</f>
         <v>-9.9236641221374045E-2</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="20">
-        <f>E55-E54</f>
+      <c r="C57" s="10"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="20">
+        <f>E56-E55</f>
         <v>-8125</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20">
-        <f>J55-J54</f>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20">
+        <f>J56-J55</f>
         <v>-8470.3251125000097</v>
       </c>
-      <c r="K56" s="20">
-        <f>K53+J56</f>
+      <c r="K57" s="20">
+        <f>K54+J57</f>
         <v>-56.5475750000478</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A57" s="56">
+    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A58" s="56">
         <v>44462</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="16">
+      <c r="B58" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="16">
         <v>2500</v>
       </c>
-      <c r="D57" s="46">
+      <c r="D58" s="46">
         <v>33.25</v>
       </c>
-      <c r="E57" s="20">
-        <f>C57*D57</f>
+      <c r="E58" s="20">
+        <f>C58*D58</f>
         <v>83125</v>
       </c>
-      <c r="F57" s="20">
-        <f>E57*0.002</f>
+      <c r="F58" s="20">
+        <f>E58*0.002</f>
         <v>166.25</v>
       </c>
-      <c r="G57" s="20">
-        <f>E57*0.00006</f>
+      <c r="G58" s="20">
+        <f>E58*0.00006</f>
         <v>4.9874999999999998</v>
       </c>
-      <c r="H57" s="20">
-        <f>E57*0.00001</f>
+      <c r="H58" s="20">
+        <f>E58*0.00001</f>
         <v>0.83125000000000004</v>
       </c>
-      <c r="I57" s="20">
-        <f>(F57+G57+H57)*0.07</f>
+      <c r="I58" s="20">
+        <f>(F58+G58+H58)*0.07</f>
         <v>12.044812500000003</v>
       </c>
-      <c r="J57" s="20">
-        <f>E57+F57+I57+G57+H57</f>
+      <c r="J58" s="20">
+        <f>E58+F58+I58+G58+H58</f>
         <v>83309.113562500002</v>
       </c>
-      <c r="K57" s="57"/>
-      <c r="L57" s="58"/>
-      <c r="M57" s="58"/>
-      <c r="N57" s="58"/>
-      <c r="O57" s="58"/>
-    </row>
-    <row r="58" spans="1:15" s="13" customFormat="1">
-      <c r="A58" s="56" t="e">
-        <f>A55</f>
+      <c r="K58" s="57"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+    </row>
+    <row r="59" spans="1:15" s="13" customFormat="1">
+      <c r="A59" s="56" t="e">
+        <f>A56</f>
         <v>#REF!</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B59" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="10">
-        <f>C57</f>
+      <c r="C59" s="10">
+        <f>C58</f>
         <v>2500</v>
       </c>
-      <c r="D58" s="34">
-        <f>D49</f>
+      <c r="D59" s="34">
+        <f>D50</f>
         <v>29.5</v>
       </c>
-      <c r="E58" s="11">
-        <f>C58*D58</f>
+      <c r="E59" s="11">
+        <f>C59*D59</f>
         <v>73750</v>
       </c>
-      <c r="F58" s="35">
-        <f>E58*0.002</f>
+      <c r="F59" s="35">
+        <f>E59*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G58" s="34">
-        <f>E58*0.000068</f>
+      <c r="G59" s="34">
+        <f>E59*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H58" s="34">
-        <f>E58*0.00001</f>
+      <c r="H59" s="34">
+        <f>E59*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I58" s="34">
-        <f>(F58+G58+H58)*0.07</f>
+      <c r="I59" s="34">
+        <f>(F59+G59+H59)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J58" s="34">
-        <f>E58-F58-G58-H58-I58</f>
+      <c r="J59" s="34">
+        <f>E59-F59-G59-H59-I59</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K58" s="10">
-        <f>K55+C58</f>
+      <c r="K59" s="10">
+        <f>K56+C59</f>
         <v>12500</v>
       </c>
     </row>
-    <row r="59" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A59" s="56" t="s">
+    <row r="60" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A60" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="25">
-        <f>(D58-D57)/D57</f>
+      <c r="B60" s="25">
+        <f>(D59-D58)/D58</f>
         <v>-0.11278195488721804</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="20">
-        <f>E58-E57</f>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="20">
+        <f>E59-E58</f>
         <v>-9375</v>
       </c>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20">
-        <f>J58-J57</f>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20">
+        <f>J59-J58</f>
         <v>-9723.0937375000067</v>
       </c>
-      <c r="K59" s="20">
-        <f>K56+J59</f>
+      <c r="K60" s="20">
+        <f>K57+J60</f>
         <v>-9779.6413125000545</v>
       </c>
     </row>
-    <row r="60" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A60" s="56">
+    <row r="61" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A61" s="56">
         <v>44452</v>
       </c>
-      <c r="B60" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="16">
+      <c r="B61" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="16">
         <v>2500</v>
       </c>
-      <c r="D60" s="46">
+      <c r="D61" s="46">
         <v>35.25</v>
       </c>
-      <c r="E60" s="20">
-        <f>C60*D60</f>
+      <c r="E61" s="20">
+        <f>C61*D61</f>
         <v>88125</v>
       </c>
-      <c r="F60" s="20">
-        <f>E60*0.002</f>
+      <c r="F61" s="20">
+        <f>E61*0.002</f>
         <v>176.25</v>
       </c>
-      <c r="G60" s="20">
-        <f>E60*0.00006</f>
+      <c r="G61" s="20">
+        <f>E61*0.00006</f>
         <v>5.2875000000000005</v>
       </c>
-      <c r="H60" s="20">
-        <f>E60*0.00001</f>
+      <c r="H61" s="20">
+        <f>E61*0.00001</f>
         <v>0.88125000000000009</v>
       </c>
-      <c r="I60" s="20">
-        <f>(F60+G60+H60)*0.07</f>
+      <c r="I61" s="20">
+        <f>(F61+G61+H61)*0.07</f>
         <v>12.7693125</v>
       </c>
-      <c r="J60" s="20">
-        <f>E60+F60+I60+G60+H60</f>
+      <c r="J61" s="20">
+        <f>E61+F61+I61+G61+H61</f>
         <v>88320.188062500005</v>
       </c>
-      <c r="K60" s="57"/>
-      <c r="L60" s="58"/>
-      <c r="M60" s="58"/>
-      <c r="N60" s="58"/>
-      <c r="O60" s="58"/>
-    </row>
-    <row r="61" spans="1:15" s="13" customFormat="1">
-      <c r="A61" s="56" t="e">
-        <f>A58</f>
+      <c r="K61" s="57"/>
+      <c r="L61" s="58"/>
+      <c r="M61" s="58"/>
+      <c r="N61" s="58"/>
+      <c r="O61" s="58"/>
+    </row>
+    <row r="62" spans="1:15" s="13" customFormat="1">
+      <c r="A62" s="56" t="e">
+        <f>A59</f>
         <v>#REF!</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B62" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="10">
-        <f>C60</f>
+      <c r="C62" s="10">
+        <f>C61</f>
         <v>2500</v>
       </c>
-      <c r="D61" s="34">
-        <f>D49</f>
+      <c r="D62" s="34">
+        <f>D50</f>
         <v>29.5</v>
       </c>
-      <c r="E61" s="11">
-        <f>C61*D61</f>
+      <c r="E62" s="11">
+        <f>C62*D62</f>
         <v>73750</v>
       </c>
-      <c r="F61" s="35">
-        <f>E61*0.002</f>
+      <c r="F62" s="35">
+        <f>E62*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G61" s="34">
-        <f>E61*0.000068</f>
+      <c r="G62" s="34">
+        <f>E62*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H61" s="34">
-        <f>E61*0.00001</f>
+      <c r="H62" s="34">
+        <f>E62*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I61" s="34">
-        <f>(F61+G61+H61)*0.07</f>
+      <c r="I62" s="34">
+        <f>(F62+G62+H62)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J61" s="34">
-        <f>E61-F61-G61-H61-I61</f>
+      <c r="J62" s="34">
+        <f>E62-F62-G62-H62-I62</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K61" s="91">
-        <f>K58+C61</f>
+      <c r="K62" s="91">
+        <f>K59+C62</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A62" s="56" t="s">
+    <row r="63" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A63" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="25">
-        <f>(D61-D60)/D60</f>
+      <c r="B63" s="25">
+        <f>(D62-D61)/D61</f>
         <v>-0.16312056737588654</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="20">
-        <f>E61-E60</f>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="20">
+        <f>E62-E61</f>
         <v>-14375</v>
       </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20">
-        <f>J61-J60</f>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20">
+        <f>J62-J61</f>
         <v>-14734.168237500009</v>
       </c>
-      <c r="K62" s="20">
-        <f>K59+J62</f>
+      <c r="K63" s="20">
+        <f>K60+J63</f>
         <v>-24513.809550000064</v>
       </c>
     </row>
-    <row r="63" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A63" s="56">
+    <row r="64" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A64" s="56">
         <v>44398</v>
       </c>
-      <c r="B63" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="16">
+      <c r="B64" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="16">
         <v>2500</v>
       </c>
-      <c r="D63" s="46">
+      <c r="D64" s="46">
         <v>37.75</v>
       </c>
-      <c r="E63" s="20">
-        <f>C63*D63</f>
+      <c r="E64" s="20">
+        <f>C64*D64</f>
         <v>94375</v>
       </c>
-      <c r="F63" s="20">
-        <f>E63*0.002</f>
+      <c r="F64" s="20">
+        <f>E64*0.002</f>
         <v>188.75</v>
       </c>
-      <c r="G63" s="20">
-        <f>E63*0.00006</f>
+      <c r="G64" s="20">
+        <f>E64*0.00006</f>
         <v>5.6625000000000005</v>
       </c>
-      <c r="H63" s="20">
-        <f>E63*0.00001</f>
+      <c r="H64" s="20">
+        <f>E64*0.00001</f>
         <v>0.94375000000000009</v>
       </c>
-      <c r="I63" s="20">
-        <f>(F63+G63+H63)*0.07</f>
+      <c r="I64" s="20">
+        <f>(F64+G64+H64)*0.07</f>
         <v>13.6749375</v>
       </c>
-      <c r="J63" s="20">
-        <f>E63+F63+I63+G63+H63</f>
+      <c r="J64" s="20">
+        <f>E64+F64+I64+G64+H64</f>
         <v>94584.031187500019</v>
       </c>
-      <c r="K63" s="57"/>
-      <c r="L63" s="58"/>
-      <c r="M63" s="58"/>
-      <c r="N63" s="58"/>
-      <c r="O63" s="58"/>
-    </row>
-    <row r="64" spans="1:15" s="13" customFormat="1">
-      <c r="A64" s="56" t="e">
-        <f>A61</f>
+      <c r="K64" s="57"/>
+      <c r="L64" s="58"/>
+      <c r="M64" s="58"/>
+      <c r="N64" s="58"/>
+      <c r="O64" s="58"/>
+    </row>
+    <row r="65" spans="1:15" s="13" customFormat="1">
+      <c r="A65" s="56" t="e">
+        <f>A62</f>
         <v>#REF!</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B65" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="10">
-        <f>C63</f>
+      <c r="C65" s="10">
+        <f>C64</f>
         <v>2500</v>
       </c>
-      <c r="D64" s="34">
-        <f>D49</f>
+      <c r="D65" s="34">
+        <f>D50</f>
         <v>29.5</v>
       </c>
-      <c r="E64" s="11">
-        <f>C64*D64</f>
+      <c r="E65" s="11">
+        <f>C65*D65</f>
         <v>73750</v>
       </c>
-      <c r="F64" s="35">
-        <f>E64*0.002</f>
+      <c r="F65" s="35">
+        <f>E65*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G64" s="34">
-        <f>E64*0.000068</f>
+      <c r="G65" s="34">
+        <f>E65*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H64" s="34">
-        <f>E64*0.00001</f>
+      <c r="H65" s="34">
+        <f>E65*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I64" s="34">
-        <f>(F64+G64+H64)*0.07</f>
+      <c r="I65" s="34">
+        <f>(F65+G65+H65)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J64" s="34">
-        <f>E64-F64-G64-H64-I64</f>
+      <c r="J65" s="34">
+        <f>E65-F65-G65-H65-I65</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K64" s="10">
-        <f>K61+C64</f>
+      <c r="K65" s="10">
+        <f>K62+C65</f>
         <v>17500</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A65" s="56" t="s">
+    <row r="66" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A66" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="25">
-        <f>(D64-D63)/D63</f>
+      <c r="B66" s="25">
+        <f>(D65-D64)/D64</f>
         <v>-0.2185430463576159</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="20">
-        <f>E64-E63</f>
+      <c r="C66" s="10"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="20">
+        <f>E65-E64</f>
         <v>-20625</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20">
-        <f>J64-J63</f>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20">
+        <f>J65-J64</f>
         <v>-20998.011362500023</v>
       </c>
-      <c r="K65" s="20">
-        <f>K62+J65</f>
+      <c r="K66" s="20">
+        <f>K63+J66</f>
         <v>-45511.820912500087</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A66" s="56">
+    <row r="67" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A67" s="56">
         <v>44368</v>
       </c>
-      <c r="B66" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="16">
+      <c r="B67" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="16">
         <v>2500</v>
       </c>
-      <c r="D66" s="46">
+      <c r="D67" s="46">
         <v>40</v>
       </c>
-      <c r="E66" s="20">
-        <f>C66*D66</f>
+      <c r="E67" s="20">
+        <f>C67*D67</f>
         <v>100000</v>
       </c>
-      <c r="F66" s="20">
-        <f>E66*0.002</f>
+      <c r="F67" s="20">
+        <f>E67*0.002</f>
         <v>200</v>
       </c>
-      <c r="G66" s="20">
-        <f>E66*0.00006</f>
+      <c r="G67" s="20">
+        <f>E67*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H66" s="20">
-        <f>E66*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I66" s="20">
-        <f>(F66+G66+H66)*0.07</f>
+      <c r="H67" s="20">
+        <f>E67*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I67" s="20">
+        <f>(F67+G67+H67)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J66" s="20">
-        <f>E66+F66+I66+G66+H66</f>
+      <c r="J67" s="20">
+        <f>E67+F67+I67+G67+H67</f>
         <v>100221.49</v>
       </c>
-      <c r="K66" s="57"/>
-      <c r="L66" s="58"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="58"/>
-      <c r="O66" s="58"/>
-    </row>
-    <row r="67" spans="1:15" s="13" customFormat="1">
-      <c r="A67" s="56" t="e">
-        <f>A64</f>
+      <c r="K67" s="57"/>
+      <c r="L67" s="58"/>
+      <c r="M67" s="58"/>
+      <c r="N67" s="58"/>
+      <c r="O67" s="58"/>
+    </row>
+    <row r="68" spans="1:15" s="13" customFormat="1">
+      <c r="A68" s="56" t="e">
+        <f>A65</f>
         <v>#REF!</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B68" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C67" s="10">
-        <f>C66</f>
+      <c r="C68" s="10">
+        <f>C67</f>
         <v>2500</v>
       </c>
-      <c r="D67" s="34">
-        <f>D52</f>
+      <c r="D68" s="34">
+        <f>D53</f>
         <v>29.5</v>
       </c>
-      <c r="E67" s="11">
-        <f>C67*D67</f>
+      <c r="E68" s="11">
+        <f>C68*D68</f>
         <v>73750</v>
       </c>
-      <c r="F67" s="35">
-        <f>E67*0.002</f>
+      <c r="F68" s="35">
+        <f>E68*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G67" s="34">
-        <f>E67*0.000068</f>
+      <c r="G68" s="34">
+        <f>E68*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H67" s="34">
-        <f>E67*0.00001</f>
+      <c r="H68" s="34">
+        <f>E68*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I67" s="34">
-        <f>(F67+G67+H67)*0.07</f>
+      <c r="I68" s="34">
+        <f>(F68+G68+H68)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J67" s="34">
-        <f>E67-F67-G67-H67-I67</f>
+      <c r="J68" s="34">
+        <f>E68-F68-G68-H68-I68</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K67" s="10">
-        <f>K64+C67</f>
+      <c r="K68" s="10">
+        <f>K65+C68</f>
         <v>20000</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A68" s="56" t="s">
+    <row r="69" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A69" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="25">
-        <f>(D67-D66)/D66</f>
+      <c r="B69" s="25">
+        <f>(D68-D67)/D67</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="20">
-        <f>E67-E66</f>
+      <c r="C69" s="10"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="20">
+        <f>E68-E67</f>
         <v>-26250</v>
       </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20">
-        <f>J67-J66</f>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20">
+        <f>J68-J67</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K68" s="20">
-        <f>K65+J68</f>
+      <c r="K69" s="20">
+        <f>K66+J69</f>
         <v>-72147.291087500096</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="19" customFormat="1" ht="15">
-      <c r="A69" s="56">
+    <row r="70" spans="1:15" s="19" customFormat="1" ht="15">
+      <c r="A70" s="56">
         <v>44368</v>
       </c>
-      <c r="B69" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="16">
+      <c r="B70" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="16">
         <v>2500</v>
       </c>
-      <c r="D69" s="46">
+      <c r="D70" s="46">
         <v>40</v>
       </c>
-      <c r="E69" s="20">
-        <f>C69*D69</f>
+      <c r="E70" s="20">
+        <f>C70*D70</f>
         <v>100000</v>
       </c>
-      <c r="F69" s="20">
-        <f>E69*0.002</f>
+      <c r="F70" s="20">
+        <f>E70*0.002</f>
         <v>200</v>
       </c>
-      <c r="G69" s="20">
-        <f>E69*0.00006</f>
+      <c r="G70" s="20">
+        <f>E70*0.00006</f>
         <v>6</v>
       </c>
-      <c r="H69" s="20">
-        <f>E69*0.00001</f>
-        <v>1</v>
-      </c>
-      <c r="I69" s="20">
-        <f>(F69+G69+H69)*0.07</f>
+      <c r="H70" s="20">
+        <f>E70*0.00001</f>
+        <v>1</v>
+      </c>
+      <c r="I70" s="20">
+        <f>(F70+G70+H70)*0.07</f>
         <v>14.490000000000002</v>
       </c>
-      <c r="J69" s="20">
-        <f>E69+F69+I69+G69+H69</f>
+      <c r="J70" s="20">
+        <f>E70+F70+I70+G70+H70</f>
         <v>100221.49</v>
       </c>
-      <c r="K69" s="57"/>
-      <c r="L69" s="58"/>
-      <c r="M69" s="58"/>
-      <c r="N69" s="58"/>
-      <c r="O69" s="58"/>
-    </row>
-    <row r="70" spans="1:15" s="13" customFormat="1">
-      <c r="A70" s="56" t="e">
-        <f>A67</f>
+      <c r="K70" s="57"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="58"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="58"/>
+    </row>
+    <row r="71" spans="1:15" s="13" customFormat="1">
+      <c r="A71" s="56" t="e">
+        <f>A68</f>
         <v>#REF!</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B71" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="10">
-        <f>C69</f>
+      <c r="C71" s="10">
+        <f>C70</f>
         <v>2500</v>
       </c>
-      <c r="D70" s="34">
-        <f>D55</f>
+      <c r="D71" s="34">
+        <f>D56</f>
         <v>29.5</v>
       </c>
-      <c r="E70" s="11">
-        <f>C70*D70</f>
+      <c r="E71" s="11">
+        <f>C71*D71</f>
         <v>73750</v>
       </c>
-      <c r="F70" s="35">
-        <f>E70*0.002</f>
+      <c r="F71" s="35">
+        <f>E71*0.002</f>
         <v>147.5</v>
       </c>
-      <c r="G70" s="34">
-        <f>E70*0.000068</f>
+      <c r="G71" s="34">
+        <f>E71*0.000068</f>
         <v>5.0149999999999997</v>
       </c>
-      <c r="H70" s="34">
-        <f>E70*0.00001</f>
+      <c r="H71" s="34">
+        <f>E71*0.00001</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I70" s="34">
-        <f>(F70+G70+H70)*0.07</f>
+      <c r="I71" s="34">
+        <f>(F71+G71+H71)*0.07</f>
         <v>10.727675000000001</v>
       </c>
-      <c r="J70" s="34">
-        <f>E70-F70-G70-H70-I70</f>
+      <c r="J71" s="34">
+        <f>E71-F71-G71-H71-I71</f>
         <v>73586.019824999996</v>
       </c>
-      <c r="K70" s="10">
-        <f>K67+C70</f>
+      <c r="K71" s="10">
+        <f>K68+C71</f>
         <v>22500</v>
       </c>
     </row>
-    <row r="71" spans="1:15" s="31" customFormat="1" ht="18.75">
-      <c r="A71" s="56" t="s">
+    <row r="72" spans="1:15" s="31" customFormat="1" ht="18.75">
+      <c r="A72" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="25">
-        <f>(D70-D69)/D69</f>
+      <c r="B72" s="25">
+        <f>(D71-D70)/D70</f>
         <v>-0.26250000000000001</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="20">
-        <f>E70-E69</f>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="20">
+        <f>E71-E70</f>
         <v>-26250</v>
       </c>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20">
-        <f>J70-J69</f>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20">
+        <f>J71-J70</f>
         <v>-26635.470175000009</v>
       </c>
-      <c r="K71" s="20">
-        <f>K68+J71</f>
+      <c r="K72" s="20">
+        <f>K69+J72</f>
         <v>-98782.761262500106</v>
       </c>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26202"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26212"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11596" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A1F028-A2E9-4090-933D-7131335F7664}"/>
+  <xr:revisionPtr revIDLastSave="11625" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E570809-7404-4AC8-9D7A-94E590E4E6C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -32,14 +32,13 @@
     <sheet name="ORI" sheetId="184" r:id="rId17"/>
     <sheet name="RCL" sheetId="161" r:id="rId18"/>
     <sheet name="SCC" sheetId="152" r:id="rId19"/>
-    <sheet name="SCCC" sheetId="177" r:id="rId20"/>
-    <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
-    <sheet name="TMT" sheetId="145" r:id="rId25"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
-    <sheet name="WHART" sheetId="171" r:id="rId27"/>
+    <sheet name="SENA" sheetId="183" r:id="rId20"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId21"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
+    <sheet name="TMT" sheetId="145" r:id="rId24"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
+    <sheet name="WHART" sheetId="171" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -143,9 +142,6 @@
   </si>
   <si>
     <t>SCC</t>
-  </si>
-  <si>
-    <t>SCCC</t>
   </si>
   <si>
     <t>SENA</t>
@@ -5138,38 +5134,38 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="E7" s="20">
         <f>C7*D7</f>
-        <v>40200</v>
+        <v>36600</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>80.400000000000006</v>
+        <v>73.2</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>2.4119999999999999</v>
+        <v>2.1960000000000002</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.40200000000000002</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>5.8249800000000018</v>
+        <v>5.3033400000000004</v>
       </c>
       <c r="J7" s="20">
         <f>E7+F7+I7+G7+H7</f>
-        <v>40289.038979999998</v>
+        <v>36681.065340000001</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-0.15189873417721519</v>
+        <v>-0.22784810126582278</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
@@ -5177,31 +5173,31 @@
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>38</v>
+        <v>37.25</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
-        <v>182400</v>
+        <v>178800</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>364.80000000000007</v>
+        <v>357.6</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="0"/>
-        <v>10.943999999999999</v>
+        <v>10.728</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="0"/>
-        <v>1.8240000000000003</v>
+        <v>1.7880000000000003</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>26.429760000000009</v>
+        <v>25.908120000000004</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="0"/>
-        <v>182803.99776</v>
+        <v>179196.02411999999</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
@@ -5220,7 +5216,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF9A6BF-841A-4E49-8659-89A8DE11562A}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
@@ -5363,80 +5359,157 @@
       </c>
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1">
-      <c r="A5" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="A5" s="49">
+        <v>44970</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
         <v>900</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="41">
         <v>50</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="69">
         <f>C5*D5</f>
         <v>45000</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <f>E5*0.002</f>
         <v>90</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="18">
         <f>E5*0.00006</f>
         <v>2.7</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="18">
         <f>E5*0.00001</f>
         <v>0.45</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="18">
         <f>(F5+G5+H5)*0.07</f>
         <v>6.5205000000000011</v>
       </c>
-      <c r="J5" s="62">
+      <c r="J5" s="69">
         <f>E5+F5+I5+G5+H5</f>
         <v>45099.670499999993</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="56"/>
-      <c r="B6" s="12">
+      <c r="A6" s="49"/>
+      <c r="B6" s="30">
         <f>(D5-D4)/D4</f>
         <v>-0.12280701754385964</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>SUM(C4:C5)</f>
         <v>4200</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="17">
         <f>E6/C6</f>
         <v>55.5</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="69">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
         <v>233100</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="16">
         <f t="shared" si="1"/>
         <v>466.20000000000005</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <f t="shared" si="1"/>
         <v>13.986000000000001</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <f t="shared" si="1"/>
         <v>2.3310000000000004</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="16">
         <f t="shared" si="1"/>
         <v>33.776190000000007</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="69">
         <f t="shared" si="1"/>
         <v>233616.29319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="56">
+        <v>44970</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="46">
+        <v>48.75</v>
+      </c>
+      <c r="E7" s="62">
+        <f>C7*D7</f>
+        <v>58500</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>117</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>3.5100000000000002</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>0.58500000000000008</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>8.4766500000000011</v>
+      </c>
+      <c r="J7" s="62">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>58629.571649999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="56"/>
+      <c r="B8" s="12">
+        <f>(D7-D6)/D6</f>
+        <v>-0.12162162162162163</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C6:C7)</f>
+        <v>5400</v>
+      </c>
+      <c r="D8" s="11">
+        <f>E8/C8</f>
+        <v>54</v>
+      </c>
+      <c r="E8" s="62">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>291600</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="2"/>
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="2"/>
+        <v>17.496000000000002</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="2"/>
+        <v>2.9160000000000004</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="2"/>
+        <v>42.252840000000006</v>
+      </c>
+      <c r="J8" s="62">
+        <f t="shared" si="2"/>
+        <v>292245.86483999999</v>
       </c>
     </row>
   </sheetData>
@@ -12210,234 +12283,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04906E79-DA79-4A53-AABA-69B4F8F4564F}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>900</v>
-      </c>
-      <c r="D2" s="17">
-        <v>174.5</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>157050</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>314.10000000000002</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>9.423</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.5705000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>22.756545000000003</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>157397.85004500003</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="39">
-        <v>44616</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>160.5</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>48150</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>96.3</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>2.8890000000000002</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>0.48150000000000004</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>6.9769350000000001</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>48256.647435000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-8.0229226361031525E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>1200</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>171</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>205200</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>410.40000000000003</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>12.312000000000001</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0520000000000005</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>29.733480000000004</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>205654.49748000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="67">
-        <v>44616</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
-        <v>300</v>
-      </c>
-      <c r="D5" s="11">
-        <v>148.5</v>
-      </c>
-      <c r="E5" s="20">
-        <f>C5*D5</f>
-        <v>44550</v>
-      </c>
-      <c r="F5" s="20">
-        <f>E5*0.002</f>
-        <v>89.100000000000009</v>
-      </c>
-      <c r="G5" s="20">
-        <f>E5*0.00006</f>
-        <v>2.673</v>
-      </c>
-      <c r="H5" s="20">
-        <f>E5*0.00001</f>
-        <v>0.44550000000000006</v>
-      </c>
-      <c r="I5" s="20">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>6.4552950000000013</v>
-      </c>
-      <c r="J5" s="20">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>44648.673795000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="25">
-        <f>(D5-D4)/D4</f>
-        <v>-0.13157894736842105</v>
-      </c>
-      <c r="C6" s="22">
-        <f>SUM(C4:C5)</f>
-        <v>1500</v>
-      </c>
-      <c r="D6" s="68">
-        <f>E6/C6</f>
-        <v>166.5</v>
-      </c>
-      <c r="E6" s="22">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>249750</v>
-      </c>
-      <c r="F6" s="22">
-        <f t="shared" si="1"/>
-        <v>499.50000000000006</v>
-      </c>
-      <c r="G6" s="22">
-        <f t="shared" si="1"/>
-        <v>14.985000000000001</v>
-      </c>
-      <c r="H6" s="22">
-        <f t="shared" si="1"/>
-        <v>2.4975000000000005</v>
-      </c>
-      <c r="I6" s="22">
-        <f t="shared" si="1"/>
-        <v>36.188775000000007</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="1"/>
-        <v>250303.17127500003</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12460,7 +12305,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -12978,7 +12823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13001,7 +12846,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="13" customFormat="1">
@@ -13170,38 +13015,38 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E7" s="20">
         <f>C7*D7</f>
-        <v>32400</v>
+        <v>25200</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>64.8</v>
+        <v>50.4</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>1.944</v>
+        <v>1.512</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.32400000000000001</v>
+        <v>0.252</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>4.6947600000000005</v>
+        <v>3.6514800000000003</v>
       </c>
       <c r="J7" s="20">
         <f>E7+F7+I7+G7+H7</f>
-        <v>32471.762759999998</v>
+        <v>25255.815480000001</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-3.5714285714285712E-2</v>
+        <v>-0.25</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
@@ -13209,31 +13054,31 @@
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>27.75</v>
+        <v>26.25</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
-        <v>133200</v>
+        <v>126000</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>266.39999999999998</v>
+        <v>252</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="0"/>
-        <v>7.992</v>
+        <v>7.5600000000000005</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="0"/>
-        <v>1.3320000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>19.30068</v>
+        <v>18.257400000000001</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="0"/>
-        <v>133495.02468</v>
+        <v>126279.07740000001</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="14.25">
@@ -13247,38 +13092,38 @@
         <v>1200</v>
       </c>
       <c r="D9" s="46">
-        <v>26.5</v>
+        <v>20</v>
       </c>
       <c r="E9" s="20">
         <f>C9*D9</f>
-        <v>31800</v>
+        <v>24000</v>
       </c>
       <c r="F9" s="20">
         <f>E9*0.002</f>
-        <v>63.6</v>
+        <v>48</v>
       </c>
       <c r="G9" s="20">
         <f>E9*0.00006</f>
-        <v>1.9080000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="H9" s="20">
         <f>E9*0.00001</f>
-        <v>0.318</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="I9" s="20">
         <f>(F9+G9+H9)*0.07</f>
-        <v>4.6078200000000002</v>
+        <v>3.4776000000000002</v>
       </c>
       <c r="J9" s="20">
         <f>E9+F9+I9+G9+H9</f>
-        <v>31870.433819999998</v>
+        <v>24053.157599999999</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="14.25">
       <c r="A10" s="56"/>
       <c r="B10" s="12">
         <f>(D9-D8)/D8</f>
-        <v>-4.5045045045045043E-2</v>
+        <v>-0.23809523809523808</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C8:C9)</f>
@@ -13286,31 +13131,31 @@
       </c>
       <c r="D10" s="11">
         <f>E10/C10</f>
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" ref="E10:J10" si="1">SUM(E8:E9)</f>
-        <v>165000</v>
+        <v>150000</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" si="1"/>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="H10" s="10">
         <f t="shared" si="1"/>
-        <v>1.6500000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="10">
         <f t="shared" si="1"/>
-        <v>23.9085</v>
+        <v>21.734999999999999</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v>165365.45850000001</v>
+        <v>150332.23500000002</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="1" customFormat="1" ht="14.25">
@@ -13324,38 +13169,38 @@
         <v>1200</v>
       </c>
       <c r="D11" s="46">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E11" s="20">
         <f>C11*D11</f>
-        <v>31200</v>
+        <v>22800</v>
       </c>
       <c r="F11" s="20">
         <f>E11*0.002</f>
-        <v>62.4</v>
+        <v>45.6</v>
       </c>
       <c r="G11" s="20">
         <f>E11*0.00006</f>
-        <v>1.8720000000000001</v>
+        <v>1.3680000000000001</v>
       </c>
       <c r="H11" s="20">
         <f>E11*0.00001</f>
-        <v>0.312</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="I11" s="20">
         <f>(F11+G11+H11)*0.07</f>
-        <v>4.5208800000000009</v>
+        <v>3.3037200000000007</v>
       </c>
       <c r="J11" s="20">
         <f>E11+F11+I11+G11+H11</f>
-        <v>31269.104880000003</v>
+        <v>22850.499719999996</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="1" customFormat="1" ht="14.25">
       <c r="A12" s="56"/>
       <c r="B12" s="12">
         <f>(D11-D10)/D10</f>
-        <v>-5.4545454545454543E-2</v>
+        <v>-0.24</v>
       </c>
       <c r="C12" s="10">
         <f>SUM(C10:C11)</f>
@@ -13363,31 +13208,31 @@
       </c>
       <c r="D12" s="11">
         <f>E12/C12</f>
-        <v>27.25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" ref="E12:J12" si="2">SUM(E10:E11)</f>
-        <v>196200</v>
+        <v>172800</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" si="2"/>
-        <v>392.4</v>
+        <v>345.6</v>
       </c>
       <c r="G12" s="10">
         <f t="shared" si="2"/>
-        <v>11.772</v>
+        <v>10.368</v>
       </c>
       <c r="H12" s="10">
         <f t="shared" si="2"/>
-        <v>1.9620000000000002</v>
+        <v>1.728</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="2"/>
-        <v>28.429380000000002</v>
+        <v>25.038720000000001</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="2"/>
-        <v>196634.56338000001</v>
+        <v>173182.73472000001</v>
       </c>
     </row>
   </sheetData>
@@ -13398,7 +13243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
@@ -13421,7 +13266,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -14633,7 +14478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14656,7 +14501,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -14874,7 +14719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14897,7 +14742,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">
@@ -15333,7 +15178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15356,7 +15201,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="19" customFormat="1" ht="16.5">
@@ -16008,7 +15853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -16034,7 +15879,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="13" customFormat="1">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11625" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E570809-7404-4AC8-9D7A-94E590E4E6C6}"/>
+  <xr:revisionPtr revIDLastSave="11673" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0381DE76-E76C-456E-856F-30324C1D5CFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="20" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -799,7 +799,7 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:S61"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="1" customWidth="1"/>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="19" customFormat="1" ht="15">
+    <row r="2" spans="1:19" s="19" customFormat="1" ht="16.5">
       <c r="A2" s="49">
         <v>44419</v>
       </c>
@@ -858,7 +858,7 @@
         <v>292245.86483999999</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="3" spans="1:19" s="13" customFormat="1">
       <c r="A3" s="39">
         <v>44476</v>
       </c>
@@ -898,7 +898,7 @@
       <c r="K3" s="11"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:19" s="21" customFormat="1" ht="12.75">
+    <row r="4" spans="1:19" s="21" customFormat="1">
       <c r="A4" s="70"/>
       <c r="B4" s="7">
         <f>(D3-D2)/D2</f>
@@ -938,7 +938,7 @@
       </c>
       <c r="L4" s="25"/>
     </row>
-    <row r="5" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="5" spans="1:19" s="13" customFormat="1">
       <c r="A5" s="39">
         <v>44502</v>
       </c>
@@ -978,7 +978,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="6" spans="1:19" s="13" customFormat="1">
       <c r="A6" s="39">
         <v>44529</v>
       </c>
@@ -1018,7 +1018,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="12"/>
     </row>
-    <row r="7" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="7" spans="1:19" s="13" customFormat="1">
       <c r="A7" s="39">
         <v>44538</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="8" spans="1:19" s="13" customFormat="1">
       <c r="A8" s="39">
         <v>44544</v>
       </c>
@@ -1098,7 +1098,7 @@
       <c r="K8" s="11"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:19" s="21" customFormat="1" ht="12.75">
+    <row r="9" spans="1:19" s="21" customFormat="1">
       <c r="A9" s="70"/>
       <c r="B9" s="7">
         <f>(D8-D7)/D7</f>
@@ -1146,7 +1146,7 @@
       <c r="R9" s="22"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="10" spans="1:19" s="13" customFormat="1">
       <c r="A10" s="39">
         <v>44545</v>
       </c>
@@ -1186,7 +1186,7 @@
       <c r="K10" s="11"/>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="1:19" s="21" customFormat="1" ht="12.75">
+    <row r="11" spans="1:19" s="21" customFormat="1">
       <c r="A11" s="70"/>
       <c r="B11" s="7">
         <f>(D10-D9)/D9</f>
@@ -1234,7 +1234,7 @@
       <c r="R11" s="22"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" spans="1:19" s="13" customFormat="1" ht="12.75">
+    <row r="12" spans="1:19" s="13" customFormat="1">
       <c r="A12" s="39">
         <v>44558</v>
       </c>
@@ -1274,7 +1274,7 @@
       <c r="K12" s="11"/>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" spans="1:19" ht="12.75">
+    <row r="13" spans="1:19">
       <c r="A13" s="49">
         <v>44579</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>162358.8138</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.25">
+    <row r="14" spans="1:19">
       <c r="A14" s="54"/>
       <c r="B14" s="74">
         <f>(D13-D12)/D12</f>
@@ -1351,7 +1351,7 @@
         <v>511129.59899999999</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="12.75">
+    <row r="15" spans="1:19">
       <c r="A15" s="49">
         <v>44601</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>201445.1949</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.25">
+    <row r="16" spans="1:19">
       <c r="A16" s="54"/>
       <c r="B16" s="74">
         <f>(D15-D14)/D14</f>
@@ -1428,7 +1428,7 @@
         <v>712574.79389999993</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12.75">
+    <row r="17" spans="1:11">
       <c r="A17" s="49">
         <v>44603</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>61636.216350000002</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="54"/>
       <c r="B18" s="74">
         <f>(D17-D16)/D16</f>
@@ -1505,7 +1505,7 @@
         <v>774211.01024999993</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="12.75">
+    <row r="19" spans="1:11">
       <c r="A19" s="49">
         <v>44623</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>58128.464200000002</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="54"/>
       <c r="B20" s="74">
         <f>(D19-D18)/D18</f>
@@ -1582,7 +1582,7 @@
         <v>832339.47444999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="12.75">
+    <row r="21" spans="1:11">
       <c r="A21" s="49">
         <v>44638</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>64392.307325000002</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="96"/>
       <c r="B22" s="97">
         <f>(D21-D28)/D28</f>
@@ -1659,7 +1659,7 @@
         <v>896731.78177500004</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="12.75">
+    <row r="23" spans="1:11">
       <c r="A23" s="49">
         <v>44658</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>62888.984974999999</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25">
+    <row r="24" spans="1:11">
       <c r="A24" s="54"/>
       <c r="B24" s="74">
         <f>(D23-D22)/D22</f>
@@ -1736,7 +1736,7 @@
         <v>959620.76675000007</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="12.75">
+    <row r="25" spans="1:11">
       <c r="A25" s="49">
         <v>44726</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>61385.662625000004</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="13" customFormat="1" ht="12.75">
+    <row r="26" spans="1:11" s="13" customFormat="1">
       <c r="A26" s="49">
         <v>44957</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>-7755.1736000000019</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25">
+    <row r="28" spans="1:11">
       <c r="A28" s="49">
         <v>44957</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>959620.76675000007</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="12.75">
+    <row r="29" spans="1:11">
       <c r="A29" s="49">
         <v>44658</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>62888.984974999999</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="13" customFormat="1" ht="12.75">
+    <row r="30" spans="1:11" s="13" customFormat="1">
       <c r="A30" s="49">
         <v>44958</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>-7013.4987349999938</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25">
+    <row r="32" spans="1:11">
       <c r="A32" s="54"/>
       <c r="B32" s="74" t="s">
         <v>2</v>
@@ -2014,7 +2014,7 @@
         <v>896731.78177500004</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="12.75">
+    <row r="33" spans="1:15">
       <c r="A33" s="49">
         <v>44638</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>64392.307325000002</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="34" spans="1:15" s="13" customFormat="1">
       <c r="A34" s="49">
         <v>44965</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>-10013.485894999998</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.25">
+    <row r="36" spans="1:15">
       <c r="A36" s="49">
         <v>44965</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>832339.47444999998</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="12.75">
+    <row r="37" spans="1:15">
       <c r="A37" s="49">
         <v>44623</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>58128.464200000002</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="38" spans="1:15" s="13" customFormat="1">
       <c r="A38" s="49">
         <v>44965</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>-3749.6427699999986</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="102" customFormat="1" ht="14.25">
+    <row r="40" spans="1:15" s="102" customFormat="1" ht="15.75">
       <c r="A40" s="49"/>
       <c r="B40" s="15" t="s">
         <v>2</v>
@@ -2297,7 +2297,7 @@
       <c r="N40" s="101"/>
       <c r="O40" s="101"/>
     </row>
-    <row r="41" spans="1:15" ht="12.75">
+    <row r="41" spans="1:15">
       <c r="A41" s="56">
         <v>44603</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>821315.11054999998</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="43" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A43" s="56"/>
       <c r="B43" s="13"/>
       <c r="C43" s="10"/>
@@ -2390,7 +2390,7 @@
       <c r="N43" s="58"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="44" spans="1:15" s="13" customFormat="1">
       <c r="A44" s="56"/>
       <c r="C44" s="10"/>
       <c r="D44" s="34"/>
@@ -2415,7 +2415,7 @@
       <c r="J45" s="20"/>
       <c r="K45" s="20"/>
     </row>
-    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="46" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A46" s="56"/>
       <c r="B46" s="13"/>
       <c r="C46" s="10"/>
@@ -2432,7 +2432,7 @@
       <c r="N46" s="58"/>
       <c r="O46" s="58"/>
     </row>
-    <row r="47" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="47" spans="1:15" s="13" customFormat="1">
       <c r="A47" s="56"/>
       <c r="C47" s="10"/>
       <c r="D47" s="34"/>
@@ -2457,7 +2457,7 @@
       <c r="J48" s="20"/>
       <c r="K48" s="20"/>
     </row>
-    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="49" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A49" s="56"/>
       <c r="B49" s="13"/>
       <c r="C49" s="10"/>
@@ -2474,7 +2474,7 @@
       <c r="N49" s="58"/>
       <c r="O49" s="58"/>
     </row>
-    <row r="50" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="50" spans="1:15" s="13" customFormat="1">
       <c r="A50" s="56"/>
       <c r="C50" s="10"/>
       <c r="D50" s="34"/>
@@ -2499,7 +2499,7 @@
       <c r="J51" s="20"/>
       <c r="K51" s="20"/>
     </row>
-    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="52" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A52" s="56"/>
       <c r="B52" s="13"/>
       <c r="C52" s="10"/>
@@ -2516,7 +2516,7 @@
       <c r="N52" s="58"/>
       <c r="O52" s="58"/>
     </row>
-    <row r="53" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="53" spans="1:15" s="13" customFormat="1">
       <c r="A53" s="56"/>
       <c r="C53" s="10"/>
       <c r="D53" s="34"/>
@@ -2541,7 +2541,7 @@
       <c r="J54" s="20"/>
       <c r="K54" s="92"/>
     </row>
-    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="55" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A55" s="56"/>
       <c r="B55" s="13"/>
       <c r="C55" s="10"/>
@@ -2558,7 +2558,7 @@
       <c r="N55" s="58"/>
       <c r="O55" s="58"/>
     </row>
-    <row r="56" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="56" spans="1:15" s="13" customFormat="1">
       <c r="A56" s="56"/>
       <c r="C56" s="10"/>
       <c r="D56" s="34"/>
@@ -2582,7 +2582,7 @@
       <c r="J57" s="20"/>
       <c r="K57" s="20"/>
     </row>
-    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="58" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A58" s="56"/>
       <c r="B58" s="13"/>
       <c r="C58" s="10"/>
@@ -2599,7 +2599,7 @@
       <c r="N58" s="58"/>
       <c r="O58" s="58"/>
     </row>
-    <row r="59" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="59" spans="1:15" s="13" customFormat="1">
       <c r="A59" s="56"/>
       <c r="C59" s="10"/>
       <c r="D59" s="34"/>
@@ -2636,7 +2636,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4115D497-67E5-4755-A37C-D801F1CE1CC8}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -2695,7 +2695,7 @@
         <v>91702.663350000003</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="3" spans="1:14" s="21" customFormat="1">
       <c r="A3" s="14">
         <v>44860</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>86692.329290000009</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="4" spans="1:14" s="21" customFormat="1">
       <c r="A4" s="42"/>
       <c r="B4" s="7">
         <f>(D3-D2)/D2</f>
@@ -2774,7 +2774,7 @@
       <c r="K4" s="24"/>
       <c r="L4" s="25"/>
     </row>
-    <row r="5" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="5" spans="1:14" s="21" customFormat="1">
       <c r="A5" s="14">
         <v>44943</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>89197.887940000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="6" spans="1:14" s="21" customFormat="1">
       <c r="A6" s="42"/>
       <c r="B6" s="7">
         <f>(D5-D4)/D4</f>
@@ -2853,7 +2853,7 @@
       <c r="K6" s="24"/>
       <c r="L6" s="25"/>
     </row>
-    <row r="7" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="7" spans="1:14" s="21" customFormat="1">
       <c r="A7" s="14">
         <v>44944</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>89197.887940000001</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="8" spans="1:14" s="21" customFormat="1">
       <c r="A8" s="42"/>
       <c r="B8" s="7">
         <f>(D7-D6)/D6</f>
@@ -2932,7 +2932,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="25"/>
     </row>
-    <row r="9" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="9" spans="1:14" s="21" customFormat="1">
       <c r="A9" s="8">
         <v>44944</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>84186.770640000002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="10" spans="1:14" s="21" customFormat="1">
       <c r="A10" s="44"/>
       <c r="B10" s="25">
         <f>(D9-D8)/D8</f>
@@ -3011,7 +3011,7 @@
       <c r="K10" s="24"/>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="11" spans="1:14" s="21" customFormat="1">
       <c r="A11" s="44"/>
       <c r="B11" s="25"/>
       <c r="C11" s="22"/>
@@ -3140,7 +3140,7 @@
         <v>178602.00065999999</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="12.75">
+    <row r="15" spans="1:14">
       <c r="A15" s="56" t="s">
         <v>4</v>
       </c>
@@ -3248,9 +3248,6 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
     </row>
-    <row r="23" spans="1:13" ht="12"/>
-    <row r="24" spans="1:13" ht="12"/>
-    <row r="25" spans="1:13" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -3261,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECE484-9DAC-4EE9-A8FE-27A01698073E}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -3320,7 +3317,7 @@
         <v>105833.89343999999</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="13" customFormat="1" ht="12.75">
+    <row r="3" spans="1:14" s="13" customFormat="1">
       <c r="A3" s="39">
         <v>44952</v>
       </c>
@@ -3404,7 +3401,7 @@
       <c r="M4" s="62"/>
       <c r="N4" s="62"/>
     </row>
-    <row r="5" spans="1:14" s="13" customFormat="1" ht="12.75">
+    <row r="5" spans="1:14" s="13" customFormat="1">
       <c r="A5" s="67">
         <v>44952</v>
       </c>
@@ -3735,9 +3732,6 @@
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="1:13" ht="12"/>
-    <row r="21" spans="1:13" ht="12"/>
-    <row r="22" spans="1:13" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -3748,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="43" customWidth="1"/>
@@ -4372,7 +4366,7 @@
         <v>110244.5806</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="18" spans="1:13" s="21" customFormat="1">
       <c r="A18" s="42"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5">
@@ -4408,7 +4402,7 @@
       </c>
       <c r="K18" s="25"/>
     </row>
-    <row r="19" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="19" spans="1:13" s="21" customFormat="1">
       <c r="A19" s="14">
         <v>44735</v>
       </c>
@@ -4446,7 +4440,7 @@
         <v>97716.787350000013</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="20" spans="1:13" s="21" customFormat="1">
       <c r="A20" s="42"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5">
@@ -4483,7 +4477,7 @@
       </c>
       <c r="K20" s="25"/>
     </row>
-    <row r="21" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="21" spans="1:13" s="21" customFormat="1">
       <c r="A21" s="14">
         <v>44746</v>
       </c>
@@ -4521,7 +4515,7 @@
         <v>91703.446589999992</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="22" spans="1:13" s="21" customFormat="1">
       <c r="A22" s="28" t="s">
         <v>4</v>
       </c>
@@ -4563,7 +4557,7 @@
       </c>
       <c r="K22" s="25"/>
     </row>
-    <row r="23" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="23" spans="1:13" s="21" customFormat="1">
       <c r="A23" s="8">
         <v>44812</v>
       </c>
@@ -4601,7 +4595,7 @@
         <v>72160.08911999999</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="24" spans="1:13" s="21" customFormat="1">
       <c r="A24" s="9" t="s">
         <v>4</v>
       </c>
@@ -4643,7 +4637,7 @@
       </c>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="25" spans="1:13" s="21" customFormat="1">
       <c r="A25" s="8">
         <v>44746</v>
       </c>
@@ -4681,7 +4675,7 @@
         <v>68151.195279999985</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="26" spans="1:13" s="21" customFormat="1">
       <c r="A26" s="9" t="s">
         <v>4</v>
       </c>
@@ -4723,7 +4717,7 @@
       </c>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="27" spans="1:13" s="21" customFormat="1">
       <c r="A27" s="9"/>
       <c r="B27" s="12"/>
       <c r="C27" s="22"/>
@@ -4736,7 +4730,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="28" spans="1:13" s="21" customFormat="1">
       <c r="A28" s="49">
         <v>44812</v>
       </c>
@@ -4775,7 +4769,7 @@
       </c>
       <c r="L28" s="25"/>
     </row>
-    <row r="29" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="29" spans="1:13" s="13" customFormat="1">
       <c r="A29" s="49">
         <v>44813</v>
       </c>
@@ -4935,7 +4929,6 @@
       <c r="F38" s="27"/>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:11" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -4946,8 +4939,8 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -5012,199 +5005,158 @@
       <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="56">
-        <v>44277</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <f>C2</f>
-        <v>3600</v>
-      </c>
-      <c r="D3" s="34">
-        <v>41.5</v>
-      </c>
-      <c r="E3" s="11">
+      <c r="A3" s="49">
+        <v>44972</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="41">
+        <v>30.5</v>
+      </c>
+      <c r="E3" s="18">
         <f>C3*D3</f>
-        <v>149400</v>
-      </c>
-      <c r="F3" s="35">
+        <v>36600</v>
+      </c>
+      <c r="F3" s="18">
         <f>E3*0.002</f>
-        <v>298.8</v>
-      </c>
-      <c r="G3" s="34">
-        <f>E3*0.000068</f>
-        <v>10.1592</v>
-      </c>
-      <c r="H3" s="34">
+        <v>73.2</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="H3" s="18">
         <f>E3*0.00001</f>
-        <v>1.4940000000000002</v>
-      </c>
-      <c r="I3" s="34">
+        <v>0.36600000000000005</v>
+      </c>
+      <c r="I3" s="18">
         <f>(F3+G3+H3)*0.07</f>
-        <v>21.731724000000003</v>
-      </c>
-      <c r="J3" s="34">
-        <f>E3-F3-G3-H3-I3</f>
-        <v>149067.815076</v>
+        <v>5.3033400000000004</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>36681.065340000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="49"/>
+      <c r="B4" s="30">
         <f>(D3-D2)/D2</f>
-        <v>5.0632911392405063E-2</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="20">
-        <f>E3-E2</f>
-        <v>7200</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20">
-        <f>J3-J2</f>
-        <v>6552.8562960000127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
-      <c r="A5" s="50"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="47"/>
-      <c r="J5" s="53">
-        <f>J1+J4</f>
-        <v>6552.8562960000127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="13" customFormat="1">
-      <c r="A6" s="39">
-        <v>44946</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16">
-        <v>3600</v>
-      </c>
-      <c r="D6" s="17">
-        <v>39.5</v>
-      </c>
-      <c r="E6" s="18">
-        <f>C6*D6</f>
-        <v>142200</v>
-      </c>
-      <c r="F6" s="18">
-        <f>E6*0.002</f>
-        <v>284.40000000000003</v>
-      </c>
-      <c r="G6" s="18">
-        <f>E6*0.00006</f>
-        <v>8.532</v>
-      </c>
-      <c r="H6" s="18">
-        <f>E6*0.00001</f>
-        <v>1.4220000000000002</v>
-      </c>
-      <c r="I6" s="18">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>20.604780000000005</v>
-      </c>
-      <c r="J6" s="18">
-        <f>E6+F6+I6+G6+H6</f>
-        <v>142514.95877999999</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="30"/>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A7" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D7" s="46">
-        <v>30.5</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>36600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>73.2</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>2.1960000000000002</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>0.36600000000000005</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>5.3033400000000004</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>36681.065340000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A8" s="56"/>
-      <c r="B8" s="12">
-        <f>(D7-D6)/D6</f>
         <v>-0.22784810126582278</v>
       </c>
-      <c r="C8" s="10">
-        <f>SUM(C6:C7)</f>
+      <c r="C4" s="16">
+        <f>SUM(C2:C3)</f>
         <v>4800</v>
       </c>
-      <c r="D8" s="11">
-        <f>E8/C8</f>
+      <c r="D4" s="17">
+        <f>E4/C4</f>
         <v>37.25</v>
       </c>
-      <c r="E8" s="10">
-        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
+      <c r="E4" s="16">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
         <v>178800</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F4" s="16">
         <f t="shared" si="0"/>
         <v>357.6</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G4" s="16">
         <f t="shared" si="0"/>
         <v>10.728</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H4" s="16">
         <f t="shared" si="0"/>
         <v>1.7880000000000003</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I4" s="16">
         <f t="shared" si="0"/>
         <v>25.908120000000004</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J4" s="16">
         <f t="shared" si="0"/>
         <v>179196.02411999999</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" ht="12">
-      <c r="A9" s="50"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="47"/>
-      <c r="J9" s="53"/>
+    <row r="5" spans="1:13" s="1" customFormat="1">
+      <c r="A5" s="56">
+        <v>44972</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D5" s="46">
+        <v>27.25</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5*D5</f>
+        <v>32700</v>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*0.002</f>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G5" s="20">
+        <f>E5*0.00006</f>
+        <v>1.962</v>
+      </c>
+      <c r="H5" s="20">
+        <f>E5*0.00001</f>
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>4.7382300000000006</v>
+      </c>
+      <c r="J5" s="20">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>32772.427230000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1">
+      <c r="A6" s="56"/>
+      <c r="B6" s="12">
+        <f>(D5-D4)/D4</f>
+        <v>-0.26845637583892618</v>
+      </c>
+      <c r="C6" s="10">
+        <f>SUM(C4:C5)</f>
+        <v>6000</v>
+      </c>
+      <c r="D6" s="11">
+        <f>E6/C6</f>
+        <v>35.25</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>211500</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>423</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="1"/>
+        <v>12.69</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="1"/>
+        <v>2.1150000000000002</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>30.646350000000005</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="1"/>
+        <v>211968.45134999999</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -5217,7 +5169,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF9A6BF-841A-4E49-8659-89A8DE11562A}">
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -5522,7 +5474,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="44" customWidth="1"/>
@@ -7401,7 +7353,7 @@
         <v>1157568.0962999999</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="13" customFormat="1" ht="12.75">
+    <row r="56" spans="1:10" s="13" customFormat="1">
       <c r="A56" s="8">
         <v>44740</v>
       </c>
@@ -7439,7 +7391,7 @@
         <v>45100.055699999997</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="12.75">
+    <row r="57" spans="1:10">
       <c r="B57" s="12">
         <f>(D56-D55)/D55</f>
         <v>-0.41558441558441561</v>
@@ -7477,7 +7429,6 @@
         <v>1202668.1519999998</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="12.75"/>
     <row r="59" spans="1:10" s="13" customFormat="1">
       <c r="A59" s="14">
         <v>44672</v>
@@ -7579,7 +7530,7 @@
         <v>5179.5432600000058</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="13" customFormat="1" ht="12.75">
+    <row r="62" spans="1:10" s="13" customFormat="1">
       <c r="A62" s="14">
         <v>44740</v>
       </c>
@@ -7619,7 +7570,7 @@
         <v>45100.055699999997</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="12.75">
+    <row r="63" spans="1:10">
       <c r="A63" s="49">
         <v>44741</v>
       </c>
@@ -7658,7 +7609,7 @@
         <v>58369.927589999999</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="12.75">
+    <row r="64" spans="1:10">
       <c r="A64" s="28">
         <f>DAYS360(A62,A63)</f>
         <v>1</v>
@@ -7682,10 +7633,6 @@
         <v>13269.871890000002</v>
       </c>
     </row>
-    <row r="65" ht="12.75"/>
-    <row r="66" ht="12.75"/>
-    <row r="67" ht="12.75"/>
-    <row r="68" ht="12.75"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -8432,7 +8379,7 @@
         <v>649435.25520000001</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" ht="12.75">
+    <row r="10" spans="1:13" s="1" customFormat="1">
       <c r="A10" s="56">
         <v>44676</v>
       </c>
@@ -8470,7 +8417,7 @@
         <v>165365.45849999998</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="11" spans="1:13" s="13" customFormat="1">
       <c r="A11" s="56">
         <v>44809</v>
       </c>
@@ -8536,7 +8483,7 @@
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" ht="12.75">
+    <row r="14" spans="1:13" s="1" customFormat="1">
       <c r="A14" s="56">
         <v>44676</v>
       </c>
@@ -8574,7 +8521,7 @@
         <v>148828.91264999998</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="15" spans="1:13" s="13" customFormat="1">
       <c r="A15" s="56">
         <v>44809</v>
       </c>
@@ -9508,7 +9455,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="12.75">
+    <row r="23" spans="1:13">
       <c r="A23" s="49">
         <v>44741</v>
       </c>
@@ -9547,7 +9494,7 @@
       </c>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="12.75">
+    <row r="24" spans="1:13">
       <c r="A24" s="90"/>
       <c r="B24" s="7">
         <f>(D23-D21)/D21</f>
@@ -9589,7 +9536,7 @@
       <c r="L24" s="25"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="12.75">
+    <row r="25" spans="1:13">
       <c r="A25" s="49">
         <v>44854</v>
       </c>
@@ -9628,7 +9575,7 @@
       </c>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="12.75">
+    <row r="26" spans="1:13">
       <c r="A26" s="90"/>
       <c r="B26" s="7">
         <f>(D25-D24)/D24</f>
@@ -9670,7 +9617,7 @@
       <c r="L26" s="25"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="12.75">
+    <row r="27" spans="1:13">
       <c r="A27" s="49">
         <v>44876</v>
       </c>
@@ -9709,7 +9656,7 @@
       </c>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="12.75">
+    <row r="28" spans="1:13">
       <c r="A28" s="90"/>
       <c r="B28" s="7">
         <f>(D27-D26)/D26</f>
@@ -9751,7 +9698,7 @@
       <c r="L28" s="25"/>
       <c r="M28" s="21"/>
     </row>
-    <row r="29" spans="1:13" ht="12.75">
+    <row r="29" spans="1:13">
       <c r="A29" s="49">
         <v>44887</v>
       </c>
@@ -9789,7 +9736,7 @@
         <v>94710.116970000017</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="12.75">
+    <row r="30" spans="1:13">
       <c r="A30" s="90"/>
       <c r="B30" s="7">
         <f>(D29-D28)/D28</f>
@@ -9829,7 +9776,7 @@
       </c>
       <c r="M30" s="21"/>
     </row>
-    <row r="31" spans="1:13" ht="12.75">
+    <row r="31" spans="1:13">
       <c r="A31" s="49">
         <v>44959</v>
       </c>
@@ -9867,7 +9814,7 @@
         <v>90951.778995000001</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="12.75">
+    <row r="32" spans="1:13">
       <c r="A32" s="90"/>
       <c r="B32" s="7">
         <f>(D31-D30)/D30</f>
@@ -9907,7 +9854,7 @@
       </c>
       <c r="M32" s="21"/>
     </row>
-    <row r="33" spans="1:13" ht="12.75">
+    <row r="33" spans="1:13">
       <c r="A33" s="56">
         <v>44959</v>
       </c>
@@ -9945,7 +9892,7 @@
         <v>86441.773425000007</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="12.75">
+    <row r="34" spans="1:13">
       <c r="B34" s="25">
         <f>(D33-D32)/D32</f>
         <v>-0.25806451612903225</v>
@@ -9984,7 +9931,7 @@
       </c>
       <c r="M34" s="21"/>
     </row>
-    <row r="35" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="35" spans="1:13" s="13" customFormat="1">
       <c r="A35" s="89"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -10037,7 +9984,7 @@
       <c r="L36" s="12"/>
       <c r="M36" s="12"/>
     </row>
-    <row r="37" spans="1:13" ht="12.75">
+    <row r="37" spans="1:13">
       <c r="A37" s="49">
         <v>44853</v>
       </c>
@@ -10076,7 +10023,7 @@
         <v>87554.891384999995</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="12.75">
+    <row r="38" spans="1:13">
       <c r="A38" s="49">
         <f>DAYS360(A36,A37)</f>
         <v>7</v>
@@ -10141,7 +10088,7 @@
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
     </row>
-    <row r="41" spans="1:13" ht="12.75">
+    <row r="41" spans="1:13">
       <c r="A41" s="56">
         <v>44853</v>
       </c>
@@ -10180,7 +10127,7 @@
         <v>88303.223790000004</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="12.75">
+    <row r="42" spans="1:13">
       <c r="A42" s="56">
         <f>DAYS360(A40,A41)</f>
         <v>7</v>
@@ -11408,7 +11355,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="24" spans="1:15" s="13" customFormat="1">
       <c r="A24" s="49">
         <v>44943</v>
       </c>
@@ -11471,7 +11418,7 @@
       </c>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:15" s="21" customFormat="1" ht="12.75">
+    <row r="26" spans="1:15" s="21" customFormat="1">
       <c r="A26" s="49">
         <v>44943</v>
       </c>
@@ -11504,7 +11451,7 @@
       </c>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="27" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A27" s="56">
         <v>44543</v>
       </c>
@@ -11547,7 +11494,7 @@
       <c r="N27" s="58"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" spans="1:15" ht="12.75">
+    <row r="28" spans="1:15">
       <c r="B28" s="3">
         <f>(D27-D26)/D26</f>
         <v>-0.25482625482625482</v>
@@ -11590,7 +11537,7 @@
       <c r="N28" s="59"/>
       <c r="O28" s="59"/>
     </row>
-    <row r="29" spans="1:15" s="21" customFormat="1" ht="12.75">
+    <row r="29" spans="1:15" s="21" customFormat="1">
       <c r="A29" s="90"/>
       <c r="B29" s="7"/>
       <c r="C29" s="5"/>
@@ -11603,7 +11550,7 @@
       <c r="J29" s="5"/>
       <c r="L29" s="25"/>
     </row>
-    <row r="30" spans="1:15" s="21" customFormat="1" ht="12.75">
+    <row r="30" spans="1:15" s="21" customFormat="1">
       <c r="A30" s="90"/>
       <c r="B30" s="7"/>
       <c r="C30" s="5"/>
@@ -11656,7 +11603,7 @@
       <c r="K31" s="11"/>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="1:15" s="13" customFormat="1" ht="12.75">
+    <row r="32" spans="1:15" s="13" customFormat="1">
       <c r="A32" s="49">
         <v>44865</v>
       </c>
@@ -12825,8 +12772,8 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -12891,120 +12838,160 @@
       <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="56">
-        <v>44277</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <f>C2</f>
-        <v>3600</v>
-      </c>
-      <c r="D3" s="34">
-        <v>29.5</v>
-      </c>
-      <c r="E3" s="11">
+      <c r="A3" s="49">
+        <v>44972</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="41">
+        <v>21</v>
+      </c>
+      <c r="E3" s="18">
         <f>C3*D3</f>
-        <v>106200</v>
-      </c>
-      <c r="F3" s="35">
+        <v>25200</v>
+      </c>
+      <c r="F3" s="18">
         <f>E3*0.002</f>
-        <v>212.4</v>
-      </c>
-      <c r="G3" s="34">
-        <f>E3*0.000068</f>
-        <v>7.2215999999999996</v>
-      </c>
-      <c r="H3" s="34">
+        <v>50.4</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>1.512</v>
+      </c>
+      <c r="H3" s="18">
         <f>E3*0.00001</f>
-        <v>1.0620000000000001</v>
-      </c>
-      <c r="I3" s="34">
+        <v>0.252</v>
+      </c>
+      <c r="I3" s="18">
         <f>(F3+G3+H3)*0.07</f>
-        <v>15.447852000000003</v>
-      </c>
-      <c r="J3" s="34">
-        <f>E3-F3-G3-H3-I3</f>
-        <v>105963.868548</v>
+        <v>3.6514800000000003</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>25255.815480000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="49"/>
+      <c r="B4" s="30">
         <f>(D3-D2)/D2</f>
-        <v>5.3571428571428568E-2</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="20">
-        <f>E3-E2</f>
-        <v>5400</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20">
-        <f>J3-J2</f>
-        <v>4940.6066279999941</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="12">
-      <c r="A5" s="50"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="47"/>
-      <c r="J5" s="53">
-        <f>J1+J4</f>
-        <v>4940.6066279999941</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="13" customFormat="1">
-      <c r="A6" s="39">
-        <f>A2</f>
-        <v>44945</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>1</v>
+        <v>-0.25</v>
+      </c>
+      <c r="C4" s="16">
+        <f>SUM(C2:C3)</f>
+        <v>4800</v>
+      </c>
+      <c r="D4" s="17">
+        <f>E4/C4</f>
+        <v>26.25</v>
+      </c>
+      <c r="E4" s="16">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>126000</v>
+      </c>
+      <c r="F4" s="16">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="G4" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="H4" s="16">
+        <f t="shared" si="0"/>
+        <v>1.26</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" si="0"/>
+        <v>18.257400000000001</v>
+      </c>
+      <c r="J4" s="16">
+        <f t="shared" si="0"/>
+        <v>126279.07740000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="12.75">
+      <c r="A5" s="49">
+        <v>44676</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>1200</v>
+      </c>
+      <c r="D5" s="41">
+        <v>19</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>22800</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>45.6</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>3.3037200000000007</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>22850.499719999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="12.75">
+      <c r="A6" s="49"/>
+      <c r="B6" s="30">
+        <f>(D5-D4)/D4</f>
+        <v>-0.27619047619047621</v>
       </c>
       <c r="C6" s="16">
-        <v>3600</v>
+        <f>SUM(C4:C5)</f>
+        <v>6000</v>
       </c>
       <c r="D6" s="17">
-        <f>D2</f>
-        <v>28</v>
-      </c>
-      <c r="E6" s="18">
-        <f>C6*D6</f>
-        <v>100800</v>
-      </c>
-      <c r="F6" s="18">
-        <f>E6*0.002</f>
-        <v>201.6</v>
-      </c>
-      <c r="G6" s="18">
-        <f>E6*0.00006</f>
-        <v>6.048</v>
-      </c>
-      <c r="H6" s="18">
-        <f>E6*0.00001</f>
-        <v>1.008</v>
-      </c>
-      <c r="I6" s="18">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>14.605920000000001</v>
-      </c>
-      <c r="J6" s="18">
-        <f>E6+F6+I6+G6+H6</f>
-        <v>101023.26192</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="30"/>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="14.25">
+        <f>E6/C6</f>
+        <v>24.8</v>
+      </c>
+      <c r="E6" s="16">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>148800</v>
+      </c>
+      <c r="F6" s="16">
+        <f t="shared" si="1"/>
+        <v>297.60000000000002</v>
+      </c>
+      <c r="G6" s="16">
+        <f t="shared" si="1"/>
+        <v>8.9280000000000008</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="1"/>
+        <v>1.488</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="1"/>
+        <v>21.561120000000003</v>
+      </c>
+      <c r="J6" s="16">
+        <f t="shared" si="1"/>
+        <v>149129.57712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1">
       <c r="A7" s="56">
         <v>44676</v>
       </c>
@@ -13015,224 +13002,70 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="20">
         <f>C7*D7</f>
-        <v>25200</v>
+        <v>20400</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>50.4</v>
+        <v>40.800000000000004</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>1.512</v>
+        <v>1.224</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.252</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>3.6514800000000003</v>
+        <v>2.9559600000000006</v>
       </c>
       <c r="J7" s="20">
         <f>E7+F7+I7+G7+H7</f>
-        <v>25255.815480000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="14.25">
+        <v>20445.183959999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-0.25</v>
+        <v>-0.31451612903225806</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
-        <v>4800</v>
+        <v>7200</v>
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>26.25</v>
+        <v>23.5</v>
       </c>
       <c r="E8" s="10">
-        <f t="shared" ref="E8:J8" si="0">SUM(E6:E7)</f>
-        <v>126000</v>
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>169200</v>
       </c>
       <c r="F8" s="10">
-        <f t="shared" si="0"/>
-        <v>252</v>
+        <f t="shared" si="2"/>
+        <v>338.40000000000003</v>
       </c>
       <c r="G8" s="10">
-        <f t="shared" si="0"/>
-        <v>7.5600000000000005</v>
+        <f t="shared" si="2"/>
+        <v>10.152000000000001</v>
       </c>
       <c r="H8" s="10">
-        <f t="shared" si="0"/>
-        <v>1.26</v>
+        <f t="shared" si="2"/>
+        <v>1.6919999999999999</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="0"/>
-        <v>18.257400000000001</v>
+        <f t="shared" si="2"/>
+        <v>24.517080000000004</v>
       </c>
       <c r="J8" s="10">
-        <f t="shared" si="0"/>
-        <v>126279.07740000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A9" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D9" s="46">
-        <v>20</v>
-      </c>
-      <c r="E9" s="20">
-        <f>C9*D9</f>
-        <v>24000</v>
-      </c>
-      <c r="F9" s="20">
-        <f>E9*0.002</f>
-        <v>48</v>
-      </c>
-      <c r="G9" s="20">
-        <f>E9*0.00006</f>
-        <v>1.44</v>
-      </c>
-      <c r="H9" s="20">
-        <f>E9*0.00001</f>
-        <v>0.24000000000000002</v>
-      </c>
-      <c r="I9" s="20">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>3.4776000000000002</v>
-      </c>
-      <c r="J9" s="20">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>24053.157599999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="12">
-        <f>(D9-D8)/D8</f>
-        <v>-0.23809523809523808</v>
-      </c>
-      <c r="C10" s="10">
-        <f>SUM(C8:C9)</f>
-        <v>6000</v>
-      </c>
-      <c r="D10" s="11">
-        <f>E10/C10</f>
-        <v>25</v>
-      </c>
-      <c r="E10" s="10">
-        <f t="shared" ref="E10:J10" si="1">SUM(E8:E9)</f>
-        <v>150000</v>
-      </c>
-      <c r="F10" s="10">
-        <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H10" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="10">
-        <f t="shared" si="1"/>
-        <v>21.734999999999999</v>
-      </c>
-      <c r="J10" s="10">
-        <f t="shared" si="1"/>
-        <v>150332.23500000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A11" s="56">
-        <v>44676</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D11" s="46">
-        <v>19</v>
-      </c>
-      <c r="E11" s="20">
-        <f>C11*D11</f>
-        <v>22800</v>
-      </c>
-      <c r="F11" s="20">
-        <f>E11*0.002</f>
-        <v>45.6</v>
-      </c>
-      <c r="G11" s="20">
-        <f>E11*0.00006</f>
-        <v>1.3680000000000001</v>
-      </c>
-      <c r="H11" s="20">
-        <f>E11*0.00001</f>
-        <v>0.22800000000000001</v>
-      </c>
-      <c r="I11" s="20">
-        <f>(F11+G11+H11)*0.07</f>
-        <v>3.3037200000000007</v>
-      </c>
-      <c r="J11" s="20">
-        <f>E11+F11+I11+G11+H11</f>
-        <v>22850.499719999996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" ht="14.25">
-      <c r="A12" s="56"/>
-      <c r="B12" s="12">
-        <f>(D11-D10)/D10</f>
-        <v>-0.24</v>
-      </c>
-      <c r="C12" s="10">
-        <f>SUM(C10:C11)</f>
-        <v>7200</v>
-      </c>
-      <c r="D12" s="11">
-        <f>E12/C12</f>
-        <v>24</v>
-      </c>
-      <c r="E12" s="10">
-        <f t="shared" ref="E12:J12" si="2">SUM(E10:E11)</f>
-        <v>172800</v>
-      </c>
-      <c r="F12" s="10">
         <f t="shared" si="2"/>
-        <v>345.6</v>
-      </c>
-      <c r="G12" s="10">
-        <f t="shared" si="2"/>
-        <v>10.368</v>
-      </c>
-      <c r="H12" s="10">
-        <f t="shared" si="2"/>
-        <v>1.728</v>
-      </c>
-      <c r="I12" s="10">
-        <f t="shared" si="2"/>
-        <v>25.038720000000001</v>
-      </c>
-      <c r="J12" s="10">
-        <f t="shared" si="2"/>
-        <v>173182.73472000001</v>
+        <v>169574.76108</v>
       </c>
     </row>
   </sheetData>
@@ -13246,7 +13079,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -14480,7 +14313,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
@@ -14545,7 +14378,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="30"/>
     </row>
-    <row r="3" spans="1:14" ht="12.75">
+    <row r="3" spans="1:14">
       <c r="A3" s="56"/>
       <c r="B3" s="25"/>
       <c r="C3" s="10"/>
@@ -14599,7 +14432,7 @@
       <c r="M5" s="62"/>
       <c r="N5" s="62"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="12.75">
+    <row r="6" spans="1:14" s="1" customFormat="1">
       <c r="A6" s="56">
         <v>44242</v>
       </c>
@@ -14705,12 +14538,6 @@
         <v>1169.0112700000027</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75"/>
-    <row r="11" spans="1:14" ht="12.75"/>
-    <row r="12" spans="1:14" ht="12.75"/>
-    <row r="13" spans="1:14" ht="12.75"/>
-    <row r="15" spans="1:14" ht="12.75"/>
-    <row r="16" spans="1:14" ht="12.75"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -14954,7 +14781,7 @@
       <c r="M6" s="62"/>
       <c r="N6" s="62"/>
     </row>
-    <row r="7" spans="1:14" s="13" customFormat="1" ht="12.75">
+    <row r="7" spans="1:14" s="13" customFormat="1">
       <c r="A7" s="67">
         <v>44473</v>
       </c>
@@ -15054,7 +14881,7 @@
       <c r="M9" s="62"/>
       <c r="N9" s="62"/>
     </row>
-    <row r="10" spans="1:14" s="13" customFormat="1" ht="12.75">
+    <row r="10" spans="1:14" s="13" customFormat="1">
       <c r="A10" s="39">
         <v>44728</v>
       </c>
@@ -15095,7 +14922,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="12"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="12.75">
+    <row r="11" spans="1:14" s="1" customFormat="1">
       <c r="A11" s="49">
         <v>44923</v>
       </c>
@@ -15134,7 +14961,7 @@
         <v>92793.21822000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="12.75">
+    <row r="12" spans="1:14" s="1" customFormat="1">
       <c r="A12" s="49" t="s">
         <v>4</v>
       </c>
@@ -15554,7 +15381,7 @@
       </c>
       <c r="K10" s="25"/>
     </row>
-    <row r="11" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="11" spans="1:14" s="21" customFormat="1">
       <c r="A11" s="14">
         <v>44956</v>
       </c>
@@ -15632,7 +15459,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="13" spans="1:14" s="21" customFormat="1">
       <c r="A13" s="8">
         <v>44956</v>
       </c>
@@ -15670,7 +15497,7 @@
         <v>75166.7595</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="21" customFormat="1" ht="12.75">
+    <row r="14" spans="1:14" s="21" customFormat="1">
       <c r="A14" s="44"/>
       <c r="B14" s="3">
         <f>(D13-D12)/D12</f>
@@ -15710,7 +15537,6 @@
       </c>
       <c r="K14" s="25"/>
     </row>
-    <row r="15" spans="1:14" ht="12"/>
     <row r="16" spans="1:14" s="63" customFormat="1" ht="21.75">
       <c r="A16" s="56">
         <v>44629</v>
@@ -16385,7 +16211,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:O72"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="89" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -16447,7 +16273,7 @@
       <c r="K2" s="17"/>
       <c r="L2" s="30"/>
     </row>
-    <row r="3" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="3" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A3" s="49">
         <v>44368</v>
       </c>
@@ -16490,7 +16316,7 @@
       <c r="N3" s="58"/>
       <c r="O3" s="58"/>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="4" spans="1:15" s="1" customFormat="1">
       <c r="A4" s="54"/>
       <c r="B4" s="74">
         <f>(D3-D2)/D2</f>
@@ -16534,7 +16360,7 @@
       <c r="N4" s="59"/>
       <c r="O4" s="59"/>
     </row>
-    <row r="5" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="5" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A5" s="49">
         <v>44398</v>
       </c>
@@ -16577,7 +16403,7 @@
       <c r="N5" s="58"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="6" spans="1:15" s="1" customFormat="1">
       <c r="A6" s="54"/>
       <c r="B6" s="74">
         <f>(D5-D4)/D4</f>
@@ -16621,7 +16447,7 @@
       <c r="N6" s="59"/>
       <c r="O6" s="59"/>
     </row>
-    <row r="7" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="7" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A7" s="49">
         <v>44452</v>
       </c>
@@ -16664,7 +16490,7 @@
       <c r="N7" s="58"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="8" spans="1:15" s="1" customFormat="1">
       <c r="A8" s="54"/>
       <c r="B8" s="74">
         <f>(D7-D6)/D6</f>
@@ -16708,7 +16534,7 @@
       <c r="N8" s="59"/>
       <c r="O8" s="59"/>
     </row>
-    <row r="9" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="9" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A9" s="49">
         <v>44462</v>
       </c>
@@ -16751,7 +16577,7 @@
       <c r="N9" s="58"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="10" spans="1:15" s="1" customFormat="1">
       <c r="A10" s="54"/>
       <c r="B10" s="74">
         <f>(D9-D8)/D8</f>
@@ -16795,7 +16621,7 @@
       <c r="N10" s="59"/>
       <c r="O10" s="59"/>
     </row>
-    <row r="11" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="11" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A11" s="49">
         <v>44496</v>
       </c>
@@ -16897,7 +16723,7 @@
         <v>-29174.188317500004</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="14" spans="1:15" s="1" customFormat="1">
       <c r="A14" s="50"/>
       <c r="B14" s="74" t="s">
         <v>2</v>
@@ -16932,7 +16758,7 @@
       <c r="N14" s="59"/>
       <c r="O14" s="59"/>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="15" spans="1:15" s="1" customFormat="1">
       <c r="A15" s="50">
         <v>44462</v>
       </c>
@@ -17027,7 +16853,7 @@
         <v>-29928.068672500005</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="18" spans="1:15" s="1" customFormat="1">
       <c r="A18" s="50"/>
       <c r="B18" s="74" t="s">
         <v>2</v>
@@ -17062,7 +16888,7 @@
       <c r="N18" s="59"/>
       <c r="O18" s="59"/>
     </row>
-    <row r="19" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="19" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A19" s="49">
         <v>44452</v>
       </c>
@@ -17163,7 +16989,7 @@
         <v>-33691.922497500003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="22" spans="1:15" s="1" customFormat="1">
       <c r="A22" s="49">
         <v>44951</v>
       </c>
@@ -17200,7 +17026,7 @@
       <c r="N22" s="59"/>
       <c r="O22" s="59"/>
     </row>
-    <row r="23" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="23" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A23" s="49">
         <v>44398</v>
       </c>
@@ -17301,7 +17127,7 @@
         <v>-34467.99465250002</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="26" spans="1:15" s="1" customFormat="1">
       <c r="A26" s="54"/>
       <c r="B26" s="74" t="s">
         <v>2</v>
@@ -17336,7 +17162,7 @@
       <c r="N26" s="59"/>
       <c r="O26" s="59"/>
     </row>
-    <row r="27" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="27" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A27" s="56">
         <v>44462</v>
       </c>
@@ -17435,7 +17261,7 @@
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" ht="14.25">
+    <row r="30" spans="1:15" s="1" customFormat="1">
       <c r="A30" s="54"/>
       <c r="B30" s="74"/>
       <c r="C30" s="51"/>
@@ -17452,7 +17278,7 @@
       <c r="N30" s="59"/>
       <c r="O30" s="59"/>
     </row>
-    <row r="31" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="31" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A31" s="49">
         <v>44550</v>
       </c>
@@ -17571,7 +17397,7 @@
       <c r="N34" s="59"/>
       <c r="O34" s="59"/>
     </row>
-    <row r="35" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="35" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A35" s="49">
         <v>44624</v>
       </c>
@@ -17882,12 +17708,12 @@
         <v>2533.0633850000013</v>
       </c>
     </row>
-    <row r="45" spans="1:15" s="1" customFormat="1" ht="12">
+    <row r="45" spans="1:15" s="1" customFormat="1">
       <c r="A45" s="50"/>
       <c r="D45" s="47"/>
       <c r="J45" s="53"/>
     </row>
-    <row r="46" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="46" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A46" s="56">
         <v>44624</v>
       </c>
@@ -18001,7 +17827,7 @@
         <v>9068.4356374999916</v>
       </c>
     </row>
-    <row r="49" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="49" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A49" s="49">
         <v>44550</v>
       </c>
@@ -18116,7 +17942,7 @@
         <v>8741.1065874999767</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="52" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A52" s="56">
         <v>44543</v>
       </c>
@@ -18231,7 +18057,7 @@
         <v>8413.7775374999619</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="55" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A55" s="56">
         <v>44496</v>
       </c>
@@ -18346,7 +18172,7 @@
         <v>-56.5475750000478</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="58" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A58" s="56">
         <v>44462</v>
       </c>
@@ -18461,7 +18287,7 @@
         <v>-9779.6413125000545</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="61" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A61" s="56">
         <v>44452</v>
       </c>
@@ -18576,7 +18402,7 @@
         <v>-24513.809550000064</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="64" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A64" s="56">
         <v>44398</v>
       </c>
@@ -18691,7 +18517,7 @@
         <v>-45511.820912500087</v>
       </c>
     </row>
-    <row r="67" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="67" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A67" s="56">
         <v>44368</v>
       </c>
@@ -18806,7 +18632,7 @@
         <v>-72147.291087500096</v>
       </c>
     </row>
-    <row r="70" spans="1:15" s="19" customFormat="1" ht="15">
+    <row r="70" spans="1:15" s="19" customFormat="1" ht="16.5">
       <c r="A70" s="56">
         <v>44368</v>
       </c>
@@ -19328,7 +19154,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FBE3BD-D1CD-48BE-9C86-B7AFE096597B}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
     <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
@@ -19695,7 +19521,7 @@
         <v>7726.2209999999905</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="12">
+    <row r="12" spans="1:14" s="1" customFormat="1">
       <c r="A12" s="50"/>
       <c r="D12" s="47"/>
       <c r="J12" s="53">
@@ -19810,7 +19636,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9557670-D125-4921-A689-63714DB07995}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
@@ -20027,7 +19853,7 @@
       <c r="K6" s="58"/>
       <c r="L6" s="58"/>
     </row>
-    <row r="7" spans="1:13" s="19" customFormat="1" ht="15">
+    <row r="7" spans="1:13" s="19" customFormat="1" ht="16.5">
       <c r="A7" s="56">
         <v>44706</v>
       </c>
@@ -20065,7 +19891,7 @@
         <v>52616.282250000004</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="19" customFormat="1" ht="15">
+    <row r="8" spans="1:13" s="19" customFormat="1" ht="16.5">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
@@ -20118,7 +19944,7 @@
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
     </row>
-    <row r="10" spans="1:13" s="19" customFormat="1" ht="15">
+    <row r="10" spans="1:13" s="19" customFormat="1" ht="16.5">
       <c r="A10" s="56">
         <v>44680</v>
       </c>
@@ -20156,7 +19982,7 @@
         <v>64041.532110000007</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="11" spans="1:13" s="13" customFormat="1">
       <c r="A11" s="56">
         <v>44809</v>
       </c>
@@ -20222,7 +20048,7 @@
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" spans="1:13" s="21" customFormat="1" ht="12.75">
+    <row r="13" spans="1:13" s="21" customFormat="1">
       <c r="A13" s="49">
         <v>44706</v>
       </c>
@@ -20261,7 +20087,7 @@
       </c>
       <c r="L13" s="25"/>
     </row>
-    <row r="14" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="14" spans="1:13" s="13" customFormat="1">
       <c r="A14" s="49">
         <v>44809</v>
       </c>
@@ -20365,7 +20191,7 @@
         <v>61636.216350000002</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="17" spans="1:13" s="13" customFormat="1">
       <c r="A17" s="49">
         <v>44860</v>
       </c>
@@ -20431,8 +20257,6 @@
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" spans="1:13" ht="12"/>
-    <row r="20" spans="1:13" ht="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -20502,7 +20326,7 @@
         <v>97214.845300000015</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="78" customFormat="1" ht="12.75">
+    <row r="3" spans="1:14" s="78" customFormat="1">
       <c r="A3" s="82">
         <v>44818</v>
       </c>
@@ -20540,7 +20364,7 @@
         <v>95211.228700000007</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="78" customFormat="1" ht="12.75">
+    <row r="4" spans="1:14" s="78" customFormat="1">
       <c r="A4" s="82"/>
       <c r="B4" s="87">
         <f>(D3-D2)/D2</f>
@@ -20580,7 +20404,7 @@
       </c>
       <c r="K4" s="81"/>
     </row>
-    <row r="5" spans="1:14" s="78" customFormat="1" ht="12.75">
+    <row r="5" spans="1:14" s="78" customFormat="1">
       <c r="A5" s="82">
         <v>44880</v>
       </c>
@@ -20618,7 +20442,7 @@
         <v>186413.56355999998</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="78" customFormat="1" ht="12.75">
+    <row r="6" spans="1:14" s="78" customFormat="1">
       <c r="A6" s="82"/>
       <c r="B6" s="87">
         <f>(D5-D4)/D4</f>
@@ -20658,7 +20482,7 @@
       </c>
       <c r="K6" s="81"/>
     </row>
-    <row r="7" spans="1:14" ht="12.75">
+    <row r="7" spans="1:14">
       <c r="A7" s="82">
         <v>44950</v>
       </c>
@@ -20739,7 +20563,7 @@
       <c r="M8" s="62"/>
       <c r="N8" s="62"/>
     </row>
-    <row r="9" spans="1:14" ht="12.75">
+    <row r="9" spans="1:14">
       <c r="A9" s="82">
         <v>44964</v>
       </c>
@@ -20777,7 +20601,7 @@
         <v>183406.89317999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75">
+    <row r="10" spans="1:14">
       <c r="A10" s="82"/>
       <c r="B10" s="87">
         <f>(D9-D8)/D8</f>
@@ -20816,7 +20640,7 @@
         <v>757680.10544000007</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="12.75">
+    <row r="11" spans="1:14">
       <c r="A11" s="77">
         <v>44964</v>
       </c>
@@ -20854,7 +20678,7 @@
         <v>179397.99934000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="12.75">
+    <row r="12" spans="1:14">
       <c r="A12" s="77"/>
       <c r="B12" s="81">
         <f>(D11-D10)/D10</f>
@@ -22950,7 +22774,7 @@
         <v>146124.18046800004</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="78" customFormat="1" ht="12.75">
+    <row r="9" spans="1:13" s="78" customFormat="1">
       <c r="A9" s="82">
         <v>44880</v>
       </c>
@@ -22988,7 +22812,7 @@
         <v>97416.120311999985</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="78" customFormat="1" ht="12.75">
+    <row r="10" spans="1:13" s="78" customFormat="1">
       <c r="A10" s="82">
         <v>44886</v>
       </c>
@@ -23026,7 +22850,7 @@
         <v>48708.060155999992</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="78" customFormat="1" ht="12.75">
+    <row r="11" spans="1:13" s="78" customFormat="1">
       <c r="A11" s="77"/>
       <c r="C11" s="79"/>
       <c r="D11" s="80"/>
@@ -23037,7 +22861,7 @@
       <c r="I11" s="94"/>
       <c r="J11" s="94"/>
     </row>
-    <row r="12" spans="1:13" s="78" customFormat="1" ht="12.75">
+    <row r="12" spans="1:13" s="78" customFormat="1">
       <c r="A12" s="77"/>
       <c r="B12" s="81"/>
       <c r="C12" s="79"/>
@@ -23270,7 +23094,7 @@
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="1:13" s="13" customFormat="1" ht="12.75">
+    <row r="20" spans="1:13" s="13" customFormat="1">
       <c r="A20" s="49"/>
       <c r="B20" s="15"/>
       <c r="C20" s="16"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,37 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11673" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0381DE76-E76C-456E-856F-30324C1D5CFC}"/>
+  <xr:revisionPtr revIDLastSave="11689" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E7ED58A-2098-4F35-BF5B-13BC26C9065E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="20" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
     <sheet name="PTTGC" sheetId="42" r:id="rId2"/>
     <sheet name="STA" sheetId="197" r:id="rId3"/>
-    <sheet name="ASP" sheetId="181" r:id="rId4"/>
-    <sheet name="BANPU" sheetId="202" r:id="rId5"/>
-    <sheet name="BCH" sheetId="150" r:id="rId6"/>
-    <sheet name="CPNREIT" sheetId="194" r:id="rId7"/>
-    <sheet name="DIF" sheetId="57" r:id="rId8"/>
-    <sheet name="DOHOME" sheetId="170" r:id="rId9"/>
-    <sheet name="GVREIT" sheetId="195" r:id="rId10"/>
-    <sheet name="IVL" sheetId="196" r:id="rId11"/>
-    <sheet name="JASIF" sheetId="46" r:id="rId12"/>
-    <sheet name="JMART" sheetId="204" r:id="rId13"/>
-    <sheet name="JMT" sheetId="205" r:id="rId14"/>
-    <sheet name="MCS" sheetId="20" r:id="rId15"/>
-    <sheet name="NER" sheetId="117" r:id="rId16"/>
-    <sheet name="ORI" sheetId="184" r:id="rId17"/>
-    <sheet name="RCL" sheetId="161" r:id="rId18"/>
-    <sheet name="SCC" sheetId="152" r:id="rId19"/>
-    <sheet name="SENA" sheetId="183" r:id="rId20"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId21"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId22"/>
-    <sheet name="TFFIF" sheetId="110" r:id="rId23"/>
-    <sheet name="TMT" sheetId="145" r:id="rId24"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId25"/>
-    <sheet name="WHART" sheetId="171" r:id="rId26"/>
+    <sheet name="ASK" sheetId="207" r:id="rId4"/>
+    <sheet name="ASP" sheetId="181" r:id="rId5"/>
+    <sheet name="BANPU" sheetId="202" r:id="rId6"/>
+    <sheet name="BCH" sheetId="150" r:id="rId7"/>
+    <sheet name="CPNREIT" sheetId="194" r:id="rId8"/>
+    <sheet name="DIF" sheetId="57" r:id="rId9"/>
+    <sheet name="DOHOME" sheetId="170" r:id="rId10"/>
+    <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
+    <sheet name="IVL" sheetId="196" r:id="rId12"/>
+    <sheet name="JASIF" sheetId="46" r:id="rId13"/>
+    <sheet name="JMART" sheetId="204" r:id="rId14"/>
+    <sheet name="JMT" sheetId="205" r:id="rId15"/>
+    <sheet name="MCS" sheetId="20" r:id="rId16"/>
+    <sheet name="NER" sheetId="117" r:id="rId17"/>
+    <sheet name="ORI" sheetId="184" r:id="rId18"/>
+    <sheet name="RCL" sheetId="161" r:id="rId19"/>
+    <sheet name="SCC" sheetId="152" r:id="rId20"/>
+    <sheet name="SENA" sheetId="183" r:id="rId21"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
+    <sheet name="TFFIF" sheetId="110" r:id="rId24"/>
+    <sheet name="TMT" sheetId="145" r:id="rId25"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId26"/>
+    <sheet name="WHART" sheetId="171" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -2635,6 +2636,845 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29654F34-1A94-4023-9770-717C53C33E1B}">
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="19" customFormat="1" ht="16.5">
+      <c r="A2" s="49">
+        <v>44428</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>8000</v>
+      </c>
+      <c r="D2" s="41">
+        <v>25</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>200000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>400</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>12</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>28.980000000000004</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>200442.98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="78" customFormat="1">
+      <c r="A3" s="82">
+        <v>44566</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="84">
+        <v>4000</v>
+      </c>
+      <c r="D3" s="85">
+        <v>22.9</v>
+      </c>
+      <c r="E3" s="86">
+        <f>C3*D3</f>
+        <v>91600</v>
+      </c>
+      <c r="F3" s="86">
+        <f>E3*0.002</f>
+        <v>183.20000000000002</v>
+      </c>
+      <c r="G3" s="86">
+        <f>E3*0.000068</f>
+        <v>6.2287999999999997</v>
+      </c>
+      <c r="H3" s="86">
+        <f>E3*0.00001</f>
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="I3" s="86">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>13.324136000000003</v>
+      </c>
+      <c r="J3" s="86">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>91803.668935999987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="78" customFormat="1">
+      <c r="A4" s="82"/>
+      <c r="B4" s="87">
+        <f>(D3-D2)/D2</f>
+        <v>-8.4000000000000061E-2</v>
+      </c>
+      <c r="C4" s="84">
+        <f>SUM(C2:C3)</f>
+        <v>12000</v>
+      </c>
+      <c r="D4" s="85">
+        <f>E4/C4</f>
+        <v>24.3</v>
+      </c>
+      <c r="E4" s="84">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>291600</v>
+      </c>
+      <c r="F4" s="84">
+        <f t="shared" si="0"/>
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G4" s="84">
+        <f t="shared" si="0"/>
+        <v>18.2288</v>
+      </c>
+      <c r="H4" s="84">
+        <f t="shared" si="0"/>
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="I4" s="84">
+        <f t="shared" si="0"/>
+        <v>42.304136000000007</v>
+      </c>
+      <c r="J4" s="84">
+        <f t="shared" si="0"/>
+        <v>292246.64893600001</v>
+      </c>
+      <c r="K4" s="81"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="54">
+        <v>44624</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="51">
+        <f>C4*6/5</f>
+        <v>14400</v>
+      </c>
+      <c r="D5" s="52">
+        <f>E5/C5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E5" s="55">
+        <v>291600</v>
+      </c>
+      <c r="F5" s="55">
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G5" s="55">
+        <v>18.2288</v>
+      </c>
+      <c r="H5" s="55">
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="I5" s="55">
+        <v>42.304136000000007</v>
+      </c>
+      <c r="J5" s="55">
+        <v>292246.64893600001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="13" customFormat="1">
+      <c r="A6" s="49">
+        <v>44630</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="16">
+        <v>4800</v>
+      </c>
+      <c r="D6" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="E6" s="17">
+        <f>C6*D6</f>
+        <v>108000</v>
+      </c>
+      <c r="F6" s="27">
+        <f>E6*0.002</f>
+        <v>216</v>
+      </c>
+      <c r="G6" s="26">
+        <f>E6*0.000068</f>
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="H6" s="26">
+        <f>E6*0.00001</f>
+        <v>1.08</v>
+      </c>
+      <c r="I6" s="26">
+        <f>(F6+G6+H6)*0.07</f>
+        <v>15.709680000000002</v>
+      </c>
+      <c r="J6" s="26">
+        <f>E6-F6-G6-H6-I6</f>
+        <v>107759.86632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="78" customFormat="1">
+      <c r="A7" s="82">
+        <v>44630</v>
+      </c>
+      <c r="B7" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="84">
+        <v>9600</v>
+      </c>
+      <c r="D7" s="85">
+        <f>D5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E7" s="86">
+        <f>C7*D7</f>
+        <v>194400</v>
+      </c>
+      <c r="F7" s="86">
+        <f>E7*0.002</f>
+        <v>388.8</v>
+      </c>
+      <c r="G7" s="86">
+        <f>E7*0.000068</f>
+        <v>13.219200000000001</v>
+      </c>
+      <c r="H7" s="86">
+        <f>E7*0.00001</f>
+        <v>1.9440000000000002</v>
+      </c>
+      <c r="I7" s="86">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>28.277424000000003</v>
+      </c>
+      <c r="J7" s="86">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>194832.24062399997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="78" customFormat="1">
+      <c r="A8" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B8" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="84">
+        <v>7200</v>
+      </c>
+      <c r="D8" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E8" s="86">
+        <f>C8*D8</f>
+        <v>145800</v>
+      </c>
+      <c r="F8" s="86">
+        <f>E8*0.002</f>
+        <v>291.60000000000002</v>
+      </c>
+      <c r="G8" s="86">
+        <f>E8*0.000068</f>
+        <v>9.9144000000000005</v>
+      </c>
+      <c r="H8" s="86">
+        <f>E8*0.00001</f>
+        <v>1.4580000000000002</v>
+      </c>
+      <c r="I8" s="86">
+        <f>(F8+G8+H8)*0.07</f>
+        <v>21.208068000000004</v>
+      </c>
+      <c r="J8" s="86">
+        <f>E8+F8+I8+G8+H8</f>
+        <v>146124.18046800004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="78" customFormat="1">
+      <c r="A9" s="82">
+        <v>44880</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="84">
+        <v>4800</v>
+      </c>
+      <c r="D9" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E9" s="86">
+        <f>C9*D9</f>
+        <v>97200</v>
+      </c>
+      <c r="F9" s="86">
+        <f>E9*0.002</f>
+        <v>194.4</v>
+      </c>
+      <c r="G9" s="86">
+        <f>E9*0.000068</f>
+        <v>6.6096000000000004</v>
+      </c>
+      <c r="H9" s="86">
+        <f>E9*0.00001</f>
+        <v>0.97200000000000009</v>
+      </c>
+      <c r="I9" s="86">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>14.138712000000002</v>
+      </c>
+      <c r="J9" s="86">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>97416.120311999985</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="78" customFormat="1">
+      <c r="A10" s="82">
+        <v>44886</v>
+      </c>
+      <c r="B10" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D10" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E10" s="86">
+        <f>C10*D10</f>
+        <v>48600</v>
+      </c>
+      <c r="F10" s="86">
+        <f>E10*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G10" s="86">
+        <f>E10*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H10" s="86">
+        <f>E10*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I10" s="86">
+        <f>(F10+G10+H10)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J10" s="86">
+        <f>E10+F10+I10+G10+H10</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="78" customFormat="1">
+      <c r="A11" s="77"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+    </row>
+    <row r="12" spans="1:13" s="78" customFormat="1">
+      <c r="A12" s="77"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="81"/>
+    </row>
+    <row r="13" spans="1:13" s="78" customFormat="1">
+      <c r="A13" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D13" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E13" s="86">
+        <f>C13*D13</f>
+        <v>48600</v>
+      </c>
+      <c r="F13" s="86">
+        <f>E13*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G13" s="86">
+        <f>E13*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H13" s="86">
+        <f>E13*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I13" s="86">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J13" s="86">
+        <f>E13+F13+I13+G13+H13</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="13" customFormat="1">
+      <c r="A14" s="49">
+        <v>44886</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="16">
+        <f>C13</f>
+        <v>2400</v>
+      </c>
+      <c r="D14" s="26">
+        <v>14.2</v>
+      </c>
+      <c r="E14" s="17">
+        <f>C14*D14</f>
+        <v>34080</v>
+      </c>
+      <c r="F14" s="27">
+        <f>E14*0.002</f>
+        <v>68.16</v>
+      </c>
+      <c r="G14" s="26">
+        <f>E14*0.000068</f>
+        <v>2.3174399999999999</v>
+      </c>
+      <c r="H14" s="26">
+        <f>E14*0.00001</f>
+        <v>0.34080000000000005</v>
+      </c>
+      <c r="I14" s="26">
+        <f>(F14+G14+H14)*0.07</f>
+        <v>4.9572768000000007</v>
+      </c>
+      <c r="J14" s="26">
+        <f>E14-F14-G14-H14-I14</f>
+        <v>34004.2244832</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A15" s="28">
+        <f>DAYS360(A13,A14)</f>
+        <v>191</v>
+      </c>
+      <c r="B15" s="30">
+        <f>(D14-D13)/D13</f>
+        <v>-0.29876543209876549</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18">
+        <f>E14-E13</f>
+        <v>-14520</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18">
+        <f>J14-J13</f>
+        <v>-14703.835672799993</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" s="13" customFormat="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+    </row>
+    <row r="17" spans="1:13" s="78" customFormat="1">
+      <c r="A17" s="82">
+        <v>44691</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D17" s="85">
+        <v>20.25</v>
+      </c>
+      <c r="E17" s="86">
+        <f>C17*D17</f>
+        <v>48600</v>
+      </c>
+      <c r="F17" s="86">
+        <f>E17*0.002</f>
+        <v>97.2</v>
+      </c>
+      <c r="G17" s="86">
+        <f>E17*0.000068</f>
+        <v>3.3048000000000002</v>
+      </c>
+      <c r="H17" s="86">
+        <f>E17*0.00001</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="I17" s="86">
+        <f>(F17+G17+H17)*0.07</f>
+        <v>7.0693560000000009</v>
+      </c>
+      <c r="J17" s="86">
+        <f>E17+F17+I17+G17+H17</f>
+        <v>48708.060155999992</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="13" customFormat="1">
+      <c r="A18" s="49">
+        <v>44880</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="16">
+        <f>C17</f>
+        <v>2400</v>
+      </c>
+      <c r="D18" s="26">
+        <v>13.7</v>
+      </c>
+      <c r="E18" s="17">
+        <f>C18*D18</f>
+        <v>32880</v>
+      </c>
+      <c r="F18" s="27">
+        <f>E18*0.002</f>
+        <v>65.760000000000005</v>
+      </c>
+      <c r="G18" s="26">
+        <f>E18*0.000068</f>
+        <v>2.23584</v>
+      </c>
+      <c r="H18" s="26">
+        <f>E18*0.00001</f>
+        <v>0.32880000000000004</v>
+      </c>
+      <c r="I18" s="26">
+        <f>(F18+G18+H18)*0.07</f>
+        <v>4.7827248000000004</v>
+      </c>
+      <c r="J18" s="26">
+        <f>E18-F18-G18-H18-I18</f>
+        <v>32806.892635199991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A19" s="28">
+        <f>DAYS360(A17,A18)</f>
+        <v>185</v>
+      </c>
+      <c r="B19" s="30">
+        <f>(D18-D17)/D17</f>
+        <v>-0.32345679012345685</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18">
+        <f>E18-E17</f>
+        <v>-15720</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18">
+        <f>J18-J17</f>
+        <v>-15901.167520800002</v>
+      </c>
+      <c r="K19" s="32"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" s="13" customFormat="1">
+      <c r="A20" s="49"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:13" s="78" customFormat="1">
+      <c r="A21" s="82">
+        <v>44644</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="84">
+        <v>2400</v>
+      </c>
+      <c r="D21" s="85">
+        <v>21.3</v>
+      </c>
+      <c r="E21" s="86">
+        <f>C21*D21</f>
+        <v>51120</v>
+      </c>
+      <c r="F21" s="86">
+        <f>E21*0.002</f>
+        <v>102.24000000000001</v>
+      </c>
+      <c r="G21" s="86">
+        <f>E21*0.000068</f>
+        <v>3.4761600000000001</v>
+      </c>
+      <c r="H21" s="86">
+        <f>E21*0.00001</f>
+        <v>0.51119999999999999</v>
+      </c>
+      <c r="I21" s="86">
+        <f>(F21+G21+H21)*0.07</f>
+        <v>7.4359152000000011</v>
+      </c>
+      <c r="J21" s="86">
+        <f>E21+F21+I21+G21+H21</f>
+        <v>51233.6632752</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="13" customFormat="1">
+      <c r="A22" s="49">
+        <v>44671</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16">
+        <f>C21</f>
+        <v>2400</v>
+      </c>
+      <c r="D22" s="26">
+        <v>22.4</v>
+      </c>
+      <c r="E22" s="17">
+        <f>C22*D22</f>
+        <v>53760</v>
+      </c>
+      <c r="F22" s="27">
+        <f>E22*0.002</f>
+        <v>107.52</v>
+      </c>
+      <c r="G22" s="26">
+        <f>E22*0.000068</f>
+        <v>3.6556799999999998</v>
+      </c>
+      <c r="H22" s="26">
+        <f>E22*0.00001</f>
+        <v>0.53760000000000008</v>
+      </c>
+      <c r="I22" s="26">
+        <f>(F22+G22+H22)*0.07</f>
+        <v>7.8199296000000009</v>
+      </c>
+      <c r="J22" s="26">
+        <f>E22-F22-G22-H22-I22</f>
+        <v>53640.466790399994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A23" s="28">
+        <f>DAYS360(A21,A22)</f>
+        <v>26</v>
+      </c>
+      <c r="B23" s="30">
+        <f>(D22-D21)/D21</f>
+        <v>5.164319248826281E-2</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18">
+        <f>E22-E21</f>
+        <v>2640</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18">
+        <f>J22-J21</f>
+        <v>2406.8035151999939</v>
+      </c>
+      <c r="K23" s="32"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" spans="1:13" s="21" customFormat="1">
+      <c r="A24" s="49">
+        <v>44538</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="16">
+        <f>C5/3</f>
+        <v>4800</v>
+      </c>
+      <c r="D24" s="17">
+        <f>D5</f>
+        <v>20.25</v>
+      </c>
+      <c r="E24" s="18">
+        <f>C24*D24</f>
+        <v>97200</v>
+      </c>
+      <c r="F24" s="18">
+        <f>E24*0.002</f>
+        <v>194.4</v>
+      </c>
+      <c r="G24" s="18">
+        <f>E24*0.000068</f>
+        <v>6.6096000000000004</v>
+      </c>
+      <c r="H24" s="18">
+        <f>E24*0.00001</f>
+        <v>0.97200000000000009</v>
+      </c>
+      <c r="I24" s="18">
+        <f>(F24+G24+H24)*0.07</f>
+        <v>14.138712000000002</v>
+      </c>
+      <c r="J24" s="18">
+        <f>E24+F24+I24+G24+H24</f>
+        <v>97416.120311999985</v>
+      </c>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="1:13" s="13" customFormat="1">
+      <c r="A25" s="49">
+        <v>44630</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="16">
+        <f>C24</f>
+        <v>4800</v>
+      </c>
+      <c r="D25" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="E25" s="17">
+        <f>C25*D25</f>
+        <v>108000</v>
+      </c>
+      <c r="F25" s="27">
+        <f>E25*0.002</f>
+        <v>216</v>
+      </c>
+      <c r="G25" s="26">
+        <f>E25*0.000068</f>
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="H25" s="26">
+        <f>E25*0.00001</f>
+        <v>1.08</v>
+      </c>
+      <c r="I25" s="26">
+        <f>(F25+G25+H25)*0.07</f>
+        <v>15.709680000000002</v>
+      </c>
+      <c r="J25" s="26">
+        <f>E25-F25-G25-H25-I25</f>
+        <v>107759.86632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="31" customFormat="1" ht="18.75">
+      <c r="A26" s="28">
+        <f>DAYS360(A24,A25)</f>
+        <v>92</v>
+      </c>
+      <c r="B26" s="30">
+        <f>(D25-D24)/D24</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18">
+        <f>E25-E24</f>
+        <v>10800</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18">
+        <f>J25-J24</f>
+        <v>10343.746008000016</v>
+      </c>
+      <c r="K26" s="32"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4115D497-67E5-4755-A37C-D801F1CE1CC8}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -3256,7 +4096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECE484-9DAC-4EE9-A8FE-27A01698073E}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -3740,7 +4580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -4937,7 +5777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5166,7 +6006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF9A6BF-841A-4E49-8659-89A8DE11562A}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -5398,38 +6238,38 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>48.75</v>
+        <v>39.75</v>
       </c>
       <c r="E7" s="62">
         <f>C7*D7</f>
-        <v>58500</v>
+        <v>47700</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>117</v>
+        <v>95.4</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>3.5100000000000002</v>
+        <v>2.8620000000000001</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.58500000000000008</v>
+        <v>0.47700000000000004</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>8.4766500000000011</v>
+        <v>6.9117300000000013</v>
       </c>
       <c r="J7" s="62">
         <f>E7+F7+I7+G7+H7</f>
-        <v>58629.571649999998</v>
+        <v>47805.650730000001</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-0.12162162162162163</v>
+        <v>-0.28378378378378377</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
@@ -5437,31 +6277,31 @@
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8" s="62">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>291600</v>
+        <v>280800</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="2"/>
-        <v>583.20000000000005</v>
+        <v>561.6</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="2"/>
-        <v>17.496000000000002</v>
+        <v>16.847999999999999</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="2"/>
-        <v>2.9160000000000004</v>
+        <v>2.8080000000000003</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="2"/>
-        <v>42.252840000000006</v>
+        <v>40.687920000000005</v>
       </c>
       <c r="J8" s="62">
         <f t="shared" si="2"/>
-        <v>292245.86483999999</v>
+        <v>281421.94391999999</v>
       </c>
     </row>
   </sheetData>
@@ -5472,7 +6312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -7641,7 +8481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8084,7 +8924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -8595,7 +9435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -10149,321 +10989,6 @@
       <c r="J42" s="20">
         <f>J41-J40</f>
         <v>4116.4531500000012</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
-    <col min="6" max="6" width="9" style="21"/>
-    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
-    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="21"/>
-    <col min="13" max="13" width="8.875" style="25"/>
-    <col min="14" max="16384" width="8.875" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="39">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>300</v>
-      </c>
-      <c r="D2" s="17">
-        <v>410</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1">
-      <c r="A3" s="39">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>300</v>
-      </c>
-      <c r="D3" s="17">
-        <v>400</v>
-      </c>
-      <c r="E3" s="18">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="18">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="18">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="18">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="18">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="18">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="70"/>
-      <c r="B4" s="7">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="71">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" spans="1:13" s="13" customFormat="1">
-      <c r="A5" s="39">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
-        <v>300</v>
-      </c>
-      <c r="D5" s="17">
-        <v>384</v>
-      </c>
-      <c r="E5" s="18">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="18">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="18">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="18">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="18">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="18">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="70"/>
-      <c r="B6" s="7">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="71">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="21"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="67">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10">
-        <v>300</v>
-      </c>
-      <c r="D7" s="11">
-        <v>382</v>
-      </c>
-      <c r="E7" s="20">
-        <f>C7*D7</f>
-        <v>114600</v>
-      </c>
-      <c r="F7" s="20">
-        <f>E7*0.002</f>
-        <v>229.20000000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <f>E7*0.00006</f>
-        <v>6.8760000000000003</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7*0.00001</f>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="I7" s="20">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>16.605540000000001</v>
-      </c>
-      <c r="J7" s="20">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>114853.82754</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="25">
-        <f>(D7-D6)/D6</f>
-        <v>-4.0201005025125629E-2</v>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="68">
-        <f>E8/C8</f>
-        <v>394</v>
-      </c>
-      <c r="E8" s="22">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>472800</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" si="2"/>
-        <v>945.6</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="2"/>
-        <v>28.368000000000002</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>4.7280000000000006</v>
-      </c>
-      <c r="I8" s="22">
-        <f t="shared" si="2"/>
-        <v>68.508720000000011</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="2"/>
-        <v>473847.20472000004</v>
       </c>
     </row>
   </sheetData>
@@ -12230,6 +12755,321 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="18" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="39">
+        <v>44459</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>300</v>
+      </c>
+      <c r="D2" s="17">
+        <v>410</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>123000</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>246</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>7.38</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.2300000000000002</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>17.822700000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>123272.4327</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="30"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1">
+      <c r="A3" s="39">
+        <v>44469</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>300</v>
+      </c>
+      <c r="D3" s="17">
+        <v>400</v>
+      </c>
+      <c r="E3" s="18">
+        <f>C3*D3</f>
+        <v>120000</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3*0.002</f>
+        <v>240</v>
+      </c>
+      <c r="G3" s="18">
+        <f>E3*0.00006</f>
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="18">
+        <f>E3*0.00001</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="I3" s="18">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.388000000000002</v>
+      </c>
+      <c r="J3" s="18">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>120265.788</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="70"/>
+      <c r="B4" s="7">
+        <f>(D3-D2)/D2</f>
+        <v>-2.4390243902439025E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>600</v>
+      </c>
+      <c r="D4" s="71">
+        <f>E4/C4</f>
+        <v>405</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>243000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>14.58</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4300000000000006</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.210700000000003</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>243538.22070000001</v>
+      </c>
+      <c r="L4" s="25"/>
+      <c r="M4" s="21"/>
+    </row>
+    <row r="5" spans="1:13" s="13" customFormat="1">
+      <c r="A5" s="39">
+        <v>44579</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>300</v>
+      </c>
+      <c r="D5" s="17">
+        <v>384</v>
+      </c>
+      <c r="E5" s="18">
+        <f>C5*D5</f>
+        <v>115200</v>
+      </c>
+      <c r="F5" s="18">
+        <f>E5*0.002</f>
+        <v>230.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*0.00006</f>
+        <v>6.9119999999999999</v>
+      </c>
+      <c r="H5" s="18">
+        <f>E5*0.00001</f>
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="I5" s="18">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>16.69248</v>
+      </c>
+      <c r="J5" s="18">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>115455.15647999999</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="7">
+        <f>(D5-D4)/D4</f>
+        <v>-5.185185185185185E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM(C4:C5)</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="71">
+        <f>E6/C6</f>
+        <v>398</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>358200</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>716.4</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>21.492000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.5820000000000007</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>51.903180000000006</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>358993.37718000001</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="67">
+        <v>44579</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>300</v>
+      </c>
+      <c r="D7" s="11">
+        <v>382</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>114600</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>229.20000000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>6.8760000000000003</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>16.605540000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>114853.82754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="25">
+        <f>(D7-D6)/D6</f>
+        <v>-4.0201005025125629E-2</v>
+      </c>
+      <c r="C8" s="22">
+        <f>SUM(C6:C7)</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="68">
+        <f>E8/C8</f>
+        <v>394</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>472800</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="2"/>
+        <v>945.6</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="2"/>
+        <v>28.368000000000002</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>4.7280000000000006</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="2"/>
+        <v>68.508720000000011</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="2"/>
+        <v>473847.20472000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12770,7 +13610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -13076,7 +13916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14311,7 +15151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D40E859-355F-466D-8C73-B562F113BB11}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -14546,7 +15386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC4F4F3-83CC-4355-B28D-286BFFC2FE1C}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -15005,7 +15845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15679,7 +16519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -18756,6 +19596,305 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592824FF-B02C-4578-B01E-5589DADB9D1A}">
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21"/>
+    <col min="7" max="7" width="6.75" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.75" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="5.625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="21"/>
+    <col min="13" max="13" width="8.875" style="25"/>
+    <col min="14" max="16384" width="8.875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1">
+      <c r="A2" s="49">
+        <v>44973</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>4500</v>
+      </c>
+      <c r="D2" s="41">
+        <v>31</v>
+      </c>
+      <c r="E2" s="18">
+        <f>C2*D2</f>
+        <v>139500</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*0.002</f>
+        <v>279</v>
+      </c>
+      <c r="G2" s="18">
+        <f>E2*0.00006</f>
+        <v>8.370000000000001</v>
+      </c>
+      <c r="H2" s="18">
+        <f>E2*0.00001</f>
+        <v>1.395</v>
+      </c>
+      <c r="I2" s="18">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>20.213550000000001</v>
+      </c>
+      <c r="J2" s="18">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>139808.97854999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="13" customFormat="1">
+      <c r="A3" s="67">
+        <v>44473</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>4500</v>
+      </c>
+      <c r="D3" s="11">
+        <v>29</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3*D3</f>
+        <v>130500</v>
+      </c>
+      <c r="F3" s="20">
+        <f>E3*0.002</f>
+        <v>261</v>
+      </c>
+      <c r="G3" s="20">
+        <f>E3*0.00006</f>
+        <v>7.83</v>
+      </c>
+      <c r="H3" s="20">
+        <f>E3*0.00001</f>
+        <v>1.3050000000000002</v>
+      </c>
+      <c r="I3" s="20">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>18.90945</v>
+      </c>
+      <c r="J3" s="20">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>130789.04445</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A4" s="56"/>
+      <c r="B4" s="76">
+        <f>(D3-D2)/D2</f>
+        <v>-6.4516129032258063E-2</v>
+      </c>
+      <c r="C4" s="10">
+        <f>SUM(C2:C3)</f>
+        <v>9000</v>
+      </c>
+      <c r="D4" s="64">
+        <f>E4/C4</f>
+        <v>30</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>270000</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" si="0"/>
+        <v>16.200000000000003</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" si="0"/>
+        <v>2.7</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" si="0"/>
+        <v>39.123000000000005</v>
+      </c>
+      <c r="J4" s="10">
+        <f t="shared" si="0"/>
+        <v>270598.02299999999</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+    </row>
+    <row r="6" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A6" s="56">
+        <v>44985</v>
+      </c>
+      <c r="C6" s="10">
+        <f>C2</f>
+        <v>4500</v>
+      </c>
+      <c r="D6" s="64">
+        <v>1.44</v>
+      </c>
+      <c r="E6" s="60">
+        <v>0</v>
+      </c>
+      <c r="F6" s="32">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="61">
+        <f>C6*D6</f>
+        <v>6480</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1">
+      <c r="A7" s="56">
+        <v>44627</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <f>C6</f>
+        <v>4500</v>
+      </c>
+      <c r="D7" s="46">
+        <f>D2</f>
+        <v>31</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v>139500</v>
+      </c>
+      <c r="F7" s="20">
+        <f>E7*0.002</f>
+        <v>279</v>
+      </c>
+      <c r="G7" s="20">
+        <f>E7*0.00006</f>
+        <v>8.370000000000001</v>
+      </c>
+      <c r="H7" s="20">
+        <f>E7*0.00001</f>
+        <v>1.395</v>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>20.213550000000001</v>
+      </c>
+      <c r="J7" s="20">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>139808.97854999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1">
+      <c r="A8" s="56">
+        <v>44277</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="10">
+        <f>C7</f>
+        <v>4500</v>
+      </c>
+      <c r="D8" s="34">
+        <v>31.25</v>
+      </c>
+      <c r="E8" s="11">
+        <f>C8*D8</f>
+        <v>140625</v>
+      </c>
+      <c r="F8" s="35">
+        <f>E8*0.002</f>
+        <v>281.25</v>
+      </c>
+      <c r="G8" s="34">
+        <f>E8*0.000068</f>
+        <v>9.5625</v>
+      </c>
+      <c r="H8" s="34">
+        <f>E8*0.00001</f>
+        <v>1.4062500000000002</v>
+      </c>
+      <c r="I8" s="34">
+        <f>(F8+G8+H8)*0.07</f>
+        <v>20.455312500000002</v>
+      </c>
+      <c r="J8" s="34">
+        <f>E8-F8-G8-H8-I8</f>
+        <v>140312.32593749999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1">
+      <c r="A9" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="20">
+        <f>E8-E7</f>
+        <v>1125</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20">
+        <f>J8-J7</f>
+        <v>503.34738750001998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="12">
+      <c r="A10" s="50"/>
+      <c r="D10" s="47"/>
+      <c r="J10" s="53">
+        <f>J6+J9</f>
+        <v>6983.34738750002</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185528E2-7E3A-4D20-9850-1E5EA06B5D92}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -19151,7 +20290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FBE3BD-D1CD-48BE-9C86-B7AFE096597B}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -19634,7 +20773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9557670-D125-4921-A689-63714DB07995}">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -20265,7 +21404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB529E6-7221-4171-9EDF-80891E84F736}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -20804,7 +21943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -22484,843 +23623,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29654F34-1A94-4023-9770-717C53C33E1B}">
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="10.125" style="50" customWidth="1"/>
-    <col min="2" max="2" width="7.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="19" customFormat="1" ht="16.5">
-      <c r="A2" s="49">
-        <v>44428</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
-        <v>8000</v>
-      </c>
-      <c r="D2" s="41">
-        <v>25</v>
-      </c>
-      <c r="E2" s="18">
-        <f>C2*D2</f>
-        <v>200000</v>
-      </c>
-      <c r="F2" s="18">
-        <f>E2*0.002</f>
-        <v>400</v>
-      </c>
-      <c r="G2" s="18">
-        <f>E2*0.00006</f>
-        <v>12</v>
-      </c>
-      <c r="H2" s="18">
-        <f>E2*0.00001</f>
-        <v>2</v>
-      </c>
-      <c r="I2" s="18">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>28.980000000000004</v>
-      </c>
-      <c r="J2" s="18">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>200442.98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="78" customFormat="1">
-      <c r="A3" s="82">
-        <v>44566</v>
-      </c>
-      <c r="B3" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="84">
-        <v>4000</v>
-      </c>
-      <c r="D3" s="85">
-        <v>22.9</v>
-      </c>
-      <c r="E3" s="86">
-        <f>C3*D3</f>
-        <v>91600</v>
-      </c>
-      <c r="F3" s="86">
-        <f>E3*0.002</f>
-        <v>183.20000000000002</v>
-      </c>
-      <c r="G3" s="86">
-        <f>E3*0.000068</f>
-        <v>6.2287999999999997</v>
-      </c>
-      <c r="H3" s="86">
-        <f>E3*0.00001</f>
-        <v>0.91600000000000004</v>
-      </c>
-      <c r="I3" s="86">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>13.324136000000003</v>
-      </c>
-      <c r="J3" s="86">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>91803.668935999987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="78" customFormat="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="87">
-        <f>(D3-D2)/D2</f>
-        <v>-8.4000000000000061E-2</v>
-      </c>
-      <c r="C4" s="84">
-        <f>SUM(C2:C3)</f>
-        <v>12000</v>
-      </c>
-      <c r="D4" s="85">
-        <f>E4/C4</f>
-        <v>24.3</v>
-      </c>
-      <c r="E4" s="84">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>291600</v>
-      </c>
-      <c r="F4" s="84">
-        <f t="shared" si="0"/>
-        <v>583.20000000000005</v>
-      </c>
-      <c r="G4" s="84">
-        <f t="shared" si="0"/>
-        <v>18.2288</v>
-      </c>
-      <c r="H4" s="84">
-        <f t="shared" si="0"/>
-        <v>2.9159999999999999</v>
-      </c>
-      <c r="I4" s="84">
-        <f t="shared" si="0"/>
-        <v>42.304136000000007</v>
-      </c>
-      <c r="J4" s="84">
-        <f t="shared" si="0"/>
-        <v>292246.64893600001</v>
-      </c>
-      <c r="K4" s="81"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="54">
-        <v>44624</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="51">
-        <f>C4*6/5</f>
-        <v>14400</v>
-      </c>
-      <c r="D5" s="52">
-        <f>E5/C5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E5" s="55">
-        <v>291600</v>
-      </c>
-      <c r="F5" s="55">
-        <v>583.20000000000005</v>
-      </c>
-      <c r="G5" s="55">
-        <v>18.2288</v>
-      </c>
-      <c r="H5" s="55">
-        <v>2.9159999999999999</v>
-      </c>
-      <c r="I5" s="55">
-        <v>42.304136000000007</v>
-      </c>
-      <c r="J5" s="55">
-        <v>292246.64893600001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="13" customFormat="1">
-      <c r="A6" s="49">
-        <v>44630</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16">
-        <v>4800</v>
-      </c>
-      <c r="D6" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="E6" s="17">
-        <f>C6*D6</f>
-        <v>108000</v>
-      </c>
-      <c r="F6" s="27">
-        <f>E6*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G6" s="26">
-        <f>E6*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H6" s="26">
-        <f>E6*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I6" s="26">
-        <f>(F6+G6+H6)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J6" s="26">
-        <f>E6-F6-G6-H6-I6</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="78" customFormat="1">
-      <c r="A7" s="82">
-        <v>44630</v>
-      </c>
-      <c r="B7" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="84">
-        <v>9600</v>
-      </c>
-      <c r="D7" s="85">
-        <f>D5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E7" s="86">
-        <f>C7*D7</f>
-        <v>194400</v>
-      </c>
-      <c r="F7" s="86">
-        <f>E7*0.002</f>
-        <v>388.8</v>
-      </c>
-      <c r="G7" s="86">
-        <f>E7*0.000068</f>
-        <v>13.219200000000001</v>
-      </c>
-      <c r="H7" s="86">
-        <f>E7*0.00001</f>
-        <v>1.9440000000000002</v>
-      </c>
-      <c r="I7" s="86">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>28.277424000000003</v>
-      </c>
-      <c r="J7" s="86">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>194832.24062399997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="78" customFormat="1">
-      <c r="A8" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B8" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="84">
-        <v>7200</v>
-      </c>
-      <c r="D8" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E8" s="86">
-        <f>C8*D8</f>
-        <v>145800</v>
-      </c>
-      <c r="F8" s="86">
-        <f>E8*0.002</f>
-        <v>291.60000000000002</v>
-      </c>
-      <c r="G8" s="86">
-        <f>E8*0.000068</f>
-        <v>9.9144000000000005</v>
-      </c>
-      <c r="H8" s="86">
-        <f>E8*0.00001</f>
-        <v>1.4580000000000002</v>
-      </c>
-      <c r="I8" s="86">
-        <f>(F8+G8+H8)*0.07</f>
-        <v>21.208068000000004</v>
-      </c>
-      <c r="J8" s="86">
-        <f>E8+F8+I8+G8+H8</f>
-        <v>146124.18046800004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="78" customFormat="1">
-      <c r="A9" s="82">
-        <v>44880</v>
-      </c>
-      <c r="B9" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="84">
-        <v>4800</v>
-      </c>
-      <c r="D9" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E9" s="86">
-        <f>C9*D9</f>
-        <v>97200</v>
-      </c>
-      <c r="F9" s="86">
-        <f>E9*0.002</f>
-        <v>194.4</v>
-      </c>
-      <c r="G9" s="86">
-        <f>E9*0.000068</f>
-        <v>6.6096000000000004</v>
-      </c>
-      <c r="H9" s="86">
-        <f>E9*0.00001</f>
-        <v>0.97200000000000009</v>
-      </c>
-      <c r="I9" s="86">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>14.138712000000002</v>
-      </c>
-      <c r="J9" s="86">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>97416.120311999985</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="78" customFormat="1">
-      <c r="A10" s="82">
-        <v>44886</v>
-      </c>
-      <c r="B10" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D10" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E10" s="86">
-        <f>C10*D10</f>
-        <v>48600</v>
-      </c>
-      <c r="F10" s="86">
-        <f>E10*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G10" s="86">
-        <f>E10*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H10" s="86">
-        <f>E10*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I10" s="86">
-        <f>(F10+G10+H10)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J10" s="86">
-        <f>E10+F10+I10+G10+H10</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="78" customFormat="1">
-      <c r="A11" s="77"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-    </row>
-    <row r="12" spans="1:13" s="78" customFormat="1">
-      <c r="A12" s="77"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="81"/>
-    </row>
-    <row r="13" spans="1:13" s="78" customFormat="1">
-      <c r="A13" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B13" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D13" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E13" s="86">
-        <f>C13*D13</f>
-        <v>48600</v>
-      </c>
-      <c r="F13" s="86">
-        <f>E13*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G13" s="86">
-        <f>E13*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H13" s="86">
-        <f>E13*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I13" s="86">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J13" s="86">
-        <f>E13+F13+I13+G13+H13</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="13" customFormat="1">
-      <c r="A14" s="49">
-        <v>44886</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="16">
-        <f>C13</f>
-        <v>2400</v>
-      </c>
-      <c r="D14" s="26">
-        <v>14.2</v>
-      </c>
-      <c r="E14" s="17">
-        <f>C14*D14</f>
-        <v>34080</v>
-      </c>
-      <c r="F14" s="27">
-        <f>E14*0.002</f>
-        <v>68.16</v>
-      </c>
-      <c r="G14" s="26">
-        <f>E14*0.000068</f>
-        <v>2.3174399999999999</v>
-      </c>
-      <c r="H14" s="26">
-        <f>E14*0.00001</f>
-        <v>0.34080000000000005</v>
-      </c>
-      <c r="I14" s="26">
-        <f>(F14+G14+H14)*0.07</f>
-        <v>4.9572768000000007</v>
-      </c>
-      <c r="J14" s="26">
-        <f>E14-F14-G14-H14-I14</f>
-        <v>34004.2244832</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A15" s="28">
-        <f>DAYS360(A13,A14)</f>
-        <v>191</v>
-      </c>
-      <c r="B15" s="30">
-        <f>(D14-D13)/D13</f>
-        <v>-0.29876543209876549</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18">
-        <f>E14-E13</f>
-        <v>-14520</v>
-      </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18">
-        <f>J14-J13</f>
-        <v>-14703.835672799993</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" spans="1:13" s="13" customFormat="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-    </row>
-    <row r="17" spans="1:13" s="78" customFormat="1">
-      <c r="A17" s="82">
-        <v>44691</v>
-      </c>
-      <c r="B17" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D17" s="85">
-        <v>20.25</v>
-      </c>
-      <c r="E17" s="86">
-        <f>C17*D17</f>
-        <v>48600</v>
-      </c>
-      <c r="F17" s="86">
-        <f>E17*0.002</f>
-        <v>97.2</v>
-      </c>
-      <c r="G17" s="86">
-        <f>E17*0.000068</f>
-        <v>3.3048000000000002</v>
-      </c>
-      <c r="H17" s="86">
-        <f>E17*0.00001</f>
-        <v>0.48600000000000004</v>
-      </c>
-      <c r="I17" s="86">
-        <f>(F17+G17+H17)*0.07</f>
-        <v>7.0693560000000009</v>
-      </c>
-      <c r="J17" s="86">
-        <f>E17+F17+I17+G17+H17</f>
-        <v>48708.060155999992</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="13" customFormat="1">
-      <c r="A18" s="49">
-        <v>44880</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="16">
-        <f>C17</f>
-        <v>2400</v>
-      </c>
-      <c r="D18" s="26">
-        <v>13.7</v>
-      </c>
-      <c r="E18" s="17">
-        <f>C18*D18</f>
-        <v>32880</v>
-      </c>
-      <c r="F18" s="27">
-        <f>E18*0.002</f>
-        <v>65.760000000000005</v>
-      </c>
-      <c r="G18" s="26">
-        <f>E18*0.000068</f>
-        <v>2.23584</v>
-      </c>
-      <c r="H18" s="26">
-        <f>E18*0.00001</f>
-        <v>0.32880000000000004</v>
-      </c>
-      <c r="I18" s="26">
-        <f>(F18+G18+H18)*0.07</f>
-        <v>4.7827248000000004</v>
-      </c>
-      <c r="J18" s="26">
-        <f>E18-F18-G18-H18-I18</f>
-        <v>32806.892635199991</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A19" s="28">
-        <f>DAYS360(A17,A18)</f>
-        <v>185</v>
-      </c>
-      <c r="B19" s="30">
-        <f>(D18-D17)/D17</f>
-        <v>-0.32345679012345685</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18">
-        <f>E18-E17</f>
-        <v>-15720</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18">
-        <f>J18-J17</f>
-        <v>-15901.167520800002</v>
-      </c>
-      <c r="K19" s="32"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" spans="1:13" s="13" customFormat="1">
-      <c r="A20" s="49"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" spans="1:13" s="78" customFormat="1">
-      <c r="A21" s="82">
-        <v>44644</v>
-      </c>
-      <c r="B21" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="84">
-        <v>2400</v>
-      </c>
-      <c r="D21" s="85">
-        <v>21.3</v>
-      </c>
-      <c r="E21" s="86">
-        <f>C21*D21</f>
-        <v>51120</v>
-      </c>
-      <c r="F21" s="86">
-        <f>E21*0.002</f>
-        <v>102.24000000000001</v>
-      </c>
-      <c r="G21" s="86">
-        <f>E21*0.000068</f>
-        <v>3.4761600000000001</v>
-      </c>
-      <c r="H21" s="86">
-        <f>E21*0.00001</f>
-        <v>0.51119999999999999</v>
-      </c>
-      <c r="I21" s="86">
-        <f>(F21+G21+H21)*0.07</f>
-        <v>7.4359152000000011</v>
-      </c>
-      <c r="J21" s="86">
-        <f>E21+F21+I21+G21+H21</f>
-        <v>51233.6632752</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="13" customFormat="1">
-      <c r="A22" s="49">
-        <v>44671</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="16">
-        <f>C21</f>
-        <v>2400</v>
-      </c>
-      <c r="D22" s="26">
-        <v>22.4</v>
-      </c>
-      <c r="E22" s="17">
-        <f>C22*D22</f>
-        <v>53760</v>
-      </c>
-      <c r="F22" s="27">
-        <f>E22*0.002</f>
-        <v>107.52</v>
-      </c>
-      <c r="G22" s="26">
-        <f>E22*0.000068</f>
-        <v>3.6556799999999998</v>
-      </c>
-      <c r="H22" s="26">
-        <f>E22*0.00001</f>
-        <v>0.53760000000000008</v>
-      </c>
-      <c r="I22" s="26">
-        <f>(F22+G22+H22)*0.07</f>
-        <v>7.8199296000000009</v>
-      </c>
-      <c r="J22" s="26">
-        <f>E22-F22-G22-H22-I22</f>
-        <v>53640.466790399994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A23" s="28">
-        <f>DAYS360(A21,A22)</f>
-        <v>26</v>
-      </c>
-      <c r="B23" s="30">
-        <f>(D22-D21)/D21</f>
-        <v>5.164319248826281E-2</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18">
-        <f>E22-E21</f>
-        <v>2640</v>
-      </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18">
-        <f>J22-J21</f>
-        <v>2406.8035151999939</v>
-      </c>
-      <c r="K23" s="32"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-    </row>
-    <row r="24" spans="1:13" s="21" customFormat="1">
-      <c r="A24" s="49">
-        <v>44538</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16">
-        <f>C5/3</f>
-        <v>4800</v>
-      </c>
-      <c r="D24" s="17">
-        <f>D5</f>
-        <v>20.25</v>
-      </c>
-      <c r="E24" s="18">
-        <f>C24*D24</f>
-        <v>97200</v>
-      </c>
-      <c r="F24" s="18">
-        <f>E24*0.002</f>
-        <v>194.4</v>
-      </c>
-      <c r="G24" s="18">
-        <f>E24*0.000068</f>
-        <v>6.6096000000000004</v>
-      </c>
-      <c r="H24" s="18">
-        <f>E24*0.00001</f>
-        <v>0.97200000000000009</v>
-      </c>
-      <c r="I24" s="18">
-        <f>(F24+G24+H24)*0.07</f>
-        <v>14.138712000000002</v>
-      </c>
-      <c r="J24" s="18">
-        <f>E24+F24+I24+G24+H24</f>
-        <v>97416.120311999985</v>
-      </c>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="1:13" s="13" customFormat="1">
-      <c r="A25" s="49">
-        <v>44630</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="16">
-        <f>C24</f>
-        <v>4800</v>
-      </c>
-      <c r="D25" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="E25" s="17">
-        <f>C25*D25</f>
-        <v>108000</v>
-      </c>
-      <c r="F25" s="27">
-        <f>E25*0.002</f>
-        <v>216</v>
-      </c>
-      <c r="G25" s="26">
-        <f>E25*0.000068</f>
-        <v>7.3440000000000003</v>
-      </c>
-      <c r="H25" s="26">
-        <f>E25*0.00001</f>
-        <v>1.08</v>
-      </c>
-      <c r="I25" s="26">
-        <f>(F25+G25+H25)*0.07</f>
-        <v>15.709680000000002</v>
-      </c>
-      <c r="J25" s="26">
-        <f>E25-F25-G25-H25-I25</f>
-        <v>107759.86632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="31" customFormat="1" ht="18.75">
-      <c r="A26" s="28">
-        <f>DAYS360(A24,A25)</f>
-        <v>92</v>
-      </c>
-      <c r="B26" s="30">
-        <f>(D25-D24)/D24</f>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18">
-        <f>E25-E24</f>
-        <v>10800</v>
-      </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18">
-        <f>J25-J24</f>
-        <v>10343.746008000016</v>
-      </c>
-      <c r="K26" s="32"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11689" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E7ED58A-2098-4F35-BF5B-13BC26C9065E}"/>
+  <xr:revisionPtr revIDLastSave="11692" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE38E6B5-CA3D-42A8-B0CE-788D3DC06F13}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="13" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="3" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -6238,38 +6238,38 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>39.75</v>
+        <v>44.25</v>
       </c>
       <c r="E7" s="62">
         <f>C7*D7</f>
-        <v>47700</v>
+        <v>53100</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>95.4</v>
+        <v>106.2</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>2.8620000000000001</v>
+        <v>3.1859999999999999</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.47700000000000004</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>6.9117300000000013</v>
+        <v>7.6941900000000008</v>
       </c>
       <c r="J7" s="62">
         <f>E7+F7+I7+G7+H7</f>
-        <v>47805.650730000001</v>
+        <v>53217.611190000003</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-0.28378378378378377</v>
+        <v>-0.20270270270270271</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
@@ -6277,31 +6277,31 @@
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="62">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>280800</v>
+        <v>286200</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="2"/>
-        <v>561.6</v>
+        <v>572.40000000000009</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="2"/>
-        <v>16.847999999999999</v>
+        <v>17.172000000000001</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="2"/>
-        <v>2.8080000000000003</v>
+        <v>2.8620000000000005</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="2"/>
-        <v>40.687920000000005</v>
+        <v>41.470380000000006</v>
       </c>
       <c r="J8" s="62">
         <f t="shared" si="2"/>
-        <v>281421.94391999999</v>
+        <v>286833.90438000002</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11692" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE38E6B5-CA3D-42A8-B0CE-788D3DC06F13}"/>
+  <xr:revisionPtr revIDLastSave="11696" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8684372E-1440-4C73-B765-1BA902CA3A18}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="3" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="14" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -5932,38 +5932,38 @@
         <v>1200</v>
       </c>
       <c r="D5" s="46">
-        <v>27.25</v>
+        <v>23.5</v>
       </c>
       <c r="E5" s="20">
         <f>C5*D5</f>
-        <v>32700</v>
+        <v>28200</v>
       </c>
       <c r="F5" s="20">
         <f>E5*0.002</f>
-        <v>65.400000000000006</v>
+        <v>56.4</v>
       </c>
       <c r="G5" s="20">
         <f>E5*0.00006</f>
-        <v>1.962</v>
+        <v>1.6919999999999999</v>
       </c>
       <c r="H5" s="20">
         <f>E5*0.00001</f>
-        <v>0.32700000000000001</v>
+        <v>0.28200000000000003</v>
       </c>
       <c r="I5" s="20">
         <f>(F5+G5+H5)*0.07</f>
-        <v>4.7382300000000006</v>
+        <v>4.0861799999999997</v>
       </c>
       <c r="J5" s="20">
         <f>E5+F5+I5+G5+H5</f>
-        <v>32772.427230000001</v>
+        <v>28262.460179999998</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1">
       <c r="A6" s="56"/>
       <c r="B6" s="12">
         <f>(D5-D4)/D4</f>
-        <v>-0.26845637583892618</v>
+        <v>-0.36912751677852351</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(C4:C5)</f>
@@ -5971,31 +5971,31 @@
       </c>
       <c r="D6" s="11">
         <f>E6/C6</f>
-        <v>35.25</v>
+        <v>34.5</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>211500</v>
+        <v>207000</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="1"/>
-        <v>12.69</v>
+        <v>12.42</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>2.1150000000000002</v>
+        <v>2.0700000000000003</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" si="1"/>
-        <v>30.646350000000005</v>
+        <v>29.994300000000003</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="1"/>
-        <v>211968.45134999999</v>
+        <v>207458.48429999998</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TempUserProfiles\NetworkService\AppData\OICE_16_974FA576_32C1D314_141A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11696" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8684372E-1440-4C73-B765-1BA902CA3A18}"/>
+  <xr:revisionPtr revIDLastSave="11750" documentId="8_{9A02EB98-7EB2-4F6F-BBDA-0A28C0527E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8004006-71F5-4CD8-B27E-85CDD7FBF0C3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="14" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" tabRatio="461" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KCE" sheetId="206" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="35">
   <si>
     <t>KCE</t>
   </si>
@@ -180,7 +180,7 @@
     <numFmt numFmtId="193" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="194" formatCode="&quot;฿&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -300,6 +300,42 @@
       <name val="Cordia New"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -327,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -431,6 +467,38 @@
     <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="194" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="191" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2309,37 +2377,37 @@
         <v>1000</v>
       </c>
       <c r="D41" s="46">
-        <v>47</v>
+        <v>44.25</v>
       </c>
       <c r="E41" s="20">
         <f>C41*D41</f>
-        <v>47000</v>
+        <v>44250</v>
       </c>
       <c r="F41" s="20">
         <f>E41*0.002</f>
-        <v>94</v>
+        <v>88.5</v>
       </c>
       <c r="G41" s="20">
         <f>E41*0.00006</f>
-        <v>2.8200000000000003</v>
+        <v>2.6550000000000002</v>
       </c>
       <c r="H41" s="20">
         <f>E41*0.00001</f>
-        <v>0.47000000000000003</v>
+        <v>0.44250000000000006</v>
       </c>
       <c r="I41" s="20">
         <f>(F41+G41+H41)*0.07</f>
-        <v>6.8102999999999998</v>
+        <v>6.4118250000000003</v>
       </c>
       <c r="J41" s="20">
         <f>E41+F41+I41+G41+H41</f>
-        <v>47104.100299999998</v>
+        <v>44348.009324999999</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="B42" s="3">
         <f>(D41-D40)/D40</f>
-        <v>-0.39158576051779936</v>
+        <v>-0.42718446601941745</v>
       </c>
       <c r="C42" s="2">
         <f>SUM(C40:C41)</f>
@@ -2347,31 +2415,31 @@
       </c>
       <c r="D42" s="47">
         <f>E42/C42</f>
-        <v>74.5</v>
+        <v>74.25</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" ref="E42:J42" si="9">SUM(E40:E41)</f>
-        <v>819500</v>
+        <v>816750</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="9"/>
-        <v>1639</v>
+        <v>1633.5</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="9"/>
-        <v>49.17</v>
+        <v>49.005000000000003</v>
       </c>
       <c r="H42" s="2">
         <f t="shared" si="9"/>
-        <v>8.1950000000000021</v>
+        <v>8.1675000000000022</v>
       </c>
       <c r="I42" s="2">
         <f t="shared" si="9"/>
-        <v>118.74554999999999</v>
+        <v>118.34707499999999</v>
       </c>
       <c r="J42" s="2">
         <f t="shared" si="9"/>
-        <v>821315.11054999998</v>
+        <v>818559.01957499993</v>
       </c>
     </row>
     <row r="43" spans="1:15" s="19" customFormat="1" ht="16.5">
@@ -5932,38 +6000,38 @@
         <v>1200</v>
       </c>
       <c r="D5" s="46">
-        <v>23.5</v>
+        <v>26</v>
       </c>
       <c r="E5" s="20">
         <f>C5*D5</f>
-        <v>28200</v>
+        <v>31200</v>
       </c>
       <c r="F5" s="20">
         <f>E5*0.002</f>
-        <v>56.4</v>
+        <v>62.4</v>
       </c>
       <c r="G5" s="20">
         <f>E5*0.00006</f>
-        <v>1.6919999999999999</v>
+        <v>1.8720000000000001</v>
       </c>
       <c r="H5" s="20">
         <f>E5*0.00001</f>
-        <v>0.28200000000000003</v>
+        <v>0.312</v>
       </c>
       <c r="I5" s="20">
         <f>(F5+G5+H5)*0.07</f>
-        <v>4.0861799999999997</v>
+        <v>4.5208800000000009</v>
       </c>
       <c r="J5" s="20">
         <f>E5+F5+I5+G5+H5</f>
-        <v>28262.460179999998</v>
+        <v>31269.104880000003</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1">
       <c r="A6" s="56"/>
       <c r="B6" s="12">
         <f>(D5-D4)/D4</f>
-        <v>-0.36912751677852351</v>
+        <v>-0.30201342281879195</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(C4:C5)</f>
@@ -5971,31 +6039,31 @@
       </c>
       <c r="D6" s="11">
         <f>E6/C6</f>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>207000</v>
+        <v>210000</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="1"/>
-        <v>12.42</v>
+        <v>12.6</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>2.0700000000000003</v>
+        <v>2.1</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" si="1"/>
-        <v>29.994300000000003</v>
+        <v>30.429000000000006</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="1"/>
-        <v>207458.48429999998</v>
+        <v>210465.12899999999</v>
       </c>
     </row>
   </sheetData>
@@ -13537,37 +13605,37 @@
         <v>15000</v>
       </c>
       <c r="D13" s="64">
-        <v>3.84</v>
+        <v>3.52</v>
       </c>
       <c r="E13" s="20">
         <f>C13*D13</f>
-        <v>57600</v>
+        <v>52800</v>
       </c>
       <c r="F13" s="20">
         <f>E13*0.002</f>
-        <v>115.2</v>
+        <v>105.60000000000001</v>
       </c>
       <c r="G13" s="20">
         <f>E13*0.00006</f>
-        <v>3.456</v>
+        <v>3.1680000000000001</v>
       </c>
       <c r="H13" s="20">
         <f>E13*0.00001</f>
-        <v>0.57600000000000007</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="I13" s="20">
         <f>(F13+G13+H13)*0.07</f>
-        <v>8.3462399999999999</v>
+        <v>7.6507200000000024</v>
       </c>
       <c r="J13" s="20">
         <f>E13+F13+I13+G13+H13</f>
-        <v>57727.578239999995</v>
+        <v>52916.946719999993</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="B14" s="25">
         <f>(D13-D12)/D12</f>
-        <v>-0.14285714285714296</v>
+        <v>-0.21428571428571436</v>
       </c>
       <c r="C14" s="22">
         <f>SUM(C12:C13)</f>
@@ -13575,31 +13643,31 @@
       </c>
       <c r="D14" s="65">
         <f>E14/C14</f>
-        <v>4.4000000000000004</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="E14" s="22">
         <f t="shared" ref="E14:J14" si="5">SUM(E12:E13)</f>
-        <v>528000</v>
+        <v>523200</v>
       </c>
       <c r="F14" s="22">
         <f t="shared" si="5"/>
-        <v>1056</v>
+        <v>1046.3999999999999</v>
       </c>
       <c r="G14" s="22">
         <f t="shared" si="5"/>
-        <v>31.680000000000003</v>
+        <v>31.392000000000003</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="5"/>
-        <v>5.2800000000000011</v>
+        <v>5.2320000000000011</v>
       </c>
       <c r="I14" s="22">
         <f t="shared" si="5"/>
-        <v>76.507199999999997</v>
+        <v>75.81168000000001</v>
       </c>
       <c r="J14" s="22">
         <f t="shared" si="5"/>
-        <v>529169.46719999996</v>
+        <v>524358.83568000002</v>
       </c>
     </row>
   </sheetData>
@@ -13842,38 +13910,38 @@
         <v>1200</v>
       </c>
       <c r="D7" s="46">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="20">
         <f>C7*D7</f>
-        <v>20400</v>
+        <v>24000</v>
       </c>
       <c r="F7" s="20">
         <f>E7*0.002</f>
-        <v>40.800000000000004</v>
+        <v>48</v>
       </c>
       <c r="G7" s="20">
         <f>E7*0.00006</f>
-        <v>1.224</v>
+        <v>1.44</v>
       </c>
       <c r="H7" s="20">
         <f>E7*0.00001</f>
-        <v>0.20400000000000001</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="I7" s="20">
         <f>(F7+G7+H7)*0.07</f>
-        <v>2.9559600000000006</v>
+        <v>3.4776000000000002</v>
       </c>
       <c r="J7" s="20">
         <f>E7+F7+I7+G7+H7</f>
-        <v>20445.183959999998</v>
+        <v>24053.157599999999</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1">
       <c r="A8" s="56"/>
       <c r="B8" s="12">
         <f>(D7-D6)/D6</f>
-        <v>-0.31451612903225806</v>
+        <v>-0.19354838709677422</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(C6:C7)</f>
@@ -13881,31 +13949,31 @@
       </c>
       <c r="D8" s="11">
         <f>E8/C8</f>
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>169200</v>
+        <v>172800</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="2"/>
-        <v>338.40000000000003</v>
+        <v>345.6</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="2"/>
-        <v>10.152000000000001</v>
+        <v>10.368</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="2"/>
-        <v>1.6919999999999999</v>
+        <v>1.728</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="2"/>
-        <v>24.517080000000004</v>
+        <v>25.038720000000001</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="2"/>
-        <v>169574.76108</v>
+        <v>173182.73472000001</v>
       </c>
     </row>
   </sheetData>
@@ -19670,31 +19738,31 @@
         <v>4500</v>
       </c>
       <c r="D3" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="20">
         <f>C3*D3</f>
-        <v>130500</v>
+        <v>126000</v>
       </c>
       <c r="F3" s="20">
         <f>E3*0.002</f>
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G3" s="20">
         <f>E3*0.00006</f>
-        <v>7.83</v>
+        <v>7.5600000000000005</v>
       </c>
       <c r="H3" s="20">
         <f>E3*0.00001</f>
-        <v>1.3050000000000002</v>
+        <v>1.26</v>
       </c>
       <c r="I3" s="20">
         <f>(F3+G3+H3)*0.07</f>
-        <v>18.90945</v>
+        <v>18.257400000000001</v>
       </c>
       <c r="J3" s="20">
         <f>E3+F3+I3+G3+H3</f>
-        <v>130789.04445</v>
+        <v>126279.07739999999</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="11"/>
@@ -19704,7 +19772,7 @@
       <c r="A4" s="56"/>
       <c r="B4" s="76">
         <f>(D3-D2)/D2</f>
-        <v>-6.4516129032258063E-2</v>
+        <v>-9.6774193548387094E-2</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(C2:C3)</f>
@@ -19712,31 +19780,31 @@
       </c>
       <c r="D4" s="64">
         <f>E4/C4</f>
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>270000</v>
+        <v>265500</v>
       </c>
       <c r="F4" s="10">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G4" s="10">
         <f t="shared" si="0"/>
-        <v>16.200000000000003</v>
+        <v>15.930000000000001</v>
       </c>
       <c r="H4" s="10">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>2.6550000000000002</v>
       </c>
       <c r="I4" s="10">
         <f t="shared" si="0"/>
-        <v>39.123000000000005</v>
+        <v>38.470950000000002</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="0"/>
-        <v>270598.02299999999</v>
+        <v>266088.05594999995</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="13"/>
@@ -20292,7 +20360,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FBE3BD-D1CD-48BE-9C86-B7AFE096597B}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="38" customWidth="1"/>
@@ -20311,83 +20379,92 @@
     <col min="14" max="16384" width="8.875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:14" ht="15.75">
+      <c r="A1" s="118"/>
+      <c r="B1" s="119" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1">
-      <c r="A2" s="49">
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A2" s="103">
         <v>44932</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16">
+      <c r="B2" s="130" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="105">
         <v>12000</v>
       </c>
-      <c r="D2" s="41">
+      <c r="D2" s="131">
         <v>12.3</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="132">
         <f>C2*D2</f>
         <v>147600</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="132">
         <f>E2*0.002</f>
         <v>295.2</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="132">
         <f>E2*0.00006</f>
         <v>8.8559999999999999</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="132">
         <f>E2*0.00001</f>
         <v>1.4760000000000002</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="132">
         <f>(F2+G2+H2)*0.07</f>
         <v>21.387240000000002</v>
       </c>
-      <c r="J2" s="18">
+      <c r="J2" s="132">
         <f>E2+F2+I2+G2+H2</f>
         <v>147926.91924000002</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="13" customFormat="1">
-      <c r="A3" s="39">
+    <row r="3" spans="1:14" s="13" customFormat="1" ht="15.75">
+      <c r="A3" s="133">
         <v>44957</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="B3" s="130" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="105">
         <v>6000</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="134">
         <v>11.4</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="132">
         <f>C3*D3</f>
         <v>68400</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="132">
         <f>E3*0.002</f>
         <v>136.80000000000001</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="132">
         <f>E3*0.00006</f>
         <v>4.1040000000000001</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="132">
         <f>E3*0.00001</f>
         <v>0.68400000000000005</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="132">
         <f>(F3+G3+H3)*0.07</f>
         <v>9.9111600000000024</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="132">
         <f>E3+F3+I3+G3+H3</f>
         <v>68551.499160000007</v>
       </c>
@@ -20396,374 +20473,667 @@
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A4" s="49"/>
-      <c r="B4" s="75">
+      <c r="A4" s="103"/>
+      <c r="B4" s="104">
         <f>(D3-D2)/D2</f>
         <v>-7.3170731707317097E-2</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="105">
         <f>SUM(C2:C3)</f>
         <v>18000</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="106">
         <f>E4/C4</f>
         <v>12</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="105">
         <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
         <v>216000</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="105">
         <f t="shared" si="0"/>
         <v>432</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="105">
         <f t="shared" si="0"/>
         <v>12.96</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="105">
         <f t="shared" si="0"/>
         <v>2.16</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="105">
         <f t="shared" si="0"/>
         <v>31.298400000000004</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="105">
         <f t="shared" si="0"/>
         <v>216478.41840000002</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-    </row>
-    <row r="5" spans="1:14" s="13" customFormat="1">
-      <c r="A5" s="67">
+      <c r="K4" s="107"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="109"/>
+    </row>
+    <row r="5" spans="1:14" s="13" customFormat="1" ht="15.75">
+      <c r="A5" s="110">
         <v>44957</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="B5" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="111">
         <v>6000</v>
       </c>
-      <c r="D5" s="11">
-        <v>10.8</v>
-      </c>
-      <c r="E5" s="20">
+      <c r="D5" s="107">
+        <v>10.4</v>
+      </c>
+      <c r="E5" s="112">
         <f>C5*D5</f>
-        <v>64800.000000000007</v>
-      </c>
-      <c r="F5" s="20">
+        <v>62400</v>
+      </c>
+      <c r="F5" s="112">
         <f>E5*0.002</f>
-        <v>129.60000000000002</v>
-      </c>
-      <c r="G5" s="20">
+        <v>124.8</v>
+      </c>
+      <c r="G5" s="112">
         <f>E5*0.00006</f>
-        <v>3.8880000000000003</v>
-      </c>
-      <c r="H5" s="20">
+        <v>3.7440000000000002</v>
+      </c>
+      <c r="H5" s="112">
         <f>E5*0.00001</f>
-        <v>0.64800000000000013</v>
-      </c>
-      <c r="I5" s="20">
+        <v>0.624</v>
+      </c>
+      <c r="I5" s="112">
         <f>(F5+G5+H5)*0.07</f>
-        <v>9.3895200000000028</v>
-      </c>
-      <c r="J5" s="20">
+        <v>9.0417600000000018</v>
+      </c>
+      <c r="J5" s="112">
         <f>E5+F5+I5+G5+H5</f>
-        <v>64943.525520000003</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
+        <v>62538.209760000005</v>
+      </c>
+      <c r="K5" s="113"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="108"/>
     </row>
     <row r="6" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A6" s="56"/>
-      <c r="B6" s="76">
+      <c r="A6" s="115"/>
+      <c r="B6" s="116">
         <f>(D5-D4)/D4</f>
-        <v>-9.9999999999999936E-2</v>
-      </c>
-      <c r="C6" s="10">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="C6" s="111">
         <f>SUM(C4:C5)</f>
         <v>24000</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="117">
         <f>E6/C6</f>
-        <v>11.7</v>
-      </c>
-      <c r="E6" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="E6" s="111">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>280800</v>
-      </c>
-      <c r="F6" s="10">
+        <v>278400</v>
+      </c>
+      <c r="F6" s="111">
         <f t="shared" si="1"/>
-        <v>561.6</v>
-      </c>
-      <c r="G6" s="10">
+        <v>556.79999999999995</v>
+      </c>
+      <c r="G6" s="111">
         <f t="shared" si="1"/>
-        <v>16.848000000000003</v>
-      </c>
-      <c r="H6" s="10">
+        <v>16.704000000000001</v>
+      </c>
+      <c r="H6" s="111">
         <f t="shared" si="1"/>
-        <v>2.8080000000000003</v>
-      </c>
-      <c r="I6" s="10">
+        <v>2.7840000000000003</v>
+      </c>
+      <c r="I6" s="111">
         <f t="shared" si="1"/>
-        <v>40.687920000000005</v>
-      </c>
-      <c r="J6" s="10">
+        <v>40.340160000000004</v>
+      </c>
+      <c r="J6" s="111">
         <f t="shared" si="1"/>
-        <v>281421.94392000005</v>
-      </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-    </row>
-    <row r="8" spans="1:14" s="63" customFormat="1" ht="21.75">
-      <c r="A8" s="56">
+        <v>279016.62816000002</v>
+      </c>
+      <c r="K6" s="107"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75">
+      <c r="A7" s="118"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="119"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75">
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="119"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75">
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="119"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75">
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="119"/>
+    </row>
+    <row r="11" spans="1:14" s="63" customFormat="1" ht="21.75">
+      <c r="A11" s="115">
         <v>44630</v>
       </c>
-      <c r="C8" s="10">
+      <c r="B11" s="31"/>
+      <c r="C11" s="111">
         <f>C2</f>
         <v>12000</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D11" s="117">
         <v>0.2</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E11" s="121">
         <v>0</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F11" s="113">
         <v>0</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G11" s="121">
         <v>0</v>
       </c>
-      <c r="H8" s="11">
-        <f>G8-E8</f>
+      <c r="H11" s="107">
+        <f>G11-E11</f>
         <v>0</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I11" s="114">
         <v>0</v>
       </c>
-      <c r="J8" s="61">
-        <f>C8*D8</f>
+      <c r="J11" s="122">
+        <f>C11*D11</f>
         <v>2400</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1">
-      <c r="A9" s="56">
+      <c r="K11" s="107"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="109"/>
+      <c r="N11" s="109"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A12" s="115">
         <v>44627</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10">
-        <f>C8</f>
+      <c r="B12" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="111">
+        <f>C11</f>
         <v>12000</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D12" s="123">
         <f>D2</f>
         <v>12.3</v>
       </c>
-      <c r="E9" s="20">
-        <f>C9*D9</f>
+      <c r="E12" s="112">
+        <f>C12*D12</f>
         <v>147600</v>
       </c>
-      <c r="F9" s="20">
-        <f>E9*0.002</f>
+      <c r="F12" s="112">
+        <f>E12*0.002</f>
         <v>295.2</v>
       </c>
-      <c r="G9" s="20">
-        <f>E9*0.00006</f>
+      <c r="G12" s="112">
+        <f>E12*0.00006</f>
         <v>8.8559999999999999</v>
       </c>
-      <c r="H9" s="20">
-        <f>E9*0.00001</f>
+      <c r="H12" s="112">
+        <f>E12*0.00001</f>
         <v>1.4760000000000002</v>
       </c>
-      <c r="I9" s="20">
-        <f>(F9+G9+H9)*0.07</f>
+      <c r="I12" s="112">
+        <f>(F12+G12+H12)*0.07</f>
         <v>21.387240000000002</v>
       </c>
-      <c r="J9" s="20">
-        <f>E9+F9+I9+G9+H9</f>
+      <c r="J12" s="112">
+        <f>E12+F12+I12+G12+H12</f>
         <v>147926.91924000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1">
-      <c r="A10" s="56">
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="124"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A13" s="115">
         <v>44277</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B13" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="10">
-        <f>C9</f>
+      <c r="C13" s="111">
+        <f>C12</f>
         <v>12000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D13" s="125">
         <v>13</v>
       </c>
-      <c r="E10" s="11">
-        <f>C10*D10</f>
+      <c r="E13" s="107">
+        <f>C13*D13</f>
         <v>156000</v>
       </c>
-      <c r="F10" s="35">
-        <f>E10*0.002</f>
+      <c r="F13" s="126">
+        <f>E13*0.002</f>
         <v>312</v>
       </c>
-      <c r="G10" s="34">
-        <f>E10*0.000068</f>
+      <c r="G13" s="125">
+        <f>E13*0.000068</f>
         <v>10.608000000000001</v>
       </c>
-      <c r="H10" s="34">
-        <f>E10*0.00001</f>
+      <c r="H13" s="125">
+        <f>E13*0.00001</f>
         <v>1.56</v>
       </c>
-      <c r="I10" s="34">
-        <f>(F10+G10+H10)*0.07</f>
+      <c r="I13" s="125">
+        <f>(F13+G13+H13)*0.07</f>
         <v>22.691760000000002</v>
       </c>
-      <c r="J10" s="34">
-        <f>E10-F10-G10-H10-I10</f>
+      <c r="J13" s="125">
+        <f>E13-F13-G13-H13-I13</f>
         <v>155653.14024000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1">
-      <c r="A11" s="56" t="s">
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="124"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A14" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="12">
-        <f>(D10-D9)/D9</f>
+      <c r="B14" s="114">
+        <f>(D13-D12)/D12</f>
         <v>5.6910569105690999E-2</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="20">
-        <f>E10-E9</f>
+      <c r="C14" s="111"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="112">
+        <f>E13-E12</f>
         <v>8400</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20">
-        <f>J10-J9</f>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112">
+        <f>J13-J12</f>
         <v>7726.2209999999905</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1">
-      <c r="A12" s="50"/>
-      <c r="D12" s="47"/>
-      <c r="J12" s="53">
-        <f>J8+J11</f>
+      <c r="K14" s="124"/>
+      <c r="L14" s="124"/>
+      <c r="M14" s="124"/>
+      <c r="N14" s="124"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1">
+      <c r="A15" s="127"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="129">
+        <f>J11+J14</f>
         <v>10126.22099999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1">
-      <c r="A14" s="56">
+      <c r="K15" s="124"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="124"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75">
+      <c r="A16" s="118"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="119"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A17" s="115">
         <v>44627</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="10">
+      <c r="B17" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="111">
         <v>30000</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D17" s="123">
         <v>3.8</v>
       </c>
-      <c r="E14" s="20">
-        <f>C14*D14</f>
+      <c r="E17" s="112">
+        <f>C17*D17</f>
         <v>114000</v>
       </c>
-      <c r="F14" s="20">
-        <f>E14*0.002</f>
+      <c r="F17" s="112">
+        <f>E17*0.002</f>
         <v>228</v>
       </c>
-      <c r="G14" s="20">
-        <f>E14*0.00006</f>
+      <c r="G17" s="112">
+        <f>E17*0.00006</f>
         <v>6.84</v>
       </c>
-      <c r="H14" s="20">
-        <f>E14*0.00001</f>
+      <c r="H17" s="112">
+        <f>E17*0.00001</f>
         <v>1.1400000000000001</v>
       </c>
-      <c r="I14" s="20">
-        <f>(F14+G14+H14)*0.07</f>
+      <c r="I17" s="112">
+        <f>(F17+G17+H17)*0.07</f>
         <v>16.518599999999999</v>
       </c>
-      <c r="J14" s="20">
-        <f>E14+F14+I14+G14+H14</f>
+      <c r="J17" s="112">
+        <f>E17+F17+I17+G17+H17</f>
         <v>114252.49859999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1">
-      <c r="A15" s="56">
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="124"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A18" s="115">
         <v>44633</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B18" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="10">
-        <f>C14</f>
+      <c r="C18" s="111">
+        <f>C17</f>
         <v>30000</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D18" s="125">
         <v>4.0199999999999996</v>
       </c>
-      <c r="E15" s="11">
-        <f>C15*D15</f>
+      <c r="E18" s="107">
+        <f>C18*D18</f>
         <v>120599.99999999999</v>
       </c>
-      <c r="F15" s="35">
-        <f>E15*0.002</f>
+      <c r="F18" s="126">
+        <f>E18*0.002</f>
         <v>241.2</v>
       </c>
-      <c r="G15" s="34">
-        <f>E15*0.000068</f>
+      <c r="G18" s="125">
+        <f>E18*0.000068</f>
         <v>8.2007999999999992</v>
       </c>
-      <c r="H15" s="34">
-        <f>E15*0.00001</f>
+      <c r="H18" s="125">
+        <f>E18*0.00001</f>
         <v>1.206</v>
       </c>
-      <c r="I15" s="34">
-        <f>(F15+G15+H15)*0.07</f>
+      <c r="I18" s="125">
+        <f>(F18+G18+H18)*0.07</f>
         <v>17.542476000000001</v>
       </c>
-      <c r="J15" s="34">
-        <f>E15-F15-G15-H15-I15</f>
+      <c r="J18" s="125">
+        <f>E18-F18-G18-H18-I18</f>
         <v>120331.85072399997</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1">
-      <c r="A16" s="56" t="s">
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="124"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="15.75">
+      <c r="A19" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="20">
-        <f>E15-E14</f>
+      <c r="B19" s="108"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="112">
+        <f>E18-E17</f>
         <v>6599.9999999999854</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20">
-        <f>J15-J14</f>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112">
+        <f>J18-J17</f>
         <v>6079.3521239999827</v>
       </c>
+      <c r="K19" s="124"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="124"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.75">
+      <c r="A20" s="118"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="119"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75">
+      <c r="A21" s="118"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="119"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75">
+      <c r="A22" s="118"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="119"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75">
+      <c r="A23" s="118"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="119"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75">
+      <c r="A24" s="118"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="120"/>
+      <c r="N24" s="119"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75">
+      <c r="A25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="120"/>
+      <c r="N25" s="119"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75">
+      <c r="A26" s="118"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="119"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75">
+      <c r="A27" s="118"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="119"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75">
+      <c r="A28" s="118"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="119"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75">
+      <c r="A29" s="118"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="119"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75">
+      <c r="A30" s="118"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="119"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -21779,106 +22149,159 @@
         <v>757680.10544000007</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="77">
-        <v>44964</v>
-      </c>
-      <c r="B11" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="79">
+    <row r="11" spans="1:14" ht="12.75">
+      <c r="A11" s="82">
+        <v>44986</v>
+      </c>
+      <c r="B11" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="84">
         <v>10000</v>
       </c>
-      <c r="D11" s="80">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="E11" s="94">
+      <c r="D11" s="85">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E11" s="86">
         <f>C11*D11</f>
-        <v>179000</v>
-      </c>
-      <c r="F11" s="94">
+        <v>164000</v>
+      </c>
+      <c r="F11" s="86">
         <f>E11*0.002</f>
-        <v>358</v>
-      </c>
-      <c r="G11" s="94">
+        <v>328</v>
+      </c>
+      <c r="G11" s="86">
         <f>E11*0.000068</f>
-        <v>12.172000000000001</v>
-      </c>
-      <c r="H11" s="94">
+        <v>11.151999999999999</v>
+      </c>
+      <c r="H11" s="86">
         <f>E11*0.00001</f>
-        <v>1.79</v>
-      </c>
-      <c r="I11" s="94">
+        <v>1.6400000000000001</v>
+      </c>
+      <c r="I11" s="86">
         <f>(F11+G11+H11)*0.07</f>
-        <v>26.037340000000004</v>
-      </c>
-      <c r="J11" s="94">
+        <v>23.855440000000002</v>
+      </c>
+      <c r="J11" s="86">
         <f>E11+F11+I11+G11+H11</f>
-        <v>179397.99934000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="77"/>
-      <c r="B12" s="81">
+        <v>164364.64744000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="12.75">
+      <c r="A12" s="82"/>
+      <c r="B12" s="87">
         <f>(D11-D10)/D10</f>
-        <v>-5.2910052910052914E-2</v>
-      </c>
-      <c r="C12" s="79">
+        <v>-0.1322751322751323</v>
+      </c>
+      <c r="C12" s="84">
         <f>SUM(C10:C11)</f>
         <v>50000</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="85">
         <f>E12/C12</f>
-        <v>18.7</v>
-      </c>
-      <c r="E12" s="79">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E12" s="84">
         <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
-        <v>935000</v>
-      </c>
-      <c r="F12" s="79">
+        <v>920000</v>
+      </c>
+      <c r="F12" s="84">
         <f t="shared" si="4"/>
-        <v>1870</v>
-      </c>
-      <c r="G12" s="79">
+        <v>1840</v>
+      </c>
+      <c r="G12" s="84">
         <f t="shared" si="4"/>
-        <v>62.804000000000002</v>
-      </c>
-      <c r="H12" s="79">
+        <v>61.784000000000006</v>
+      </c>
+      <c r="H12" s="84">
         <f t="shared" si="4"/>
-        <v>9.3500000000000014</v>
-      </c>
-      <c r="I12" s="79">
+        <v>9.2000000000000011</v>
+      </c>
+      <c r="I12" s="84">
         <f t="shared" si="4"/>
-        <v>135.95078000000001</v>
-      </c>
-      <c r="J12" s="79">
+        <v>133.76888000000002</v>
+      </c>
+      <c r="J12" s="84">
         <f t="shared" si="4"/>
-        <v>937078.10478000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="78" customFormat="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-    </row>
-    <row r="14" spans="1:14" s="13" customFormat="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
+        <v>922044.75288000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="77">
+        <v>44964</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D13" s="80">
+        <v>14.2</v>
+      </c>
+      <c r="E13" s="94">
+        <f>C13*D13</f>
+        <v>142000</v>
+      </c>
+      <c r="F13" s="94">
+        <f>E13*0.002</f>
+        <v>284</v>
+      </c>
+      <c r="G13" s="94">
+        <f>E13*0.000068</f>
+        <v>9.6560000000000006</v>
+      </c>
+      <c r="H13" s="94">
+        <f>E13*0.00001</f>
+        <v>1.4200000000000002</v>
+      </c>
+      <c r="I13" s="94">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>20.655320000000003</v>
+      </c>
+      <c r="J13" s="94">
+        <f>E13+F13+I13+G13+H13</f>
+        <v>142315.73131999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="77"/>
+      <c r="B14" s="81">
+        <f>(D13-D12)/D12</f>
+        <v>-0.22826086956521738</v>
+      </c>
+      <c r="C14" s="79">
+        <f>SUM(C12:C13)</f>
+        <v>60000</v>
+      </c>
+      <c r="D14" s="80">
+        <f>E14/C14</f>
+        <v>17.7</v>
+      </c>
+      <c r="E14" s="79">
+        <f t="shared" ref="E14:J14" si="5">SUM(E12:E13)</f>
+        <v>1062000</v>
+      </c>
+      <c r="F14" s="79">
+        <f t="shared" si="5"/>
+        <v>2124</v>
+      </c>
+      <c r="G14" s="79">
+        <f t="shared" si="5"/>
+        <v>71.440000000000012</v>
+      </c>
+      <c r="H14" s="79">
+        <f t="shared" si="5"/>
+        <v>10.620000000000001</v>
+      </c>
+      <c r="I14" s="79">
+        <f t="shared" si="5"/>
+        <v>154.42420000000004</v>
+      </c>
+      <c r="J14" s="79">
+        <f t="shared" si="5"/>
+        <v>1064360.4842000001</v>
+      </c>
     </row>
     <row r="15" spans="1:14" s="31" customFormat="1" ht="18.75">
       <c r="A15" s="28"/>
